--- a/DCT - Guide/Migration Approach.xlsx
+++ b/DCT - Guide/Migration Approach.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\70023796\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{972E033D-414F-442E-B642-BAD0EDC25F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62E3F0DE-D07E-4187-A7AA-FE2DD1CA68FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{7CAA1510-BEF0-44FB-B9DF-6BA498C876D6}"/>
   </bookViews>
@@ -38,8 +38,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={31A57323-7DF0-4B2F-9222-8FFF99F19E88}</author>
+  </authors>
+  <commentList>
+    <comment ref="C31" authorId="0" shapeId="0" xr:uid="{31A57323-7DF0-4B2F-9222-8FFF99F19E88}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    If needed then in 3 Migration Templates or 1 Migration Template with Sum, we will have to fill in Open items per month-end (6 months in total)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="120">
   <si>
     <t>Asset Cumulative values (Acquisition + Accum. Depreciation)</t>
   </si>
@@ -442,12 +460,95 @@
   <si>
     <t>AP</t>
   </si>
+  <si>
+    <t>Flow:</t>
+  </si>
+  <si>
+    <t>1 LSMW / Z Program Template</t>
+  </si>
+  <si>
+    <t>1 Migration Template</t>
+  </si>
+  <si>
+    <t>3 Migration Templates</t>
+  </si>
+  <si>
+    <t>3 Migration Templates or 1 Migration Template with Sum</t>
+  </si>
+  <si>
+    <t>_Extract details Open BS/AR/AP or Sum in 3 Temporary Migration GLACs</t>
+  </si>
+  <si>
+    <t>_Extract ending Acquisition + Accum.Depreciation per Asset</t>
+  </si>
+  <si>
+    <t>_Extract Asset Transactions</t>
+  </si>
+  <si>
+    <t>1 Migration Template (Use Non-Open BS Template)</t>
+  </si>
+  <si>
+    <t>1 LSMW / Z Program Template or 1 Migration Template (Risk in incorrect posting dates)</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
+    <t>_Extract Asset Posted Depreciation</t>
+  </si>
+  <si>
+    <t>1 Migration Template (Use P&amp;L Template)</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>_Extract ending Acquisition + Accum.Depreciation + Posted Depreciation per Asset</t>
+  </si>
+  <si>
+    <t>_Extract details Open BS + Non-Open BS + P&amp;L/AR/AP on 30-Jun</t>
+  </si>
+  <si>
+    <r>
+      <t>_Extract details Open BS/AR/AP or Sum in 3 Temporary Migration GLACs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> per month</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">_For Open BS/AR/AP, we post the Ending Balance on 31-Dec-2025 then reverse on 30-June-2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(If monthly report needed then reverse the posting at the beginning of next month)</t>
+    </r>
+  </si>
+  <si>
+    <t>_Extract ending balances for Non-Open BS GLACs (Profit Center-wise)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -508,6 +609,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -559,7 +676,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="47">
     <border>
       <left/>
       <right/>
@@ -736,11 +853,394 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -870,127 +1370,190 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="33" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="39" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1008,6 +1571,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Hoang Quoc Dat Kenway" id="{2920EFAE-7A21-43FB-8C0D-D5DAB7101B10}" userId="S::quocdat.hoang@stengg.com::a802ecaa-97f9-4122-bc68-f1bb33478329" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1325,16 +1894,25 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C31" dT="2026-04-03T03:22:09.60" personId="{2920EFAE-7A21-43FB-8C0D-D5DAB7101B10}" id="{31A57323-7DF0-4B2F-9222-8FFF99F19E88}">
+    <text>If needed then in 3 Migration Templates or 1 Migration Template with Sum, we will have to fill in Open items per month-end (6 months in total)</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB4B1054-9445-434F-B8C4-4275AFE8E718}">
-  <dimension ref="B2:X34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB4B1054-9445-434F-B8C4-4275AFE8E718}">
+  <dimension ref="B2:X37"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9.23046875" style="1"/>
     <col min="2" max="2" width="10.84375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="59.15234375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.61328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="19.61328125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="68.07421875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.61328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="22.921875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19.61328125" style="2" customWidth="1"/>
     <col min="7" max="7" width="26.53515625" style="2" customWidth="1"/>
     <col min="8" max="8" width="9.23046875" style="1"/>
     <col min="9" max="9" width="9.07421875" style="2" customWidth="1"/>
@@ -1345,18 +1923,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:24" ht="14.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="74" t="s">
+      <c r="C2" s="96"/>
+      <c r="D2" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="75"/>
-      <c r="F2" s="45" t="s">
+      <c r="E2" s="64"/>
+      <c r="F2" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="G2" s="47"/>
+      <c r="G2" s="66"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
         <v>85</v>
@@ -1368,24 +1946,24 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="2:24" ht="14.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="84" t="s">
+    <row r="3" spans="2:24" ht="14.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="97"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="85" t="s">
+      <c r="E3" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="84" t="s">
+      <c r="F3" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="85" t="s">
+      <c r="G3" s="57" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="10" t="s">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="K3" s="8"/>
       <c r="L3" s="2"/>
@@ -1393,41 +1971,45 @@
       <c r="N3" s="2"/>
     </row>
     <row r="4" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="98" t="s">
         <v>92</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="58" t="s">
         <v>87</v>
       </c>
-      <c r="E4" s="41" t="s">
+      <c r="E4" s="58" t="s">
         <v>88</v>
       </c>
-      <c r="F4" s="41"/>
-      <c r="G4" s="43"/>
+      <c r="F4" s="94" t="s">
+        <v>114</v>
+      </c>
+      <c r="G4" s="95"/>
       <c r="I4" s="1"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="2:24" x14ac:dyDescent="0.4">
-      <c r="B5" s="68"/>
+    <row r="5" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B5" s="99"/>
       <c r="C5" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
+      <c r="D5" s="94" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="95"/>
       <c r="F5" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="G5" s="43" t="s">
+      <c r="G5" s="59" t="s">
         <v>88</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="50" t="s">
+      <c r="J5" s="45" t="s">
         <v>19</v>
       </c>
       <c r="K5" s="14" t="s">
@@ -1447,241 +2029,167 @@
       <c r="W5" s="16"/>
       <c r="X5" s="17"/>
     </row>
-    <row r="6" spans="2:24" x14ac:dyDescent="0.4">
-      <c r="B6" s="68"/>
-      <c r="C6" s="40" t="s">
+    <row r="6" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B6" s="100"/>
+      <c r="C6" s="55" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="76" t="s">
+      <c r="D6" s="94" t="s">
+        <v>114</v>
+      </c>
+      <c r="E6" s="95"/>
+      <c r="F6" s="60" t="s">
+        <v>89</v>
+      </c>
+      <c r="G6" s="61" t="s">
+        <v>90</v>
+      </c>
+      <c r="I6" s="1"/>
+      <c r="J6" s="46"/>
+      <c r="K6" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6" s="2"/>
+      <c r="X6" s="19"/>
+    </row>
+    <row r="7" spans="2:24" x14ac:dyDescent="0.4">
+      <c r="B7" s="101" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="54" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" s="67" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="69"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="46"/>
+      <c r="K7" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="27"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="30"/>
+      <c r="Q7" s="30"/>
+      <c r="R7" s="30"/>
+      <c r="S7" s="30"/>
+      <c r="T7" s="30"/>
+      <c r="U7" s="30"/>
+      <c r="V7" s="30"/>
+      <c r="W7" s="30"/>
+      <c r="X7" s="31"/>
+    </row>
+    <row r="8" spans="2:24" x14ac:dyDescent="0.4">
+      <c r="B8" s="102"/>
+      <c r="C8" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="70" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" s="71"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="72"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8" s="2"/>
+      <c r="X8" s="19"/>
+    </row>
+    <row r="9" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B9" s="103"/>
+      <c r="C9" s="55" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="73" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" s="74"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="75"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="46"/>
+      <c r="K9" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="2"/>
+      <c r="X9" s="19"/>
+    </row>
+    <row r="10" spans="2:24" x14ac:dyDescent="0.4">
+      <c r="B10" s="101" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="52" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" s="76" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="78"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="46"/>
+      <c r="K10" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="L10" s="36"/>
+      <c r="M10" s="37"/>
+      <c r="N10" s="37"/>
+      <c r="O10" s="37"/>
+      <c r="P10" s="37"/>
+      <c r="Q10" s="37"/>
+      <c r="R10" s="37"/>
+      <c r="S10" s="37"/>
+      <c r="T10" s="37"/>
+      <c r="U10" s="37"/>
+      <c r="V10" s="37"/>
+      <c r="W10" s="37"/>
+      <c r="X10" s="38"/>
+    </row>
+    <row r="11" spans="2:24" x14ac:dyDescent="0.4">
+      <c r="B11" s="102"/>
+      <c r="C11" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" s="79"/>
+      <c r="E11" s="80"/>
+      <c r="F11" s="80"/>
+      <c r="G11" s="81"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="46" t="s">
+        <v>30</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11" s="2"/>
+      <c r="X11" s="19"/>
+    </row>
+    <row r="12" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B12" s="102"/>
+      <c r="C12" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="76" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="77" t="s">
-        <v>89</v>
-      </c>
-      <c r="G6" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="I6" s="1"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="L6" s="53"/>
-      <c r="M6" s="54"/>
-      <c r="N6" s="54"/>
-      <c r="O6" s="54"/>
-      <c r="P6" s="54"/>
-      <c r="Q6" s="54"/>
-      <c r="R6" s="54"/>
-      <c r="S6" s="54"/>
-      <c r="T6" s="54"/>
-      <c r="U6" s="54"/>
-      <c r="V6" s="54"/>
-      <c r="W6" s="54"/>
-      <c r="X6" s="19"/>
-    </row>
-    <row r="7" spans="2:24" x14ac:dyDescent="0.4">
-      <c r="B7" s="68" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7" s="78" t="s">
-        <v>98</v>
-      </c>
-      <c r="D7" s="79" t="s">
+      <c r="E12" s="89"/>
+      <c r="F12" s="82" t="s">
         <v>87</v>
       </c>
-      <c r="E7" s="79" t="s">
-        <v>87</v>
-      </c>
-      <c r="F7" s="79" t="s">
-        <v>87</v>
-      </c>
-      <c r="G7" s="79" t="s">
-        <v>87</v>
-      </c>
-      <c r="I7" s="1"/>
-      <c r="J7" s="51"/>
-      <c r="K7" s="55" t="s">
-        <v>34</v>
-      </c>
-      <c r="L7" s="56"/>
-      <c r="M7" s="57"/>
-      <c r="N7" s="57"/>
-      <c r="O7" s="57"/>
-      <c r="P7" s="57"/>
-      <c r="Q7" s="57"/>
-      <c r="R7" s="57"/>
-      <c r="S7" s="57"/>
-      <c r="T7" s="57"/>
-      <c r="U7" s="57"/>
-      <c r="V7" s="57"/>
-      <c r="W7" s="57"/>
-      <c r="X7" s="31"/>
-    </row>
-    <row r="8" spans="2:24" x14ac:dyDescent="0.4">
-      <c r="B8" s="68"/>
-      <c r="C8" s="78" t="s">
-        <v>99</v>
-      </c>
-      <c r="D8" s="79" t="s">
-        <v>87</v>
-      </c>
-      <c r="E8" s="79" t="s">
-        <v>87</v>
-      </c>
-      <c r="F8" s="79" t="s">
-        <v>87</v>
-      </c>
-      <c r="G8" s="79" t="s">
-        <v>87</v>
-      </c>
-      <c r="I8" s="1"/>
-      <c r="J8" s="51" t="s">
-        <v>18</v>
-      </c>
-      <c r="K8" s="58" t="s">
-        <v>27</v>
-      </c>
-      <c r="L8" s="53"/>
-      <c r="M8" s="54"/>
-      <c r="N8" s="54"/>
-      <c r="O8" s="54"/>
-      <c r="P8" s="54"/>
-      <c r="Q8" s="54"/>
-      <c r="R8" s="54"/>
-      <c r="S8" s="54"/>
-      <c r="T8" s="54"/>
-      <c r="U8" s="54"/>
-      <c r="V8" s="54"/>
-      <c r="W8" s="54"/>
-      <c r="X8" s="19"/>
-    </row>
-    <row r="9" spans="2:24" x14ac:dyDescent="0.4">
-      <c r="B9" s="68"/>
-      <c r="C9" s="80" t="s">
-        <v>100</v>
-      </c>
-      <c r="D9" s="79" t="s">
-        <v>87</v>
-      </c>
-      <c r="E9" s="79" t="s">
-        <v>87</v>
-      </c>
-      <c r="F9" s="79" t="s">
-        <v>87</v>
-      </c>
-      <c r="G9" s="79" t="s">
-        <v>87</v>
-      </c>
-      <c r="I9" s="1"/>
-      <c r="J9" s="51"/>
-      <c r="K9" s="58" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" s="53"/>
-      <c r="M9" s="54"/>
-      <c r="N9" s="54"/>
-      <c r="O9" s="54"/>
-      <c r="P9" s="54"/>
-      <c r="Q9" s="54"/>
-      <c r="R9" s="54"/>
-      <c r="S9" s="54"/>
-      <c r="T9" s="54"/>
-      <c r="U9" s="54"/>
-      <c r="V9" s="54"/>
-      <c r="W9" s="54"/>
-      <c r="X9" s="19"/>
-    </row>
-    <row r="10" spans="2:24" x14ac:dyDescent="0.4">
-      <c r="B10" s="68" t="s">
-        <v>94</v>
-      </c>
-      <c r="C10" s="65" t="s">
-        <v>98</v>
-      </c>
-      <c r="D10" s="64" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" s="64" t="s">
-        <v>87</v>
-      </c>
-      <c r="F10" s="64" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10" s="64" t="s">
-        <v>87</v>
-      </c>
-      <c r="I10" s="1"/>
-      <c r="J10" s="51"/>
-      <c r="K10" s="59" t="s">
-        <v>65</v>
-      </c>
-      <c r="L10" s="60"/>
-      <c r="M10" s="61"/>
-      <c r="N10" s="61"/>
-      <c r="O10" s="61"/>
-      <c r="P10" s="61"/>
-      <c r="Q10" s="61"/>
-      <c r="R10" s="61"/>
-      <c r="S10" s="61"/>
-      <c r="T10" s="61"/>
-      <c r="U10" s="61"/>
-      <c r="V10" s="61"/>
-      <c r="W10" s="61"/>
-      <c r="X10" s="38"/>
-    </row>
-    <row r="11" spans="2:24" x14ac:dyDescent="0.4">
-      <c r="B11" s="68"/>
-      <c r="C11" s="66" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="51" t="s">
-        <v>30</v>
-      </c>
-      <c r="K11" s="58" t="s">
-        <v>35</v>
-      </c>
-      <c r="L11" s="53"/>
-      <c r="M11" s="54"/>
-      <c r="N11" s="54"/>
-      <c r="O11" s="54"/>
-      <c r="P11" s="54"/>
-      <c r="Q11" s="54"/>
-      <c r="R11" s="54"/>
-      <c r="S11" s="54"/>
-      <c r="T11" s="54"/>
-      <c r="U11" s="54"/>
-      <c r="V11" s="54"/>
-      <c r="W11" s="54"/>
-      <c r="X11" s="19"/>
-    </row>
-    <row r="12" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="68"/>
-      <c r="C12" s="67" t="s">
-        <v>83</v>
-      </c>
-      <c r="D12" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="81" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="81" t="s">
-        <v>87</v>
-      </c>
+      <c r="G12" s="83"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="62"/>
+      <c r="J12" s="47"/>
       <c r="K12" s="25" t="s">
         <v>62</v>
       </c>
@@ -1700,18 +2208,18 @@
       <c r="X12" s="29"/>
     </row>
     <row r="13" spans="2:24" x14ac:dyDescent="0.4">
-      <c r="B13" s="68"/>
-      <c r="C13" s="72" t="s">
+      <c r="B13" s="102"/>
+      <c r="C13" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="82"/>
-      <c r="G13" s="82"/>
+      <c r="D13" s="90"/>
+      <c r="E13" s="91"/>
+      <c r="F13" s="84"/>
+      <c r="G13" s="85"/>
       <c r="I13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J13" s="50" t="s">
+      <c r="J13" s="45" t="s">
         <v>19</v>
       </c>
       <c r="K13" s="14" t="s">
@@ -1732,214 +2240,162 @@
       <c r="X13" s="17"/>
     </row>
     <row r="14" spans="2:24" x14ac:dyDescent="0.4">
-      <c r="B14" s="68"/>
-      <c r="C14" s="72" t="s">
+      <c r="B14" s="102"/>
+      <c r="C14" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="70"/>
-      <c r="E14" s="70"/>
-      <c r="F14" s="82"/>
-      <c r="G14" s="82"/>
+      <c r="D14" s="90"/>
+      <c r="E14" s="91"/>
+      <c r="F14" s="84"/>
+      <c r="G14" s="85"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="63"/>
-      <c r="K14" s="52" t="s">
+      <c r="J14" s="48"/>
+      <c r="K14" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L14" s="53"/>
-      <c r="M14" s="54"/>
-      <c r="N14" s="54"/>
-      <c r="O14" s="54"/>
-      <c r="P14" s="54"/>
-      <c r="Q14" s="54"/>
-      <c r="R14" s="54"/>
-      <c r="S14" s="54"/>
-      <c r="T14" s="54"/>
-      <c r="U14" s="54"/>
-      <c r="V14" s="54"/>
-      <c r="W14" s="54"/>
+      <c r="L14" s="2"/>
       <c r="X14" s="19"/>
     </row>
-    <row r="15" spans="2:24" x14ac:dyDescent="0.4">
-      <c r="B15" s="68"/>
-      <c r="C15" s="73" t="s">
+    <row r="15" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B15" s="103"/>
+      <c r="C15" s="53" t="s">
         <v>80</v>
       </c>
-      <c r="D15" s="71"/>
-      <c r="E15" s="71"/>
-      <c r="F15" s="83"/>
-      <c r="G15" s="83"/>
+      <c r="D15" s="92"/>
+      <c r="E15" s="93"/>
+      <c r="F15" s="86"/>
+      <c r="G15" s="87"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="63"/>
-      <c r="K15" s="52" t="s">
+      <c r="J15" s="48"/>
+      <c r="K15" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L15" s="53"/>
-      <c r="M15" s="54"/>
-      <c r="N15" s="54"/>
-      <c r="O15" s="54"/>
-      <c r="P15" s="54"/>
-      <c r="Q15" s="54"/>
-      <c r="R15" s="54"/>
-      <c r="S15" s="54"/>
-      <c r="T15" s="54"/>
-      <c r="U15" s="54"/>
-      <c r="V15" s="54"/>
-      <c r="W15" s="54"/>
+      <c r="L15" s="2"/>
       <c r="X15" s="19"/>
     </row>
     <row r="16" spans="2:24" x14ac:dyDescent="0.4">
       <c r="C16" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="I16" s="1"/>
-      <c r="J16" s="63"/>
-      <c r="K16" s="55" t="s">
+      <c r="J16" s="48"/>
+      <c r="K16" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="L16" s="56"/>
-      <c r="M16" s="57"/>
-      <c r="N16" s="57"/>
-      <c r="O16" s="57"/>
-      <c r="P16" s="57"/>
-      <c r="Q16" s="57"/>
-      <c r="R16" s="57"/>
-      <c r="S16" s="57"/>
-      <c r="T16" s="57"/>
-      <c r="U16" s="57"/>
-      <c r="V16" s="57"/>
-      <c r="W16" s="57"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="30"/>
+      <c r="P16" s="30"/>
+      <c r="Q16" s="30"/>
+      <c r="R16" s="30"/>
+      <c r="S16" s="30"/>
+      <c r="T16" s="30"/>
+      <c r="U16" s="30"/>
+      <c r="V16" s="30"/>
+      <c r="W16" s="30"/>
       <c r="X16" s="31"/>
     </row>
-    <row r="17" spans="4:24" x14ac:dyDescent="0.4">
-      <c r="D17" s="1"/>
+    <row r="17" spans="2:24" x14ac:dyDescent="0.4">
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="51" t="s">
+      <c r="J17" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="K17" s="58" t="s">
+      <c r="K17" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="L17" s="53"/>
-      <c r="M17" s="54"/>
-      <c r="N17" s="54"/>
-      <c r="O17" s="54"/>
-      <c r="P17" s="54"/>
-      <c r="Q17" s="54"/>
-      <c r="R17" s="54"/>
-      <c r="S17" s="54"/>
-      <c r="T17" s="54"/>
-      <c r="U17" s="54"/>
-      <c r="V17" s="54"/>
-      <c r="W17" s="54"/>
+      <c r="L17" s="2"/>
       <c r="X17" s="19"/>
     </row>
-    <row r="18" spans="4:24" x14ac:dyDescent="0.4">
-      <c r="D18" s="1"/>
+    <row r="18" spans="2:24" x14ac:dyDescent="0.4">
+      <c r="B18" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="62" t="s">
+        <v>22</v>
+      </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="51"/>
-      <c r="K18" s="58" t="s">
+      <c r="J18" s="46"/>
+      <c r="K18" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="L18" s="53"/>
-      <c r="M18" s="54"/>
-      <c r="N18" s="54"/>
-      <c r="O18" s="54"/>
-      <c r="P18" s="54"/>
-      <c r="Q18" s="54"/>
-      <c r="R18" s="54"/>
-      <c r="S18" s="54"/>
-      <c r="T18" s="54"/>
-      <c r="U18" s="54"/>
-      <c r="V18" s="54"/>
-      <c r="W18" s="54"/>
+      <c r="L18" s="2"/>
       <c r="X18" s="19"/>
     </row>
-    <row r="19" spans="4:24" x14ac:dyDescent="0.4">
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
+    <row r="19" spans="2:24" x14ac:dyDescent="0.4">
+      <c r="C19" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" s="106">
+        <v>2025</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="63"/>
-      <c r="K19" s="58" t="s">
+      <c r="J19" s="48"/>
+      <c r="K19" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="L19" s="53"/>
-      <c r="M19" s="54"/>
-      <c r="N19" s="54"/>
-      <c r="O19" s="54"/>
-      <c r="P19" s="54"/>
-      <c r="Q19" s="54"/>
-      <c r="R19" s="54"/>
-      <c r="S19" s="54"/>
-      <c r="T19" s="54"/>
-      <c r="U19" s="54"/>
-      <c r="V19" s="54"/>
-      <c r="W19" s="54"/>
+      <c r="L19" s="2"/>
       <c r="X19" s="19"/>
     </row>
-    <row r="20" spans="4:24" x14ac:dyDescent="0.4">
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
+    <row r="20" spans="2:24" x14ac:dyDescent="0.4">
+      <c r="C20" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="63"/>
-      <c r="K20" s="55" t="s">
+      <c r="J20" s="48"/>
+      <c r="K20" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="L20" s="56"/>
-      <c r="M20" s="57"/>
-      <c r="N20" s="57"/>
-      <c r="O20" s="57"/>
-      <c r="P20" s="57"/>
-      <c r="Q20" s="57"/>
-      <c r="R20" s="57"/>
-      <c r="S20" s="57"/>
-      <c r="T20" s="57"/>
-      <c r="U20" s="57"/>
-      <c r="V20" s="57"/>
-      <c r="W20" s="57"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
+      <c r="S20" s="30"/>
+      <c r="T20" s="30"/>
+      <c r="U20" s="30"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="30"/>
       <c r="X20" s="31"/>
     </row>
-    <row r="21" spans="4:24" x14ac:dyDescent="0.4">
-      <c r="D21" s="1"/>
+    <row r="21" spans="2:24" x14ac:dyDescent="0.4">
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="51" t="s">
+      <c r="J21" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="K21" s="58" t="s">
+      <c r="K21" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="L21" s="53"/>
-      <c r="M21" s="54"/>
-      <c r="N21" s="54"/>
-      <c r="O21" s="54"/>
-      <c r="P21" s="54"/>
-      <c r="Q21" s="54"/>
-      <c r="R21" s="54"/>
-      <c r="S21" s="54"/>
-      <c r="T21" s="54"/>
-      <c r="U21" s="54"/>
-      <c r="V21" s="54"/>
-      <c r="W21" s="54"/>
+      <c r="L21" s="2"/>
       <c r="X21" s="19"/>
     </row>
-    <row r="22" spans="4:24" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="D22" s="1"/>
+    <row r="22" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C22" s="62" t="s">
+        <v>23</v>
+      </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -1962,96 +2418,181 @@
       <c r="W22" s="28"/>
       <c r="X22" s="29"/>
     </row>
-    <row r="23" spans="4:24" x14ac:dyDescent="0.4">
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
+    <row r="23" spans="2:24" x14ac:dyDescent="0.4">
+      <c r="C23" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D23" s="106">
+        <v>2025</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="I23" s="1"/>
     </row>
-    <row r="24" spans="4:24" x14ac:dyDescent="0.4">
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
+    <row r="24" spans="2:24" x14ac:dyDescent="0.4">
+      <c r="C24" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D24" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="I24" s="1"/>
     </row>
-    <row r="25" spans="4:24" x14ac:dyDescent="0.4">
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
+    <row r="25" spans="2:24" x14ac:dyDescent="0.4">
+      <c r="C25" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>113</v>
+      </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="I25" s="1"/>
     </row>
-    <row r="26" spans="4:24" x14ac:dyDescent="0.4">
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
+    <row r="26" spans="2:24" x14ac:dyDescent="0.4">
+      <c r="C26" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D26" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>110</v>
+      </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="I26" s="1"/>
     </row>
-    <row r="27" spans="4:24" x14ac:dyDescent="0.4">
-      <c r="D27" s="1"/>
+    <row r="27" spans="2:24" x14ac:dyDescent="0.4">
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="I27" s="1"/>
     </row>
-    <row r="28" spans="4:24" x14ac:dyDescent="0.4">
-      <c r="D28" s="1"/>
+    <row r="28" spans="2:24" x14ac:dyDescent="0.4">
+      <c r="C28" s="62" t="s">
+        <v>111</v>
+      </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="I28" s="1"/>
     </row>
-    <row r="29" spans="4:24" x14ac:dyDescent="0.4">
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
+    <row r="29" spans="2:24" x14ac:dyDescent="0.4">
+      <c r="C29" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" s="106">
+        <v>2025</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>105</v>
+      </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="I29" s="1"/>
     </row>
-    <row r="30" spans="4:24" x14ac:dyDescent="0.4">
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
+    <row r="30" spans="2:24" x14ac:dyDescent="0.4">
+      <c r="C30" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D30" s="106">
+        <v>2025</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="I30" s="1"/>
     </row>
-    <row r="31" spans="4:24" x14ac:dyDescent="0.4">
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
+    <row r="31" spans="2:24" x14ac:dyDescent="0.4">
+      <c r="C31" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="D31" s="36">
+        <v>2026</v>
+      </c>
+      <c r="E31" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="F31" s="37"/>
+      <c r="G31" s="37"/>
       <c r="I31" s="1"/>
     </row>
-    <row r="32" spans="4:24" x14ac:dyDescent="0.4">
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
+    <row r="32" spans="2:24" x14ac:dyDescent="0.4">
+      <c r="C32" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D32" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="I32" s="1"/>
     </row>
-    <row r="33" s="1" customFormat="1" x14ac:dyDescent="0.4"/>
-    <row r="34" s="1" customFormat="1" x14ac:dyDescent="0.4"/>
+    <row r="33" spans="4:9" x14ac:dyDescent="0.4">
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34" spans="4:9" x14ac:dyDescent="0.4">
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="I34" s="1"/>
+    </row>
+    <row r="35" spans="4:9" x14ac:dyDescent="0.4">
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" spans="4:9" x14ac:dyDescent="0.4">
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="I36" s="1"/>
+    </row>
+    <row r="37" spans="4:9" x14ac:dyDescent="0.4">
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="I37" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="F12:F15"/>
+  <mergeCells count="15">
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="B10:B15"/>
     <mergeCell ref="B7:B9"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="D12:D15"/>
-    <mergeCell ref="G12:G15"/>
+    <mergeCell ref="D10:G11"/>
+    <mergeCell ref="F12:G15"/>
+    <mergeCell ref="D12:E15"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D5:E5"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="F2:G2"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="F4:G4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2069,21 +2610,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="105" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="45">
+      <c r="D2" s="65">
         <v>46203</v>
       </c>
-      <c r="E2" s="46"/>
-      <c r="F2" s="47"/>
+      <c r="E2" s="104"/>
+      <c r="F2" s="66"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B3" s="49"/>
-      <c r="C3" s="48"/>
+      <c r="B3" s="96"/>
+      <c r="C3" s="105"/>
       <c r="D3" s="7" t="s">
         <v>6</v>
       </c>

--- a/DCT - Guide/Migration Approach.xlsx
+++ b/DCT - Guide/Migration Approach.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\70023796\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62E3F0DE-D07E-4187-A7AA-FE2DD1CA68FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3ED8B0E-94F2-402D-9C78-20C741D4DA86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{7CAA1510-BEF0-44FB-B9DF-6BA498C876D6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{7CAA1510-BEF0-44FB-B9DF-6BA498C876D6}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opt3" sheetId="4" r:id="rId1"/>
-    <sheet name="Strategy Options" sheetId="1" r:id="rId2"/>
-    <sheet name="LSMW Table" sheetId="2" r:id="rId3"/>
-    <sheet name="LSMW Temp" sheetId="3" r:id="rId4"/>
+    <sheet name="Recap" sheetId="6" r:id="rId1"/>
+    <sheet name="Opt3 (Final)" sheetId="5" r:id="rId2"/>
+    <sheet name="Opt3" sheetId="4" r:id="rId3"/>
+    <sheet name="Strategy Options" sheetId="1" r:id="rId4"/>
+    <sheet name="LSMW Table" sheetId="2" r:id="rId5"/>
+    <sheet name="LSMW Temp" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,6 +43,29 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={FA784C6A-A253-4B1B-A59C-363C6A3F003D}</author>
+  </authors>
+  <commentList>
+    <comment ref="C17" authorId="0" shapeId="0" xr:uid="{FA784C6A-A253-4B1B-A59C-363C6A3F003D}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    1 Migration Open BS
+1 Migration Normal AR
+1 Migration Downpayment AR
+1 Migration Normal AP
+1 Migration Downpayment AP
+1 Migration Inventory</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
     <author>tc={31A57323-7DF0-4B2F-9222-8FFF99F19E88}</author>
   </authors>
   <commentList>
@@ -57,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="285">
   <si>
     <t>Asset Cumulative values (Acquisition + Accum. Depreciation)</t>
   </si>
@@ -131,12 +156,6 @@
     <t>Choice 2</t>
   </si>
   <si>
-    <t>2. Delink Asset GLACs (Acquisition + Accumulated Depreciation) to post ending balance on 31-Dec-2025 first, then reverse on 30-Jan-2026 (Without Asset No.)</t>
-  </si>
-  <si>
-    <t>3. Relink Asset GLACs (Acquisition + Accumulated Depreciation) to upload template to migrate all Assets on 30-Jan-2026</t>
-  </si>
-  <si>
     <t>1. Set Transfer Date 30.06.2026 + Closed FY 2025 + Highest Open FY 2026 (FAA_CMP_LDT)</t>
   </si>
   <si>
@@ -150,15 +169,6 @@
   </si>
   <si>
     <t>_For Asset transaction in current FY</t>
-  </si>
-  <si>
-    <t>3. Relink Asset GLACs (Acquisition + Accumulated Depreciation) to upload template to migrate all Posted Depreciation on 30-Jan-2026</t>
-  </si>
-  <si>
-    <t>2. Delink Asset GLACs (Acquisition + Accumulated Depreciation) to post monthly accumulated depreciation + post monthly depreciation cost via P&amp;L Template, then reverse on 30-Jan 2026 (Without Asset No.)</t>
-  </si>
-  <si>
-    <t>1. Upload template to migrate all asset transactions on 30-Jan-2026 regardless of Asset Value Date (aka Reference Date in Template)</t>
   </si>
   <si>
     <t>OK</t>
@@ -309,9 +319,6 @@
   </si>
   <si>
     <t>3* (or AFAB)</t>
-  </si>
-  <si>
-    <t>* Use delink to post direct to Asset GLACs then reverse on 30-Jan-2026</t>
   </si>
   <si>
     <t>Asset Transactions in current FY</t>
@@ -543,12 +550,597 @@
   <si>
     <t>_Extract ending balances for Non-Open BS GLACs (Profit Center-wise)</t>
   </si>
+  <si>
+    <t>Choice 1 (Transfer Date: 31.12.2025)</t>
+  </si>
+  <si>
+    <t>Choice 2 (Transfer Date: 30.06.2026)</t>
+  </si>
+  <si>
+    <t>_Extract ending Acquisition + Accum.Depreciation per GL</t>
+  </si>
+  <si>
+    <t>Jan-26 -&gt; June-26
+Transaction Details</t>
+  </si>
+  <si>
+    <t>BS/P&amp;L Template</t>
+  </si>
+  <si>
+    <t>BS/P&amp;L Template
+Open AR Template
+Open AP Template</t>
+  </si>
+  <si>
+    <t>Asset Template</t>
+  </si>
+  <si>
+    <t>2025
+Ending Balances</t>
+  </si>
+  <si>
+    <t>Direct GL Post*</t>
+  </si>
+  <si>
+    <t>* Use delink to post direct to Asset GLACs then reverse on 30-Jun-2026</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">_Extract ending balances of Acquisition + Accum.Dep + Posted Dep + Transactions </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>per Asset</t>
+    </r>
+  </si>
+  <si>
+    <t>_Extract ending balances of Non-Open BS GLACs (Profit Center-wise)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">_Extract ending balances of Acquisition + Accum.Dep </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>per GL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Profit Center-wise)</t>
+    </r>
+  </si>
+  <si>
+    <t>Summation*</t>
+  </si>
+  <si>
+    <t>* Post directly to GLACs then reverse on 30-Jun-2026</t>
+  </si>
+  <si>
+    <t>Posting Dates will always be 30-June-2026, can switch to LSMW / Z-Program if needed</t>
+  </si>
+  <si>
+    <t>1. Upload template to migrate all asset transactions on 30-Jun-2026 regardless of Asset Value Date (aka Reference Date in Template)</t>
+  </si>
+  <si>
+    <t>2. Delink Asset GLACs (Acquisition + Accumulated Depreciation) to post monthly accumulated depreciation + post monthly depreciation cost via P&amp;L Template, then reverse on 30-Jun 2026 (Without Asset No.)</t>
+  </si>
+  <si>
+    <t>2. Delink Asset GLACs (Acquisition + Accumulated Depreciation) to post ending balance on 31-Dec-2025 first, then reverse on 30-Jun-2026 (Without Asset No.)</t>
+  </si>
+  <si>
+    <t>3. Relink Asset GLACs (Acquisition + Accumulated Depreciation) to upload template to migrate all Assets on 30-Jun-2026</t>
+  </si>
+  <si>
+    <t>3. Relink Asset GLACs (Acquisition + Accumulated Depreciation) to upload template to migrate all Posted Depreciation on 30-Jun-2026</t>
+  </si>
+  <si>
+    <t>_Extract Open BS/AR/AP + Inventory into Summation in 6 Temporary Migration GLACs (Profit Center-wise)</t>
+  </si>
+  <si>
+    <t>2. Delink Asset GLACs (Acquisition + Accumulated Depreciation) to post monthly accumulated depreciation + post monthly depreciation cost via P&amp;L Template, then reverse on 30-Jun-2026 (Without Asset No.)</t>
+  </si>
+  <si>
+    <t>Templates</t>
+  </si>
+  <si>
+    <t>Mock 0</t>
+  </si>
+  <si>
+    <t>(Ending Balance 2025)</t>
+  </si>
+  <si>
+    <t>Mock 1</t>
+  </si>
+  <si>
+    <t>(Ending Balance 2025 + Jan 2026)</t>
+  </si>
+  <si>
+    <t>APC + Accum.Dep on 31st-Dec-2025</t>
+  </si>
+  <si>
+    <t>Asset Legacy No.</t>
+  </si>
+  <si>
+    <t>APC + Accum. Dep on 31st-Dec-2025</t>
+  </si>
+  <si>
+    <t>Migration GLAC</t>
+  </si>
+  <si>
+    <t>STEP 1</t>
+  </si>
+  <si>
+    <t>(For Balance Sheet/Trial Balance Report)</t>
+  </si>
+  <si>
+    <t>Open GL BS</t>
+  </si>
+  <si>
+    <t>Detail Open on 31st-Dec-2025</t>
+  </si>
+  <si>
+    <t>GL Level</t>
+  </si>
+  <si>
+    <t>Ending Balance on 31st-Dec-2025</t>
+  </si>
+  <si>
+    <t>Customer Legacy No.</t>
+  </si>
+  <si>
+    <t>Vendor Legacy No.</t>
+  </si>
+  <si>
+    <t>Non-Open GL BS</t>
+  </si>
+  <si>
+    <t>P&amp;L</t>
+  </si>
+  <si>
+    <t>Reverse STEP 1 postings on 31st-Jan-2026</t>
+  </si>
+  <si>
+    <t>STEP 2</t>
+  </si>
+  <si>
+    <t>APC + Accum.Dep + Posted Dep + Asset Trans CY on 31st-Jan-2026</t>
+  </si>
+  <si>
+    <t>STEP 3</t>
+  </si>
+  <si>
+    <t>Detail Open on 31st-Jan-2026</t>
+  </si>
+  <si>
+    <t>Ending Balance/Detail from Jan-&gt;June 2026</t>
+  </si>
+  <si>
+    <t>(Exclude WBS BS)</t>
+  </si>
+  <si>
+    <t>(Exclude WBS P&amp;L)</t>
+  </si>
+  <si>
+    <t>Project/WBS</t>
+  </si>
+  <si>
+    <t>*Different Template &amp; Custom Program for project migration</t>
+  </si>
+  <si>
+    <t>2025 (Splitting per Profit Center)</t>
+  </si>
+  <si>
+    <t>2026 (Splitting per Profit Center if decide to post sum values only)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GL P&amp;L </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>not needed</t>
+    </r>
+  </si>
+  <si>
+    <t>Inventory 2025 Migration GLAC</t>
+  </si>
+  <si>
+    <t>GL Migration</t>
+  </si>
+  <si>
+    <t>AP Migration</t>
+  </si>
+  <si>
+    <t>Summation of all Open AP items</t>
+  </si>
+  <si>
+    <t>Summation of all Open Downpayment AP items</t>
+  </si>
+  <si>
+    <t>AR Migration</t>
+  </si>
+  <si>
+    <t>Summation of all Open AR items</t>
+  </si>
+  <si>
+    <t>Summation of all Open Downpayment AR items</t>
+  </si>
+  <si>
+    <t>Per P&amp;L GLs</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inventory </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>not needed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> as it's automatically filled from other workstreams</t>
+    </r>
+  </si>
+  <si>
+    <t>Per Open BS GLs</t>
+  </si>
+  <si>
+    <t>Per Customer Open items</t>
+  </si>
+  <si>
+    <t>Per Vendor Open items</t>
+  </si>
+  <si>
+    <t>Per Inventory Code</t>
+  </si>
+  <si>
+    <t>Per Asset</t>
+  </si>
+  <si>
+    <t>Per Non-Open BS GLs including Acquisition/Accum.Dep GLs</t>
+  </si>
+  <si>
+    <t>Per Non-Open BS GLs without Acquistion/Accum.Dep GLs</t>
+  </si>
+  <si>
+    <t>No WBS related Info</t>
+  </si>
+  <si>
+    <t>Open AP with Vendor Code</t>
+  </si>
+  <si>
+    <t>Open AR with Customer Code</t>
+  </si>
+  <si>
+    <t>Acquisition/Accum.Dep/Dep Cost with Asset Code</t>
+  </si>
+  <si>
+    <t>Asset Migration</t>
+  </si>
+  <si>
+    <t>GL P&amp;L</t>
+  </si>
+  <si>
+    <t>For 2026, you get to pick whether you want to input the sum values or details in point 6 &amp; 7</t>
+  </si>
+  <si>
+    <t>Summation of all transactions per Open BS GLAC</t>
+  </si>
+  <si>
+    <t>Summation of all transactions per Inventory GLAC</t>
+  </si>
+  <si>
+    <t>Open BS GLACs</t>
+  </si>
+  <si>
+    <t>Non-Open BS GLACs</t>
+  </si>
+  <si>
+    <t>AP Downpayment Migration</t>
+  </si>
+  <si>
+    <t>AR Downpayment Migration</t>
+  </si>
+  <si>
+    <t>COAv11</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>BS</t>
+  </si>
+  <si>
+    <t>PL</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>100FL01A00</t>
+  </si>
+  <si>
+    <t>PPE Accum Depn-Freehold Land &amp; Building</t>
+  </si>
+  <si>
+    <t>Subledger</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Vendor</t>
+  </si>
+  <si>
+    <t>Open GL</t>
+  </si>
+  <si>
+    <t>Non-Open GL</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>100PM01A00</t>
+  </si>
+  <si>
+    <t>PPE Accum Depn-Plant and Machinery</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>MM Migration</t>
+  </si>
+  <si>
+    <t>Fixed Assets Migration</t>
+  </si>
+  <si>
+    <t>Migration</t>
+  </si>
+  <si>
+    <t>AP Downpayment Migration</t>
+  </si>
+  <si>
+    <t>AR Downpayment Migration</t>
+  </si>
+  <si>
+    <t>158NT05000</t>
+  </si>
+  <si>
+    <t>Related Parties-Interest Rec'b-Non-Trade-ST</t>
+  </si>
+  <si>
+    <t>206OT54000</t>
+  </si>
+  <si>
+    <t>Vendor Retention</t>
+  </si>
+  <si>
+    <t>156TD00000</t>
+  </si>
+  <si>
+    <t>Trade-Debtors</t>
+  </si>
+  <si>
+    <t>153AC01000</t>
+  </si>
+  <si>
+    <t>Adv Paym't Rec'd from Cust (CttA)</t>
+  </si>
+  <si>
+    <t>206AP00000</t>
+  </si>
+  <si>
+    <t>Trade-Creditors</t>
+  </si>
+  <si>
+    <t>159AP00000</t>
+  </si>
+  <si>
+    <t>Advance Payments to Suppliers-(No Reval-Non Monetary)</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Non-Open BS</t>
+  </si>
+  <si>
+    <t>Open BS</t>
+  </si>
+  <si>
+    <t>100CP02C00</t>
+  </si>
+  <si>
+    <t>PPE-Server  Software</t>
+  </si>
+  <si>
+    <t>100CP03C00</t>
+  </si>
+  <si>
+    <t>PPE-Computers</t>
+  </si>
+  <si>
+    <t>711PP11000</t>
+  </si>
+  <si>
+    <t>PPE-Motor Vehicles</t>
+  </si>
+  <si>
+    <t>711PP12000</t>
+  </si>
+  <si>
+    <t>PPE-Helicopters and aircraft</t>
+  </si>
+  <si>
+    <t>Asset BS</t>
+  </si>
+  <si>
+    <t>Asset P&amp;L</t>
+  </si>
+  <si>
+    <t>188CC01M00</t>
+  </si>
+  <si>
+    <t>CCE-ST Engg-SGD (Main)</t>
+  </si>
+  <si>
+    <t>300SC01000</t>
+  </si>
+  <si>
+    <t>Share Capital</t>
+  </si>
+  <si>
+    <t>705AW01000</t>
+  </si>
+  <si>
+    <t>Allowances-Allowances (Direct)</t>
+  </si>
+  <si>
+    <t>610SC02000</t>
+  </si>
+  <si>
+    <t>Cost Component-Subcontracting</t>
+  </si>
+  <si>
+    <t>610OH01000</t>
+  </si>
+  <si>
+    <t>Cost Component-Factory Overheads</t>
+  </si>
+  <si>
+    <t>810DQ00000</t>
+  </si>
+  <si>
+    <t>Operating-Income Dividend Income-Quoted External</t>
+  </si>
+  <si>
+    <t>500SD01000</t>
+  </si>
+  <si>
+    <t>Revenue-Sales Order-Main</t>
+  </si>
+  <si>
+    <t>735EX06000</t>
+  </si>
+  <si>
+    <t>ERP External-IT Cloud Services</t>
+  </si>
+  <si>
+    <t>152RM00000</t>
+  </si>
+  <si>
+    <t>Raw Materials</t>
+  </si>
+  <si>
+    <t>152TG00000</t>
+  </si>
+  <si>
+    <t>Trading Goods</t>
+  </si>
+  <si>
+    <t>152SP00000</t>
+  </si>
+  <si>
+    <t>Spare Parts</t>
+  </si>
+  <si>
+    <t>152PG00000</t>
+  </si>
+  <si>
+    <t>Packaging Goods</t>
+  </si>
+  <si>
+    <t>152OS00000</t>
+  </si>
+  <si>
+    <t>Operating Supplies</t>
+  </si>
+  <si>
+    <t>152SF00000</t>
+  </si>
+  <si>
+    <t>Semi-Finished Goods</t>
+  </si>
+  <si>
+    <t>152FG00000</t>
+  </si>
+  <si>
+    <t>Finished Goods</t>
+  </si>
+  <si>
+    <t>Inventory</t>
+  </si>
+  <si>
+    <t>Dr</t>
+  </si>
+  <si>
+    <t>Cr</t>
+  </si>
+  <si>
+    <t>Offset</t>
+  </si>
+  <si>
+    <t>Sum (Profit Center wise)</t>
+  </si>
+  <si>
+    <t>BLANK</t>
+  </si>
+  <si>
+    <t>Detail per Subledger</t>
+  </si>
+  <si>
+    <t>Material</t>
+  </si>
+  <si>
+    <t>Post on 31-Dec-2025 then reverse on 30-June-2026</t>
+  </si>
+  <si>
+    <t>Auto Post based on config for RED GLACs</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -625,8 +1217,47 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -675,8 +1306,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="47">
+  <borders count="57">
     <border>
       <left/>
       <right/>
@@ -1069,30 +1712,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -1157,19 +1776,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -1236,11 +1842,172 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="255">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1400,7 +2167,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1412,18 +2179,282 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="6" borderId="32" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="3" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="3" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="47" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="49" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="48" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="6" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="6" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="6" borderId="29" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1436,126 +2467,144 @@
     <xf numFmtId="17" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="33" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="39" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="17" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="55" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="55" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1571,6 +2620,80 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>6803</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>43542</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>6802</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>48986</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{212B57D4-F283-4392-BEC2-8721069C5AC2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="659946" y="413656"/>
+          <a:ext cx="11908970" cy="2411187"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1896,6 +3019,19 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C17" dT="2026-04-07T00:59:03.13" personId="{2920EFAE-7A21-43FB-8C0D-D5DAB7101B10}" id="{FA784C6A-A253-4B1B-A59C-363C6A3F003D}">
+    <text>1 Migration Open BS
+1 Migration Normal AR
+1 Migration Downpayment AR
+1 Migration Normal AP
+1 Migration Downpayment AP
+1 Migration Inventory</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="C31" dT="2026-04-03T03:22:09.60" personId="{2920EFAE-7A21-43FB-8C0D-D5DAB7101B10}" id="{31A57323-7DF0-4B2F-9222-8FFF99F19E88}">
     <text>If needed then in 3 Migration Templates or 1 Migration Template with Sum, we will have to fill in Open items per month-end (6 months in total)</text>
   </threadedComment>
@@ -1903,52 +3039,2483 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB4B1054-9445-434F-B8C4-4275AFE8E718}">
-  <dimension ref="B2:X37"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{747B6A5D-6923-4A79-B973-0CEE24D7FE03}">
+  <sheetPr codeName="Sheet6"/>
+  <dimension ref="A2:AI55"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.23046875" style="1"/>
-    <col min="2" max="2" width="10.84375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="68.07421875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.61328125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="22.921875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="19.61328125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="26.53515625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.23046875" style="1"/>
-    <col min="9" max="9" width="9.07421875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="27.3046875" style="1" customWidth="1"/>
-    <col min="11" max="15" width="9.23046875" style="1"/>
-    <col min="16" max="16" width="48.23046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.23046875" style="1"/>
+    <col min="2" max="2" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.54296875" customWidth="1"/>
+    <col min="5" max="5" width="16.54296875" customWidth="1"/>
+    <col min="6" max="6" width="18.54296875" customWidth="1"/>
+    <col min="10" max="10" width="12.453125" customWidth="1"/>
+    <col min="11" max="11" width="18.7265625" customWidth="1"/>
+    <col min="12" max="12" width="17.453125" customWidth="1"/>
+    <col min="13" max="13" width="18.81640625" customWidth="1"/>
+    <col min="14" max="14" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.26953125" customWidth="1"/>
+    <col min="19" max="19" width="13.08984375" style="2" customWidth="1"/>
+    <col min="20" max="20" width="12.08984375" style="186" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="47.453125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.7265625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.36328125" customWidth="1"/>
+    <col min="25" max="25" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:24" ht="14.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="96" t="s">
+    <row r="2" spans="19:35" x14ac:dyDescent="0.35">
+      <c r="Y2" s="211">
+        <v>2025</v>
+      </c>
+      <c r="Z2" s="245" t="s">
+        <v>283</v>
+      </c>
+      <c r="AA2" s="210"/>
+      <c r="AB2" s="210"/>
+      <c r="AC2" s="210"/>
+      <c r="AE2" s="211">
+        <v>2026</v>
+      </c>
+      <c r="AF2" s="250" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="3" spans="19:35" x14ac:dyDescent="0.35">
+      <c r="S3" s="187" t="s">
+        <v>232</v>
+      </c>
+      <c r="T3" s="202" t="s">
+        <v>199</v>
+      </c>
+      <c r="U3" s="188" t="s">
+        <v>214</v>
+      </c>
+      <c r="V3" s="188" t="s">
+        <v>200</v>
+      </c>
+      <c r="W3" s="188" t="s">
+        <v>206</v>
+      </c>
+      <c r="Z3" s="207" t="s">
+        <v>279</v>
+      </c>
+      <c r="AA3" s="76" t="s">
+        <v>206</v>
+      </c>
+      <c r="AC3" s="76" t="s">
+        <v>278</v>
+      </c>
+      <c r="AF3" s="207" t="s">
+        <v>281</v>
+      </c>
+      <c r="AG3" s="76" t="s">
+        <v>206</v>
+      </c>
+      <c r="AI3" s="76" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="4" spans="19:35" x14ac:dyDescent="0.35">
+      <c r="S4" s="199" t="s">
+        <v>243</v>
+      </c>
+      <c r="T4" s="203" t="s">
+        <v>235</v>
+      </c>
+      <c r="U4" s="189" t="s">
+        <v>236</v>
+      </c>
+      <c r="V4" s="189" t="s">
+        <v>201</v>
+      </c>
+      <c r="W4" s="189" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y4" s="213" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z4" s="214" t="str">
+        <f>T4</f>
+        <v>100CP02C00</v>
+      </c>
+      <c r="AA4" s="214" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB4" s="214" t="s">
+        <v>277</v>
+      </c>
+      <c r="AC4" s="215">
+        <f>$T$34</f>
+        <v>9000000000</v>
+      </c>
+      <c r="AE4" s="213" t="s">
+        <v>276</v>
+      </c>
+      <c r="AF4" s="246" t="str">
+        <f>T4</f>
+        <v>100CP02C00</v>
+      </c>
+      <c r="AG4" s="214" t="s">
+        <v>86</v>
+      </c>
+      <c r="AH4" s="214" t="s">
+        <v>277</v>
+      </c>
+      <c r="AI4" s="215">
+        <f>$T$38</f>
+        <v>9000000004</v>
+      </c>
+    </row>
+    <row r="5" spans="19:35" x14ac:dyDescent="0.35">
+      <c r="S5" s="200"/>
+      <c r="T5" s="203" t="s">
+        <v>237</v>
+      </c>
+      <c r="U5" s="189" t="s">
+        <v>238</v>
+      </c>
+      <c r="V5" s="189" t="s">
+        <v>201</v>
+      </c>
+      <c r="W5" s="189" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y5" s="206" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z5" s="209" t="str">
+        <f t="shared" ref="Z5:Z7" si="0">T5</f>
+        <v>100CP03C00</v>
+      </c>
+      <c r="AA5" s="209" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB5" s="209" t="s">
+        <v>277</v>
+      </c>
+      <c r="AC5" s="216">
+        <f>$T$34</f>
+        <v>9000000000</v>
+      </c>
+      <c r="AE5" s="206" t="s">
+        <v>276</v>
+      </c>
+      <c r="AF5" s="247" t="str">
+        <f t="shared" ref="AF5:AF31" si="1">T5</f>
+        <v>100CP03C00</v>
+      </c>
+      <c r="AG5" s="209" t="s">
+        <v>86</v>
+      </c>
+      <c r="AH5" s="209" t="s">
+        <v>277</v>
+      </c>
+      <c r="AI5" s="216">
+        <f t="shared" ref="AI5:AI9" si="2">$T$38</f>
+        <v>9000000004</v>
+      </c>
+    </row>
+    <row r="6" spans="19:35" x14ac:dyDescent="0.35">
+      <c r="S6" s="200"/>
+      <c r="T6" s="203" t="s">
+        <v>204</v>
+      </c>
+      <c r="U6" s="189" t="s">
+        <v>205</v>
+      </c>
+      <c r="V6" s="189" t="s">
+        <v>201</v>
+      </c>
+      <c r="W6" s="189" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y6" s="206" t="s">
+        <v>277</v>
+      </c>
+      <c r="Z6" s="209" t="str">
+        <f t="shared" si="0"/>
+        <v>100FL01A00</v>
+      </c>
+      <c r="AA6" s="209" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB6" s="209" t="s">
+        <v>276</v>
+      </c>
+      <c r="AC6" s="216">
+        <f>$T$34</f>
+        <v>9000000000</v>
+      </c>
+      <c r="AE6" s="206" t="s">
+        <v>277</v>
+      </c>
+      <c r="AF6" s="247" t="str">
+        <f t="shared" si="1"/>
+        <v>100FL01A00</v>
+      </c>
+      <c r="AG6" s="209" t="s">
+        <v>86</v>
+      </c>
+      <c r="AH6" s="209" t="s">
+        <v>276</v>
+      </c>
+      <c r="AI6" s="216">
+        <f t="shared" si="2"/>
+        <v>9000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="19:35" x14ac:dyDescent="0.35">
+      <c r="S7" s="201"/>
+      <c r="T7" s="203" t="s">
+        <v>212</v>
+      </c>
+      <c r="U7" s="189" t="s">
+        <v>213</v>
+      </c>
+      <c r="V7" s="189" t="s">
+        <v>201</v>
+      </c>
+      <c r="W7" s="189" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y7" s="206" t="s">
+        <v>277</v>
+      </c>
+      <c r="Z7" s="209" t="str">
+        <f t="shared" si="0"/>
+        <v>100PM01A00</v>
+      </c>
+      <c r="AA7" s="209" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB7" s="209" t="s">
+        <v>276</v>
+      </c>
+      <c r="AC7" s="216">
+        <f>$T$34</f>
+        <v>9000000000</v>
+      </c>
+      <c r="AE7" s="206" t="s">
+        <v>277</v>
+      </c>
+      <c r="AF7" s="247" t="str">
+        <f t="shared" si="1"/>
+        <v>100PM01A00</v>
+      </c>
+      <c r="AG7" s="209" t="s">
+        <v>86</v>
+      </c>
+      <c r="AH7" s="209" t="s">
+        <v>276</v>
+      </c>
+      <c r="AI7" s="216">
+        <f t="shared" si="2"/>
+        <v>9000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="19:35" x14ac:dyDescent="0.35">
+      <c r="S8" s="193" t="s">
+        <v>244</v>
+      </c>
+      <c r="T8" s="204" t="s">
+        <v>239</v>
+      </c>
+      <c r="U8" s="190" t="s">
+        <v>240</v>
+      </c>
+      <c r="V8" s="190" t="s">
+        <v>202</v>
+      </c>
+      <c r="W8" s="190" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y8" s="217"/>
+      <c r="Z8" s="218"/>
+      <c r="AA8" s="218"/>
+      <c r="AB8" s="218"/>
+      <c r="AC8" s="219"/>
+      <c r="AE8" s="226" t="s">
+        <v>276</v>
+      </c>
+      <c r="AF8" s="248" t="str">
+        <f t="shared" si="1"/>
+        <v>711PP11000</v>
+      </c>
+      <c r="AG8" s="212" t="s">
+        <v>86</v>
+      </c>
+      <c r="AH8" s="212" t="s">
+        <v>276</v>
+      </c>
+      <c r="AI8" s="227">
+        <f t="shared" si="2"/>
+        <v>9000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="19:35" x14ac:dyDescent="0.35">
+      <c r="S9" s="195"/>
+      <c r="T9" s="204" t="s">
+        <v>241</v>
+      </c>
+      <c r="U9" s="190" t="s">
+        <v>242</v>
+      </c>
+      <c r="V9" s="190" t="s">
+        <v>202</v>
+      </c>
+      <c r="W9" s="190" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y9" s="220"/>
+      <c r="Z9" s="221"/>
+      <c r="AA9" s="221"/>
+      <c r="AB9" s="221"/>
+      <c r="AC9" s="222"/>
+      <c r="AE9" s="228" t="s">
+        <v>276</v>
+      </c>
+      <c r="AF9" s="249" t="str">
+        <f t="shared" si="1"/>
+        <v>711PP12000</v>
+      </c>
+      <c r="AG9" s="229" t="s">
+        <v>86</v>
+      </c>
+      <c r="AH9" s="229" t="s">
+        <v>276</v>
+      </c>
+      <c r="AI9" s="230">
+        <f t="shared" si="2"/>
+        <v>9000000004</v>
+      </c>
+    </row>
+    <row r="10" spans="19:35" x14ac:dyDescent="0.35">
+      <c r="S10" s="192" t="s">
+        <v>93</v>
+      </c>
+      <c r="T10" s="203" t="s">
+        <v>224</v>
+      </c>
+      <c r="U10" s="189" t="s">
+        <v>225</v>
+      </c>
+      <c r="V10" s="189" t="s">
+        <v>201</v>
+      </c>
+      <c r="W10" s="189" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y10" s="213" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z10" s="214" t="str">
+        <f>T10</f>
+        <v>156TD00000</v>
+      </c>
+      <c r="AA10" s="214" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB10" s="214" t="s">
+        <v>277</v>
+      </c>
+      <c r="AC10" s="215">
+        <f>$T$34</f>
+        <v>9000000000</v>
+      </c>
+      <c r="AE10" s="213" t="s">
+        <v>276</v>
+      </c>
+      <c r="AF10" s="246" t="str">
+        <f t="shared" si="1"/>
+        <v>156TD00000</v>
+      </c>
+      <c r="AG10" s="214" t="s">
+        <v>207</v>
+      </c>
+      <c r="AH10" s="214" t="s">
+        <v>277</v>
+      </c>
+      <c r="AI10" s="215">
+        <f>T36</f>
+        <v>9000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="19:35" x14ac:dyDescent="0.35">
+      <c r="S11" s="192"/>
+      <c r="T11" s="203" t="s">
+        <v>226</v>
+      </c>
+      <c r="U11" s="189" t="s">
+        <v>227</v>
+      </c>
+      <c r="V11" s="189" t="s">
+        <v>201</v>
+      </c>
+      <c r="W11" s="189" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y11" s="223" t="s">
+        <v>277</v>
+      </c>
+      <c r="Z11" s="224" t="str">
+        <f t="shared" ref="Z11:Z13" si="3">T11</f>
+        <v>153AC01000</v>
+      </c>
+      <c r="AA11" s="224" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB11" s="224" t="s">
+        <v>276</v>
+      </c>
+      <c r="AC11" s="225">
+        <f t="shared" ref="AC11:AC25" si="4">$T$34</f>
+        <v>9000000000</v>
+      </c>
+      <c r="AE11" s="223" t="s">
+        <v>277</v>
+      </c>
+      <c r="AF11" s="251" t="str">
+        <f t="shared" si="1"/>
+        <v>153AC01000</v>
+      </c>
+      <c r="AG11" s="224" t="s">
+        <v>207</v>
+      </c>
+      <c r="AH11" s="224" t="s">
+        <v>276</v>
+      </c>
+      <c r="AI11" s="225">
+        <f>T40</f>
+        <v>9000000006</v>
+      </c>
+    </row>
+    <row r="12" spans="19:35" x14ac:dyDescent="0.35">
+      <c r="S12" s="192" t="s">
+        <v>94</v>
+      </c>
+      <c r="T12" s="203" t="s">
+        <v>228</v>
+      </c>
+      <c r="U12" s="189" t="s">
+        <v>229</v>
+      </c>
+      <c r="V12" s="189" t="s">
+        <v>201</v>
+      </c>
+      <c r="W12" s="189" t="s">
+        <v>208</v>
+      </c>
+      <c r="Y12" s="213" t="s">
+        <v>277</v>
+      </c>
+      <c r="Z12" s="214" t="str">
+        <f t="shared" si="3"/>
+        <v>206AP00000</v>
+      </c>
+      <c r="AA12" s="214" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB12" s="214" t="s">
+        <v>276</v>
+      </c>
+      <c r="AC12" s="215">
+        <f t="shared" si="4"/>
+        <v>9000000000</v>
+      </c>
+      <c r="AE12" s="213" t="s">
+        <v>277</v>
+      </c>
+      <c r="AF12" s="246" t="str">
+        <f t="shared" si="1"/>
+        <v>206AP00000</v>
+      </c>
+      <c r="AG12" s="214" t="s">
+        <v>208</v>
+      </c>
+      <c r="AH12" s="214" t="s">
+        <v>276</v>
+      </c>
+      <c r="AI12" s="215">
+        <f>T35</f>
+        <v>9000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="19:35" x14ac:dyDescent="0.35">
+      <c r="S13" s="192"/>
+      <c r="T13" s="203" t="s">
+        <v>230</v>
+      </c>
+      <c r="U13" s="189" t="s">
+        <v>231</v>
+      </c>
+      <c r="V13" s="189" t="s">
+        <v>201</v>
+      </c>
+      <c r="W13" s="189" t="s">
+        <v>208</v>
+      </c>
+      <c r="Y13" s="223" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z13" s="224" t="str">
+        <f t="shared" si="3"/>
+        <v>159AP00000</v>
+      </c>
+      <c r="AA13" s="224" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB13" s="224" t="s">
+        <v>277</v>
+      </c>
+      <c r="AC13" s="225">
+        <f t="shared" si="4"/>
+        <v>9000000000</v>
+      </c>
+      <c r="AE13" s="223" t="s">
+        <v>276</v>
+      </c>
+      <c r="AF13" s="251" t="str">
+        <f t="shared" si="1"/>
+        <v>159AP00000</v>
+      </c>
+      <c r="AG13" s="224" t="s">
+        <v>208</v>
+      </c>
+      <c r="AH13" s="224" t="s">
+        <v>277</v>
+      </c>
+      <c r="AI13" s="225">
+        <f>T39</f>
+        <v>9000000005</v>
+      </c>
+    </row>
+    <row r="14" spans="19:35" x14ac:dyDescent="0.35">
+      <c r="S14" s="192" t="s">
+        <v>234</v>
+      </c>
+      <c r="T14" s="203" t="s">
+        <v>220</v>
+      </c>
+      <c r="U14" s="189" t="s">
+        <v>221</v>
+      </c>
+      <c r="V14" s="189" t="s">
+        <v>201</v>
+      </c>
+      <c r="W14" s="189" t="s">
+        <v>209</v>
+      </c>
+      <c r="Y14" s="213" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z14" s="214" t="str">
+        <f>T14</f>
+        <v>158NT05000</v>
+      </c>
+      <c r="AA14" s="214" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB14" s="214" t="s">
+        <v>277</v>
+      </c>
+      <c r="AC14" s="215">
+        <f t="shared" si="4"/>
+        <v>9000000000</v>
+      </c>
+      <c r="AE14" s="213" t="s">
+        <v>276</v>
+      </c>
+      <c r="AF14" s="214" t="str">
+        <f t="shared" si="1"/>
+        <v>158NT05000</v>
+      </c>
+      <c r="AG14" s="214" t="s">
+        <v>280</v>
+      </c>
+      <c r="AH14" s="214" t="s">
+        <v>277</v>
+      </c>
+      <c r="AI14" s="215">
+        <f t="shared" ref="AI11:AI25" si="5">$T$34</f>
+        <v>9000000000</v>
+      </c>
+    </row>
+    <row r="15" spans="19:35" x14ac:dyDescent="0.35">
+      <c r="S15" s="192"/>
+      <c r="T15" s="203" t="s">
+        <v>222</v>
+      </c>
+      <c r="U15" s="189" t="s">
+        <v>223</v>
+      </c>
+      <c r="V15" s="189" t="s">
+        <v>201</v>
+      </c>
+      <c r="W15" s="189" t="s">
+        <v>209</v>
+      </c>
+      <c r="Y15" s="223" t="s">
+        <v>277</v>
+      </c>
+      <c r="Z15" s="224" t="str">
+        <f t="shared" ref="Z15:Z25" si="6">T15</f>
+        <v>206OT54000</v>
+      </c>
+      <c r="AA15" s="224" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB15" s="224" t="s">
+        <v>276</v>
+      </c>
+      <c r="AC15" s="225">
+        <f t="shared" si="4"/>
+        <v>9000000000</v>
+      </c>
+      <c r="AE15" s="223" t="s">
+        <v>277</v>
+      </c>
+      <c r="AF15" s="224" t="str">
+        <f t="shared" si="1"/>
+        <v>206OT54000</v>
+      </c>
+      <c r="AG15" s="224" t="s">
+        <v>280</v>
+      </c>
+      <c r="AH15" s="224" t="s">
+        <v>276</v>
+      </c>
+      <c r="AI15" s="225">
+        <f t="shared" si="5"/>
+        <v>9000000000</v>
+      </c>
+    </row>
+    <row r="16" spans="19:35" x14ac:dyDescent="0.35">
+      <c r="S16" s="192" t="s">
+        <v>233</v>
+      </c>
+      <c r="T16" s="203" t="s">
+        <v>245</v>
+      </c>
+      <c r="U16" s="189" t="s">
+        <v>246</v>
+      </c>
+      <c r="V16" s="189" t="s">
+        <v>201</v>
+      </c>
+      <c r="W16" s="189" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y16" s="213" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z16" s="214" t="str">
+        <f t="shared" si="6"/>
+        <v>188CC01M00</v>
+      </c>
+      <c r="AA16" s="214" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB16" s="214" t="s">
+        <v>277</v>
+      </c>
+      <c r="AC16" s="215">
+        <f t="shared" si="4"/>
+        <v>9000000000</v>
+      </c>
+      <c r="AE16" s="213" t="s">
+        <v>276</v>
+      </c>
+      <c r="AF16" s="214" t="str">
+        <f t="shared" si="1"/>
+        <v>188CC01M00</v>
+      </c>
+      <c r="AG16" s="214" t="s">
+        <v>280</v>
+      </c>
+      <c r="AH16" s="214" t="s">
+        <v>277</v>
+      </c>
+      <c r="AI16" s="215">
+        <f t="shared" si="5"/>
+        <v>9000000000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B17" s="76" t="s">
+        <v>137</v>
+      </c>
+      <c r="D17" s="76" t="s">
+        <v>138</v>
+      </c>
+      <c r="E17" s="76" t="s">
+        <v>139</v>
+      </c>
+      <c r="H17" s="76" t="s">
+        <v>140</v>
+      </c>
+      <c r="I17" s="76" t="s">
+        <v>141</v>
+      </c>
+      <c r="S17" s="192"/>
+      <c r="T17" s="203" t="s">
+        <v>247</v>
+      </c>
+      <c r="U17" s="189" t="s">
+        <v>248</v>
+      </c>
+      <c r="V17" s="189" t="s">
+        <v>201</v>
+      </c>
+      <c r="W17" s="189" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y17" s="206" t="s">
+        <v>277</v>
+      </c>
+      <c r="Z17" s="209" t="str">
+        <f t="shared" si="6"/>
+        <v>300SC01000</v>
+      </c>
+      <c r="AA17" s="209" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB17" s="209" t="s">
+        <v>276</v>
+      </c>
+      <c r="AC17" s="216">
+        <f t="shared" si="4"/>
+        <v>9000000000</v>
+      </c>
+      <c r="AE17" s="206" t="s">
+        <v>277</v>
+      </c>
+      <c r="AF17" s="209" t="str">
+        <f t="shared" si="1"/>
+        <v>300SC01000</v>
+      </c>
+      <c r="AG17" s="209" t="s">
+        <v>280</v>
+      </c>
+      <c r="AH17" s="209" t="s">
+        <v>276</v>
+      </c>
+      <c r="AI17" s="216">
+        <f t="shared" si="5"/>
+        <v>9000000000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
+        <v>1</v>
+      </c>
+      <c r="B18" t="s">
+        <v>120</v>
+      </c>
+      <c r="D18" s="77" t="s">
+        <v>142</v>
+      </c>
+      <c r="E18" s="78"/>
+      <c r="F18" s="79" t="s">
+        <v>143</v>
+      </c>
+      <c r="H18" s="77" t="s">
+        <v>144</v>
+      </c>
+      <c r="I18" s="78"/>
+      <c r="J18" s="78"/>
+      <c r="K18" s="78"/>
+      <c r="L18" s="78"/>
+      <c r="M18" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="N18" s="79"/>
+      <c r="P18" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q18" s="109" t="s">
+        <v>147</v>
+      </c>
+      <c r="S18" s="192"/>
+      <c r="T18" s="234" t="s">
+        <v>261</v>
+      </c>
+      <c r="U18" s="235" t="s">
+        <v>262</v>
+      </c>
+      <c r="V18" s="235" t="s">
+        <v>201</v>
+      </c>
+      <c r="W18" s="235" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y18" s="236" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z18" s="237" t="str">
+        <f t="shared" si="6"/>
+        <v>152RM00000</v>
+      </c>
+      <c r="AA18" s="237" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB18" s="237" t="s">
+        <v>277</v>
+      </c>
+      <c r="AC18" s="238">
+        <f t="shared" si="4"/>
+        <v>9000000000</v>
+      </c>
+      <c r="AE18" s="242" t="s">
+        <v>276</v>
+      </c>
+      <c r="AF18" s="252" t="str">
+        <f t="shared" si="1"/>
+        <v>152RM00000</v>
+      </c>
+      <c r="AG18" s="243" t="s">
+        <v>282</v>
+      </c>
+      <c r="AH18" s="243" t="s">
+        <v>277</v>
+      </c>
+      <c r="AI18" s="244">
+        <f>$T$37</f>
+        <v>9000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
+        <v>2</v>
+      </c>
+      <c r="B19" t="s">
+        <v>148</v>
+      </c>
+      <c r="D19" s="80" t="s">
+        <v>149</v>
+      </c>
+      <c r="F19" s="81" t="s">
+        <v>150</v>
+      </c>
+      <c r="H19" s="80" t="s">
+        <v>151</v>
+      </c>
+      <c r="M19" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="N19" s="81"/>
+      <c r="Q19" s="110"/>
+      <c r="S19" s="192"/>
+      <c r="T19" s="234" t="s">
+        <v>263</v>
+      </c>
+      <c r="U19" s="235" t="s">
+        <v>264</v>
+      </c>
+      <c r="V19" s="235" t="s">
+        <v>201</v>
+      </c>
+      <c r="W19" s="235" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y19" s="236" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z19" s="237" t="str">
+        <f t="shared" si="6"/>
+        <v>152TG00000</v>
+      </c>
+      <c r="AA19" s="237" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB19" s="237" t="s">
+        <v>277</v>
+      </c>
+      <c r="AC19" s="238">
+        <f t="shared" si="4"/>
+        <v>9000000000</v>
+      </c>
+      <c r="AE19" s="236" t="s">
+        <v>276</v>
+      </c>
+      <c r="AF19" s="253" t="str">
+        <f t="shared" si="1"/>
+        <v>152TG00000</v>
+      </c>
+      <c r="AG19" s="237" t="s">
+        <v>282</v>
+      </c>
+      <c r="AH19" s="237" t="s">
+        <v>277</v>
+      </c>
+      <c r="AI19" s="238">
+        <f t="shared" ref="AI19:AI25" si="7">$T$37</f>
+        <v>9000000003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="80" t="s">
+        <v>149</v>
+      </c>
+      <c r="F20" s="81" t="s">
+        <v>152</v>
+      </c>
+      <c r="H20" s="80" t="s">
+        <v>151</v>
+      </c>
+      <c r="M20" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="N20" s="81"/>
+      <c r="Q20" s="110"/>
+      <c r="S20" s="192"/>
+      <c r="T20" s="234" t="s">
+        <v>265</v>
+      </c>
+      <c r="U20" s="235" t="s">
+        <v>266</v>
+      </c>
+      <c r="V20" s="235" t="s">
+        <v>201</v>
+      </c>
+      <c r="W20" s="235" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y20" s="236" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z20" s="237" t="str">
+        <f t="shared" si="6"/>
+        <v>152SP00000</v>
+      </c>
+      <c r="AA20" s="237" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB20" s="237" t="s">
+        <v>277</v>
+      </c>
+      <c r="AC20" s="238">
+        <f t="shared" si="4"/>
+        <v>9000000000</v>
+      </c>
+      <c r="AE20" s="236" t="s">
+        <v>276</v>
+      </c>
+      <c r="AF20" s="253" t="str">
+        <f t="shared" si="1"/>
+        <v>152SP00000</v>
+      </c>
+      <c r="AG20" s="237" t="s">
+        <v>282</v>
+      </c>
+      <c r="AH20" s="237" t="s">
+        <v>277</v>
+      </c>
+      <c r="AI20" s="238">
+        <f t="shared" si="7"/>
+        <v>9000000003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="80" t="s">
+        <v>149</v>
+      </c>
+      <c r="F21" s="81" t="s">
+        <v>153</v>
+      </c>
+      <c r="H21" s="80" t="s">
+        <v>151</v>
+      </c>
+      <c r="M21" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="N21" s="81"/>
+      <c r="Q21" s="110"/>
+      <c r="S21" s="192"/>
+      <c r="T21" s="234" t="s">
+        <v>267</v>
+      </c>
+      <c r="U21" s="235" t="s">
+        <v>268</v>
+      </c>
+      <c r="V21" s="235" t="s">
+        <v>201</v>
+      </c>
+      <c r="W21" s="235" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y21" s="236" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z21" s="237" t="str">
+        <f t="shared" si="6"/>
+        <v>152PG00000</v>
+      </c>
+      <c r="AA21" s="237" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB21" s="237" t="s">
+        <v>277</v>
+      </c>
+      <c r="AC21" s="238">
+        <f t="shared" si="4"/>
+        <v>9000000000</v>
+      </c>
+      <c r="AE21" s="236" t="s">
+        <v>276</v>
+      </c>
+      <c r="AF21" s="253" t="str">
+        <f t="shared" si="1"/>
+        <v>152PG00000</v>
+      </c>
+      <c r="AG21" s="237" t="s">
+        <v>282</v>
+      </c>
+      <c r="AH21" s="237" t="s">
+        <v>277</v>
+      </c>
+      <c r="AI21" s="238">
+        <f t="shared" si="7"/>
+        <v>9000000003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
+        <v>5</v>
+      </c>
+      <c r="B22" t="s">
+        <v>154</v>
+      </c>
+      <c r="D22" s="80" t="s">
+        <v>151</v>
+      </c>
+      <c r="F22" s="81" t="s">
+        <v>150</v>
+      </c>
+      <c r="H22" s="80" t="s">
+        <v>151</v>
+      </c>
+      <c r="M22" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="N22" s="81"/>
+      <c r="Q22" s="110"/>
+      <c r="S22" s="192"/>
+      <c r="T22" s="234" t="s">
+        <v>265</v>
+      </c>
+      <c r="U22" s="235" t="s">
+        <v>266</v>
+      </c>
+      <c r="V22" s="235" t="s">
+        <v>201</v>
+      </c>
+      <c r="W22" s="235" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y22" s="236" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z22" s="237" t="str">
+        <f t="shared" si="6"/>
+        <v>152SP00000</v>
+      </c>
+      <c r="AA22" s="237" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB22" s="237" t="s">
+        <v>277</v>
+      </c>
+      <c r="AC22" s="238">
+        <f t="shared" si="4"/>
+        <v>9000000000</v>
+      </c>
+      <c r="AE22" s="236" t="s">
+        <v>276</v>
+      </c>
+      <c r="AF22" s="253" t="str">
+        <f t="shared" si="1"/>
+        <v>152SP00000</v>
+      </c>
+      <c r="AG22" s="237" t="s">
+        <v>282</v>
+      </c>
+      <c r="AH22" s="237" t="s">
+        <v>277</v>
+      </c>
+      <c r="AI22" s="238">
+        <f t="shared" si="7"/>
+        <v>9000000003</v>
+      </c>
+    </row>
+    <row r="23" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="2">
+        <v>6</v>
+      </c>
+      <c r="B23" t="s">
+        <v>155</v>
+      </c>
+      <c r="D23" s="82" t="s">
+        <v>108</v>
+      </c>
+      <c r="E23" s="83"/>
+      <c r="F23" s="84"/>
+      <c r="H23" s="82" t="s">
+        <v>108</v>
+      </c>
+      <c r="I23" s="83"/>
+      <c r="J23" s="83"/>
+      <c r="K23" s="83"/>
+      <c r="L23" s="83"/>
+      <c r="M23" s="83"/>
+      <c r="N23" s="84"/>
+      <c r="Q23" s="110"/>
+      <c r="S23" s="192"/>
+      <c r="T23" s="234" t="s">
+        <v>269</v>
+      </c>
+      <c r="U23" s="235" t="s">
+        <v>270</v>
+      </c>
+      <c r="V23" s="235" t="s">
+        <v>201</v>
+      </c>
+      <c r="W23" s="235" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y23" s="236" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z23" s="237" t="str">
+        <f t="shared" si="6"/>
+        <v>152OS00000</v>
+      </c>
+      <c r="AA23" s="237" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB23" s="237" t="s">
+        <v>277</v>
+      </c>
+      <c r="AC23" s="238">
+        <f t="shared" si="4"/>
+        <v>9000000000</v>
+      </c>
+      <c r="AE23" s="236" t="s">
+        <v>276</v>
+      </c>
+      <c r="AF23" s="253" t="str">
+        <f t="shared" si="1"/>
+        <v>152OS00000</v>
+      </c>
+      <c r="AG23" s="237" t="s">
+        <v>282</v>
+      </c>
+      <c r="AH23" s="237" t="s">
+        <v>277</v>
+      </c>
+      <c r="AI23" s="238">
+        <f t="shared" si="7"/>
+        <v>9000000003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="Q24" s="110"/>
+      <c r="S24" s="192"/>
+      <c r="T24" s="234" t="s">
+        <v>271</v>
+      </c>
+      <c r="U24" s="235" t="s">
+        <v>272</v>
+      </c>
+      <c r="V24" s="235" t="s">
+        <v>201</v>
+      </c>
+      <c r="W24" s="235" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y24" s="236" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z24" s="237" t="str">
+        <f t="shared" si="6"/>
+        <v>152SF00000</v>
+      </c>
+      <c r="AA24" s="237" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB24" s="237" t="s">
+        <v>277</v>
+      </c>
+      <c r="AC24" s="238">
+        <f t="shared" si="4"/>
+        <v>9000000000</v>
+      </c>
+      <c r="AE24" s="236" t="s">
+        <v>276</v>
+      </c>
+      <c r="AF24" s="253" t="str">
+        <f t="shared" si="1"/>
+        <v>152SF00000</v>
+      </c>
+      <c r="AG24" s="237" t="s">
+        <v>282</v>
+      </c>
+      <c r="AH24" s="237" t="s">
+        <v>277</v>
+      </c>
+      <c r="AI24" s="238">
+        <f t="shared" si="7"/>
+        <v>9000000003</v>
+      </c>
+    </row>
+    <row r="25" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H25" s="85" t="s">
+        <v>156</v>
+      </c>
+      <c r="I25" s="86"/>
+      <c r="J25" s="86"/>
+      <c r="K25" s="86"/>
+      <c r="L25" s="86"/>
+      <c r="M25" s="86"/>
+      <c r="N25" s="87"/>
+      <c r="P25" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q25" s="111"/>
+      <c r="S25" s="192"/>
+      <c r="T25" s="234" t="s">
+        <v>273</v>
+      </c>
+      <c r="U25" s="235" t="s">
+        <v>274</v>
+      </c>
+      <c r="V25" s="235" t="s">
+        <v>201</v>
+      </c>
+      <c r="W25" s="235" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y25" s="239" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z25" s="240" t="str">
+        <f t="shared" si="6"/>
+        <v>152FG00000</v>
+      </c>
+      <c r="AA25" s="240" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB25" s="240" t="s">
+        <v>277</v>
+      </c>
+      <c r="AC25" s="241">
+        <f t="shared" si="4"/>
+        <v>9000000000</v>
+      </c>
+      <c r="AE25" s="239" t="s">
+        <v>276</v>
+      </c>
+      <c r="AF25" s="254" t="str">
+        <f t="shared" si="1"/>
+        <v>152FG00000</v>
+      </c>
+      <c r="AG25" s="240" t="s">
+        <v>282</v>
+      </c>
+      <c r="AH25" s="240" t="s">
+        <v>277</v>
+      </c>
+      <c r="AI25" s="241">
+        <f t="shared" si="7"/>
+        <v>9000000003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="S26" s="193" t="s">
+        <v>155</v>
+      </c>
+      <c r="T26" s="204" t="s">
+        <v>249</v>
+      </c>
+      <c r="U26" s="190" t="s">
+        <v>250</v>
+      </c>
+      <c r="V26" s="190" t="s">
+        <v>202</v>
+      </c>
+      <c r="W26" s="190" t="s">
+        <v>211</v>
+      </c>
+      <c r="Y26" s="208"/>
+      <c r="Z26" s="208"/>
+      <c r="AA26" s="208"/>
+      <c r="AB26" s="208"/>
+      <c r="AC26" s="208"/>
+      <c r="AE26" s="231" t="s">
+        <v>276</v>
+      </c>
+      <c r="AF26" s="232" t="str">
+        <f t="shared" si="1"/>
+        <v>705AW01000</v>
+      </c>
+      <c r="AG26" s="232" t="s">
+        <v>280</v>
+      </c>
+      <c r="AH26" s="232" t="s">
+        <v>277</v>
+      </c>
+      <c r="AI26" s="233">
+        <f>$T$34</f>
+        <v>9000000000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="H27" s="77" t="s">
+        <v>158</v>
+      </c>
+      <c r="I27" s="78"/>
+      <c r="J27" s="78"/>
+      <c r="K27" s="78"/>
+      <c r="L27" s="78"/>
+      <c r="M27" s="88" t="s">
+        <v>143</v>
+      </c>
+      <c r="N27" s="89"/>
+      <c r="P27" t="s">
+        <v>159</v>
+      </c>
+      <c r="S27" s="194"/>
+      <c r="T27" s="204" t="s">
+        <v>259</v>
+      </c>
+      <c r="U27" s="190" t="s">
+        <v>260</v>
+      </c>
+      <c r="V27" s="190" t="s">
+        <v>202</v>
+      </c>
+      <c r="W27" s="190" t="s">
+        <v>211</v>
+      </c>
+      <c r="Y27" s="208"/>
+      <c r="Z27" s="208"/>
+      <c r="AA27" s="208"/>
+      <c r="AB27" s="208"/>
+      <c r="AC27" s="208"/>
+      <c r="AE27" s="226" t="s">
+        <v>276</v>
+      </c>
+      <c r="AF27" s="212" t="str">
+        <f t="shared" si="1"/>
+        <v>735EX06000</v>
+      </c>
+      <c r="AG27" s="212" t="s">
+        <v>280</v>
+      </c>
+      <c r="AH27" s="212" t="s">
+        <v>277</v>
+      </c>
+      <c r="AI27" s="227">
+        <f t="shared" ref="AI27:AI31" si="8">$T$34</f>
+        <v>9000000000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="H28" s="80" t="s">
+        <v>160</v>
+      </c>
+      <c r="M28" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="N28" s="90"/>
+      <c r="S28" s="194"/>
+      <c r="T28" s="204" t="s">
+        <v>251</v>
+      </c>
+      <c r="U28" s="190" t="s">
+        <v>252</v>
+      </c>
+      <c r="V28" s="190" t="s">
+        <v>202</v>
+      </c>
+      <c r="W28" s="190" t="s">
+        <v>211</v>
+      </c>
+      <c r="Y28" s="208"/>
+      <c r="Z28" s="208"/>
+      <c r="AA28" s="208"/>
+      <c r="AB28" s="208"/>
+      <c r="AC28" s="208"/>
+      <c r="AE28" s="226" t="s">
+        <v>276</v>
+      </c>
+      <c r="AF28" s="212" t="str">
+        <f t="shared" si="1"/>
+        <v>610SC02000</v>
+      </c>
+      <c r="AG28" s="212" t="s">
+        <v>280</v>
+      </c>
+      <c r="AH28" s="212" t="s">
+        <v>277</v>
+      </c>
+      <c r="AI28" s="227">
+        <f t="shared" si="8"/>
+        <v>9000000000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="H29" s="80" t="s">
+        <v>160</v>
+      </c>
+      <c r="M29" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="N29" s="90"/>
+      <c r="S29" s="194"/>
+      <c r="T29" s="204" t="s">
+        <v>253</v>
+      </c>
+      <c r="U29" s="190" t="s">
+        <v>254</v>
+      </c>
+      <c r="V29" s="190" t="s">
+        <v>202</v>
+      </c>
+      <c r="W29" s="190" t="s">
+        <v>211</v>
+      </c>
+      <c r="Y29" s="208"/>
+      <c r="Z29" s="208"/>
+      <c r="AA29" s="208"/>
+      <c r="AB29" s="208"/>
+      <c r="AC29" s="208"/>
+      <c r="AE29" s="226" t="s">
+        <v>276</v>
+      </c>
+      <c r="AF29" s="212" t="str">
+        <f t="shared" si="1"/>
+        <v>610OH01000</v>
+      </c>
+      <c r="AG29" s="212" t="s">
+        <v>280</v>
+      </c>
+      <c r="AH29" s="212" t="s">
+        <v>277</v>
+      </c>
+      <c r="AI29" s="227">
+        <f t="shared" si="8"/>
+        <v>9000000000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="H30" s="80" t="s">
+        <v>160</v>
+      </c>
+      <c r="M30" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="N30" s="90"/>
+      <c r="S30" s="194"/>
+      <c r="T30" s="204" t="s">
+        <v>257</v>
+      </c>
+      <c r="U30" s="190" t="s">
+        <v>258</v>
+      </c>
+      <c r="V30" s="190" t="s">
+        <v>202</v>
+      </c>
+      <c r="W30" s="190" t="s">
+        <v>203</v>
+      </c>
+      <c r="Y30" s="208"/>
+      <c r="Z30" s="208"/>
+      <c r="AA30" s="208"/>
+      <c r="AB30" s="208"/>
+      <c r="AC30" s="208"/>
+      <c r="AE30" s="226" t="s">
+        <v>277</v>
+      </c>
+      <c r="AF30" s="212" t="str">
+        <f t="shared" si="1"/>
+        <v>500SD01000</v>
+      </c>
+      <c r="AG30" s="212" t="s">
+        <v>280</v>
+      </c>
+      <c r="AH30" s="212" t="s">
+        <v>276</v>
+      </c>
+      <c r="AI30" s="227">
+        <f t="shared" si="8"/>
+        <v>9000000000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="H31" s="80" t="s">
+        <v>161</v>
+      </c>
+      <c r="L31" t="s">
+        <v>162</v>
+      </c>
+      <c r="M31" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="N31" s="90"/>
+      <c r="S31" s="195"/>
+      <c r="T31" s="204" t="s">
+        <v>255</v>
+      </c>
+      <c r="U31" s="190" t="s">
+        <v>256</v>
+      </c>
+      <c r="V31" s="190" t="s">
+        <v>202</v>
+      </c>
+      <c r="W31" s="190" t="s">
+        <v>203</v>
+      </c>
+      <c r="Y31" s="208"/>
+      <c r="Z31" s="208"/>
+      <c r="AA31" s="208"/>
+      <c r="AB31" s="208"/>
+      <c r="AC31" s="208"/>
+      <c r="AE31" s="228" t="s">
+        <v>277</v>
+      </c>
+      <c r="AF31" s="229" t="str">
+        <f t="shared" si="1"/>
+        <v>810DQ00000</v>
+      </c>
+      <c r="AG31" s="229" t="s">
+        <v>280</v>
+      </c>
+      <c r="AH31" s="229" t="s">
+        <v>276</v>
+      </c>
+      <c r="AI31" s="230">
+        <f t="shared" si="8"/>
+        <v>9000000000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H32" s="82" t="s">
+        <v>161</v>
+      </c>
+      <c r="I32" s="83"/>
+      <c r="J32" s="83"/>
+      <c r="K32" s="83"/>
+      <c r="L32" s="83" t="s">
+        <v>163</v>
+      </c>
+      <c r="M32" s="91" t="s">
+        <v>150</v>
+      </c>
+      <c r="N32" s="84"/>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A34" s="92">
+        <v>7</v>
+      </c>
+      <c r="B34" s="93" t="s">
+        <v>164</v>
+      </c>
+      <c r="C34" s="93"/>
+      <c r="D34" s="93" t="s">
+        <v>165</v>
+      </c>
+      <c r="E34" s="93"/>
+      <c r="F34" s="93"/>
+      <c r="S34" s="196" t="s">
+        <v>217</v>
+      </c>
+      <c r="T34" s="205">
+        <v>9000000000</v>
+      </c>
+      <c r="U34" s="191" t="s">
+        <v>170</v>
+      </c>
+      <c r="V34" s="191" t="s">
+        <v>201</v>
+      </c>
+      <c r="W34" s="191" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="S35" s="197"/>
+      <c r="T35" s="205">
+        <v>9000000001</v>
+      </c>
+      <c r="U35" s="191" t="s">
+        <v>171</v>
+      </c>
+      <c r="V35" s="191" t="s">
+        <v>201</v>
+      </c>
+      <c r="W35" s="191" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="S36" s="197"/>
+      <c r="T36" s="205">
+        <v>9000000002</v>
+      </c>
+      <c r="U36" s="191" t="s">
+        <v>174</v>
+      </c>
+      <c r="V36" s="191" t="s">
+        <v>201</v>
+      </c>
+      <c r="W36" s="191" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B37" s="95" t="s">
+        <v>166</v>
+      </c>
+      <c r="C37" s="96"/>
+      <c r="D37" s="96"/>
+      <c r="E37" s="96"/>
+      <c r="F37" s="97"/>
+      <c r="H37" s="95" t="s">
+        <v>167</v>
+      </c>
+      <c r="I37" s="96"/>
+      <c r="J37" s="96"/>
+      <c r="K37" s="96"/>
+      <c r="L37" s="96"/>
+      <c r="M37" s="97"/>
+      <c r="S37" s="197"/>
+      <c r="T37" s="205">
+        <v>9000000003</v>
+      </c>
+      <c r="U37" s="191" t="s">
+        <v>215</v>
+      </c>
+      <c r="V37" s="191" t="s">
+        <v>201</v>
+      </c>
+      <c r="W37" s="191" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B38" s="98">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>193</v>
+      </c>
+      <c r="F38" s="99"/>
+      <c r="H38" s="94">
+        <v>1</v>
+      </c>
+      <c r="I38" t="s">
+        <v>179</v>
+      </c>
+      <c r="M38" s="99"/>
+      <c r="S38" s="197"/>
+      <c r="T38" s="205">
+        <v>9000000004</v>
+      </c>
+      <c r="U38" s="191" t="s">
+        <v>216</v>
+      </c>
+      <c r="V38" s="191" t="s">
+        <v>201</v>
+      </c>
+      <c r="W38" s="191" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B39" s="98"/>
+      <c r="D39" s="107" t="s">
+        <v>195</v>
+      </c>
+      <c r="E39" s="107"/>
+      <c r="F39" s="108" t="s">
+        <v>170</v>
+      </c>
+      <c r="H39" s="94"/>
+      <c r="J39" s="105" t="s">
+        <v>148</v>
+      </c>
+      <c r="K39" s="105"/>
+      <c r="L39" s="105"/>
+      <c r="M39" s="106" t="s">
+        <v>170</v>
+      </c>
+      <c r="S39" s="197"/>
+      <c r="T39" s="205">
+        <v>9000000005</v>
+      </c>
+      <c r="U39" s="191" t="s">
+        <v>218</v>
+      </c>
+      <c r="V39" s="191" t="s">
+        <v>201</v>
+      </c>
+      <c r="W39" s="191" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B40" s="98">
+        <v>2</v>
+      </c>
+      <c r="C40" t="s">
+        <v>172</v>
+      </c>
+      <c r="F40" s="99"/>
+      <c r="H40" s="94">
+        <v>2</v>
+      </c>
+      <c r="I40" t="s">
+        <v>181</v>
+      </c>
+      <c r="M40" s="99"/>
+      <c r="S40" s="198"/>
+      <c r="T40" s="205">
+        <v>9000000006</v>
+      </c>
+      <c r="U40" s="191" t="s">
+        <v>219</v>
+      </c>
+      <c r="V40" s="191" t="s">
+        <v>201</v>
+      </c>
+      <c r="W40" s="191" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B41" s="98"/>
+      <c r="D41" s="107" t="s">
+        <v>171</v>
+      </c>
+      <c r="E41" s="107"/>
+      <c r="F41" s="108" t="s">
+        <v>170</v>
+      </c>
+      <c r="H41" s="94"/>
+      <c r="J41" s="105" t="s">
+        <v>187</v>
+      </c>
+      <c r="K41" s="105"/>
+      <c r="L41" s="105"/>
+      <c r="M41" s="106" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B42" s="98">
+        <v>3</v>
+      </c>
+      <c r="C42" t="s">
+        <v>173</v>
+      </c>
+      <c r="F42" s="99"/>
+      <c r="H42" s="94">
+        <v>3</v>
+      </c>
+      <c r="I42" t="s">
+        <v>180</v>
+      </c>
+      <c r="M42" s="99"/>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B43" s="98"/>
+      <c r="D43" s="107" t="s">
+        <v>197</v>
+      </c>
+      <c r="E43" s="107"/>
+      <c r="F43" s="108" t="s">
+        <v>170</v>
+      </c>
+      <c r="H43" s="94"/>
+      <c r="J43" s="105" t="s">
+        <v>188</v>
+      </c>
+      <c r="K43" s="105"/>
+      <c r="L43" s="105"/>
+      <c r="M43" s="106" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B44" s="98">
+        <v>4</v>
+      </c>
+      <c r="C44" t="s">
+        <v>175</v>
+      </c>
+      <c r="F44" s="99"/>
+      <c r="H44" s="94">
+        <v>4</v>
+      </c>
+      <c r="I44" t="s">
+        <v>182</v>
+      </c>
+      <c r="M44" s="99"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B45" s="98"/>
+      <c r="D45" s="107" t="s">
+        <v>174</v>
+      </c>
+      <c r="E45" s="107"/>
+      <c r="F45" s="108" t="s">
+        <v>170</v>
+      </c>
+      <c r="H45" s="94"/>
+      <c r="J45" t="s">
+        <v>178</v>
+      </c>
+      <c r="M45" s="99"/>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B46" s="98">
+        <v>5</v>
+      </c>
+      <c r="C46" t="s">
+        <v>176</v>
+      </c>
+      <c r="F46" s="99"/>
+      <c r="H46" s="94">
+        <v>5</v>
+      </c>
+      <c r="I46" t="s">
+        <v>183</v>
+      </c>
+      <c r="M46" s="99"/>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B47" s="98"/>
+      <c r="D47" s="107" t="s">
+        <v>198</v>
+      </c>
+      <c r="E47" s="107"/>
+      <c r="F47" s="108" t="s">
+        <v>170</v>
+      </c>
+      <c r="H47" s="94"/>
+      <c r="J47" s="105" t="s">
+        <v>189</v>
+      </c>
+      <c r="K47" s="105"/>
+      <c r="L47" s="105"/>
+      <c r="M47" s="106" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B48" s="98">
+        <v>6</v>
+      </c>
+      <c r="C48" t="s">
+        <v>194</v>
+      </c>
+      <c r="F48" s="99"/>
+      <c r="H48" s="94">
+        <v>6</v>
+      </c>
+      <c r="I48" t="s">
+        <v>185</v>
+      </c>
+      <c r="M48" s="99"/>
+    </row>
+    <row r="49" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B49" s="98"/>
+      <c r="D49" s="107" t="s">
+        <v>169</v>
+      </c>
+      <c r="E49" s="107"/>
+      <c r="F49" s="108" t="s">
+        <v>170</v>
+      </c>
+      <c r="H49" s="94"/>
+      <c r="J49" s="105" t="s">
+        <v>154</v>
+      </c>
+      <c r="K49" s="105"/>
+      <c r="L49" s="105"/>
+      <c r="M49" s="106" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B50" s="98">
+        <v>7</v>
+      </c>
+      <c r="C50" t="s">
+        <v>184</v>
+      </c>
+      <c r="F50" s="99"/>
+      <c r="H50" s="94">
+        <v>7</v>
+      </c>
+      <c r="I50" t="s">
+        <v>177</v>
+      </c>
+      <c r="M50" s="99"/>
+    </row>
+    <row r="51" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B51" s="98"/>
+      <c r="D51" s="105" t="s">
+        <v>196</v>
+      </c>
+      <c r="E51" s="105"/>
+      <c r="F51" s="106" t="s">
+        <v>170</v>
+      </c>
+      <c r="H51" s="103"/>
+      <c r="J51" s="105" t="s">
+        <v>191</v>
+      </c>
+      <c r="K51" s="105"/>
+      <c r="L51" s="105"/>
+      <c r="M51" s="106" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="52" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B52" s="98">
         <v>8</v>
       </c>
-      <c r="C2" s="96"/>
-      <c r="D2" s="63" t="s">
+      <c r="C52" t="s">
+        <v>177</v>
+      </c>
+      <c r="F52" s="99"/>
+      <c r="H52" s="103"/>
+      <c r="M52" s="99"/>
+    </row>
+    <row r="53" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B53" s="100"/>
+      <c r="C53" s="101"/>
+      <c r="D53" s="101" t="s">
+        <v>168</v>
+      </c>
+      <c r="E53" s="101"/>
+      <c r="F53" s="102"/>
+      <c r="H53" s="104" t="s">
+        <v>192</v>
+      </c>
+      <c r="I53" s="101"/>
+      <c r="J53" s="101"/>
+      <c r="K53" s="101"/>
+      <c r="L53" s="101"/>
+      <c r="M53" s="102"/>
+    </row>
+    <row r="55" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B55" s="112" t="s">
+        <v>186</v>
+      </c>
+      <c r="C55" s="112"/>
+      <c r="D55" s="112"/>
+      <c r="E55" s="112"/>
+      <c r="F55" s="112"/>
+      <c r="G55" s="112"/>
+      <c r="H55" s="112"/>
+      <c r="I55" s="112"/>
+      <c r="J55" s="112"/>
+      <c r="K55" s="112"/>
+      <c r="L55" s="112"/>
+      <c r="M55" s="112"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="Q18:Q25"/>
+    <mergeCell ref="B55:M55"/>
+    <mergeCell ref="S10:S11"/>
+    <mergeCell ref="S12:S13"/>
+    <mergeCell ref="S14:S15"/>
+    <mergeCell ref="S4:S7"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="S16:S25"/>
+    <mergeCell ref="S26:S31"/>
+    <mergeCell ref="S34:S40"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3357B9CC-5A3A-40CC-AF80-897C28F6CB19}">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="B1:T35"/>
+  <sheetFormatPr defaultColWidth="9.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.26953125" style="1"/>
+    <col min="2" max="2" width="10.81640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="84.08984375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.6328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.08984375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="27.26953125" style="1" customWidth="1"/>
+    <col min="8" max="12" width="9.26953125" style="1"/>
+    <col min="13" max="13" width="48.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.26953125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:20" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="122" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="123"/>
+      <c r="D2" s="116" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" s="118" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="M2" s="8"/>
+    </row>
+    <row r="3" spans="2:20" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="124"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="117"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="8"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B4" s="113" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="54" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="75" t="s">
+        <v>122</v>
+      </c>
+      <c r="E4" s="127" t="s">
+        <v>81</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="15"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+      <c r="S4" s="16"/>
+      <c r="T4" s="17"/>
+    </row>
+    <row r="5" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B5" s="120"/>
+      <c r="C5" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="9"/>
+      <c r="E5" s="128"/>
+      <c r="F5"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="T5" s="19"/>
+    </row>
+    <row r="6" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="126"/>
+      <c r="C6" s="55" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" s="65"/>
+      <c r="E6" s="129"/>
+      <c r="F6"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="T6" s="19"/>
+    </row>
+    <row r="7" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B7" s="113" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="54" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" s="139" t="s">
+        <v>127</v>
+      </c>
+      <c r="E7" s="136" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="27"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="30"/>
+      <c r="Q7" s="30"/>
+      <c r="R7" s="30"/>
+      <c r="S7" s="30"/>
+      <c r="T7" s="31"/>
+    </row>
+    <row r="8" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B8" s="120"/>
+      <c r="C8" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" s="140"/>
+      <c r="E8" s="137"/>
+      <c r="F8"/>
+      <c r="G8" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="T8" s="19"/>
+    </row>
+    <row r="9" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="121"/>
+      <c r="C9" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" s="141"/>
+      <c r="E9" s="138"/>
+      <c r="F9"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="T9" s="19"/>
+    </row>
+    <row r="10" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B10" s="113" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="73" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="66" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="142" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="T10" s="19"/>
+    </row>
+    <row r="11" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B11" s="114"/>
+      <c r="C11" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="133"/>
+      <c r="E11" s="143"/>
+      <c r="F11"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" s="27"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="30"/>
+      <c r="P11" s="30"/>
+      <c r="Q11" s="30"/>
+      <c r="R11" s="30"/>
+      <c r="S11" s="30"/>
+      <c r="T11" s="31"/>
+    </row>
+    <row r="12" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B12" s="114"/>
+      <c r="C12" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="134"/>
+      <c r="E12" s="143"/>
+      <c r="F12"/>
+      <c r="G12" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="T12" s="19"/>
+    </row>
+    <row r="13" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B13" s="115"/>
+      <c r="C13" s="53" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="135"/>
+      <c r="E13" s="144"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="I13" s="26"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="28"/>
+      <c r="N13" s="28"/>
+      <c r="O13" s="28"/>
+      <c r="P13" s="28"/>
+      <c r="Q13" s="28"/>
+      <c r="R13" s="28"/>
+      <c r="S13" s="28"/>
+      <c r="T13" s="29"/>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="C14" s="74" t="s">
+        <v>128</v>
+      </c>
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B16" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="D16" s="145">
+        <v>2025</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C17" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="D17" s="146"/>
+      <c r="E17" s="132" t="s">
+        <v>118</v>
+      </c>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C18" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="D18" s="147"/>
+      <c r="E18" s="132"/>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C20" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="130">
+        <v>2026</v>
+      </c>
+      <c r="E20" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="3:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="C21" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="D21" s="131"/>
+      <c r="E21" s="67" t="s">
+        <v>119</v>
+      </c>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="F27" s="1"/>
+    </row>
+    <row r="28" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="F29" s="1"/>
+    </row>
+    <row r="30" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="F30" s="1"/>
+    </row>
+    <row r="31" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="F32" s="1"/>
+    </row>
+    <row r="33" spans="4:6" x14ac:dyDescent="0.35">
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" spans="4:6" x14ac:dyDescent="0.35">
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+    </row>
+    <row r="35" spans="4:6" x14ac:dyDescent="0.35">
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E10:E13"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B2:C3"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="E4:E6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB4B1054-9445-434F-B8C4-4275AFE8E718}">
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="B2:X37"/>
+  <sheetFormatPr defaultColWidth="9.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.26953125" style="1"/>
+    <col min="2" max="2" width="10.81640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="68.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.6328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="22.90625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19.6328125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="26.54296875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9.26953125" style="1"/>
+    <col min="9" max="9" width="9.08984375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="27.26953125" style="1" customWidth="1"/>
+    <col min="11" max="15" width="9.26953125" style="1"/>
+    <col min="16" max="16" width="48.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.26953125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:24" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="148" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="148"/>
+      <c r="D2" s="171" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="64"/>
-      <c r="F2" s="65" t="s">
-        <v>86</v>
-      </c>
-      <c r="G2" s="66"/>
+      <c r="E2" s="172"/>
+      <c r="F2" s="173" t="s">
+        <v>80</v>
+      </c>
+      <c r="G2" s="174"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="P2" s="8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="2:24" ht="14.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="97"/>
-      <c r="C3" s="97"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="2:24" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="149"/>
+      <c r="C3" s="149"/>
       <c r="D3" s="56" t="s">
         <v>22</v>
       </c>
@@ -1963,48 +5530,50 @@
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="10" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="K3" s="8"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
     </row>
-    <row r="4" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="98" t="s">
-        <v>92</v>
-      </c>
-      <c r="C4" s="54" t="s">
-        <v>95</v>
+    <row r="4" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="150" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="70" t="s">
+        <v>89</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>88</v>
-      </c>
-      <c r="F4" s="94" t="s">
-        <v>114</v>
-      </c>
-      <c r="G4" s="95"/>
+        <v>82</v>
+      </c>
+      <c r="F4" s="71" t="s">
+        <v>108</v>
+      </c>
+      <c r="G4" s="72" t="s">
+        <v>81</v>
+      </c>
       <c r="I4" s="1"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="99"/>
-      <c r="C5" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="D5" s="94" t="s">
-        <v>114</v>
-      </c>
-      <c r="E5" s="95"/>
+    <row r="5" spans="2:24" x14ac:dyDescent="0.35">
+      <c r="B5" s="151"/>
+      <c r="C5" s="68" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="170" t="s">
+        <v>108</v>
+      </c>
+      <c r="E5" s="170"/>
       <c r="F5" s="43" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="G5" s="59" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>22</v>
@@ -2013,7 +5582,7 @@
         <v>19</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L5" s="15"/>
       <c r="M5" s="16"/>
@@ -2029,46 +5598,46 @@
       <c r="W5" s="16"/>
       <c r="X5" s="17"/>
     </row>
-    <row r="6" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="100"/>
-      <c r="C6" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="D6" s="94" t="s">
-        <v>114</v>
-      </c>
-      <c r="E6" s="95"/>
+    <row r="6" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="152"/>
+      <c r="C6" s="69" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" s="169" t="s">
+        <v>108</v>
+      </c>
+      <c r="E6" s="169"/>
       <c r="F6" s="60" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="G6" s="61" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="46"/>
       <c r="K6" s="10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L6" s="2"/>
       <c r="X6" s="19"/>
     </row>
-    <row r="7" spans="2:24" x14ac:dyDescent="0.4">
-      <c r="B7" s="101" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7" s="54" t="s">
-        <v>98</v>
-      </c>
-      <c r="D7" s="67" t="s">
+    <row r="7" spans="2:24" x14ac:dyDescent="0.35">
+      <c r="B7" s="153" t="s">
         <v>87</v>
       </c>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="69"/>
+      <c r="C7" s="64" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" s="175" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="176"/>
+      <c r="F7" s="176"/>
+      <c r="G7" s="177"/>
       <c r="I7" s="1"/>
       <c r="J7" s="46"/>
       <c r="K7" s="24" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L7" s="27"/>
       <c r="M7" s="30"/>
@@ -2084,38 +5653,38 @@
       <c r="W7" s="30"/>
       <c r="X7" s="31"/>
     </row>
-    <row r="8" spans="2:24" x14ac:dyDescent="0.4">
-      <c r="B8" s="102"/>
+    <row r="8" spans="2:24" x14ac:dyDescent="0.35">
+      <c r="B8" s="120"/>
       <c r="C8" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="D8" s="70" t="s">
-        <v>87</v>
-      </c>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="72"/>
+        <v>93</v>
+      </c>
+      <c r="D8" s="178" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" s="179"/>
+      <c r="F8" s="179"/>
+      <c r="G8" s="180"/>
       <c r="I8" s="1"/>
       <c r="J8" s="46" t="s">
         <v>18</v>
       </c>
       <c r="K8" s="20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L8" s="2"/>
       <c r="X8" s="19"/>
     </row>
-    <row r="9" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="103"/>
+    <row r="9" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="126"/>
       <c r="C9" s="55" t="s">
-        <v>100</v>
-      </c>
-      <c r="D9" s="73" t="s">
-        <v>87</v>
-      </c>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="75"/>
+        <v>94</v>
+      </c>
+      <c r="D9" s="181" t="s">
+        <v>81</v>
+      </c>
+      <c r="E9" s="182"/>
+      <c r="F9" s="182"/>
+      <c r="G9" s="183"/>
       <c r="I9" s="1"/>
       <c r="J9" s="46"/>
       <c r="K9" s="20" t="s">
@@ -2124,23 +5693,23 @@
       <c r="L9" s="2"/>
       <c r="X9" s="19"/>
     </row>
-    <row r="10" spans="2:24" x14ac:dyDescent="0.4">
-      <c r="B10" s="101" t="s">
-        <v>94</v>
+    <row r="10" spans="2:24" x14ac:dyDescent="0.35">
+      <c r="B10" s="113" t="s">
+        <v>88</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>98</v>
-      </c>
-      <c r="D10" s="76" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="78"/>
+        <v>92</v>
+      </c>
+      <c r="D10" s="154" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="155"/>
+      <c r="F10" s="155"/>
+      <c r="G10" s="156"/>
       <c r="I10" s="1"/>
       <c r="J10" s="46"/>
       <c r="K10" s="35" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="L10" s="36"/>
       <c r="M10" s="37"/>
@@ -2156,42 +5725,42 @@
       <c r="W10" s="37"/>
       <c r="X10" s="38"/>
     </row>
-    <row r="11" spans="2:24" x14ac:dyDescent="0.4">
-      <c r="B11" s="102"/>
+    <row r="11" spans="2:24" x14ac:dyDescent="0.35">
+      <c r="B11" s="120"/>
       <c r="C11" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" s="79"/>
-      <c r="E11" s="80"/>
-      <c r="F11" s="80"/>
-      <c r="G11" s="81"/>
+        <v>78</v>
+      </c>
+      <c r="D11" s="157"/>
+      <c r="E11" s="158"/>
+      <c r="F11" s="158"/>
+      <c r="G11" s="159"/>
       <c r="I11" s="1"/>
       <c r="J11" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="K11" s="20" t="s">
         <v>30</v>
-      </c>
-      <c r="K11" s="20" t="s">
-        <v>35</v>
       </c>
       <c r="L11" s="2"/>
       <c r="X11" s="19"/>
     </row>
-    <row r="12" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="102"/>
+    <row r="12" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="120"/>
       <c r="C12" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="D12" s="88" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" s="166" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="89"/>
-      <c r="F12" s="82" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="83"/>
+      <c r="E12" s="133"/>
+      <c r="F12" s="160" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" s="161"/>
       <c r="I12" s="1"/>
       <c r="J12" s="47"/>
       <c r="K12" s="25" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="L12" s="26"/>
       <c r="M12" s="28"/>
@@ -2207,15 +5776,15 @@
       <c r="W12" s="28"/>
       <c r="X12" s="29"/>
     </row>
-    <row r="13" spans="2:24" x14ac:dyDescent="0.4">
-      <c r="B13" s="102"/>
+    <row r="13" spans="2:24" x14ac:dyDescent="0.35">
+      <c r="B13" s="120"/>
       <c r="C13" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" s="90"/>
-      <c r="E13" s="91"/>
-      <c r="F13" s="84"/>
-      <c r="G13" s="85"/>
+        <v>76</v>
+      </c>
+      <c r="D13" s="167"/>
+      <c r="E13" s="134"/>
+      <c r="F13" s="162"/>
+      <c r="G13" s="163"/>
       <c r="I13" s="1" t="s">
         <v>23</v>
       </c>
@@ -2223,7 +5792,7 @@
         <v>19</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L13" s="15"/>
       <c r="M13" s="16"/>
@@ -2239,43 +5808,43 @@
       <c r="W13" s="16"/>
       <c r="X13" s="17"/>
     </row>
-    <row r="14" spans="2:24" x14ac:dyDescent="0.4">
-      <c r="B14" s="102"/>
+    <row r="14" spans="2:24" x14ac:dyDescent="0.35">
+      <c r="B14" s="120"/>
       <c r="C14" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="D14" s="90"/>
-      <c r="E14" s="91"/>
-      <c r="F14" s="84"/>
-      <c r="G14" s="85"/>
+        <v>75</v>
+      </c>
+      <c r="D14" s="167"/>
+      <c r="E14" s="134"/>
+      <c r="F14" s="162"/>
+      <c r="G14" s="163"/>
       <c r="I14" s="1"/>
       <c r="J14" s="48"/>
       <c r="K14" s="10" t="s">
-        <v>24</v>
+        <v>132</v>
       </c>
       <c r="L14" s="2"/>
       <c r="X14" s="19"/>
     </row>
-    <row r="15" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B15" s="103"/>
+    <row r="15" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B15" s="126"/>
       <c r="C15" s="53" t="s">
-        <v>80</v>
-      </c>
-      <c r="D15" s="92"/>
-      <c r="E15" s="93"/>
-      <c r="F15" s="86"/>
-      <c r="G15" s="87"/>
+        <v>74</v>
+      </c>
+      <c r="D15" s="168"/>
+      <c r="E15" s="135"/>
+      <c r="F15" s="164"/>
+      <c r="G15" s="165"/>
       <c r="I15" s="1"/>
       <c r="J15" s="48"/>
       <c r="K15" s="10" t="s">
-        <v>25</v>
+        <v>133</v>
       </c>
       <c r="L15" s="2"/>
       <c r="X15" s="19"/>
     </row>
-    <row r="16" spans="2:24" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:24" x14ac:dyDescent="0.35">
       <c r="C16" s="39" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
@@ -2283,7 +5852,7 @@
       <c r="I16" s="1"/>
       <c r="J16" s="48"/>
       <c r="K16" s="24" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L16" s="27"/>
       <c r="M16" s="30"/>
@@ -2299,7 +5868,7 @@
       <c r="W16" s="30"/>
       <c r="X16" s="31"/>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:24" x14ac:dyDescent="0.35">
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -2308,62 +5877,62 @@
         <v>18</v>
       </c>
       <c r="K17" s="20" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L17" s="2"/>
       <c r="X17" s="19"/>
     </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B18" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C18" s="62" t="s">
-        <v>22</v>
+        <v>114</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="46"/>
       <c r="K18" s="20" t="s">
-        <v>32</v>
+        <v>136</v>
       </c>
       <c r="L18" s="2"/>
       <c r="X18" s="19"/>
     </row>
-    <row r="19" spans="2:24" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:24" x14ac:dyDescent="0.35">
       <c r="C19" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D19" s="106">
+        <v>101</v>
+      </c>
+      <c r="D19" s="63">
         <v>2025</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="F19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="48"/>
       <c r="K19" s="20" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="L19" s="2"/>
       <c r="X19" s="19"/>
     </row>
-    <row r="20" spans="2:24" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:24" x14ac:dyDescent="0.35">
       <c r="C20" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D20" s="2">
         <v>2026</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="48"/>
       <c r="K20" s="24" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L20" s="27"/>
       <c r="M20" s="30"/>
@@ -2379,22 +5948,22 @@
       <c r="W20" s="30"/>
       <c r="X20" s="31"/>
     </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:24" x14ac:dyDescent="0.35">
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="46" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K21" s="20" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="L21" s="2"/>
       <c r="X21" s="19"/>
     </row>
-    <row r="22" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C22" s="62" t="s">
-        <v>23</v>
+        <v>115</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
@@ -2402,7 +5971,7 @@
       <c r="I22" s="1"/>
       <c r="J22" s="21"/>
       <c r="K22" s="25" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="L22" s="26"/>
       <c r="M22" s="28"/>
@@ -2418,155 +5987,155 @@
       <c r="W22" s="28"/>
       <c r="X22" s="29"/>
     </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:24" x14ac:dyDescent="0.35">
       <c r="C23" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D23" s="106">
+        <v>116</v>
+      </c>
+      <c r="D23" s="63">
         <v>2025</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="I23" s="1"/>
     </row>
-    <row r="24" spans="2:24" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:24" x14ac:dyDescent="0.35">
       <c r="C24" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D24" s="2">
         <v>2026</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="I24" s="1"/>
     </row>
-    <row r="25" spans="2:24" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:24" x14ac:dyDescent="0.35">
       <c r="C25" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D25" s="2">
         <v>2026</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="I25" s="1"/>
     </row>
-    <row r="26" spans="2:24" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:24" x14ac:dyDescent="0.35">
       <c r="C26" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D26" s="2">
         <v>2026</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="I26" s="1"/>
     </row>
-    <row r="27" spans="2:24" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:24" x14ac:dyDescent="0.35">
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="I27" s="1"/>
     </row>
-    <row r="28" spans="2:24" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:24" x14ac:dyDescent="0.35">
       <c r="C28" s="62" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="I28" s="1"/>
     </row>
-    <row r="29" spans="2:24" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:24" x14ac:dyDescent="0.35">
       <c r="C29" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D29" s="106">
+        <v>100</v>
+      </c>
+      <c r="D29" s="63">
         <v>2025</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="I29" s="1"/>
     </row>
-    <row r="30" spans="2:24" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:24" x14ac:dyDescent="0.35">
       <c r="C30" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D30" s="106">
+        <v>113</v>
+      </c>
+      <c r="D30" s="63">
         <v>2025</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="I30" s="1"/>
     </row>
-    <row r="31" spans="2:24" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:24" x14ac:dyDescent="0.35">
       <c r="C31" s="37" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D31" s="36">
         <v>2026</v>
       </c>
       <c r="E31" s="37" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F31" s="37"/>
       <c r="G31" s="37"/>
       <c r="I31" s="1"/>
     </row>
-    <row r="32" spans="2:24" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:24" x14ac:dyDescent="0.35">
       <c r="C32" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D32" s="2">
         <v>2026</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="I32" s="1"/>
     </row>
-    <row r="33" spans="4:9" x14ac:dyDescent="0.4">
+    <row r="33" spans="4:9" x14ac:dyDescent="0.35">
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="I33" s="1"/>
     </row>
-    <row r="34" spans="4:9" x14ac:dyDescent="0.4">
+    <row r="34" spans="4:9" x14ac:dyDescent="0.35">
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="I34" s="1"/>
     </row>
-    <row r="35" spans="4:9" x14ac:dyDescent="0.4">
+    <row r="35" spans="4:9" x14ac:dyDescent="0.35">
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="I35" s="1"/>
     </row>
-    <row r="36" spans="4:9" x14ac:dyDescent="0.4">
+    <row r="36" spans="4:9" x14ac:dyDescent="0.35">
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="I36" s="1"/>
     </row>
-    <row r="37" spans="4:9" x14ac:dyDescent="0.4">
+    <row r="37" spans="4:9" x14ac:dyDescent="0.35">
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
@@ -2574,7 +6143,7 @@
       <c r="I37" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="14">
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="B10:B15"/>
@@ -2589,42 +6158,42 @@
     <mergeCell ref="D7:G7"/>
     <mergeCell ref="D8:G8"/>
     <mergeCell ref="D9:G9"/>
-    <mergeCell ref="F4:G4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A16251E-9A23-4E00-B427-42544FA8AA6F}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="B2:R36"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.23046875" style="1"/>
-    <col min="2" max="2" width="69.53515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" style="1"/>
+    <col min="2" max="2" width="69.54296875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" style="2" customWidth="1"/>
-    <col min="4" max="4" width="26.765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="19.765625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.23046875" style="1"/>
+    <col min="4" max="4" width="26.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="19.7265625" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9.26953125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B2" s="96" t="s">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B2" s="148" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="105" t="s">
+      <c r="C2" s="185" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="65">
+      <c r="D2" s="173">
         <v>46203</v>
       </c>
-      <c r="E2" s="104"/>
-      <c r="F2" s="66"/>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B3" s="96"/>
-      <c r="C3" s="105"/>
+      <c r="E2" s="184"/>
+      <c r="F2" s="174"/>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B3" s="148"/>
+      <c r="C3" s="185"/>
       <c r="D3" s="7" t="s">
         <v>6</v>
       </c>
@@ -2635,12 +6204,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="40" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="41" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D4" s="43"/>
       <c r="E4" s="43"/>
@@ -2648,24 +6217,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="40" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="43"/>
       <c r="D5" s="43" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E5" s="43" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F5" s="41" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="40" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>15</v>
@@ -2678,7 +6247,7 @@
       </c>
       <c r="F6" s="42"/>
     </row>
-    <row r="7" spans="2:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>2</v>
       </c>
@@ -2691,7 +6260,7 @@
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
     </row>
-    <row r="8" spans="2:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>3</v>
       </c>
@@ -2704,7 +6273,7 @@
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
     </row>
-    <row r="9" spans="2:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="3" t="s">
         <v>4</v>
       </c>
@@ -2717,9 +6286,9 @@
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
     </row>
-    <row r="10" spans="2:6" ht="38.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="38.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="44" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C10" s="42" t="s">
         <v>13</v>
@@ -2734,9 +6303,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="65.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="65.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="44" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>15</v>
@@ -2751,44 +6320,44 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B12" s="39" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B14" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B15" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.4">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B16" s="10" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B18" s="10" t="s">
         <v>16</v>
       </c>
@@ -2797,7 +6366,7 @@
       </c>
       <c r="D18" s="11"/>
     </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C19" s="12" t="s">
         <v>22</v>
       </c>
@@ -2805,7 +6374,7 @@
         <v>19</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F19" s="15"/>
       <c r="G19" s="16"/>
@@ -2821,19 +6390,19 @@
       <c r="Q19" s="16"/>
       <c r="R19" s="17"/>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C20" s="18"/>
       <c r="D20" s="10"/>
       <c r="E20" s="10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="R20" s="19"/>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C21" s="18"/>
       <c r="D21" s="10"/>
       <c r="E21" s="24" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F21" s="27"/>
       <c r="G21" s="30"/>
@@ -2849,7 +6418,7 @@
       <c r="Q21" s="30"/>
       <c r="R21" s="31"/>
     </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C22" s="18"/>
       <c r="D22" s="10" t="s">
         <v>18</v>
@@ -2859,7 +6428,7 @@
       </c>
       <c r="R22" s="19"/>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C23" s="18"/>
       <c r="D23" s="10"/>
       <c r="E23" s="20" t="s">
@@ -2867,11 +6436,11 @@
       </c>
       <c r="R23" s="19"/>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C24" s="18"/>
       <c r="D24" s="10"/>
       <c r="E24" s="35" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F24" s="36"/>
       <c r="G24" s="37"/>
@@ -2887,21 +6456,21 @@
       <c r="Q24" s="37"/>
       <c r="R24" s="38"/>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C25" s="18"/>
       <c r="D25" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="E25" s="20" t="s">
-        <v>35</v>
-      </c>
       <c r="R25" s="19"/>
     </row>
-    <row r="26" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C26" s="21"/>
       <c r="D26" s="22"/>
       <c r="E26" s="25" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F26" s="26"/>
       <c r="G26" s="28"/>
@@ -2917,7 +6486,7 @@
       <c r="Q26" s="28"/>
       <c r="R26" s="29"/>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C27" s="12" t="s">
         <v>23</v>
       </c>
@@ -2925,7 +6494,7 @@
         <v>19</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F27" s="15"/>
       <c r="G27" s="16"/>
@@ -2941,27 +6510,27 @@
       <c r="Q27" s="16"/>
       <c r="R27" s="17"/>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C28" s="18"/>
       <c r="D28" s="1"/>
       <c r="E28" s="10" t="s">
-        <v>24</v>
+        <v>132</v>
       </c>
       <c r="R28" s="19"/>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C29" s="18"/>
       <c r="D29" s="1"/>
       <c r="E29" s="10" t="s">
-        <v>25</v>
+        <v>133</v>
       </c>
       <c r="R29" s="19"/>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C30" s="18"/>
       <c r="D30" s="1"/>
       <c r="E30" s="24" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F30" s="27"/>
       <c r="G30" s="30"/>
@@ -2977,37 +6546,37 @@
       <c r="Q30" s="30"/>
       <c r="R30" s="31"/>
     </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C31" s="18"/>
       <c r="D31" s="10" t="s">
         <v>18</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="R31" s="19"/>
     </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C32" s="18"/>
       <c r="D32" s="10"/>
       <c r="E32" s="20" t="s">
-        <v>32</v>
+        <v>136</v>
       </c>
       <c r="R32" s="19"/>
     </row>
-    <row r="33" spans="3:18" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:18" x14ac:dyDescent="0.35">
       <c r="C33" s="18"/>
       <c r="D33" s="1"/>
       <c r="E33" s="20" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="R33" s="19"/>
     </row>
-    <row r="34" spans="3:18" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:18" x14ac:dyDescent="0.35">
       <c r="C34" s="18"/>
       <c r="D34" s="1"/>
       <c r="E34" s="24" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F34" s="27"/>
       <c r="G34" s="30"/>
@@ -3023,21 +6592,21 @@
       <c r="Q34" s="30"/>
       <c r="R34" s="31"/>
     </row>
-    <row r="35" spans="3:18" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:18" x14ac:dyDescent="0.35">
       <c r="C35" s="18"/>
       <c r="D35" s="10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="R35" s="19"/>
     </row>
-    <row r="36" spans="3:18" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C36" s="21"/>
       <c r="D36" s="23"/>
       <c r="E36" s="25" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F36" s="26"/>
       <c r="G36" s="28"/>
@@ -3063,158 +6632,159 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0970813E-53AE-4159-B6D6-1146B744B584}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.07421875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="2.84375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="2.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C1">
         <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C2">
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C3">
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C5">
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C6">
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C7">
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C8">
         <v>31</v>
       </c>
       <c r="D8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="34" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A9" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" s="34" t="s">
-        <v>56</v>
       </c>
       <c r="C9" s="34">
         <v>3</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C10">
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -3222,52 +6792,53 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43016F89-DC87-4D67-AF59-135AD0C8A97B}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.15234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.61328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.07421875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.07421875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.15234375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.84375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.61328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.15234375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="30.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="30.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C1" s="32" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D1" s="32" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E1" s="32" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F1" s="32" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G1" s="32" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H1" s="32" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="I1" s="32" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1830</v>
       </c>
@@ -3275,19 +6846,19 @@
         <v>10000000000</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D2">
         <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H2">
         <v>500</v>
@@ -3296,7 +6867,7 @@
         <v>9000000004</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1830</v>
       </c>
@@ -3304,19 +6875,19 @@
         <v>10000000000</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D3">
         <v>105</v>
       </c>
       <c r="E3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H3">
         <v>150</v>
@@ -3325,7 +6896,7 @@
         <v>9000000004</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1830</v>
       </c>
@@ -3333,19 +6904,19 @@
         <v>10000000001</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D4">
         <v>100</v>
       </c>
       <c r="E4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H4">
         <v>700</v>
@@ -3354,7 +6925,7 @@
         <v>9000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1830</v>
       </c>
@@ -3362,19 +6933,19 @@
         <v>10000000001</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D5">
         <v>105</v>
       </c>
       <c r="E5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H5">
         <v>100</v>

--- a/DCT - Guide/Migration Approach.xlsx
+++ b/DCT - Guide/Migration Approach.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\70023796\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3ED8B0E-94F2-402D-9C78-20C741D4DA86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B50ED3E1-3F7C-4AE3-9C8D-1179F4E7D4C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{7CAA1510-BEF0-44FB-B9DF-6BA498C876D6}"/>
   </bookViews>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="291">
   <si>
     <t>Asset Cumulative values (Acquisition + Accum. Depreciation)</t>
   </si>
@@ -1135,12 +1135,31 @@
   <si>
     <t>Auto Post based on config for RED GLACs</t>
   </si>
+  <si>
+    <t>GL Template</t>
+  </si>
+  <si>
+    <t>Open AR Template</t>
+  </si>
+  <si>
+    <t>Open AP Template</t>
+  </si>
+  <si>
+    <t>GL Template
+(EXCLUDE WBS-related)</t>
+  </si>
+  <si>
+    <t>WBS migration will use custom template specifically designed for Project migration</t>
+  </si>
+  <si>
+    <t>Cross Workstream</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1256,6 +1275,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -2007,7 +2034,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="255">
+  <cellXfs count="262">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2269,237 +2296,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="3" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="3" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="47" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="49" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="48" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="6" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="6" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="6" borderId="29" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2510,36 +2306,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2553,20 +2319,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2587,7 +2346,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2595,16 +2354,301 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="55" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="47" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="49" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="48" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="6" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="6" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="6" borderId="29" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="3" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="3" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="55" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="56" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3041,7 +3085,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{747B6A5D-6923-4A79-B973-0CEE24D7FE03}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A2:AI55"/>
+  <dimension ref="A2:AK55"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14.26953125" bestFit="1" customWidth="1"/>
@@ -3055,7 +3099,7 @@
     <col min="14" max="14" width="13.36328125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13.26953125" customWidth="1"/>
     <col min="19" max="19" width="13.08984375" style="2" customWidth="1"/>
-    <col min="20" max="20" width="12.08984375" style="186" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.08984375" style="109" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="47.453125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="4.7265625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="12.36328125" customWidth="1"/>
@@ -3064,47 +3108,46 @@
     <col min="27" max="27" width="9.6328125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="2.90625" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="2.90625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.90625" style="109" customWidth="1"/>
+    <col min="32" max="32" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="22.7265625" style="109" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="19:35" x14ac:dyDescent="0.35">
-      <c r="Y2" s="211">
+    <row r="2" spans="19:37" x14ac:dyDescent="0.35">
+      <c r="Y2" s="261">
         <v>2025</v>
       </c>
-      <c r="Z2" s="245" t="s">
+      <c r="Z2" s="153" t="s">
         <v>283</v>
       </c>
-      <c r="AA2" s="210"/>
-      <c r="AB2" s="210"/>
-      <c r="AC2" s="210"/>
-      <c r="AE2" s="211">
+      <c r="AF2" s="261">
         <v>2026</v>
       </c>
-      <c r="AF2" s="250" t="s">
+      <c r="AG2" s="153" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="3" spans="19:35" x14ac:dyDescent="0.35">
-      <c r="S3" s="187" t="s">
+    <row r="3" spans="19:37" x14ac:dyDescent="0.35">
+      <c r="S3" s="110" t="s">
         <v>232</v>
       </c>
-      <c r="T3" s="202" t="s">
+      <c r="T3" s="115" t="s">
         <v>199</v>
       </c>
-      <c r="U3" s="188" t="s">
+      <c r="U3" s="111" t="s">
         <v>214</v>
       </c>
-      <c r="V3" s="188" t="s">
+      <c r="V3" s="111" t="s">
         <v>200</v>
       </c>
-      <c r="W3" s="188" t="s">
+      <c r="W3" s="111" t="s">
         <v>206</v>
       </c>
-      <c r="Z3" s="207" t="s">
+      <c r="Z3" s="76" t="s">
         <v>279</v>
       </c>
       <c r="AA3" s="76" t="s">
@@ -3113,642 +3156,684 @@
       <c r="AC3" s="76" t="s">
         <v>278</v>
       </c>
-      <c r="AF3" s="207" t="s">
+      <c r="AD3" s="255" t="s">
+        <v>81</v>
+      </c>
+      <c r="AG3" s="76" t="s">
         <v>281</v>
       </c>
-      <c r="AG3" s="76" t="s">
+      <c r="AH3" s="76" t="s">
         <v>206</v>
       </c>
-      <c r="AI3" s="76" t="s">
+      <c r="AJ3" s="76" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="4" spans="19:35" x14ac:dyDescent="0.35">
-      <c r="S4" s="199" t="s">
+      <c r="AK3" s="255" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="19:37" x14ac:dyDescent="0.35">
+      <c r="S4" s="167" t="s">
         <v>243</v>
       </c>
-      <c r="T4" s="203" t="s">
+      <c r="T4" s="116" t="s">
         <v>235</v>
       </c>
-      <c r="U4" s="189" t="s">
+      <c r="U4" s="112" t="s">
         <v>236</v>
       </c>
-      <c r="V4" s="189" t="s">
+      <c r="V4" s="112" t="s">
         <v>201</v>
       </c>
-      <c r="W4" s="189" t="s">
+      <c r="W4" s="112" t="s">
         <v>86</v>
       </c>
-      <c r="Y4" s="213" t="s">
+      <c r="Y4" s="122" t="s">
         <v>276</v>
       </c>
-      <c r="Z4" s="214" t="str">
+      <c r="Z4" s="123" t="str">
         <f>T4</f>
         <v>100CP02C00</v>
       </c>
-      <c r="AA4" s="214" t="s">
+      <c r="AA4" s="123" t="s">
         <v>280</v>
       </c>
-      <c r="AB4" s="214" t="s">
+      <c r="AB4" s="123" t="s">
         <v>277</v>
       </c>
-      <c r="AC4" s="215">
+      <c r="AC4" s="124">
         <f>$T$34</f>
         <v>9000000000</v>
       </c>
-      <c r="AE4" s="213" t="s">
+      <c r="AD4" s="167" t="s">
+        <v>285</v>
+      </c>
+      <c r="AF4" s="122" t="s">
         <v>276</v>
       </c>
-      <c r="AF4" s="246" t="str">
+      <c r="AG4" s="154" t="str">
         <f>T4</f>
         <v>100CP02C00</v>
       </c>
-      <c r="AG4" s="214" t="s">
+      <c r="AH4" s="123" t="s">
         <v>86</v>
       </c>
-      <c r="AH4" s="214" t="s">
+      <c r="AI4" s="123" t="s">
         <v>277</v>
       </c>
-      <c r="AI4" s="215">
+      <c r="AJ4" s="124">
         <f>$T$38</f>
         <v>9000000004</v>
       </c>
-    </row>
-    <row r="5" spans="19:35" x14ac:dyDescent="0.35">
-      <c r="S5" s="200"/>
-      <c r="T5" s="203" t="s">
+      <c r="AK4" s="167" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="19:37" x14ac:dyDescent="0.35">
+      <c r="S5" s="168"/>
+      <c r="T5" s="116" t="s">
         <v>237</v>
       </c>
-      <c r="U5" s="189" t="s">
+      <c r="U5" s="112" t="s">
         <v>238</v>
       </c>
-      <c r="V5" s="189" t="s">
+      <c r="V5" s="112" t="s">
         <v>201</v>
       </c>
-      <c r="W5" s="189" t="s">
+      <c r="W5" s="112" t="s">
         <v>86</v>
       </c>
-      <c r="Y5" s="206" t="s">
+      <c r="Y5" s="119" t="s">
         <v>276</v>
       </c>
-      <c r="Z5" s="209" t="str">
+      <c r="Z5" s="121" t="str">
         <f t="shared" ref="Z5:Z7" si="0">T5</f>
         <v>100CP03C00</v>
       </c>
-      <c r="AA5" s="209" t="s">
+      <c r="AA5" s="121" t="s">
         <v>280</v>
       </c>
-      <c r="AB5" s="209" t="s">
+      <c r="AB5" s="121" t="s">
         <v>277</v>
       </c>
-      <c r="AC5" s="216">
+      <c r="AC5" s="125">
         <f>$T$34</f>
         <v>9000000000</v>
       </c>
-      <c r="AE5" s="206" t="s">
+      <c r="AD5" s="168"/>
+      <c r="AF5" s="119" t="s">
         <v>276</v>
       </c>
-      <c r="AF5" s="247" t="str">
-        <f t="shared" ref="AF5:AF31" si="1">T5</f>
+      <c r="AG5" s="155" t="str">
+        <f t="shared" ref="AG5:AG31" si="1">T5</f>
         <v>100CP03C00</v>
       </c>
-      <c r="AG5" s="209" t="s">
+      <c r="AH5" s="121" t="s">
         <v>86</v>
       </c>
-      <c r="AH5" s="209" t="s">
+      <c r="AI5" s="121" t="s">
         <v>277</v>
       </c>
-      <c r="AI5" s="216">
-        <f t="shared" ref="AI5:AI9" si="2">$T$38</f>
+      <c r="AJ5" s="125">
+        <f t="shared" ref="AJ5:AJ9" si="2">$T$38</f>
         <v>9000000004</v>
       </c>
-    </row>
-    <row r="6" spans="19:35" x14ac:dyDescent="0.35">
-      <c r="S6" s="200"/>
-      <c r="T6" s="203" t="s">
+      <c r="AK5" s="168"/>
+    </row>
+    <row r="6" spans="19:37" x14ac:dyDescent="0.35">
+      <c r="S6" s="168"/>
+      <c r="T6" s="116" t="s">
         <v>204</v>
       </c>
-      <c r="U6" s="189" t="s">
+      <c r="U6" s="112" t="s">
         <v>205</v>
       </c>
-      <c r="V6" s="189" t="s">
+      <c r="V6" s="112" t="s">
         <v>201</v>
       </c>
-      <c r="W6" s="189" t="s">
+      <c r="W6" s="112" t="s">
         <v>86</v>
       </c>
-      <c r="Y6" s="206" t="s">
+      <c r="Y6" s="119" t="s">
         <v>277</v>
       </c>
-      <c r="Z6" s="209" t="str">
+      <c r="Z6" s="121" t="str">
         <f t="shared" si="0"/>
         <v>100FL01A00</v>
       </c>
-      <c r="AA6" s="209" t="s">
+      <c r="AA6" s="121" t="s">
         <v>280</v>
       </c>
-      <c r="AB6" s="209" t="s">
+      <c r="AB6" s="121" t="s">
         <v>276</v>
       </c>
-      <c r="AC6" s="216">
+      <c r="AC6" s="125">
         <f>$T$34</f>
         <v>9000000000</v>
       </c>
-      <c r="AE6" s="206" t="s">
+      <c r="AD6" s="168"/>
+      <c r="AF6" s="119" t="s">
         <v>277</v>
       </c>
-      <c r="AF6" s="247" t="str">
+      <c r="AG6" s="155" t="str">
         <f t="shared" si="1"/>
         <v>100FL01A00</v>
       </c>
-      <c r="AG6" s="209" t="s">
+      <c r="AH6" s="121" t="s">
         <v>86</v>
       </c>
-      <c r="AH6" s="209" t="s">
+      <c r="AI6" s="121" t="s">
         <v>276</v>
       </c>
-      <c r="AI6" s="216">
+      <c r="AJ6" s="125">
         <f t="shared" si="2"/>
         <v>9000000004</v>
       </c>
-    </row>
-    <row r="7" spans="19:35" x14ac:dyDescent="0.35">
-      <c r="S7" s="201"/>
-      <c r="T7" s="203" t="s">
+      <c r="AK6" s="168"/>
+    </row>
+    <row r="7" spans="19:37" x14ac:dyDescent="0.35">
+      <c r="S7" s="169"/>
+      <c r="T7" s="116" t="s">
         <v>212</v>
       </c>
-      <c r="U7" s="189" t="s">
+      <c r="U7" s="112" t="s">
         <v>213</v>
       </c>
-      <c r="V7" s="189" t="s">
+      <c r="V7" s="112" t="s">
         <v>201</v>
       </c>
-      <c r="W7" s="189" t="s">
+      <c r="W7" s="112" t="s">
         <v>86</v>
       </c>
-      <c r="Y7" s="206" t="s">
+      <c r="Y7" s="119" t="s">
         <v>277</v>
       </c>
-      <c r="Z7" s="209" t="str">
+      <c r="Z7" s="121" t="str">
         <f t="shared" si="0"/>
         <v>100PM01A00</v>
       </c>
-      <c r="AA7" s="209" t="s">
+      <c r="AA7" s="121" t="s">
         <v>280</v>
       </c>
-      <c r="AB7" s="209" t="s">
+      <c r="AB7" s="121" t="s">
         <v>276</v>
       </c>
-      <c r="AC7" s="216">
+      <c r="AC7" s="125">
         <f>$T$34</f>
         <v>9000000000</v>
       </c>
-      <c r="AE7" s="206" t="s">
+      <c r="AD7" s="168"/>
+      <c r="AF7" s="119" t="s">
         <v>277</v>
       </c>
-      <c r="AF7" s="247" t="str">
+      <c r="AG7" s="155" t="str">
         <f t="shared" si="1"/>
         <v>100PM01A00</v>
       </c>
-      <c r="AG7" s="209" t="s">
+      <c r="AH7" s="121" t="s">
         <v>86</v>
       </c>
-      <c r="AH7" s="209" t="s">
+      <c r="AI7" s="121" t="s">
         <v>276</v>
       </c>
-      <c r="AI7" s="216">
+      <c r="AJ7" s="125">
         <f t="shared" si="2"/>
         <v>9000000004</v>
       </c>
-    </row>
-    <row r="8" spans="19:35" x14ac:dyDescent="0.35">
-      <c r="S8" s="193" t="s">
+      <c r="AK7" s="168"/>
+    </row>
+    <row r="8" spans="19:37" x14ac:dyDescent="0.35">
+      <c r="S8" s="170" t="s">
         <v>244</v>
       </c>
-      <c r="T8" s="204" t="s">
+      <c r="T8" s="117" t="s">
         <v>239</v>
       </c>
-      <c r="U8" s="190" t="s">
+      <c r="U8" s="113" t="s">
         <v>240</v>
       </c>
-      <c r="V8" s="190" t="s">
+      <c r="V8" s="113" t="s">
         <v>202</v>
       </c>
-      <c r="W8" s="190" t="s">
+      <c r="W8" s="113" t="s">
         <v>86</v>
       </c>
-      <c r="Y8" s="217"/>
-      <c r="Z8" s="218"/>
-      <c r="AA8" s="218"/>
-      <c r="AB8" s="218"/>
-      <c r="AC8" s="219"/>
-      <c r="AE8" s="226" t="s">
+      <c r="Y8" s="126"/>
+      <c r="Z8" s="120"/>
+      <c r="AA8" s="120"/>
+      <c r="AB8" s="120"/>
+      <c r="AC8" s="127"/>
+      <c r="AD8" s="168"/>
+      <c r="AF8" s="134" t="s">
         <v>276</v>
       </c>
-      <c r="AF8" s="248" t="str">
+      <c r="AG8" s="156" t="str">
         <f t="shared" si="1"/>
         <v>711PP11000</v>
       </c>
-      <c r="AG8" s="212" t="s">
+      <c r="AH8" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="AH8" s="212" t="s">
+      <c r="AI8" s="107" t="s">
         <v>276</v>
       </c>
-      <c r="AI8" s="227">
+      <c r="AJ8" s="135">
         <f t="shared" si="2"/>
         <v>9000000004</v>
       </c>
-    </row>
-    <row r="9" spans="19:35" x14ac:dyDescent="0.35">
-      <c r="S9" s="195"/>
-      <c r="T9" s="204" t="s">
+      <c r="AK8" s="168"/>
+    </row>
+    <row r="9" spans="19:37" x14ac:dyDescent="0.35">
+      <c r="S9" s="171"/>
+      <c r="T9" s="117" t="s">
         <v>241</v>
       </c>
-      <c r="U9" s="190" t="s">
+      <c r="U9" s="113" t="s">
         <v>242</v>
       </c>
-      <c r="V9" s="190" t="s">
+      <c r="V9" s="113" t="s">
         <v>202</v>
       </c>
-      <c r="W9" s="190" t="s">
+      <c r="W9" s="113" t="s">
         <v>86</v>
       </c>
-      <c r="Y9" s="220"/>
-      <c r="Z9" s="221"/>
-      <c r="AA9" s="221"/>
-      <c r="AB9" s="221"/>
-      <c r="AC9" s="222"/>
-      <c r="AE9" s="228" t="s">
+      <c r="Y9" s="128"/>
+      <c r="Z9" s="129"/>
+      <c r="AA9" s="129"/>
+      <c r="AB9" s="129"/>
+      <c r="AC9" s="130"/>
+      <c r="AD9" s="168"/>
+      <c r="AF9" s="136" t="s">
         <v>276</v>
       </c>
-      <c r="AF9" s="249" t="str">
+      <c r="AG9" s="157" t="str">
         <f t="shared" si="1"/>
         <v>711PP12000</v>
       </c>
-      <c r="AG9" s="229" t="s">
+      <c r="AH9" s="137" t="s">
         <v>86</v>
       </c>
-      <c r="AH9" s="229" t="s">
+      <c r="AI9" s="137" t="s">
         <v>276</v>
       </c>
-      <c r="AI9" s="230">
+      <c r="AJ9" s="138">
         <f t="shared" si="2"/>
         <v>9000000004</v>
       </c>
-    </row>
-    <row r="10" spans="19:35" x14ac:dyDescent="0.35">
-      <c r="S10" s="192" t="s">
+      <c r="AK9" s="169"/>
+    </row>
+    <row r="10" spans="19:37" x14ac:dyDescent="0.35">
+      <c r="S10" s="166" t="s">
         <v>93</v>
       </c>
-      <c r="T10" s="203" t="s">
+      <c r="T10" s="116" t="s">
         <v>224</v>
       </c>
-      <c r="U10" s="189" t="s">
+      <c r="U10" s="112" t="s">
         <v>225</v>
       </c>
-      <c r="V10" s="189" t="s">
+      <c r="V10" s="112" t="s">
         <v>201</v>
       </c>
-      <c r="W10" s="189" t="s">
+      <c r="W10" s="112" t="s">
         <v>207</v>
       </c>
-      <c r="Y10" s="213" t="s">
+      <c r="Y10" s="122" t="s">
         <v>276</v>
       </c>
-      <c r="Z10" s="214" t="str">
+      <c r="Z10" s="123" t="str">
         <f>T10</f>
         <v>156TD00000</v>
       </c>
-      <c r="AA10" s="214" t="s">
+      <c r="AA10" s="123" t="s">
         <v>280</v>
       </c>
-      <c r="AB10" s="214" t="s">
+      <c r="AB10" s="123" t="s">
         <v>277</v>
       </c>
-      <c r="AC10" s="215">
+      <c r="AC10" s="124">
         <f>$T$34</f>
         <v>9000000000</v>
       </c>
-      <c r="AE10" s="213" t="s">
+      <c r="AD10" s="168"/>
+      <c r="AF10" s="122" t="s">
         <v>276</v>
       </c>
-      <c r="AF10" s="246" t="str">
+      <c r="AG10" s="154" t="str">
         <f t="shared" si="1"/>
         <v>156TD00000</v>
       </c>
-      <c r="AG10" s="214" t="s">
+      <c r="AH10" s="123" t="s">
         <v>207</v>
       </c>
-      <c r="AH10" s="214" t="s">
+      <c r="AI10" s="123" t="s">
         <v>277</v>
       </c>
-      <c r="AI10" s="215">
+      <c r="AJ10" s="124">
         <f>T36</f>
         <v>9000000002</v>
       </c>
-    </row>
-    <row r="11" spans="19:35" x14ac:dyDescent="0.35">
-      <c r="S11" s="192"/>
-      <c r="T11" s="203" t="s">
+      <c r="AK10" s="167" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="11" spans="19:37" x14ac:dyDescent="0.35">
+      <c r="S11" s="166"/>
+      <c r="T11" s="116" t="s">
         <v>226</v>
       </c>
-      <c r="U11" s="189" t="s">
+      <c r="U11" s="112" t="s">
         <v>227</v>
       </c>
-      <c r="V11" s="189" t="s">
+      <c r="V11" s="112" t="s">
         <v>201</v>
       </c>
-      <c r="W11" s="189" t="s">
+      <c r="W11" s="112" t="s">
         <v>207</v>
       </c>
-      <c r="Y11" s="223" t="s">
+      <c r="Y11" s="131" t="s">
         <v>277</v>
       </c>
-      <c r="Z11" s="224" t="str">
+      <c r="Z11" s="132" t="str">
         <f t="shared" ref="Z11:Z13" si="3">T11</f>
         <v>153AC01000</v>
       </c>
-      <c r="AA11" s="224" t="s">
+      <c r="AA11" s="132" t="s">
         <v>280</v>
       </c>
-      <c r="AB11" s="224" t="s">
+      <c r="AB11" s="132" t="s">
         <v>276</v>
       </c>
-      <c r="AC11" s="225">
+      <c r="AC11" s="133">
         <f t="shared" ref="AC11:AC25" si="4">$T$34</f>
         <v>9000000000</v>
       </c>
-      <c r="AE11" s="223" t="s">
+      <c r="AD11" s="168"/>
+      <c r="AF11" s="131" t="s">
         <v>277</v>
       </c>
-      <c r="AF11" s="251" t="str">
+      <c r="AG11" s="158" t="str">
         <f t="shared" si="1"/>
         <v>153AC01000</v>
       </c>
-      <c r="AG11" s="224" t="s">
+      <c r="AH11" s="132" t="s">
         <v>207</v>
       </c>
-      <c r="AH11" s="224" t="s">
+      <c r="AI11" s="132" t="s">
         <v>276</v>
       </c>
-      <c r="AI11" s="225">
+      <c r="AJ11" s="133">
         <f>T40</f>
         <v>9000000006</v>
       </c>
-    </row>
-    <row r="12" spans="19:35" x14ac:dyDescent="0.35">
-      <c r="S12" s="192" t="s">
+      <c r="AK11" s="169"/>
+    </row>
+    <row r="12" spans="19:37" x14ac:dyDescent="0.35">
+      <c r="S12" s="166" t="s">
         <v>94</v>
       </c>
-      <c r="T12" s="203" t="s">
+      <c r="T12" s="116" t="s">
         <v>228</v>
       </c>
-      <c r="U12" s="189" t="s">
+      <c r="U12" s="112" t="s">
         <v>229</v>
       </c>
-      <c r="V12" s="189" t="s">
+      <c r="V12" s="112" t="s">
         <v>201</v>
       </c>
-      <c r="W12" s="189" t="s">
+      <c r="W12" s="112" t="s">
         <v>208</v>
       </c>
-      <c r="Y12" s="213" t="s">
+      <c r="Y12" s="122" t="s">
         <v>277</v>
       </c>
-      <c r="Z12" s="214" t="str">
+      <c r="Z12" s="123" t="str">
         <f t="shared" si="3"/>
         <v>206AP00000</v>
       </c>
-      <c r="AA12" s="214" t="s">
+      <c r="AA12" s="123" t="s">
         <v>280</v>
       </c>
-      <c r="AB12" s="214" t="s">
+      <c r="AB12" s="123" t="s">
         <v>276</v>
       </c>
-      <c r="AC12" s="215">
+      <c r="AC12" s="124">
         <f t="shared" si="4"/>
         <v>9000000000</v>
       </c>
-      <c r="AE12" s="213" t="s">
+      <c r="AD12" s="168"/>
+      <c r="AF12" s="122" t="s">
         <v>277</v>
       </c>
-      <c r="AF12" s="246" t="str">
+      <c r="AG12" s="154" t="str">
         <f t="shared" si="1"/>
         <v>206AP00000</v>
       </c>
-      <c r="AG12" s="214" t="s">
+      <c r="AH12" s="123" t="s">
         <v>208</v>
       </c>
-      <c r="AH12" s="214" t="s">
+      <c r="AI12" s="123" t="s">
         <v>276</v>
       </c>
-      <c r="AI12" s="215">
+      <c r="AJ12" s="124">
         <f>T35</f>
         <v>9000000001</v>
       </c>
-    </row>
-    <row r="13" spans="19:35" x14ac:dyDescent="0.35">
-      <c r="S13" s="192"/>
-      <c r="T13" s="203" t="s">
+      <c r="AK12" s="167" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="13" spans="19:37" x14ac:dyDescent="0.35">
+      <c r="S13" s="166"/>
+      <c r="T13" s="116" t="s">
         <v>230</v>
       </c>
-      <c r="U13" s="189" t="s">
+      <c r="U13" s="112" t="s">
         <v>231</v>
       </c>
-      <c r="V13" s="189" t="s">
+      <c r="V13" s="112" t="s">
         <v>201</v>
       </c>
-      <c r="W13" s="189" t="s">
+      <c r="W13" s="112" t="s">
         <v>208</v>
       </c>
-      <c r="Y13" s="223" t="s">
+      <c r="Y13" s="131" t="s">
         <v>276</v>
       </c>
-      <c r="Z13" s="224" t="str">
+      <c r="Z13" s="132" t="str">
         <f t="shared" si="3"/>
         <v>159AP00000</v>
       </c>
-      <c r="AA13" s="224" t="s">
+      <c r="AA13" s="132" t="s">
         <v>280</v>
       </c>
-      <c r="AB13" s="224" t="s">
+      <c r="AB13" s="132" t="s">
         <v>277</v>
       </c>
-      <c r="AC13" s="225">
+      <c r="AC13" s="133">
         <f t="shared" si="4"/>
         <v>9000000000</v>
       </c>
-      <c r="AE13" s="223" t="s">
+      <c r="AD13" s="168"/>
+      <c r="AF13" s="131" t="s">
         <v>276</v>
       </c>
-      <c r="AF13" s="251" t="str">
+      <c r="AG13" s="158" t="str">
         <f t="shared" si="1"/>
         <v>159AP00000</v>
       </c>
-      <c r="AG13" s="224" t="s">
+      <c r="AH13" s="132" t="s">
         <v>208</v>
       </c>
-      <c r="AH13" s="224" t="s">
+      <c r="AI13" s="132" t="s">
         <v>277</v>
       </c>
-      <c r="AI13" s="225">
+      <c r="AJ13" s="133">
         <f>T39</f>
         <v>9000000005</v>
       </c>
-    </row>
-    <row r="14" spans="19:35" x14ac:dyDescent="0.35">
-      <c r="S14" s="192" t="s">
+      <c r="AK13" s="169"/>
+    </row>
+    <row r="14" spans="19:37" x14ac:dyDescent="0.35">
+      <c r="S14" s="166" t="s">
         <v>234</v>
       </c>
-      <c r="T14" s="203" t="s">
+      <c r="T14" s="116" t="s">
         <v>220</v>
       </c>
-      <c r="U14" s="189" t="s">
+      <c r="U14" s="112" t="s">
         <v>221</v>
       </c>
-      <c r="V14" s="189" t="s">
+      <c r="V14" s="112" t="s">
         <v>201</v>
       </c>
-      <c r="W14" s="189" t="s">
+      <c r="W14" s="112" t="s">
         <v>209</v>
       </c>
-      <c r="Y14" s="213" t="s">
+      <c r="Y14" s="122" t="s">
         <v>276</v>
       </c>
-      <c r="Z14" s="214" t="str">
+      <c r="Z14" s="123" t="str">
         <f>T14</f>
         <v>158NT05000</v>
       </c>
-      <c r="AA14" s="214" t="s">
+      <c r="AA14" s="123" t="s">
         <v>280</v>
       </c>
-      <c r="AB14" s="214" t="s">
+      <c r="AB14" s="123" t="s">
         <v>277</v>
       </c>
-      <c r="AC14" s="215">
+      <c r="AC14" s="124">
         <f t="shared" si="4"/>
         <v>9000000000</v>
       </c>
-      <c r="AE14" s="213" t="s">
+      <c r="AD14" s="168"/>
+      <c r="AF14" s="122" t="s">
         <v>276</v>
       </c>
-      <c r="AF14" s="214" t="str">
+      <c r="AG14" s="123" t="str">
         <f t="shared" si="1"/>
         <v>158NT05000</v>
       </c>
-      <c r="AG14" s="214" t="s">
+      <c r="AH14" s="123" t="s">
         <v>280</v>
       </c>
-      <c r="AH14" s="214" t="s">
+      <c r="AI14" s="123" t="s">
         <v>277</v>
       </c>
-      <c r="AI14" s="215">
-        <f t="shared" ref="AI11:AI25" si="5">$T$34</f>
+      <c r="AJ14" s="124">
+        <f t="shared" ref="AJ14:AJ17" si="5">$T$34</f>
         <v>9000000000</v>
       </c>
-    </row>
-    <row r="15" spans="19:35" x14ac:dyDescent="0.35">
-      <c r="S15" s="192"/>
-      <c r="T15" s="203" t="s">
+      <c r="AK14" s="259" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="15" spans="19:37" x14ac:dyDescent="0.35">
+      <c r="S15" s="166"/>
+      <c r="T15" s="116" t="s">
         <v>222</v>
       </c>
-      <c r="U15" s="189" t="s">
+      <c r="U15" s="112" t="s">
         <v>223</v>
       </c>
-      <c r="V15" s="189" t="s">
+      <c r="V15" s="112" t="s">
         <v>201</v>
       </c>
-      <c r="W15" s="189" t="s">
+      <c r="W15" s="112" t="s">
         <v>209</v>
       </c>
-      <c r="Y15" s="223" t="s">
+      <c r="Y15" s="131" t="s">
         <v>277</v>
       </c>
-      <c r="Z15" s="224" t="str">
+      <c r="Z15" s="132" t="str">
         <f t="shared" ref="Z15:Z25" si="6">T15</f>
         <v>206OT54000</v>
       </c>
-      <c r="AA15" s="224" t="s">
+      <c r="AA15" s="132" t="s">
         <v>280</v>
       </c>
-      <c r="AB15" s="224" t="s">
+      <c r="AB15" s="132" t="s">
         <v>276</v>
       </c>
-      <c r="AC15" s="225">
+      <c r="AC15" s="133">
         <f t="shared" si="4"/>
         <v>9000000000</v>
       </c>
-      <c r="AE15" s="223" t="s">
+      <c r="AD15" s="168"/>
+      <c r="AF15" s="131" t="s">
         <v>277</v>
       </c>
-      <c r="AF15" s="224" t="str">
+      <c r="AG15" s="132" t="str">
         <f t="shared" si="1"/>
         <v>206OT54000</v>
       </c>
-      <c r="AG15" s="224" t="s">
+      <c r="AH15" s="132" t="s">
         <v>280</v>
       </c>
-      <c r="AH15" s="224" t="s">
+      <c r="AI15" s="132" t="s">
         <v>276</v>
       </c>
-      <c r="AI15" s="225">
+      <c r="AJ15" s="133">
         <f t="shared" si="5"/>
         <v>9000000000</v>
       </c>
-    </row>
-    <row r="16" spans="19:35" x14ac:dyDescent="0.35">
-      <c r="S16" s="192" t="s">
+      <c r="AK15" s="168"/>
+    </row>
+    <row r="16" spans="19:37" x14ac:dyDescent="0.35">
+      <c r="S16" s="166" t="s">
         <v>233</v>
       </c>
-      <c r="T16" s="203" t="s">
+      <c r="T16" s="116" t="s">
         <v>245</v>
       </c>
-      <c r="U16" s="189" t="s">
+      <c r="U16" s="112" t="s">
         <v>246</v>
       </c>
-      <c r="V16" s="189" t="s">
+      <c r="V16" s="112" t="s">
         <v>201</v>
       </c>
-      <c r="W16" s="189" t="s">
+      <c r="W16" s="112" t="s">
         <v>210</v>
       </c>
-      <c r="Y16" s="213" t="s">
+      <c r="Y16" s="122" t="s">
         <v>276</v>
       </c>
-      <c r="Z16" s="214" t="str">
+      <c r="Z16" s="123" t="str">
         <f t="shared" si="6"/>
         <v>188CC01M00</v>
       </c>
-      <c r="AA16" s="214" t="s">
+      <c r="AA16" s="123" t="s">
         <v>280</v>
       </c>
-      <c r="AB16" s="214" t="s">
+      <c r="AB16" s="123" t="s">
         <v>277</v>
       </c>
-      <c r="AC16" s="215">
+      <c r="AC16" s="124">
         <f t="shared" si="4"/>
         <v>9000000000</v>
       </c>
-      <c r="AE16" s="213" t="s">
+      <c r="AD16" s="168"/>
+      <c r="AF16" s="122" t="s">
         <v>276</v>
       </c>
-      <c r="AF16" s="214" t="str">
+      <c r="AG16" s="123" t="str">
         <f t="shared" si="1"/>
         <v>188CC01M00</v>
       </c>
-      <c r="AG16" s="214" t="s">
+      <c r="AH16" s="123" t="s">
         <v>280</v>
       </c>
-      <c r="AH16" s="214" t="s">
+      <c r="AI16" s="123" t="s">
         <v>277</v>
       </c>
-      <c r="AI16" s="215">
+      <c r="AJ16" s="124">
         <f t="shared" si="5"/>
         <v>9000000000</v>
       </c>
-    </row>
-    <row r="17" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AK16" s="168"/>
+    </row>
+    <row r="17" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B17" s="76" t="s">
         <v>137</v>
       </c>
@@ -3764,55 +3849,57 @@
       <c r="I17" s="76" t="s">
         <v>141</v>
       </c>
-      <c r="S17" s="192"/>
-      <c r="T17" s="203" t="s">
+      <c r="S17" s="166"/>
+      <c r="T17" s="116" t="s">
         <v>247</v>
       </c>
-      <c r="U17" s="189" t="s">
+      <c r="U17" s="112" t="s">
         <v>248</v>
       </c>
-      <c r="V17" s="189" t="s">
+      <c r="V17" s="112" t="s">
         <v>201</v>
       </c>
-      <c r="W17" s="189" t="s">
+      <c r="W17" s="112" t="s">
         <v>210</v>
       </c>
-      <c r="Y17" s="206" t="s">
+      <c r="Y17" s="119" t="s">
         <v>277</v>
       </c>
-      <c r="Z17" s="209" t="str">
+      <c r="Z17" s="121" t="str">
         <f t="shared" si="6"/>
         <v>300SC01000</v>
       </c>
-      <c r="AA17" s="209" t="s">
+      <c r="AA17" s="121" t="s">
         <v>280</v>
       </c>
-      <c r="AB17" s="209" t="s">
+      <c r="AB17" s="121" t="s">
         <v>276</v>
       </c>
-      <c r="AC17" s="216">
+      <c r="AC17" s="125">
         <f t="shared" si="4"/>
         <v>9000000000</v>
       </c>
-      <c r="AE17" s="206" t="s">
+      <c r="AD17" s="168"/>
+      <c r="AF17" s="119" t="s">
         <v>277</v>
       </c>
-      <c r="AF17" s="209" t="str">
+      <c r="AG17" s="121" t="str">
         <f t="shared" si="1"/>
         <v>300SC01000</v>
       </c>
-      <c r="AG17" s="209" t="s">
+      <c r="AH17" s="121" t="s">
         <v>280</v>
       </c>
-      <c r="AH17" s="209" t="s">
+      <c r="AI17" s="121" t="s">
         <v>276</v>
       </c>
-      <c r="AI17" s="216">
+      <c r="AJ17" s="125">
         <f t="shared" si="5"/>
         <v>9000000000</v>
       </c>
-    </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="AK17" s="168"/>
+    </row>
+    <row r="18" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>1</v>
       </c>
@@ -3840,58 +3927,62 @@
       <c r="P18" t="s">
         <v>146</v>
       </c>
-      <c r="Q18" s="109" t="s">
+      <c r="Q18" s="162" t="s">
         <v>147</v>
       </c>
-      <c r="S18" s="192"/>
-      <c r="T18" s="234" t="s">
+      <c r="S18" s="166"/>
+      <c r="T18" s="142" t="s">
         <v>261</v>
       </c>
-      <c r="U18" s="235" t="s">
+      <c r="U18" s="143" t="s">
         <v>262</v>
       </c>
-      <c r="V18" s="235" t="s">
+      <c r="V18" s="143" t="s">
         <v>201</v>
       </c>
-      <c r="W18" s="235" t="s">
+      <c r="W18" s="143" t="s">
         <v>275</v>
       </c>
-      <c r="Y18" s="236" t="s">
+      <c r="Y18" s="144" t="s">
         <v>276</v>
       </c>
-      <c r="Z18" s="237" t="str">
+      <c r="Z18" s="145" t="str">
         <f t="shared" si="6"/>
         <v>152RM00000</v>
       </c>
-      <c r="AA18" s="237" t="s">
+      <c r="AA18" s="145" t="s">
         <v>280</v>
       </c>
-      <c r="AB18" s="237" t="s">
+      <c r="AB18" s="145" t="s">
         <v>277</v>
       </c>
-      <c r="AC18" s="238">
+      <c r="AC18" s="146">
         <f t="shared" si="4"/>
         <v>9000000000</v>
       </c>
-      <c r="AE18" s="242" t="s">
+      <c r="AD18" s="168"/>
+      <c r="AF18" s="150" t="s">
         <v>276</v>
       </c>
-      <c r="AF18" s="252" t="str">
+      <c r="AG18" s="159" t="str">
         <f t="shared" si="1"/>
         <v>152RM00000</v>
       </c>
-      <c r="AG18" s="243" t="s">
+      <c r="AH18" s="151" t="s">
         <v>282</v>
       </c>
-      <c r="AH18" s="243" t="s">
+      <c r="AI18" s="151" t="s">
         <v>277</v>
       </c>
-      <c r="AI18" s="244">
+      <c r="AJ18" s="152">
         <f>$T$37</f>
         <v>9000000003</v>
       </c>
-    </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="AK18" s="257" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>2</v>
       </c>
@@ -3911,56 +4002,58 @@
         <v>145</v>
       </c>
       <c r="N19" s="81"/>
-      <c r="Q19" s="110"/>
-      <c r="S19" s="192"/>
-      <c r="T19" s="234" t="s">
+      <c r="Q19" s="163"/>
+      <c r="S19" s="166"/>
+      <c r="T19" s="142" t="s">
         <v>263</v>
       </c>
-      <c r="U19" s="235" t="s">
+      <c r="U19" s="143" t="s">
         <v>264</v>
       </c>
-      <c r="V19" s="235" t="s">
+      <c r="V19" s="143" t="s">
         <v>201</v>
       </c>
-      <c r="W19" s="235" t="s">
+      <c r="W19" s="143" t="s">
         <v>275</v>
       </c>
-      <c r="Y19" s="236" t="s">
+      <c r="Y19" s="144" t="s">
         <v>276</v>
       </c>
-      <c r="Z19" s="237" t="str">
+      <c r="Z19" s="145" t="str">
         <f t="shared" si="6"/>
         <v>152TG00000</v>
       </c>
-      <c r="AA19" s="237" t="s">
+      <c r="AA19" s="145" t="s">
         <v>280</v>
       </c>
-      <c r="AB19" s="237" t="s">
+      <c r="AB19" s="145" t="s">
         <v>277</v>
       </c>
-      <c r="AC19" s="238">
+      <c r="AC19" s="146">
         <f t="shared" si="4"/>
         <v>9000000000</v>
       </c>
-      <c r="AE19" s="236" t="s">
+      <c r="AD19" s="168"/>
+      <c r="AF19" s="144" t="s">
         <v>276</v>
       </c>
-      <c r="AF19" s="253" t="str">
+      <c r="AG19" s="160" t="str">
         <f t="shared" si="1"/>
         <v>152TG00000</v>
       </c>
-      <c r="AG19" s="237" t="s">
+      <c r="AH19" s="145" t="s">
         <v>282</v>
       </c>
-      <c r="AH19" s="237" t="s">
+      <c r="AI19" s="145" t="s">
         <v>277</v>
       </c>
-      <c r="AI19" s="238">
-        <f t="shared" ref="AI19:AI25" si="7">$T$37</f>
+      <c r="AJ19" s="146">
+        <f t="shared" ref="AJ19:AJ25" si="7">$T$37</f>
         <v>9000000003</v>
       </c>
-    </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="AK19" s="256"/>
+    </row>
+    <row r="20" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>3</v>
       </c>
@@ -3980,56 +4073,58 @@
         <v>145</v>
       </c>
       <c r="N20" s="81"/>
-      <c r="Q20" s="110"/>
-      <c r="S20" s="192"/>
-      <c r="T20" s="234" t="s">
+      <c r="Q20" s="163"/>
+      <c r="S20" s="166"/>
+      <c r="T20" s="142" t="s">
         <v>265</v>
       </c>
-      <c r="U20" s="235" t="s">
+      <c r="U20" s="143" t="s">
         <v>266</v>
       </c>
-      <c r="V20" s="235" t="s">
+      <c r="V20" s="143" t="s">
         <v>201</v>
       </c>
-      <c r="W20" s="235" t="s">
+      <c r="W20" s="143" t="s">
         <v>275</v>
       </c>
-      <c r="Y20" s="236" t="s">
+      <c r="Y20" s="144" t="s">
         <v>276</v>
       </c>
-      <c r="Z20" s="237" t="str">
+      <c r="Z20" s="145" t="str">
         <f t="shared" si="6"/>
         <v>152SP00000</v>
       </c>
-      <c r="AA20" s="237" t="s">
+      <c r="AA20" s="145" t="s">
         <v>280</v>
       </c>
-      <c r="AB20" s="237" t="s">
+      <c r="AB20" s="145" t="s">
         <v>277</v>
       </c>
-      <c r="AC20" s="238">
+      <c r="AC20" s="146">
         <f t="shared" si="4"/>
         <v>9000000000</v>
       </c>
-      <c r="AE20" s="236" t="s">
+      <c r="AD20" s="168"/>
+      <c r="AF20" s="144" t="s">
         <v>276</v>
       </c>
-      <c r="AF20" s="253" t="str">
+      <c r="AG20" s="160" t="str">
         <f t="shared" si="1"/>
         <v>152SP00000</v>
       </c>
-      <c r="AG20" s="237" t="s">
+      <c r="AH20" s="145" t="s">
         <v>282</v>
       </c>
-      <c r="AH20" s="237" t="s">
+      <c r="AI20" s="145" t="s">
         <v>277</v>
       </c>
-      <c r="AI20" s="238">
+      <c r="AJ20" s="146">
         <f t="shared" si="7"/>
         <v>9000000003</v>
       </c>
-    </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="AK20" s="256"/>
+    </row>
+    <row r="21" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>4</v>
       </c>
@@ -4049,56 +4144,58 @@
         <v>145</v>
       </c>
       <c r="N21" s="81"/>
-      <c r="Q21" s="110"/>
-      <c r="S21" s="192"/>
-      <c r="T21" s="234" t="s">
+      <c r="Q21" s="163"/>
+      <c r="S21" s="166"/>
+      <c r="T21" s="142" t="s">
         <v>267</v>
       </c>
-      <c r="U21" s="235" t="s">
+      <c r="U21" s="143" t="s">
         <v>268</v>
       </c>
-      <c r="V21" s="235" t="s">
+      <c r="V21" s="143" t="s">
         <v>201</v>
       </c>
-      <c r="W21" s="235" t="s">
+      <c r="W21" s="143" t="s">
         <v>275</v>
       </c>
-      <c r="Y21" s="236" t="s">
+      <c r="Y21" s="144" t="s">
         <v>276</v>
       </c>
-      <c r="Z21" s="237" t="str">
+      <c r="Z21" s="145" t="str">
         <f t="shared" si="6"/>
         <v>152PG00000</v>
       </c>
-      <c r="AA21" s="237" t="s">
+      <c r="AA21" s="145" t="s">
         <v>280</v>
       </c>
-      <c r="AB21" s="237" t="s">
+      <c r="AB21" s="145" t="s">
         <v>277</v>
       </c>
-      <c r="AC21" s="238">
+      <c r="AC21" s="146">
         <f t="shared" si="4"/>
         <v>9000000000</v>
       </c>
-      <c r="AE21" s="236" t="s">
+      <c r="AD21" s="168"/>
+      <c r="AF21" s="144" t="s">
         <v>276</v>
       </c>
-      <c r="AF21" s="253" t="str">
+      <c r="AG21" s="160" t="str">
         <f t="shared" si="1"/>
         <v>152PG00000</v>
       </c>
-      <c r="AG21" s="237" t="s">
+      <c r="AH21" s="145" t="s">
         <v>282</v>
       </c>
-      <c r="AH21" s="237" t="s">
+      <c r="AI21" s="145" t="s">
         <v>277</v>
       </c>
-      <c r="AI21" s="238">
+      <c r="AJ21" s="146">
         <f t="shared" si="7"/>
         <v>9000000003</v>
       </c>
-    </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="AK21" s="256"/>
+    </row>
+    <row r="22" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>5</v>
       </c>
@@ -4118,56 +4215,58 @@
         <v>150</v>
       </c>
       <c r="N22" s="81"/>
-      <c r="Q22" s="110"/>
-      <c r="S22" s="192"/>
-      <c r="T22" s="234" t="s">
+      <c r="Q22" s="163"/>
+      <c r="S22" s="166"/>
+      <c r="T22" s="142" t="s">
         <v>265</v>
       </c>
-      <c r="U22" s="235" t="s">
+      <c r="U22" s="143" t="s">
         <v>266</v>
       </c>
-      <c r="V22" s="235" t="s">
+      <c r="V22" s="143" t="s">
         <v>201</v>
       </c>
-      <c r="W22" s="235" t="s">
+      <c r="W22" s="143" t="s">
         <v>275</v>
       </c>
-      <c r="Y22" s="236" t="s">
+      <c r="Y22" s="144" t="s">
         <v>276</v>
       </c>
-      <c r="Z22" s="237" t="str">
+      <c r="Z22" s="145" t="str">
         <f t="shared" si="6"/>
         <v>152SP00000</v>
       </c>
-      <c r="AA22" s="237" t="s">
+      <c r="AA22" s="145" t="s">
         <v>280</v>
       </c>
-      <c r="AB22" s="237" t="s">
+      <c r="AB22" s="145" t="s">
         <v>277</v>
       </c>
-      <c r="AC22" s="238">
+      <c r="AC22" s="146">
         <f t="shared" si="4"/>
         <v>9000000000</v>
       </c>
-      <c r="AE22" s="236" t="s">
+      <c r="AD22" s="168"/>
+      <c r="AF22" s="144" t="s">
         <v>276</v>
       </c>
-      <c r="AF22" s="253" t="str">
+      <c r="AG22" s="160" t="str">
         <f t="shared" si="1"/>
         <v>152SP00000</v>
       </c>
-      <c r="AG22" s="237" t="s">
+      <c r="AH22" s="145" t="s">
         <v>282</v>
       </c>
-      <c r="AH22" s="237" t="s">
+      <c r="AI22" s="145" t="s">
         <v>277</v>
       </c>
-      <c r="AI22" s="238">
+      <c r="AJ22" s="146">
         <f t="shared" si="7"/>
         <v>9000000003</v>
       </c>
-    </row>
-    <row r="23" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AK22" s="256"/>
+    </row>
+    <row r="23" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>6</v>
       </c>
@@ -4188,106 +4287,110 @@
       <c r="L23" s="83"/>
       <c r="M23" s="83"/>
       <c r="N23" s="84"/>
-      <c r="Q23" s="110"/>
-      <c r="S23" s="192"/>
-      <c r="T23" s="234" t="s">
+      <c r="Q23" s="163"/>
+      <c r="S23" s="166"/>
+      <c r="T23" s="142" t="s">
         <v>269</v>
       </c>
-      <c r="U23" s="235" t="s">
+      <c r="U23" s="143" t="s">
         <v>270</v>
       </c>
-      <c r="V23" s="235" t="s">
+      <c r="V23" s="143" t="s">
         <v>201</v>
       </c>
-      <c r="W23" s="235" t="s">
+      <c r="W23" s="143" t="s">
         <v>275</v>
       </c>
-      <c r="Y23" s="236" t="s">
+      <c r="Y23" s="144" t="s">
         <v>276</v>
       </c>
-      <c r="Z23" s="237" t="str">
+      <c r="Z23" s="145" t="str">
         <f t="shared" si="6"/>
         <v>152OS00000</v>
       </c>
-      <c r="AA23" s="237" t="s">
+      <c r="AA23" s="145" t="s">
         <v>280</v>
       </c>
-      <c r="AB23" s="237" t="s">
+      <c r="AB23" s="145" t="s">
         <v>277</v>
       </c>
-      <c r="AC23" s="238">
+      <c r="AC23" s="146">
         <f t="shared" si="4"/>
         <v>9000000000</v>
       </c>
-      <c r="AE23" s="236" t="s">
+      <c r="AD23" s="168"/>
+      <c r="AF23" s="144" t="s">
         <v>276</v>
       </c>
-      <c r="AF23" s="253" t="str">
+      <c r="AG23" s="160" t="str">
         <f t="shared" si="1"/>
         <v>152OS00000</v>
       </c>
-      <c r="AG23" s="237" t="s">
+      <c r="AH23" s="145" t="s">
         <v>282</v>
       </c>
-      <c r="AH23" s="237" t="s">
+      <c r="AI23" s="145" t="s">
         <v>277</v>
       </c>
-      <c r="AI23" s="238">
+      <c r="AJ23" s="146">
         <f t="shared" si="7"/>
         <v>9000000003</v>
       </c>
-    </row>
-    <row r="24" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="Q24" s="110"/>
-      <c r="S24" s="192"/>
-      <c r="T24" s="234" t="s">
+      <c r="AK23" s="256"/>
+    </row>
+    <row r="24" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="Q24" s="163"/>
+      <c r="S24" s="166"/>
+      <c r="T24" s="142" t="s">
         <v>271</v>
       </c>
-      <c r="U24" s="235" t="s">
+      <c r="U24" s="143" t="s">
         <v>272</v>
       </c>
-      <c r="V24" s="235" t="s">
+      <c r="V24" s="143" t="s">
         <v>201</v>
       </c>
-      <c r="W24" s="235" t="s">
+      <c r="W24" s="143" t="s">
         <v>275</v>
       </c>
-      <c r="Y24" s="236" t="s">
+      <c r="Y24" s="144" t="s">
         <v>276</v>
       </c>
-      <c r="Z24" s="237" t="str">
+      <c r="Z24" s="145" t="str">
         <f t="shared" si="6"/>
         <v>152SF00000</v>
       </c>
-      <c r="AA24" s="237" t="s">
+      <c r="AA24" s="145" t="s">
         <v>280</v>
       </c>
-      <c r="AB24" s="237" t="s">
+      <c r="AB24" s="145" t="s">
         <v>277</v>
       </c>
-      <c r="AC24" s="238">
+      <c r="AC24" s="146">
         <f t="shared" si="4"/>
         <v>9000000000</v>
       </c>
-      <c r="AE24" s="236" t="s">
+      <c r="AD24" s="168"/>
+      <c r="AF24" s="144" t="s">
         <v>276</v>
       </c>
-      <c r="AF24" s="253" t="str">
+      <c r="AG24" s="160" t="str">
         <f t="shared" si="1"/>
         <v>152SF00000</v>
       </c>
-      <c r="AG24" s="237" t="s">
+      <c r="AH24" s="145" t="s">
         <v>282</v>
       </c>
-      <c r="AH24" s="237" t="s">
+      <c r="AI24" s="145" t="s">
         <v>277</v>
       </c>
-      <c r="AI24" s="238">
+      <c r="AJ24" s="146">
         <f t="shared" si="7"/>
         <v>9000000003</v>
       </c>
-    </row>
-    <row r="25" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AK24" s="256"/>
+    </row>
+    <row r="25" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="H25" s="85" t="s">
         <v>156</v>
       </c>
@@ -4300,95 +4403,101 @@
       <c r="P25" t="s">
         <v>157</v>
       </c>
-      <c r="Q25" s="111"/>
-      <c r="S25" s="192"/>
-      <c r="T25" s="234" t="s">
+      <c r="Q25" s="164"/>
+      <c r="S25" s="166"/>
+      <c r="T25" s="142" t="s">
         <v>273</v>
       </c>
-      <c r="U25" s="235" t="s">
+      <c r="U25" s="143" t="s">
         <v>274</v>
       </c>
-      <c r="V25" s="235" t="s">
+      <c r="V25" s="143" t="s">
         <v>201</v>
       </c>
-      <c r="W25" s="235" t="s">
+      <c r="W25" s="143" t="s">
         <v>275</v>
       </c>
-      <c r="Y25" s="239" t="s">
+      <c r="Y25" s="147" t="s">
         <v>276</v>
       </c>
-      <c r="Z25" s="240" t="str">
+      <c r="Z25" s="148" t="str">
         <f t="shared" si="6"/>
         <v>152FG00000</v>
       </c>
-      <c r="AA25" s="240" t="s">
+      <c r="AA25" s="148" t="s">
         <v>280</v>
       </c>
-      <c r="AB25" s="240" t="s">
+      <c r="AB25" s="148" t="s">
         <v>277</v>
       </c>
-      <c r="AC25" s="241">
+      <c r="AC25" s="149">
         <f t="shared" si="4"/>
         <v>9000000000</v>
       </c>
-      <c r="AE25" s="239" t="s">
+      <c r="AD25" s="168"/>
+      <c r="AF25" s="147" t="s">
         <v>276</v>
       </c>
-      <c r="AF25" s="254" t="str">
+      <c r="AG25" s="161" t="str">
         <f t="shared" si="1"/>
         <v>152FG00000</v>
       </c>
-      <c r="AG25" s="240" t="s">
+      <c r="AH25" s="148" t="s">
         <v>282</v>
       </c>
-      <c r="AH25" s="240" t="s">
+      <c r="AI25" s="148" t="s">
         <v>277</v>
       </c>
-      <c r="AI25" s="241">
+      <c r="AJ25" s="149">
         <f t="shared" si="7"/>
         <v>9000000003</v>
       </c>
-    </row>
-    <row r="26" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="S26" s="193" t="s">
+      <c r="AK25" s="258"/>
+    </row>
+    <row r="26" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="S26" s="170" t="s">
         <v>155</v>
       </c>
-      <c r="T26" s="204" t="s">
+      <c r="T26" s="117" t="s">
         <v>249</v>
       </c>
-      <c r="U26" s="190" t="s">
+      <c r="U26" s="113" t="s">
         <v>250</v>
       </c>
-      <c r="V26" s="190" t="s">
+      <c r="V26" s="113" t="s">
         <v>202</v>
       </c>
-      <c r="W26" s="190" t="s">
+      <c r="W26" s="113" t="s">
         <v>211</v>
       </c>
-      <c r="Y26" s="208"/>
-      <c r="Z26" s="208"/>
-      <c r="AA26" s="208"/>
-      <c r="AB26" s="208"/>
-      <c r="AC26" s="208"/>
-      <c r="AE26" s="231" t="s">
+      <c r="Y26" s="249"/>
+      <c r="Z26" s="250"/>
+      <c r="AA26" s="250"/>
+      <c r="AB26" s="250"/>
+      <c r="AC26" s="251"/>
+      <c r="AD26" s="168"/>
+      <c r="AF26" s="139" t="s">
         <v>276</v>
       </c>
-      <c r="AF26" s="232" t="str">
+      <c r="AG26" s="140" t="str">
         <f t="shared" si="1"/>
         <v>705AW01000</v>
       </c>
-      <c r="AG26" s="232" t="s">
+      <c r="AH26" s="140" t="s">
         <v>280</v>
       </c>
-      <c r="AH26" s="232" t="s">
+      <c r="AI26" s="140" t="s">
         <v>277</v>
       </c>
-      <c r="AI26" s="233">
+      <c r="AJ26" s="141">
         <f>$T$34</f>
         <v>9000000000</v>
       </c>
-    </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="AK26" s="259" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="27" spans="1:37" x14ac:dyDescent="0.35">
       <c r="H27" s="77" t="s">
         <v>158</v>
       </c>
@@ -4403,43 +4512,45 @@
       <c r="P27" t="s">
         <v>159</v>
       </c>
-      <c r="S27" s="194"/>
-      <c r="T27" s="204" t="s">
+      <c r="S27" s="172"/>
+      <c r="T27" s="117" t="s">
         <v>259</v>
       </c>
-      <c r="U27" s="190" t="s">
+      <c r="U27" s="113" t="s">
         <v>260</v>
       </c>
-      <c r="V27" s="190" t="s">
+      <c r="V27" s="113" t="s">
         <v>202</v>
       </c>
-      <c r="W27" s="190" t="s">
+      <c r="W27" s="113" t="s">
         <v>211</v>
       </c>
-      <c r="Y27" s="208"/>
-      <c r="Z27" s="208"/>
-      <c r="AA27" s="208"/>
-      <c r="AB27" s="208"/>
-      <c r="AC27" s="208"/>
-      <c r="AE27" s="226" t="s">
+      <c r="Y27" s="126"/>
+      <c r="Z27" s="252"/>
+      <c r="AA27" s="252"/>
+      <c r="AB27" s="252"/>
+      <c r="AC27" s="253"/>
+      <c r="AD27" s="168"/>
+      <c r="AF27" s="134" t="s">
         <v>276</v>
       </c>
-      <c r="AF27" s="212" t="str">
+      <c r="AG27" s="107" t="str">
         <f t="shared" si="1"/>
         <v>735EX06000</v>
       </c>
-      <c r="AG27" s="212" t="s">
+      <c r="AH27" s="107" t="s">
         <v>280</v>
       </c>
-      <c r="AH27" s="212" t="s">
+      <c r="AI27" s="107" t="s">
         <v>277</v>
       </c>
-      <c r="AI27" s="227">
-        <f t="shared" ref="AI27:AI31" si="8">$T$34</f>
+      <c r="AJ27" s="135">
+        <f t="shared" ref="AJ27:AJ31" si="8">$T$34</f>
         <v>9000000000</v>
       </c>
-    </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="AK27" s="168"/>
+    </row>
+    <row r="28" spans="1:37" x14ac:dyDescent="0.35">
       <c r="H28" s="80" t="s">
         <v>160</v>
       </c>
@@ -4447,43 +4558,45 @@
         <v>150</v>
       </c>
       <c r="N28" s="90"/>
-      <c r="S28" s="194"/>
-      <c r="T28" s="204" t="s">
+      <c r="S28" s="172"/>
+      <c r="T28" s="117" t="s">
         <v>251</v>
       </c>
-      <c r="U28" s="190" t="s">
+      <c r="U28" s="113" t="s">
         <v>252</v>
       </c>
-      <c r="V28" s="190" t="s">
+      <c r="V28" s="113" t="s">
         <v>202</v>
       </c>
-      <c r="W28" s="190" t="s">
+      <c r="W28" s="113" t="s">
         <v>211</v>
       </c>
-      <c r="Y28" s="208"/>
-      <c r="Z28" s="208"/>
-      <c r="AA28" s="208"/>
-      <c r="AB28" s="208"/>
-      <c r="AC28" s="208"/>
-      <c r="AE28" s="226" t="s">
+      <c r="Y28" s="126"/>
+      <c r="Z28" s="252"/>
+      <c r="AA28" s="252"/>
+      <c r="AB28" s="252"/>
+      <c r="AC28" s="253"/>
+      <c r="AD28" s="168"/>
+      <c r="AF28" s="134" t="s">
         <v>276</v>
       </c>
-      <c r="AF28" s="212" t="str">
+      <c r="AG28" s="107" t="str">
         <f t="shared" si="1"/>
         <v>610SC02000</v>
       </c>
-      <c r="AG28" s="212" t="s">
+      <c r="AH28" s="107" t="s">
         <v>280</v>
       </c>
-      <c r="AH28" s="212" t="s">
+      <c r="AI28" s="107" t="s">
         <v>277</v>
       </c>
-      <c r="AI28" s="227">
+      <c r="AJ28" s="135">
         <f t="shared" si="8"/>
         <v>9000000000</v>
       </c>
-    </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="AK28" s="168"/>
+    </row>
+    <row r="29" spans="1:37" x14ac:dyDescent="0.35">
       <c r="H29" s="80" t="s">
         <v>160</v>
       </c>
@@ -4491,43 +4604,45 @@
         <v>152</v>
       </c>
       <c r="N29" s="90"/>
-      <c r="S29" s="194"/>
-      <c r="T29" s="204" t="s">
+      <c r="S29" s="172"/>
+      <c r="T29" s="117" t="s">
         <v>253</v>
       </c>
-      <c r="U29" s="190" t="s">
+      <c r="U29" s="113" t="s">
         <v>254</v>
       </c>
-      <c r="V29" s="190" t="s">
+      <c r="V29" s="113" t="s">
         <v>202</v>
       </c>
-      <c r="W29" s="190" t="s">
+      <c r="W29" s="113" t="s">
         <v>211</v>
       </c>
-      <c r="Y29" s="208"/>
-      <c r="Z29" s="208"/>
-      <c r="AA29" s="208"/>
-      <c r="AB29" s="208"/>
-      <c r="AC29" s="208"/>
-      <c r="AE29" s="226" t="s">
+      <c r="Y29" s="126"/>
+      <c r="Z29" s="252"/>
+      <c r="AA29" s="252"/>
+      <c r="AB29" s="252"/>
+      <c r="AC29" s="253"/>
+      <c r="AD29" s="168"/>
+      <c r="AF29" s="134" t="s">
         <v>276</v>
       </c>
-      <c r="AF29" s="212" t="str">
+      <c r="AG29" s="107" t="str">
         <f t="shared" si="1"/>
         <v>610OH01000</v>
       </c>
-      <c r="AG29" s="212" t="s">
+      <c r="AH29" s="107" t="s">
         <v>280</v>
       </c>
-      <c r="AH29" s="212" t="s">
+      <c r="AI29" s="107" t="s">
         <v>277</v>
       </c>
-      <c r="AI29" s="227">
+      <c r="AJ29" s="135">
         <f t="shared" si="8"/>
         <v>9000000000</v>
       </c>
-    </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="AK29" s="168"/>
+    </row>
+    <row r="30" spans="1:37" x14ac:dyDescent="0.35">
       <c r="H30" s="80" t="s">
         <v>160</v>
       </c>
@@ -4535,43 +4650,45 @@
         <v>153</v>
       </c>
       <c r="N30" s="90"/>
-      <c r="S30" s="194"/>
-      <c r="T30" s="204" t="s">
+      <c r="S30" s="172"/>
+      <c r="T30" s="117" t="s">
         <v>257</v>
       </c>
-      <c r="U30" s="190" t="s">
+      <c r="U30" s="113" t="s">
         <v>258</v>
       </c>
-      <c r="V30" s="190" t="s">
+      <c r="V30" s="113" t="s">
         <v>202</v>
       </c>
-      <c r="W30" s="190" t="s">
+      <c r="W30" s="113" t="s">
         <v>203</v>
       </c>
-      <c r="Y30" s="208"/>
-      <c r="Z30" s="208"/>
-      <c r="AA30" s="208"/>
-      <c r="AB30" s="208"/>
-      <c r="AC30" s="208"/>
-      <c r="AE30" s="226" t="s">
+      <c r="Y30" s="126"/>
+      <c r="Z30" s="252"/>
+      <c r="AA30" s="252"/>
+      <c r="AB30" s="252"/>
+      <c r="AC30" s="253"/>
+      <c r="AD30" s="168"/>
+      <c r="AF30" s="134" t="s">
         <v>277</v>
       </c>
-      <c r="AF30" s="212" t="str">
+      <c r="AG30" s="107" t="str">
         <f t="shared" si="1"/>
         <v>500SD01000</v>
       </c>
-      <c r="AG30" s="212" t="s">
+      <c r="AH30" s="107" t="s">
         <v>280</v>
       </c>
-      <c r="AH30" s="212" t="s">
+      <c r="AI30" s="107" t="s">
         <v>276</v>
       </c>
-      <c r="AI30" s="227">
+      <c r="AJ30" s="135">
         <f t="shared" si="8"/>
         <v>9000000000</v>
       </c>
-    </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="AK30" s="168"/>
+    </row>
+    <row r="31" spans="1:37" x14ac:dyDescent="0.35">
       <c r="H31" s="80" t="s">
         <v>161</v>
       </c>
@@ -4582,43 +4699,45 @@
         <v>150</v>
       </c>
       <c r="N31" s="90"/>
-      <c r="S31" s="195"/>
-      <c r="T31" s="204" t="s">
+      <c r="S31" s="171"/>
+      <c r="T31" s="117" t="s">
         <v>255</v>
       </c>
-      <c r="U31" s="190" t="s">
+      <c r="U31" s="113" t="s">
         <v>256</v>
       </c>
-      <c r="V31" s="190" t="s">
+      <c r="V31" s="113" t="s">
         <v>202</v>
       </c>
-      <c r="W31" s="190" t="s">
+      <c r="W31" s="113" t="s">
         <v>203</v>
       </c>
-      <c r="Y31" s="208"/>
-      <c r="Z31" s="208"/>
-      <c r="AA31" s="208"/>
-      <c r="AB31" s="208"/>
-      <c r="AC31" s="208"/>
-      <c r="AE31" s="228" t="s">
+      <c r="Y31" s="128"/>
+      <c r="Z31" s="129"/>
+      <c r="AA31" s="129"/>
+      <c r="AB31" s="129"/>
+      <c r="AC31" s="254"/>
+      <c r="AD31" s="169"/>
+      <c r="AF31" s="136" t="s">
         <v>277</v>
       </c>
-      <c r="AF31" s="229" t="str">
+      <c r="AG31" s="137" t="str">
         <f t="shared" si="1"/>
         <v>810DQ00000</v>
       </c>
-      <c r="AG31" s="229" t="s">
+      <c r="AH31" s="137" t="s">
         <v>280</v>
       </c>
-      <c r="AH31" s="229" t="s">
+      <c r="AI31" s="137" t="s">
         <v>276</v>
       </c>
-      <c r="AI31" s="230">
+      <c r="AJ31" s="138">
         <f t="shared" si="8"/>
         <v>9000000000</v>
       </c>
-    </row>
-    <row r="32" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AK31" s="169"/>
+    </row>
+    <row r="32" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="H32" s="82" t="s">
         <v>161</v>
       </c>
@@ -4633,7 +4752,12 @@
       </c>
       <c r="N32" s="84"/>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AF33" s="260" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="34" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A34" s="92">
         <v>7</v>
       </c>
@@ -4646,53 +4770,53 @@
       </c>
       <c r="E34" s="93"/>
       <c r="F34" s="93"/>
-      <c r="S34" s="196" t="s">
+      <c r="S34" s="173" t="s">
         <v>217</v>
       </c>
-      <c r="T34" s="205">
+      <c r="T34" s="118">
         <v>9000000000</v>
       </c>
-      <c r="U34" s="191" t="s">
+      <c r="U34" s="114" t="s">
         <v>170</v>
       </c>
-      <c r="V34" s="191" t="s">
+      <c r="V34" s="114" t="s">
         <v>201</v>
       </c>
-      <c r="W34" s="191" t="s">
+      <c r="W34" s="114" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="S35" s="197"/>
-      <c r="T35" s="205">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="S35" s="174"/>
+      <c r="T35" s="118">
         <v>9000000001</v>
       </c>
-      <c r="U35" s="191" t="s">
+      <c r="U35" s="114" t="s">
         <v>171</v>
       </c>
-      <c r="V35" s="191" t="s">
+      <c r="V35" s="114" t="s">
         <v>201</v>
       </c>
-      <c r="W35" s="191" t="s">
+      <c r="W35" s="114" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="S36" s="197"/>
-      <c r="T36" s="205">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="S36" s="174"/>
+      <c r="T36" s="118">
         <v>9000000002</v>
       </c>
-      <c r="U36" s="191" t="s">
+      <c r="U36" s="114" t="s">
         <v>174</v>
       </c>
-      <c r="V36" s="191" t="s">
+      <c r="V36" s="114" t="s">
         <v>201</v>
       </c>
-      <c r="W36" s="191" t="s">
+      <c r="W36" s="114" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B37" s="95" t="s">
         <v>166</v>
       </c>
@@ -4708,21 +4832,21 @@
       <c r="K37" s="96"/>
       <c r="L37" s="96"/>
       <c r="M37" s="97"/>
-      <c r="S37" s="197"/>
-      <c r="T37" s="205">
+      <c r="S37" s="174"/>
+      <c r="T37" s="118">
         <v>9000000003</v>
       </c>
-      <c r="U37" s="191" t="s">
+      <c r="U37" s="114" t="s">
         <v>215</v>
       </c>
-      <c r="V37" s="191" t="s">
+      <c r="V37" s="114" t="s">
         <v>201</v>
       </c>
-      <c r="W37" s="191" t="s">
+      <c r="W37" s="114" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B38" s="98">
         <v>1</v>
       </c>
@@ -4737,21 +4861,21 @@
         <v>179</v>
       </c>
       <c r="M38" s="99"/>
-      <c r="S38" s="197"/>
-      <c r="T38" s="205">
+      <c r="S38" s="174"/>
+      <c r="T38" s="118">
         <v>9000000004</v>
       </c>
-      <c r="U38" s="191" t="s">
+      <c r="U38" s="114" t="s">
         <v>216</v>
       </c>
-      <c r="V38" s="191" t="s">
+      <c r="V38" s="114" t="s">
         <v>201</v>
       </c>
-      <c r="W38" s="191" t="s">
+      <c r="W38" s="114" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B39" s="98"/>
       <c r="D39" s="107" t="s">
         <v>195</v>
@@ -4769,21 +4893,21 @@
       <c r="M39" s="106" t="s">
         <v>170</v>
       </c>
-      <c r="S39" s="197"/>
-      <c r="T39" s="205">
+      <c r="S39" s="174"/>
+      <c r="T39" s="118">
         <v>9000000005</v>
       </c>
-      <c r="U39" s="191" t="s">
+      <c r="U39" s="114" t="s">
         <v>218</v>
       </c>
-      <c r="V39" s="191" t="s">
+      <c r="V39" s="114" t="s">
         <v>201</v>
       </c>
-      <c r="W39" s="191" t="s">
+      <c r="W39" s="114" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B40" s="98">
         <v>2</v>
       </c>
@@ -4798,21 +4922,21 @@
         <v>181</v>
       </c>
       <c r="M40" s="99"/>
-      <c r="S40" s="198"/>
-      <c r="T40" s="205">
+      <c r="S40" s="175"/>
+      <c r="T40" s="118">
         <v>9000000006</v>
       </c>
-      <c r="U40" s="191" t="s">
+      <c r="U40" s="114" t="s">
         <v>219</v>
       </c>
-      <c r="V40" s="191" t="s">
+      <c r="V40" s="114" t="s">
         <v>201</v>
       </c>
-      <c r="W40" s="191" t="s">
+      <c r="W40" s="114" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B41" s="98"/>
       <c r="D41" s="107" t="s">
         <v>171</v>
@@ -4831,7 +4955,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B42" s="98">
         <v>3</v>
       </c>
@@ -4847,7 +4971,7 @@
       </c>
       <c r="M42" s="99"/>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B43" s="98"/>
       <c r="D43" s="107" t="s">
         <v>197</v>
@@ -4866,7 +4990,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B44" s="98">
         <v>4</v>
       </c>
@@ -4882,7 +5006,7 @@
       </c>
       <c r="M44" s="99"/>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B45" s="98"/>
       <c r="D45" s="107" t="s">
         <v>174</v>
@@ -4897,7 +5021,7 @@
       </c>
       <c r="M45" s="99"/>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B46" s="98">
         <v>5</v>
       </c>
@@ -4913,7 +5037,7 @@
       </c>
       <c r="M46" s="99"/>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B47" s="98"/>
       <c r="D47" s="107" t="s">
         <v>198</v>
@@ -4932,7 +5056,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B48" s="98">
         <v>6</v>
       </c>
@@ -5031,33 +5155,40 @@
       <c r="M53" s="102"/>
     </row>
     <row r="55" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B55" s="112" t="s">
+      <c r="B55" s="165" t="s">
         <v>186</v>
       </c>
-      <c r="C55" s="112"/>
-      <c r="D55" s="112"/>
-      <c r="E55" s="112"/>
-      <c r="F55" s="112"/>
-      <c r="G55" s="112"/>
-      <c r="H55" s="112"/>
-      <c r="I55" s="112"/>
-      <c r="J55" s="112"/>
-      <c r="K55" s="112"/>
-      <c r="L55" s="112"/>
-      <c r="M55" s="112"/>
+      <c r="C55" s="165"/>
+      <c r="D55" s="165"/>
+      <c r="E55" s="165"/>
+      <c r="F55" s="165"/>
+      <c r="G55" s="165"/>
+      <c r="H55" s="165"/>
+      <c r="I55" s="165"/>
+      <c r="J55" s="165"/>
+      <c r="K55" s="165"/>
+      <c r="L55" s="165"/>
+      <c r="M55" s="165"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="17">
+    <mergeCell ref="AD4:AD31"/>
+    <mergeCell ref="AK4:AK9"/>
+    <mergeCell ref="AK10:AK11"/>
+    <mergeCell ref="AK12:AK13"/>
+    <mergeCell ref="AK14:AK17"/>
+    <mergeCell ref="AK18:AK25"/>
+    <mergeCell ref="AK26:AK31"/>
+    <mergeCell ref="S4:S7"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="S16:S25"/>
+    <mergeCell ref="S26:S31"/>
+    <mergeCell ref="S34:S40"/>
     <mergeCell ref="Q18:Q25"/>
     <mergeCell ref="B55:M55"/>
     <mergeCell ref="S10:S11"/>
     <mergeCell ref="S12:S13"/>
     <mergeCell ref="S14:S15"/>
-    <mergeCell ref="S4:S7"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="S16:S25"/>
-    <mergeCell ref="S26:S31"/>
-    <mergeCell ref="S34:S40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -5084,14 +5215,14 @@
   <sheetData>
     <row r="1" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:20" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="122" t="s">
+      <c r="B2" s="203" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="123"/>
-      <c r="D2" s="116" t="s">
+      <c r="C2" s="204"/>
+      <c r="D2" s="197" t="s">
         <v>121</v>
       </c>
-      <c r="E2" s="118" t="s">
+      <c r="E2" s="199" t="s">
         <v>117</v>
       </c>
       <c r="F2" s="1"/>
@@ -5104,10 +5235,10 @@
       <c r="M2" s="8"/>
     </row>
     <row r="3" spans="2:20" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="124"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="117"/>
-      <c r="E3" s="119"/>
+      <c r="B3" s="205"/>
+      <c r="C3" s="206"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="200"/>
       <c r="F3" s="1"/>
       <c r="G3" s="10" t="s">
         <v>17</v>
@@ -5118,7 +5249,7 @@
       <c r="K3" s="2"/>
     </row>
     <row r="4" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B4" s="113" t="s">
+      <c r="B4" s="194" t="s">
         <v>86</v>
       </c>
       <c r="C4" s="54" t="s">
@@ -5127,7 +5258,7 @@
       <c r="D4" s="75" t="s">
         <v>122</v>
       </c>
-      <c r="E4" s="127" t="s">
+      <c r="E4" s="208" t="s">
         <v>81</v>
       </c>
       <c r="F4" s="1"/>
@@ -5151,12 +5282,12 @@
       <c r="T4" s="17"/>
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B5" s="120"/>
+      <c r="B5" s="201"/>
       <c r="C5" s="40" t="s">
         <v>90</v>
       </c>
       <c r="D5" s="9"/>
-      <c r="E5" s="128"/>
+      <c r="E5" s="209"/>
       <c r="F5"/>
       <c r="G5" s="48"/>
       <c r="H5" s="10" t="s">
@@ -5166,12 +5297,12 @@
       <c r="T5" s="19"/>
     </row>
     <row r="6" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="126"/>
+      <c r="B6" s="207"/>
       <c r="C6" s="55" t="s">
         <v>91</v>
       </c>
       <c r="D6" s="65"/>
-      <c r="E6" s="129"/>
+      <c r="E6" s="210"/>
       <c r="F6"/>
       <c r="G6" s="48"/>
       <c r="H6" s="10" t="s">
@@ -5181,16 +5312,16 @@
       <c r="T6" s="19"/>
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B7" s="113" t="s">
+      <c r="B7" s="194" t="s">
         <v>87</v>
       </c>
       <c r="C7" s="54" t="s">
         <v>92</v>
       </c>
-      <c r="D7" s="139" t="s">
+      <c r="D7" s="185" t="s">
         <v>127</v>
       </c>
-      <c r="E7" s="136" t="s">
+      <c r="E7" s="182" t="s">
         <v>81</v>
       </c>
       <c r="F7"/>
@@ -5212,12 +5343,12 @@
       <c r="T7" s="31"/>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B8" s="120"/>
+      <c r="B8" s="201"/>
       <c r="C8" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="D8" s="140"/>
-      <c r="E8" s="137"/>
+      <c r="D8" s="186"/>
+      <c r="E8" s="183"/>
       <c r="F8"/>
       <c r="G8" s="46" t="s">
         <v>18</v>
@@ -5229,12 +5360,12 @@
       <c r="T8" s="19"/>
     </row>
     <row r="9" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="121"/>
+      <c r="B9" s="202"/>
       <c r="C9" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="D9" s="141"/>
-      <c r="E9" s="138"/>
+      <c r="D9" s="187"/>
+      <c r="E9" s="184"/>
       <c r="F9"/>
       <c r="G9" s="46"/>
       <c r="H9" s="20" t="s">
@@ -5244,7 +5375,7 @@
       <c r="T9" s="19"/>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B10" s="113" t="s">
+      <c r="B10" s="194" t="s">
         <v>88</v>
       </c>
       <c r="C10" s="73" t="s">
@@ -5253,7 +5384,7 @@
       <c r="D10" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="E10" s="142" t="s">
+      <c r="E10" s="188" t="s">
         <v>81</v>
       </c>
       <c r="F10"/>
@@ -5265,12 +5396,12 @@
       <c r="T10" s="19"/>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B11" s="114"/>
+      <c r="B11" s="195"/>
       <c r="C11" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="D11" s="133"/>
-      <c r="E11" s="143"/>
+      <c r="D11" s="179"/>
+      <c r="E11" s="189"/>
       <c r="F11"/>
       <c r="G11" s="48"/>
       <c r="H11" s="24" t="s">
@@ -5290,12 +5421,12 @@
       <c r="T11" s="31"/>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B12" s="114"/>
+      <c r="B12" s="195"/>
       <c r="C12" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="134"/>
-      <c r="E12" s="143"/>
+      <c r="D12" s="180"/>
+      <c r="E12" s="189"/>
       <c r="F12"/>
       <c r="G12" s="46" t="s">
         <v>28</v>
@@ -5307,12 +5438,12 @@
       <c r="T12" s="19"/>
     </row>
     <row r="13" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="115"/>
+      <c r="B13" s="196"/>
       <c r="C13" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="135"/>
-      <c r="E13" s="144"/>
+      <c r="D13" s="181"/>
+      <c r="E13" s="190"/>
       <c r="F13" s="1"/>
       <c r="G13" s="21"/>
       <c r="H13" s="25" t="s">
@@ -5348,7 +5479,7 @@
       <c r="C16" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="D16" s="145">
+      <c r="D16" s="191">
         <v>2025</v>
       </c>
       <c r="E16" s="43" t="s">
@@ -5360,8 +5491,8 @@
       <c r="C17" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="D17" s="146"/>
-      <c r="E17" s="132" t="s">
+      <c r="D17" s="192"/>
+      <c r="E17" s="178" t="s">
         <v>118</v>
       </c>
       <c r="F17" s="1"/>
@@ -5370,8 +5501,8 @@
       <c r="C18" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="D18" s="147"/>
-      <c r="E18" s="132"/>
+      <c r="D18" s="193"/>
+      <c r="E18" s="178"/>
       <c r="F18" s="1"/>
     </row>
     <row r="19" spans="3:6" x14ac:dyDescent="0.35">
@@ -5381,7 +5512,7 @@
       <c r="C20" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="D20" s="130">
+      <c r="D20" s="176">
         <v>2026</v>
       </c>
       <c r="E20" s="43" t="s">
@@ -5393,7 +5524,7 @@
       <c r="C21" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="D21" s="131"/>
+      <c r="D21" s="177"/>
       <c r="E21" s="67" t="s">
         <v>119</v>
       </c>
@@ -5448,6 +5579,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B2:C3"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="E4:E6"/>
     <mergeCell ref="D20:D21"/>
     <mergeCell ref="E17:E18"/>
     <mergeCell ref="D11:D13"/>
@@ -5455,13 +5593,6 @@
     <mergeCell ref="D7:D9"/>
     <mergeCell ref="E10:E13"/>
     <mergeCell ref="D16:D18"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B2:C3"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="E4:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -5490,18 +5621,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:24" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="148" t="s">
+      <c r="B2" s="211" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="148"/>
-      <c r="D2" s="171" t="s">
+      <c r="C2" s="211"/>
+      <c r="D2" s="234" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="172"/>
-      <c r="F2" s="173" t="s">
+      <c r="E2" s="235"/>
+      <c r="F2" s="236" t="s">
         <v>80</v>
       </c>
-      <c r="G2" s="174"/>
+      <c r="G2" s="237"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
         <v>79</v>
@@ -5514,8 +5645,8 @@
       </c>
     </row>
     <row r="3" spans="2:24" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="149"/>
-      <c r="C3" s="149"/>
+      <c r="B3" s="212"/>
+      <c r="C3" s="212"/>
       <c r="D3" s="56" t="s">
         <v>22</v>
       </c>
@@ -5538,7 +5669,7 @@
       <c r="N3" s="2"/>
     </row>
     <row r="4" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="150" t="s">
+      <c r="B4" s="213" t="s">
         <v>86</v>
       </c>
       <c r="C4" s="70" t="s">
@@ -5561,14 +5692,14 @@
       <c r="M4" s="2"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="B5" s="151"/>
+      <c r="B5" s="214"/>
       <c r="C5" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="170" t="s">
+      <c r="D5" s="233" t="s">
         <v>108</v>
       </c>
-      <c r="E5" s="170"/>
+      <c r="E5" s="233"/>
       <c r="F5" s="43" t="s">
         <v>85</v>
       </c>
@@ -5599,14 +5730,14 @@
       <c r="X5" s="17"/>
     </row>
     <row r="6" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="152"/>
+      <c r="B6" s="215"/>
       <c r="C6" s="69" t="s">
         <v>91</v>
       </c>
-      <c r="D6" s="169" t="s">
+      <c r="D6" s="232" t="s">
         <v>108</v>
       </c>
-      <c r="E6" s="169"/>
+      <c r="E6" s="232"/>
       <c r="F6" s="60" t="s">
         <v>83</v>
       </c>
@@ -5622,18 +5753,18 @@
       <c r="X6" s="19"/>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="B7" s="153" t="s">
+      <c r="B7" s="216" t="s">
         <v>87</v>
       </c>
       <c r="C7" s="64" t="s">
         <v>92</v>
       </c>
-      <c r="D7" s="175" t="s">
+      <c r="D7" s="238" t="s">
         <v>81</v>
       </c>
-      <c r="E7" s="176"/>
-      <c r="F7" s="176"/>
-      <c r="G7" s="177"/>
+      <c r="E7" s="239"/>
+      <c r="F7" s="239"/>
+      <c r="G7" s="240"/>
       <c r="I7" s="1"/>
       <c r="J7" s="46"/>
       <c r="K7" s="24" t="s">
@@ -5654,16 +5785,16 @@
       <c r="X7" s="31"/>
     </row>
     <row r="8" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="B8" s="120"/>
+      <c r="B8" s="201"/>
       <c r="C8" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="D8" s="178" t="s">
+      <c r="D8" s="241" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="179"/>
-      <c r="F8" s="179"/>
-      <c r="G8" s="180"/>
+      <c r="E8" s="242"/>
+      <c r="F8" s="242"/>
+      <c r="G8" s="243"/>
       <c r="I8" s="1"/>
       <c r="J8" s="46" t="s">
         <v>18</v>
@@ -5675,16 +5806,16 @@
       <c r="X8" s="19"/>
     </row>
     <row r="9" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="126"/>
+      <c r="B9" s="207"/>
       <c r="C9" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="D9" s="181" t="s">
+      <c r="D9" s="244" t="s">
         <v>81</v>
       </c>
-      <c r="E9" s="182"/>
-      <c r="F9" s="182"/>
-      <c r="G9" s="183"/>
+      <c r="E9" s="245"/>
+      <c r="F9" s="245"/>
+      <c r="G9" s="246"/>
       <c r="I9" s="1"/>
       <c r="J9" s="46"/>
       <c r="K9" s="20" t="s">
@@ -5694,18 +5825,18 @@
       <c r="X9" s="19"/>
     </row>
     <row r="10" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="B10" s="113" t="s">
+      <c r="B10" s="194" t="s">
         <v>88</v>
       </c>
       <c r="C10" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="154" t="s">
+      <c r="D10" s="217" t="s">
         <v>81</v>
       </c>
-      <c r="E10" s="155"/>
-      <c r="F10" s="155"/>
-      <c r="G10" s="156"/>
+      <c r="E10" s="218"/>
+      <c r="F10" s="218"/>
+      <c r="G10" s="219"/>
       <c r="I10" s="1"/>
       <c r="J10" s="46"/>
       <c r="K10" s="35" t="s">
@@ -5726,14 +5857,14 @@
       <c r="X10" s="38"/>
     </row>
     <row r="11" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="B11" s="120"/>
+      <c r="B11" s="201"/>
       <c r="C11" s="49" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="157"/>
-      <c r="E11" s="158"/>
-      <c r="F11" s="158"/>
-      <c r="G11" s="159"/>
+      <c r="D11" s="220"/>
+      <c r="E11" s="221"/>
+      <c r="F11" s="221"/>
+      <c r="G11" s="222"/>
       <c r="I11" s="1"/>
       <c r="J11" s="46" t="s">
         <v>28</v>
@@ -5745,18 +5876,18 @@
       <c r="X11" s="19"/>
     </row>
     <row r="12" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="120"/>
+      <c r="B12" s="201"/>
       <c r="C12" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="D12" s="166" t="s">
+      <c r="D12" s="229" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="133"/>
-      <c r="F12" s="160" t="s">
+      <c r="E12" s="179"/>
+      <c r="F12" s="223" t="s">
         <v>81</v>
       </c>
-      <c r="G12" s="161"/>
+      <c r="G12" s="224"/>
       <c r="I12" s="1"/>
       <c r="J12" s="47"/>
       <c r="K12" s="25" t="s">
@@ -5777,14 +5908,14 @@
       <c r="X12" s="29"/>
     </row>
     <row r="13" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="B13" s="120"/>
+      <c r="B13" s="201"/>
       <c r="C13" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="D13" s="167"/>
-      <c r="E13" s="134"/>
-      <c r="F13" s="162"/>
-      <c r="G13" s="163"/>
+      <c r="D13" s="230"/>
+      <c r="E13" s="180"/>
+      <c r="F13" s="225"/>
+      <c r="G13" s="226"/>
       <c r="I13" s="1" t="s">
         <v>23</v>
       </c>
@@ -5809,14 +5940,14 @@
       <c r="X13" s="17"/>
     </row>
     <row r="14" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="B14" s="120"/>
+      <c r="B14" s="201"/>
       <c r="C14" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="167"/>
-      <c r="E14" s="134"/>
-      <c r="F14" s="162"/>
-      <c r="G14" s="163"/>
+      <c r="D14" s="230"/>
+      <c r="E14" s="180"/>
+      <c r="F14" s="225"/>
+      <c r="G14" s="226"/>
       <c r="I14" s="1"/>
       <c r="J14" s="48"/>
       <c r="K14" s="10" t="s">
@@ -5826,14 +5957,14 @@
       <c r="X14" s="19"/>
     </row>
     <row r="15" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="126"/>
+      <c r="B15" s="207"/>
       <c r="C15" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="D15" s="168"/>
-      <c r="E15" s="135"/>
-      <c r="F15" s="164"/>
-      <c r="G15" s="165"/>
+      <c r="D15" s="231"/>
+      <c r="E15" s="181"/>
+      <c r="F15" s="227"/>
+      <c r="G15" s="228"/>
       <c r="I15" s="1"/>
       <c r="J15" s="48"/>
       <c r="K15" s="10" t="s">
@@ -6179,21 +6310,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B2" s="148" t="s">
+      <c r="B2" s="211" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="185" t="s">
+      <c r="C2" s="248" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="173">
+      <c r="D2" s="236">
         <v>46203</v>
       </c>
-      <c r="E2" s="184"/>
-      <c r="F2" s="174"/>
+      <c r="E2" s="247"/>
+      <c r="F2" s="237"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B3" s="148"/>
-      <c r="C3" s="185"/>
+      <c r="B3" s="211"/>
+      <c r="C3" s="248"/>
       <c r="D3" s="7" t="s">
         <v>6</v>
       </c>

--- a/DCT - Guide/Migration Approach.xlsx
+++ b/DCT - Guide/Migration Approach.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\70023796\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\70023796\Desktop\Project\Main_Link\RepoGit\Additional\DCT - Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B50ED3E1-3F7C-4AE3-9C8D-1179F4E7D4C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D664F6B-F89F-4C5A-8A3D-5872CF68DE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{7CAA1510-BEF0-44FB-B9DF-6BA498C876D6}"/>
   </bookViews>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="299">
   <si>
     <t>Asset Cumulative values (Acquisition + Accum. Depreciation)</t>
   </si>
@@ -1139,20 +1139,46 @@
     <t>GL Template</t>
   </si>
   <si>
-    <t>Open AR Template</t>
-  </si>
-  <si>
-    <t>Open AP Template</t>
+    <t>WBS migration will use custom template specifically designed for Project migration</t>
+  </si>
+  <si>
+    <t>Cross Workstream</t>
+  </si>
+  <si>
+    <t>Use F.80 or upload LTMC with opposite sign to reverse</t>
   </si>
   <si>
     <t>GL Template
-(EXCLUDE WBS-related)</t>
-  </si>
-  <si>
-    <t>WBS migration will use custom template specifically designed for Project migration</t>
-  </si>
-  <si>
-    <t>Cross Workstream</t>
+(Enter Dummy WBS if project-related)</t>
+  </si>
+  <si>
+    <t>Project migration program will transfer the WBS info between Dummy WBS -&gt; Real WBS</t>
+  </si>
+  <si>
+    <t>Cr AR (Dummy WBS)</t>
+  </si>
+  <si>
+    <t>Dr AR (Real WBS)</t>
+  </si>
+  <si>
+    <t>Dr Input Cost (Real WBS)</t>
+  </si>
+  <si>
+    <t>Dr Revenue (Real WBS)</t>
+  </si>
+  <si>
+    <t>Cr Revenue (Dummy WBS)</t>
+  </si>
+  <si>
+    <t>Cr Input Cost (Dummy WBS)</t>
+  </si>
+  <si>
+    <t>Open AR Template
+(Enter Dummy WBS if project-related)</t>
+  </si>
+  <si>
+    <t>Open AP Template
+(Enter Dummy WBS if project-related)</t>
   </si>
 </sst>
 </file>
@@ -2034,7 +2060,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="262">
+  <cellXfs count="263">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2315,16 +2341,11 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2332,323 +2353,335 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="55" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="55" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="47" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="49" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="48" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="6" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="6" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="6" borderId="29" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="3" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="3" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="55" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="56" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="47" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="49" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="48" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="6" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="6" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="6" borderId="29" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="3" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="3" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3096,38 +3129,38 @@
     <col min="11" max="11" width="18.7265625" customWidth="1"/>
     <col min="12" max="12" width="17.453125" customWidth="1"/>
     <col min="13" max="13" width="18.81640625" customWidth="1"/>
-    <col min="14" max="14" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13.26953125" customWidth="1"/>
-    <col min="19" max="19" width="13.08984375" style="2" customWidth="1"/>
-    <col min="20" max="20" width="12.08984375" style="109" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.1796875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="12.1796875" style="109" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="47.453125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="4.7265625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.36328125" customWidth="1"/>
-    <col min="25" max="25" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.453125" customWidth="1"/>
+    <col min="25" max="25" width="5.7265625" customWidth="1"/>
     <col min="26" max="26" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="2.90625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.90625" style="109" customWidth="1"/>
-    <col min="32" max="32" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="2.81640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.81640625" style="109" customWidth="1"/>
+    <col min="32" max="32" width="6.1796875" customWidth="1"/>
     <col min="33" max="33" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="2.90625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="22.7265625" style="109" customWidth="1"/>
+    <col min="34" max="34" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="2.81640625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="35.81640625" style="109" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="Y2" s="261">
+      <c r="Y2" s="156">
         <v>2025</v>
       </c>
-      <c r="Z2" s="153" t="s">
+      <c r="Z2" s="143" t="s">
         <v>283</v>
       </c>
-      <c r="AF2" s="261">
+      <c r="AF2" s="156">
         <v>2026</v>
       </c>
-      <c r="AG2" s="153" t="s">
+      <c r="AG2" s="143" t="s">
         <v>284</v>
       </c>
     </row>
@@ -3156,7 +3189,7 @@
       <c r="AC3" s="76" t="s">
         <v>278</v>
       </c>
-      <c r="AD3" s="255" t="s">
+      <c r="AD3" s="155" t="s">
         <v>81</v>
       </c>
       <c r="AG3" s="76" t="s">
@@ -3168,12 +3201,12 @@
       <c r="AJ3" s="76" t="s">
         <v>278</v>
       </c>
-      <c r="AK3" s="255" t="s">
+      <c r="AK3" s="155" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="4" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="S4" s="167" t="s">
+      <c r="S4" s="174" t="s">
         <v>243</v>
       </c>
       <c r="T4" s="116" t="s">
@@ -3188,49 +3221,49 @@
       <c r="W4" s="112" t="s">
         <v>86</v>
       </c>
-      <c r="Y4" s="122" t="s">
+      <c r="Y4" s="121" t="s">
         <v>276</v>
       </c>
-      <c r="Z4" s="123" t="str">
+      <c r="Z4" s="122" t="str">
         <f>T4</f>
         <v>100CP02C00</v>
       </c>
-      <c r="AA4" s="123" t="s">
+      <c r="AA4" s="122" t="s">
         <v>280</v>
       </c>
-      <c r="AB4" s="123" t="s">
+      <c r="AB4" s="122" t="s">
         <v>277</v>
       </c>
-      <c r="AC4" s="124">
+      <c r="AC4" s="160">
         <f>$T$34</f>
         <v>9000000000</v>
       </c>
-      <c r="AD4" s="167" t="s">
+      <c r="AD4" s="174" t="s">
         <v>285</v>
       </c>
-      <c r="AF4" s="122" t="s">
+      <c r="AF4" s="121" t="s">
         <v>276</v>
       </c>
-      <c r="AG4" s="154" t="str">
+      <c r="AG4" s="144" t="str">
         <f>T4</f>
         <v>100CP02C00</v>
       </c>
-      <c r="AH4" s="123" t="s">
+      <c r="AH4" s="122" t="s">
         <v>86</v>
       </c>
-      <c r="AI4" s="123" t="s">
+      <c r="AI4" s="122" t="s">
         <v>277</v>
       </c>
-      <c r="AJ4" s="124">
+      <c r="AJ4" s="160">
         <f>$T$38</f>
         <v>9000000004</v>
       </c>
-      <c r="AK4" s="167" t="s">
+      <c r="AK4" s="174" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="5" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="S5" s="168"/>
+      <c r="S5" s="175"/>
       <c r="T5" s="116" t="s">
         <v>237</v>
       </c>
@@ -3243,45 +3276,45 @@
       <c r="W5" s="112" t="s">
         <v>86</v>
       </c>
-      <c r="Y5" s="119" t="s">
+      <c r="Y5" s="118" t="s">
         <v>276</v>
       </c>
-      <c r="Z5" s="121" t="str">
+      <c r="Z5" s="120" t="str">
         <f t="shared" ref="Z5:Z7" si="0">T5</f>
         <v>100CP03C00</v>
       </c>
-      <c r="AA5" s="121" t="s">
+      <c r="AA5" s="120" t="s">
         <v>280</v>
       </c>
-      <c r="AB5" s="121" t="s">
+      <c r="AB5" s="120" t="s">
         <v>277</v>
       </c>
-      <c r="AC5" s="125">
+      <c r="AC5" s="161">
         <f>$T$34</f>
         <v>9000000000</v>
       </c>
-      <c r="AD5" s="168"/>
-      <c r="AF5" s="119" t="s">
+      <c r="AD5" s="175"/>
+      <c r="AF5" s="118" t="s">
         <v>276</v>
       </c>
-      <c r="AG5" s="155" t="str">
+      <c r="AG5" s="145" t="str">
         <f t="shared" ref="AG5:AG31" si="1">T5</f>
         <v>100CP03C00</v>
       </c>
-      <c r="AH5" s="121" t="s">
+      <c r="AH5" s="120" t="s">
         <v>86</v>
       </c>
-      <c r="AI5" s="121" t="s">
+      <c r="AI5" s="120" t="s">
         <v>277</v>
       </c>
-      <c r="AJ5" s="125">
+      <c r="AJ5" s="161">
         <f t="shared" ref="AJ5:AJ9" si="2">$T$38</f>
         <v>9000000004</v>
       </c>
-      <c r="AK5" s="168"/>
+      <c r="AK5" s="175"/>
     </row>
     <row r="6" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="S6" s="168"/>
+      <c r="S6" s="175"/>
       <c r="T6" s="116" t="s">
         <v>204</v>
       </c>
@@ -3294,45 +3327,45 @@
       <c r="W6" s="112" t="s">
         <v>86</v>
       </c>
-      <c r="Y6" s="119" t="s">
+      <c r="Y6" s="118" t="s">
         <v>277</v>
       </c>
-      <c r="Z6" s="121" t="str">
+      <c r="Z6" s="120" t="str">
         <f t="shared" si="0"/>
         <v>100FL01A00</v>
       </c>
-      <c r="AA6" s="121" t="s">
+      <c r="AA6" s="120" t="s">
         <v>280</v>
       </c>
-      <c r="AB6" s="121" t="s">
+      <c r="AB6" s="120" t="s">
         <v>276</v>
       </c>
-      <c r="AC6" s="125">
+      <c r="AC6" s="161">
         <f>$T$34</f>
         <v>9000000000</v>
       </c>
-      <c r="AD6" s="168"/>
-      <c r="AF6" s="119" t="s">
+      <c r="AD6" s="175"/>
+      <c r="AF6" s="118" t="s">
         <v>277</v>
       </c>
-      <c r="AG6" s="155" t="str">
+      <c r="AG6" s="145" t="str">
         <f t="shared" si="1"/>
         <v>100FL01A00</v>
       </c>
-      <c r="AH6" s="121" t="s">
+      <c r="AH6" s="120" t="s">
         <v>86</v>
       </c>
-      <c r="AI6" s="121" t="s">
+      <c r="AI6" s="120" t="s">
         <v>276</v>
       </c>
-      <c r="AJ6" s="125">
+      <c r="AJ6" s="161">
         <f t="shared" si="2"/>
         <v>9000000004</v>
       </c>
-      <c r="AK6" s="168"/>
+      <c r="AK6" s="175"/>
     </row>
     <row r="7" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="S7" s="169"/>
+      <c r="S7" s="176"/>
       <c r="T7" s="116" t="s">
         <v>212</v>
       </c>
@@ -3345,45 +3378,45 @@
       <c r="W7" s="112" t="s">
         <v>86</v>
       </c>
-      <c r="Y7" s="119" t="s">
+      <c r="Y7" s="118" t="s">
         <v>277</v>
       </c>
-      <c r="Z7" s="121" t="str">
+      <c r="Z7" s="120" t="str">
         <f t="shared" si="0"/>
         <v>100PM01A00</v>
       </c>
-      <c r="AA7" s="121" t="s">
+      <c r="AA7" s="120" t="s">
         <v>280</v>
       </c>
-      <c r="AB7" s="121" t="s">
+      <c r="AB7" s="120" t="s">
         <v>276</v>
       </c>
-      <c r="AC7" s="125">
+      <c r="AC7" s="161">
         <f>$T$34</f>
         <v>9000000000</v>
       </c>
-      <c r="AD7" s="168"/>
-      <c r="AF7" s="119" t="s">
+      <c r="AD7" s="175"/>
+      <c r="AF7" s="118" t="s">
         <v>277</v>
       </c>
-      <c r="AG7" s="155" t="str">
+      <c r="AG7" s="145" t="str">
         <f t="shared" si="1"/>
         <v>100PM01A00</v>
       </c>
-      <c r="AH7" s="121" t="s">
+      <c r="AH7" s="120" t="s">
         <v>86</v>
       </c>
-      <c r="AI7" s="121" t="s">
+      <c r="AI7" s="120" t="s">
         <v>276</v>
       </c>
-      <c r="AJ7" s="125">
+      <c r="AJ7" s="161">
         <f t="shared" si="2"/>
         <v>9000000004</v>
       </c>
-      <c r="AK7" s="168"/>
+      <c r="AK7" s="176"/>
     </row>
     <row r="8" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="S8" s="170" t="s">
+      <c r="S8" s="177" t="s">
         <v>244</v>
       </c>
       <c r="T8" s="117" t="s">
@@ -3398,33 +3431,34 @@
       <c r="W8" s="113" t="s">
         <v>86</v>
       </c>
-      <c r="Y8" s="126"/>
-      <c r="Z8" s="120"/>
-      <c r="AA8" s="120"/>
-      <c r="AB8" s="120"/>
-      <c r="AC8" s="127"/>
-      <c r="AD8" s="168"/>
-      <c r="AF8" s="134" t="s">
+      <c r="Y8" s="123"/>
+      <c r="Z8" s="119"/>
+      <c r="AA8" s="119"/>
+      <c r="AB8" s="119"/>
+      <c r="AC8" s="124"/>
+      <c r="AD8" s="175"/>
+      <c r="AF8" s="130" t="s">
         <v>276</v>
       </c>
-      <c r="AG8" s="156" t="str">
+      <c r="AG8" s="261" t="str">
         <f t="shared" si="1"/>
         <v>711PP11000</v>
       </c>
       <c r="AH8" s="107" t="s">
-        <v>86</v>
+        <v>280</v>
       </c>
       <c r="AI8" s="107" t="s">
         <v>276</v>
       </c>
-      <c r="AJ8" s="135">
-        <f t="shared" si="2"/>
-        <v>9000000004</v>
-      </c>
-      <c r="AK8" s="168"/>
+      <c r="AJ8" s="165">
+        <v>9000000000</v>
+      </c>
+      <c r="AK8" s="174" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="9" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="S9" s="171"/>
+      <c r="S9" s="178"/>
       <c r="T9" s="117" t="s">
         <v>241</v>
       </c>
@@ -3437,33 +3471,32 @@
       <c r="W9" s="113" t="s">
         <v>86</v>
       </c>
-      <c r="Y9" s="128"/>
-      <c r="Z9" s="129"/>
-      <c r="AA9" s="129"/>
-      <c r="AB9" s="129"/>
-      <c r="AC9" s="130"/>
-      <c r="AD9" s="168"/>
-      <c r="AF9" s="136" t="s">
+      <c r="Y9" s="125"/>
+      <c r="Z9" s="126"/>
+      <c r="AA9" s="126"/>
+      <c r="AB9" s="126"/>
+      <c r="AC9" s="127"/>
+      <c r="AD9" s="175"/>
+      <c r="AF9" s="131" t="s">
         <v>276</v>
       </c>
-      <c r="AG9" s="157" t="str">
+      <c r="AG9" s="262" t="str">
         <f t="shared" si="1"/>
         <v>711PP12000</v>
       </c>
-      <c r="AH9" s="137" t="s">
-        <v>86</v>
-      </c>
-      <c r="AI9" s="137" t="s">
+      <c r="AH9" s="132" t="s">
+        <v>280</v>
+      </c>
+      <c r="AI9" s="132" t="s">
         <v>276</v>
       </c>
-      <c r="AJ9" s="138">
-        <f t="shared" si="2"/>
-        <v>9000000004</v>
-      </c>
-      <c r="AK9" s="169"/>
+      <c r="AJ9" s="166">
+        <v>9000000000</v>
+      </c>
+      <c r="AK9" s="176"/>
     </row>
     <row r="10" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="S10" s="166" t="s">
+      <c r="S10" s="173" t="s">
         <v>93</v>
       </c>
       <c r="T10" s="116" t="s">
@@ -3478,47 +3511,47 @@
       <c r="W10" s="112" t="s">
         <v>207</v>
       </c>
-      <c r="Y10" s="122" t="s">
+      <c r="Y10" s="121" t="s">
         <v>276</v>
       </c>
-      <c r="Z10" s="123" t="str">
-        <f>T10</f>
-        <v>156TD00000</v>
-      </c>
-      <c r="AA10" s="123" t="s">
+      <c r="Z10" s="157">
+        <f>T36</f>
+        <v>9000000002</v>
+      </c>
+      <c r="AA10" s="122" t="s">
         <v>280</v>
       </c>
-      <c r="AB10" s="123" t="s">
+      <c r="AB10" s="122" t="s">
         <v>277</v>
       </c>
-      <c r="AC10" s="124">
+      <c r="AC10" s="160">
         <f>$T$34</f>
         <v>9000000000</v>
       </c>
-      <c r="AD10" s="168"/>
-      <c r="AF10" s="122" t="s">
+      <c r="AD10" s="175"/>
+      <c r="AF10" s="121" t="s">
         <v>276</v>
       </c>
-      <c r="AG10" s="154" t="str">
+      <c r="AG10" s="144" t="str">
         <f t="shared" si="1"/>
         <v>156TD00000</v>
       </c>
-      <c r="AH10" s="123" t="s">
+      <c r="AH10" s="122" t="s">
         <v>207</v>
       </c>
-      <c r="AI10" s="123" t="s">
+      <c r="AI10" s="122" t="s">
         <v>277</v>
       </c>
-      <c r="AJ10" s="124">
+      <c r="AJ10" s="160">
         <f>T36</f>
         <v>9000000002</v>
       </c>
-      <c r="AK10" s="167" t="s">
-        <v>286</v>
+      <c r="AK10" s="183" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="11" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="S11" s="166"/>
+      <c r="S11" s="173"/>
       <c r="T11" s="116" t="s">
         <v>226</v>
       </c>
@@ -3531,45 +3564,45 @@
       <c r="W11" s="112" t="s">
         <v>207</v>
       </c>
-      <c r="Y11" s="131" t="s">
+      <c r="Y11" s="128" t="s">
         <v>277</v>
       </c>
-      <c r="Z11" s="132" t="str">
-        <f t="shared" ref="Z11:Z13" si="3">T11</f>
-        <v>153AC01000</v>
-      </c>
-      <c r="AA11" s="132" t="s">
+      <c r="Z11" s="158">
+        <f>T40</f>
+        <v>9000000006</v>
+      </c>
+      <c r="AA11" s="129" t="s">
         <v>280</v>
       </c>
-      <c r="AB11" s="132" t="s">
+      <c r="AB11" s="129" t="s">
         <v>276</v>
       </c>
-      <c r="AC11" s="133">
-        <f t="shared" ref="AC11:AC25" si="4">$T$34</f>
+      <c r="AC11" s="162">
+        <f t="shared" ref="AC11:AC25" si="3">$T$34</f>
         <v>9000000000</v>
       </c>
-      <c r="AD11" s="168"/>
-      <c r="AF11" s="131" t="s">
+      <c r="AD11" s="175"/>
+      <c r="AF11" s="128" t="s">
         <v>277</v>
       </c>
-      <c r="AG11" s="158" t="str">
+      <c r="AG11" s="146" t="str">
         <f t="shared" si="1"/>
         <v>153AC01000</v>
       </c>
-      <c r="AH11" s="132" t="s">
+      <c r="AH11" s="129" t="s">
         <v>207</v>
       </c>
-      <c r="AI11" s="132" t="s">
+      <c r="AI11" s="129" t="s">
         <v>276</v>
       </c>
-      <c r="AJ11" s="133">
+      <c r="AJ11" s="162">
         <f>T40</f>
         <v>9000000006</v>
       </c>
-      <c r="AK11" s="169"/>
+      <c r="AK11" s="176"/>
     </row>
     <row r="12" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="S12" s="166" t="s">
+      <c r="S12" s="173" t="s">
         <v>94</v>
       </c>
       <c r="T12" s="116" t="s">
@@ -3584,254 +3617,254 @@
       <c r="W12" s="112" t="s">
         <v>208</v>
       </c>
-      <c r="Y12" s="122" t="s">
+      <c r="Y12" s="121" t="s">
         <v>277</v>
       </c>
-      <c r="Z12" s="123" t="str">
+      <c r="Z12" s="157">
+        <f>T35</f>
+        <v>9000000001</v>
+      </c>
+      <c r="AA12" s="122" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB12" s="122" t="s">
+        <v>276</v>
+      </c>
+      <c r="AC12" s="160">
         <f t="shared" si="3"/>
+        <v>9000000000</v>
+      </c>
+      <c r="AD12" s="175"/>
+      <c r="AF12" s="121" t="s">
+        <v>277</v>
+      </c>
+      <c r="AG12" s="144" t="str">
+        <f t="shared" si="1"/>
         <v>206AP00000</v>
       </c>
-      <c r="AA12" s="123" t="s">
+      <c r="AH12" s="122" t="s">
+        <v>208</v>
+      </c>
+      <c r="AI12" s="122" t="s">
+        <v>276</v>
+      </c>
+      <c r="AJ12" s="160">
+        <f>T35</f>
+        <v>9000000001</v>
+      </c>
+      <c r="AK12" s="183" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="13" spans="19:37" x14ac:dyDescent="0.35">
+      <c r="S13" s="173"/>
+      <c r="T13" s="116" t="s">
+        <v>230</v>
+      </c>
+      <c r="U13" s="112" t="s">
+        <v>231</v>
+      </c>
+      <c r="V13" s="112" t="s">
+        <v>201</v>
+      </c>
+      <c r="W13" s="112" t="s">
+        <v>208</v>
+      </c>
+      <c r="Y13" s="128" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z13" s="158">
+        <f>T39</f>
+        <v>9000000005</v>
+      </c>
+      <c r="AA13" s="129" t="s">
         <v>280</v>
       </c>
-      <c r="AB12" s="123" t="s">
+      <c r="AB13" s="129" t="s">
+        <v>277</v>
+      </c>
+      <c r="AC13" s="162">
+        <f t="shared" si="3"/>
+        <v>9000000000</v>
+      </c>
+      <c r="AD13" s="175"/>
+      <c r="AF13" s="128" t="s">
         <v>276</v>
       </c>
-      <c r="AC12" s="124">
+      <c r="AG13" s="146" t="str">
+        <f t="shared" si="1"/>
+        <v>159AP00000</v>
+      </c>
+      <c r="AH13" s="129" t="s">
+        <v>208</v>
+      </c>
+      <c r="AI13" s="129" t="s">
+        <v>277</v>
+      </c>
+      <c r="AJ13" s="162">
+        <f>T39</f>
+        <v>9000000005</v>
+      </c>
+      <c r="AK13" s="176"/>
+    </row>
+    <row r="14" spans="19:37" x14ac:dyDescent="0.35">
+      <c r="S14" s="173" t="s">
+        <v>234</v>
+      </c>
+      <c r="T14" s="116" t="s">
+        <v>220</v>
+      </c>
+      <c r="U14" s="112" t="s">
+        <v>221</v>
+      </c>
+      <c r="V14" s="112" t="s">
+        <v>201</v>
+      </c>
+      <c r="W14" s="112" t="s">
+        <v>209</v>
+      </c>
+      <c r="Y14" s="121" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z14" s="122" t="str">
+        <f>T14</f>
+        <v>158NT05000</v>
+      </c>
+      <c r="AA14" s="122" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB14" s="122" t="s">
+        <v>277</v>
+      </c>
+      <c r="AC14" s="160">
+        <f t="shared" si="3"/>
+        <v>9000000000</v>
+      </c>
+      <c r="AD14" s="175"/>
+      <c r="AF14" s="121" t="s">
+        <v>276</v>
+      </c>
+      <c r="AG14" s="122" t="str">
+        <f t="shared" si="1"/>
+        <v>158NT05000</v>
+      </c>
+      <c r="AH14" s="122" t="s">
+        <v>280</v>
+      </c>
+      <c r="AI14" s="122" t="s">
+        <v>277</v>
+      </c>
+      <c r="AJ14" s="160">
+        <f t="shared" ref="AJ14:AJ17" si="4">$T$34</f>
+        <v>9000000000</v>
+      </c>
+      <c r="AK14" s="184" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="15" spans="19:37" x14ac:dyDescent="0.35">
+      <c r="S15" s="173"/>
+      <c r="T15" s="116" t="s">
+        <v>222</v>
+      </c>
+      <c r="U15" s="112" t="s">
+        <v>223</v>
+      </c>
+      <c r="V15" s="112" t="s">
+        <v>201</v>
+      </c>
+      <c r="W15" s="112" t="s">
+        <v>209</v>
+      </c>
+      <c r="Y15" s="128" t="s">
+        <v>277</v>
+      </c>
+      <c r="Z15" s="129" t="str">
+        <f t="shared" ref="Z15:Z25" si="5">T15</f>
+        <v>206OT54000</v>
+      </c>
+      <c r="AA15" s="129" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB15" s="129" t="s">
+        <v>276</v>
+      </c>
+      <c r="AC15" s="162">
+        <f t="shared" si="3"/>
+        <v>9000000000</v>
+      </c>
+      <c r="AD15" s="175"/>
+      <c r="AF15" s="128" t="s">
+        <v>277</v>
+      </c>
+      <c r="AG15" s="129" t="str">
+        <f t="shared" si="1"/>
+        <v>206OT54000</v>
+      </c>
+      <c r="AH15" s="129" t="s">
+        <v>280</v>
+      </c>
+      <c r="AI15" s="129" t="s">
+        <v>276</v>
+      </c>
+      <c r="AJ15" s="162">
         <f t="shared" si="4"/>
         <v>9000000000</v>
       </c>
-      <c r="AD12" s="168"/>
-      <c r="AF12" s="122" t="s">
+      <c r="AK15" s="175"/>
+    </row>
+    <row r="16" spans="19:37" x14ac:dyDescent="0.35">
+      <c r="S16" s="173" t="s">
+        <v>233</v>
+      </c>
+      <c r="T16" s="116" t="s">
+        <v>245</v>
+      </c>
+      <c r="U16" s="112" t="s">
+        <v>246</v>
+      </c>
+      <c r="V16" s="112" t="s">
+        <v>201</v>
+      </c>
+      <c r="W16" s="112" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y16" s="121" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z16" s="122" t="str">
+        <f t="shared" si="5"/>
+        <v>188CC01M00</v>
+      </c>
+      <c r="AA16" s="122" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB16" s="122" t="s">
         <v>277</v>
       </c>
-      <c r="AG12" s="154" t="str">
+      <c r="AC16" s="160">
+        <f t="shared" si="3"/>
+        <v>9000000000</v>
+      </c>
+      <c r="AD16" s="175"/>
+      <c r="AF16" s="121" t="s">
+        <v>276</v>
+      </c>
+      <c r="AG16" s="122" t="str">
         <f t="shared" si="1"/>
-        <v>206AP00000</v>
-      </c>
-      <c r="AH12" s="123" t="s">
-        <v>208</v>
-      </c>
-      <c r="AI12" s="123" t="s">
-        <v>276</v>
-      </c>
-      <c r="AJ12" s="124">
-        <f>T35</f>
-        <v>9000000001</v>
-      </c>
-      <c r="AK12" s="167" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="13" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="S13" s="166"/>
-      <c r="T13" s="116" t="s">
-        <v>230</v>
-      </c>
-      <c r="U13" s="112" t="s">
-        <v>231</v>
-      </c>
-      <c r="V13" s="112" t="s">
-        <v>201</v>
-      </c>
-      <c r="W13" s="112" t="s">
-        <v>208</v>
-      </c>
-      <c r="Y13" s="131" t="s">
-        <v>276</v>
-      </c>
-      <c r="Z13" s="132" t="str">
-        <f t="shared" si="3"/>
-        <v>159AP00000</v>
-      </c>
-      <c r="AA13" s="132" t="s">
+        <v>188CC01M00</v>
+      </c>
+      <c r="AH16" s="122" t="s">
         <v>280</v>
       </c>
-      <c r="AB13" s="132" t="s">
+      <c r="AI16" s="122" t="s">
         <v>277</v>
       </c>
-      <c r="AC13" s="133">
+      <c r="AJ16" s="160">
         <f t="shared" si="4"/>
         <v>9000000000</v>
       </c>
-      <c r="AD13" s="168"/>
-      <c r="AF13" s="131" t="s">
-        <v>276</v>
-      </c>
-      <c r="AG13" s="158" t="str">
-        <f t="shared" si="1"/>
-        <v>159AP00000</v>
-      </c>
-      <c r="AH13" s="132" t="s">
-        <v>208</v>
-      </c>
-      <c r="AI13" s="132" t="s">
-        <v>277</v>
-      </c>
-      <c r="AJ13" s="133">
-        <f>T39</f>
-        <v>9000000005</v>
-      </c>
-      <c r="AK13" s="169"/>
-    </row>
-    <row r="14" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="S14" s="166" t="s">
-        <v>234</v>
-      </c>
-      <c r="T14" s="116" t="s">
-        <v>220</v>
-      </c>
-      <c r="U14" s="112" t="s">
-        <v>221</v>
-      </c>
-      <c r="V14" s="112" t="s">
-        <v>201</v>
-      </c>
-      <c r="W14" s="112" t="s">
-        <v>209</v>
-      </c>
-      <c r="Y14" s="122" t="s">
-        <v>276</v>
-      </c>
-      <c r="Z14" s="123" t="str">
-        <f>T14</f>
-        <v>158NT05000</v>
-      </c>
-      <c r="AA14" s="123" t="s">
-        <v>280</v>
-      </c>
-      <c r="AB14" s="123" t="s">
-        <v>277</v>
-      </c>
-      <c r="AC14" s="124">
-        <f t="shared" si="4"/>
-        <v>9000000000</v>
-      </c>
-      <c r="AD14" s="168"/>
-      <c r="AF14" s="122" t="s">
-        <v>276</v>
-      </c>
-      <c r="AG14" s="123" t="str">
-        <f t="shared" si="1"/>
-        <v>158NT05000</v>
-      </c>
-      <c r="AH14" s="123" t="s">
-        <v>280</v>
-      </c>
-      <c r="AI14" s="123" t="s">
-        <v>277</v>
-      </c>
-      <c r="AJ14" s="124">
-        <f t="shared" ref="AJ14:AJ17" si="5">$T$34</f>
-        <v>9000000000</v>
-      </c>
-      <c r="AK14" s="259" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="15" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="S15" s="166"/>
-      <c r="T15" s="116" t="s">
-        <v>222</v>
-      </c>
-      <c r="U15" s="112" t="s">
-        <v>223</v>
-      </c>
-      <c r="V15" s="112" t="s">
-        <v>201</v>
-      </c>
-      <c r="W15" s="112" t="s">
-        <v>209</v>
-      </c>
-      <c r="Y15" s="131" t="s">
-        <v>277</v>
-      </c>
-      <c r="Z15" s="132" t="str">
-        <f t="shared" ref="Z15:Z25" si="6">T15</f>
-        <v>206OT54000</v>
-      </c>
-      <c r="AA15" s="132" t="s">
-        <v>280</v>
-      </c>
-      <c r="AB15" s="132" t="s">
-        <v>276</v>
-      </c>
-      <c r="AC15" s="133">
-        <f t="shared" si="4"/>
-        <v>9000000000</v>
-      </c>
-      <c r="AD15" s="168"/>
-      <c r="AF15" s="131" t="s">
-        <v>277</v>
-      </c>
-      <c r="AG15" s="132" t="str">
-        <f t="shared" si="1"/>
-        <v>206OT54000</v>
-      </c>
-      <c r="AH15" s="132" t="s">
-        <v>280</v>
-      </c>
-      <c r="AI15" s="132" t="s">
-        <v>276</v>
-      </c>
-      <c r="AJ15" s="133">
-        <f t="shared" si="5"/>
-        <v>9000000000</v>
-      </c>
-      <c r="AK15" s="168"/>
-    </row>
-    <row r="16" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="S16" s="166" t="s">
-        <v>233</v>
-      </c>
-      <c r="T16" s="116" t="s">
-        <v>245</v>
-      </c>
-      <c r="U16" s="112" t="s">
-        <v>246</v>
-      </c>
-      <c r="V16" s="112" t="s">
-        <v>201</v>
-      </c>
-      <c r="W16" s="112" t="s">
-        <v>210</v>
-      </c>
-      <c r="Y16" s="122" t="s">
-        <v>276</v>
-      </c>
-      <c r="Z16" s="123" t="str">
-        <f t="shared" si="6"/>
-        <v>188CC01M00</v>
-      </c>
-      <c r="AA16" s="123" t="s">
-        <v>280</v>
-      </c>
-      <c r="AB16" s="123" t="s">
-        <v>277</v>
-      </c>
-      <c r="AC16" s="124">
-        <f t="shared" si="4"/>
-        <v>9000000000</v>
-      </c>
-      <c r="AD16" s="168"/>
-      <c r="AF16" s="122" t="s">
-        <v>276</v>
-      </c>
-      <c r="AG16" s="123" t="str">
-        <f t="shared" si="1"/>
-        <v>188CC01M00</v>
-      </c>
-      <c r="AH16" s="123" t="s">
-        <v>280</v>
-      </c>
-      <c r="AI16" s="123" t="s">
-        <v>277</v>
-      </c>
-      <c r="AJ16" s="124">
-        <f t="shared" si="5"/>
-        <v>9000000000</v>
-      </c>
-      <c r="AK16" s="168"/>
+      <c r="AK16" s="175"/>
     </row>
     <row r="17" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B17" s="76" t="s">
@@ -3849,7 +3882,7 @@
       <c r="I17" s="76" t="s">
         <v>141</v>
       </c>
-      <c r="S17" s="166"/>
+      <c r="S17" s="173"/>
       <c r="T17" s="116" t="s">
         <v>247</v>
       </c>
@@ -3862,42 +3895,42 @@
       <c r="W17" s="112" t="s">
         <v>210</v>
       </c>
-      <c r="Y17" s="119" t="s">
+      <c r="Y17" s="118" t="s">
         <v>277</v>
       </c>
-      <c r="Z17" s="121" t="str">
-        <f t="shared" si="6"/>
+      <c r="Z17" s="120" t="str">
+        <f t="shared" si="5"/>
         <v>300SC01000</v>
       </c>
-      <c r="AA17" s="121" t="s">
+      <c r="AA17" s="120" t="s">
         <v>280</v>
       </c>
-      <c r="AB17" s="121" t="s">
+      <c r="AB17" s="120" t="s">
         <v>276</v>
       </c>
-      <c r="AC17" s="125">
+      <c r="AC17" s="161">
+        <f t="shared" si="3"/>
+        <v>9000000000</v>
+      </c>
+      <c r="AD17" s="175"/>
+      <c r="AF17" s="118" t="s">
+        <v>277</v>
+      </c>
+      <c r="AG17" s="120" t="str">
+        <f t="shared" si="1"/>
+        <v>300SC01000</v>
+      </c>
+      <c r="AH17" s="120" t="s">
+        <v>280</v>
+      </c>
+      <c r="AI17" s="120" t="s">
+        <v>276</v>
+      </c>
+      <c r="AJ17" s="161">
         <f t="shared" si="4"/>
         <v>9000000000</v>
       </c>
-      <c r="AD17" s="168"/>
-      <c r="AF17" s="119" t="s">
-        <v>277</v>
-      </c>
-      <c r="AG17" s="121" t="str">
-        <f t="shared" si="1"/>
-        <v>300SC01000</v>
-      </c>
-      <c r="AH17" s="121" t="s">
-        <v>280</v>
-      </c>
-      <c r="AI17" s="121" t="s">
-        <v>276</v>
-      </c>
-      <c r="AJ17" s="125">
-        <f t="shared" si="5"/>
-        <v>9000000000</v>
-      </c>
-      <c r="AK17" s="168"/>
+      <c r="AK17" s="175"/>
     </row>
     <row r="18" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
@@ -3927,59 +3960,59 @@
       <c r="P18" t="s">
         <v>146</v>
       </c>
-      <c r="Q18" s="162" t="s">
+      <c r="Q18" s="169" t="s">
         <v>147</v>
       </c>
-      <c r="S18" s="166"/>
-      <c r="T18" s="142" t="s">
+      <c r="S18" s="173"/>
+      <c r="T18" s="135" t="s">
         <v>261</v>
       </c>
-      <c r="U18" s="143" t="s">
+      <c r="U18" s="136" t="s">
         <v>262</v>
       </c>
-      <c r="V18" s="143" t="s">
+      <c r="V18" s="136" t="s">
         <v>201</v>
       </c>
-      <c r="W18" s="143" t="s">
+      <c r="W18" s="136" t="s">
         <v>275</v>
       </c>
-      <c r="Y18" s="144" t="s">
+      <c r="Y18" s="137" t="s">
         <v>276</v>
       </c>
-      <c r="Z18" s="145" t="str">
-        <f t="shared" si="6"/>
+      <c r="Z18" s="138" t="str">
+        <f t="shared" si="5"/>
         <v>152RM00000</v>
       </c>
-      <c r="AA18" s="145" t="s">
+      <c r="AA18" s="138" t="s">
         <v>280</v>
       </c>
-      <c r="AB18" s="145" t="s">
+      <c r="AB18" s="138" t="s">
         <v>277</v>
       </c>
-      <c r="AC18" s="146">
-        <f t="shared" si="4"/>
+      <c r="AC18" s="163">
+        <f t="shared" si="3"/>
         <v>9000000000</v>
       </c>
-      <c r="AD18" s="168"/>
-      <c r="AF18" s="150" t="s">
+      <c r="AD18" s="175"/>
+      <c r="AF18" s="141" t="s">
         <v>276</v>
       </c>
-      <c r="AG18" s="159" t="str">
+      <c r="AG18" s="147" t="str">
         <f t="shared" si="1"/>
         <v>152RM00000</v>
       </c>
-      <c r="AH18" s="151" t="s">
+      <c r="AH18" s="142" t="s">
         <v>282</v>
       </c>
-      <c r="AI18" s="151" t="s">
+      <c r="AI18" s="142" t="s">
         <v>277</v>
       </c>
-      <c r="AJ18" s="152">
+      <c r="AJ18" s="167">
         <f>$T$37</f>
         <v>9000000003</v>
       </c>
-      <c r="AK18" s="257" t="s">
-        <v>290</v>
+      <c r="AK18" s="185" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:37" x14ac:dyDescent="0.35">
@@ -4002,56 +4035,56 @@
         <v>145</v>
       </c>
       <c r="N19" s="81"/>
-      <c r="Q19" s="163"/>
-      <c r="S19" s="166"/>
-      <c r="T19" s="142" t="s">
+      <c r="Q19" s="170"/>
+      <c r="S19" s="173"/>
+      <c r="T19" s="135" t="s">
         <v>263</v>
       </c>
-      <c r="U19" s="143" t="s">
+      <c r="U19" s="136" t="s">
         <v>264</v>
       </c>
-      <c r="V19" s="143" t="s">
+      <c r="V19" s="136" t="s">
         <v>201</v>
       </c>
-      <c r="W19" s="143" t="s">
+      <c r="W19" s="136" t="s">
         <v>275</v>
       </c>
-      <c r="Y19" s="144" t="s">
+      <c r="Y19" s="137" t="s">
         <v>276</v>
       </c>
-      <c r="Z19" s="145" t="str">
-        <f t="shared" si="6"/>
+      <c r="Z19" s="138" t="str">
+        <f t="shared" si="5"/>
         <v>152TG00000</v>
       </c>
-      <c r="AA19" s="145" t="s">
+      <c r="AA19" s="138" t="s">
         <v>280</v>
       </c>
-      <c r="AB19" s="145" t="s">
+      <c r="AB19" s="138" t="s">
         <v>277</v>
       </c>
-      <c r="AC19" s="146">
-        <f t="shared" si="4"/>
+      <c r="AC19" s="163">
+        <f t="shared" si="3"/>
         <v>9000000000</v>
       </c>
-      <c r="AD19" s="168"/>
-      <c r="AF19" s="144" t="s">
+      <c r="AD19" s="175"/>
+      <c r="AF19" s="137" t="s">
         <v>276</v>
       </c>
-      <c r="AG19" s="160" t="str">
+      <c r="AG19" s="148" t="str">
         <f t="shared" si="1"/>
         <v>152TG00000</v>
       </c>
-      <c r="AH19" s="145" t="s">
+      <c r="AH19" s="138" t="s">
         <v>282</v>
       </c>
-      <c r="AI19" s="145" t="s">
+      <c r="AI19" s="138" t="s">
         <v>277</v>
       </c>
-      <c r="AJ19" s="146">
-        <f t="shared" ref="AJ19:AJ25" si="7">$T$37</f>
+      <c r="AJ19" s="163">
+        <f t="shared" ref="AJ19:AJ25" si="6">$T$37</f>
         <v>9000000003</v>
       </c>
-      <c r="AK19" s="256"/>
+      <c r="AK19" s="186"/>
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
@@ -4073,56 +4106,56 @@
         <v>145</v>
       </c>
       <c r="N20" s="81"/>
-      <c r="Q20" s="163"/>
-      <c r="S20" s="166"/>
-      <c r="T20" s="142" t="s">
+      <c r="Q20" s="170"/>
+      <c r="S20" s="173"/>
+      <c r="T20" s="135" t="s">
         <v>265</v>
       </c>
-      <c r="U20" s="143" t="s">
+      <c r="U20" s="136" t="s">
         <v>266</v>
       </c>
-      <c r="V20" s="143" t="s">
+      <c r="V20" s="136" t="s">
         <v>201</v>
       </c>
-      <c r="W20" s="143" t="s">
+      <c r="W20" s="136" t="s">
         <v>275</v>
       </c>
-      <c r="Y20" s="144" t="s">
+      <c r="Y20" s="137" t="s">
         <v>276</v>
       </c>
-      <c r="Z20" s="145" t="str">
-        <f t="shared" si="6"/>
+      <c r="Z20" s="138" t="str">
+        <f t="shared" si="5"/>
         <v>152SP00000</v>
       </c>
-      <c r="AA20" s="145" t="s">
+      <c r="AA20" s="138" t="s">
         <v>280</v>
       </c>
-      <c r="AB20" s="145" t="s">
+      <c r="AB20" s="138" t="s">
         <v>277</v>
       </c>
-      <c r="AC20" s="146">
-        <f t="shared" si="4"/>
+      <c r="AC20" s="163">
+        <f t="shared" si="3"/>
         <v>9000000000</v>
       </c>
-      <c r="AD20" s="168"/>
-      <c r="AF20" s="144" t="s">
+      <c r="AD20" s="175"/>
+      <c r="AF20" s="137" t="s">
         <v>276</v>
       </c>
-      <c r="AG20" s="160" t="str">
+      <c r="AG20" s="148" t="str">
         <f t="shared" si="1"/>
         <v>152SP00000</v>
       </c>
-      <c r="AH20" s="145" t="s">
+      <c r="AH20" s="138" t="s">
         <v>282</v>
       </c>
-      <c r="AI20" s="145" t="s">
+      <c r="AI20" s="138" t="s">
         <v>277</v>
       </c>
-      <c r="AJ20" s="146">
-        <f t="shared" si="7"/>
+      <c r="AJ20" s="163">
+        <f t="shared" si="6"/>
         <v>9000000003</v>
       </c>
-      <c r="AK20" s="256"/>
+      <c r="AK20" s="186"/>
     </row>
     <row r="21" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
@@ -4144,56 +4177,56 @@
         <v>145</v>
       </c>
       <c r="N21" s="81"/>
-      <c r="Q21" s="163"/>
-      <c r="S21" s="166"/>
-      <c r="T21" s="142" t="s">
+      <c r="Q21" s="170"/>
+      <c r="S21" s="173"/>
+      <c r="T21" s="135" t="s">
         <v>267</v>
       </c>
-      <c r="U21" s="143" t="s">
+      <c r="U21" s="136" t="s">
         <v>268</v>
       </c>
-      <c r="V21" s="143" t="s">
+      <c r="V21" s="136" t="s">
         <v>201</v>
       </c>
-      <c r="W21" s="143" t="s">
+      <c r="W21" s="136" t="s">
         <v>275</v>
       </c>
-      <c r="Y21" s="144" t="s">
+      <c r="Y21" s="137" t="s">
         <v>276</v>
       </c>
-      <c r="Z21" s="145" t="str">
-        <f t="shared" si="6"/>
+      <c r="Z21" s="138" t="str">
+        <f t="shared" si="5"/>
         <v>152PG00000</v>
       </c>
-      <c r="AA21" s="145" t="s">
+      <c r="AA21" s="138" t="s">
         <v>280</v>
       </c>
-      <c r="AB21" s="145" t="s">
+      <c r="AB21" s="138" t="s">
         <v>277</v>
       </c>
-      <c r="AC21" s="146">
-        <f t="shared" si="4"/>
+      <c r="AC21" s="163">
+        <f t="shared" si="3"/>
         <v>9000000000</v>
       </c>
-      <c r="AD21" s="168"/>
-      <c r="AF21" s="144" t="s">
+      <c r="AD21" s="175"/>
+      <c r="AF21" s="137" t="s">
         <v>276</v>
       </c>
-      <c r="AG21" s="160" t="str">
+      <c r="AG21" s="148" t="str">
         <f t="shared" si="1"/>
         <v>152PG00000</v>
       </c>
-      <c r="AH21" s="145" t="s">
+      <c r="AH21" s="138" t="s">
         <v>282</v>
       </c>
-      <c r="AI21" s="145" t="s">
+      <c r="AI21" s="138" t="s">
         <v>277</v>
       </c>
-      <c r="AJ21" s="146">
-        <f t="shared" si="7"/>
+      <c r="AJ21" s="163">
+        <f t="shared" si="6"/>
         <v>9000000003</v>
       </c>
-      <c r="AK21" s="256"/>
+      <c r="AK21" s="186"/>
     </row>
     <row r="22" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
@@ -4215,56 +4248,56 @@
         <v>150</v>
       </c>
       <c r="N22" s="81"/>
-      <c r="Q22" s="163"/>
-      <c r="S22" s="166"/>
-      <c r="T22" s="142" t="s">
+      <c r="Q22" s="170"/>
+      <c r="S22" s="173"/>
+      <c r="T22" s="135" t="s">
         <v>265</v>
       </c>
-      <c r="U22" s="143" t="s">
+      <c r="U22" s="136" t="s">
         <v>266</v>
       </c>
-      <c r="V22" s="143" t="s">
+      <c r="V22" s="136" t="s">
         <v>201</v>
       </c>
-      <c r="W22" s="143" t="s">
+      <c r="W22" s="136" t="s">
         <v>275</v>
       </c>
-      <c r="Y22" s="144" t="s">
+      <c r="Y22" s="137" t="s">
         <v>276</v>
       </c>
-      <c r="Z22" s="145" t="str">
-        <f t="shared" si="6"/>
+      <c r="Z22" s="138" t="str">
+        <f t="shared" si="5"/>
         <v>152SP00000</v>
       </c>
-      <c r="AA22" s="145" t="s">
+      <c r="AA22" s="138" t="s">
         <v>280</v>
       </c>
-      <c r="AB22" s="145" t="s">
+      <c r="AB22" s="138" t="s">
         <v>277</v>
       </c>
-      <c r="AC22" s="146">
-        <f t="shared" si="4"/>
+      <c r="AC22" s="163">
+        <f t="shared" si="3"/>
         <v>9000000000</v>
       </c>
-      <c r="AD22" s="168"/>
-      <c r="AF22" s="144" t="s">
+      <c r="AD22" s="175"/>
+      <c r="AF22" s="137" t="s">
         <v>276</v>
       </c>
-      <c r="AG22" s="160" t="str">
+      <c r="AG22" s="148" t="str">
         <f t="shared" si="1"/>
         <v>152SP00000</v>
       </c>
-      <c r="AH22" s="145" t="s">
+      <c r="AH22" s="138" t="s">
         <v>282</v>
       </c>
-      <c r="AI22" s="145" t="s">
+      <c r="AI22" s="138" t="s">
         <v>277</v>
       </c>
-      <c r="AJ22" s="146">
-        <f t="shared" si="7"/>
+      <c r="AJ22" s="163">
+        <f t="shared" si="6"/>
         <v>9000000003</v>
       </c>
-      <c r="AK22" s="256"/>
+      <c r="AK22" s="186"/>
     </row>
     <row r="23" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
@@ -4287,108 +4320,108 @@
       <c r="L23" s="83"/>
       <c r="M23" s="83"/>
       <c r="N23" s="84"/>
-      <c r="Q23" s="163"/>
-      <c r="S23" s="166"/>
-      <c r="T23" s="142" t="s">
+      <c r="Q23" s="170"/>
+      <c r="S23" s="173"/>
+      <c r="T23" s="135" t="s">
         <v>269</v>
       </c>
-      <c r="U23" s="143" t="s">
+      <c r="U23" s="136" t="s">
         <v>270</v>
       </c>
-      <c r="V23" s="143" t="s">
+      <c r="V23" s="136" t="s">
         <v>201</v>
       </c>
-      <c r="W23" s="143" t="s">
+      <c r="W23" s="136" t="s">
         <v>275</v>
       </c>
-      <c r="Y23" s="144" t="s">
+      <c r="Y23" s="137" t="s">
         <v>276</v>
       </c>
-      <c r="Z23" s="145" t="str">
-        <f t="shared" si="6"/>
+      <c r="Z23" s="138" t="str">
+        <f t="shared" si="5"/>
         <v>152OS00000</v>
       </c>
-      <c r="AA23" s="145" t="s">
+      <c r="AA23" s="138" t="s">
         <v>280</v>
       </c>
-      <c r="AB23" s="145" t="s">
+      <c r="AB23" s="138" t="s">
         <v>277</v>
       </c>
-      <c r="AC23" s="146">
-        <f t="shared" si="4"/>
+      <c r="AC23" s="163">
+        <f t="shared" si="3"/>
         <v>9000000000</v>
       </c>
-      <c r="AD23" s="168"/>
-      <c r="AF23" s="144" t="s">
+      <c r="AD23" s="175"/>
+      <c r="AF23" s="137" t="s">
         <v>276</v>
       </c>
-      <c r="AG23" s="160" t="str">
+      <c r="AG23" s="148" t="str">
         <f t="shared" si="1"/>
         <v>152OS00000</v>
       </c>
-      <c r="AH23" s="145" t="s">
+      <c r="AH23" s="138" t="s">
         <v>282</v>
       </c>
-      <c r="AI23" s="145" t="s">
+      <c r="AI23" s="138" t="s">
         <v>277</v>
       </c>
-      <c r="AJ23" s="146">
-        <f t="shared" si="7"/>
+      <c r="AJ23" s="163">
+        <f t="shared" si="6"/>
         <v>9000000003</v>
       </c>
-      <c r="AK23" s="256"/>
+      <c r="AK23" s="186"/>
     </row>
     <row r="24" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="Q24" s="163"/>
-      <c r="S24" s="166"/>
-      <c r="T24" s="142" t="s">
+      <c r="Q24" s="170"/>
+      <c r="S24" s="173"/>
+      <c r="T24" s="135" t="s">
         <v>271</v>
       </c>
-      <c r="U24" s="143" t="s">
+      <c r="U24" s="136" t="s">
         <v>272</v>
       </c>
-      <c r="V24" s="143" t="s">
+      <c r="V24" s="136" t="s">
         <v>201</v>
       </c>
-      <c r="W24" s="143" t="s">
+      <c r="W24" s="136" t="s">
         <v>275</v>
       </c>
-      <c r="Y24" s="144" t="s">
+      <c r="Y24" s="137" t="s">
         <v>276</v>
       </c>
-      <c r="Z24" s="145" t="str">
-        <f t="shared" si="6"/>
+      <c r="Z24" s="138" t="str">
+        <f t="shared" si="5"/>
         <v>152SF00000</v>
       </c>
-      <c r="AA24" s="145" t="s">
+      <c r="AA24" s="138" t="s">
         <v>280</v>
       </c>
-      <c r="AB24" s="145" t="s">
+      <c r="AB24" s="138" t="s">
         <v>277</v>
       </c>
-      <c r="AC24" s="146">
-        <f t="shared" si="4"/>
+      <c r="AC24" s="163">
+        <f t="shared" si="3"/>
         <v>9000000000</v>
       </c>
-      <c r="AD24" s="168"/>
-      <c r="AF24" s="144" t="s">
+      <c r="AD24" s="175"/>
+      <c r="AF24" s="137" t="s">
         <v>276</v>
       </c>
-      <c r="AG24" s="160" t="str">
+      <c r="AG24" s="148" t="str">
         <f t="shared" si="1"/>
         <v>152SF00000</v>
       </c>
-      <c r="AH24" s="145" t="s">
+      <c r="AH24" s="138" t="s">
         <v>282</v>
       </c>
-      <c r="AI24" s="145" t="s">
+      <c r="AI24" s="138" t="s">
         <v>277</v>
       </c>
-      <c r="AJ24" s="146">
-        <f t="shared" si="7"/>
+      <c r="AJ24" s="163">
+        <f t="shared" si="6"/>
         <v>9000000003</v>
       </c>
-      <c r="AK24" s="256"/>
+      <c r="AK24" s="186"/>
     </row>
     <row r="25" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="H25" s="85" t="s">
@@ -4403,59 +4436,59 @@
       <c r="P25" t="s">
         <v>157</v>
       </c>
-      <c r="Q25" s="164"/>
-      <c r="S25" s="166"/>
-      <c r="T25" s="142" t="s">
+      <c r="Q25" s="171"/>
+      <c r="S25" s="173"/>
+      <c r="T25" s="135" t="s">
         <v>273</v>
       </c>
-      <c r="U25" s="143" t="s">
+      <c r="U25" s="136" t="s">
         <v>274</v>
       </c>
-      <c r="V25" s="143" t="s">
+      <c r="V25" s="136" t="s">
         <v>201</v>
       </c>
-      <c r="W25" s="143" t="s">
+      <c r="W25" s="136" t="s">
         <v>275</v>
       </c>
-      <c r="Y25" s="147" t="s">
+      <c r="Y25" s="139" t="s">
         <v>276</v>
       </c>
-      <c r="Z25" s="148" t="str">
-        <f t="shared" si="6"/>
+      <c r="Z25" s="140" t="str">
+        <f t="shared" si="5"/>
         <v>152FG00000</v>
       </c>
-      <c r="AA25" s="148" t="s">
+      <c r="AA25" s="140" t="s">
         <v>280</v>
       </c>
-      <c r="AB25" s="148" t="s">
+      <c r="AB25" s="140" t="s">
         <v>277</v>
       </c>
-      <c r="AC25" s="149">
-        <f t="shared" si="4"/>
+      <c r="AC25" s="164">
+        <f t="shared" si="3"/>
         <v>9000000000</v>
       </c>
-      <c r="AD25" s="168"/>
-      <c r="AF25" s="147" t="s">
+      <c r="AD25" s="175"/>
+      <c r="AF25" s="139" t="s">
         <v>276</v>
       </c>
-      <c r="AG25" s="161" t="str">
+      <c r="AG25" s="149" t="str">
         <f t="shared" si="1"/>
         <v>152FG00000</v>
       </c>
-      <c r="AH25" s="148" t="s">
+      <c r="AH25" s="140" t="s">
         <v>282</v>
       </c>
-      <c r="AI25" s="148" t="s">
+      <c r="AI25" s="140" t="s">
         <v>277</v>
       </c>
-      <c r="AJ25" s="149">
-        <f t="shared" si="7"/>
+      <c r="AJ25" s="164">
+        <f t="shared" si="6"/>
         <v>9000000003</v>
       </c>
-      <c r="AK25" s="258"/>
+      <c r="AK25" s="187"/>
     </row>
     <row r="26" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="S26" s="170" t="s">
+      <c r="S26" s="177" t="s">
         <v>155</v>
       </c>
       <c r="T26" s="117" t="s">
@@ -4470,31 +4503,31 @@
       <c r="W26" s="113" t="s">
         <v>211</v>
       </c>
-      <c r="Y26" s="249"/>
-      <c r="Z26" s="250"/>
-      <c r="AA26" s="250"/>
-      <c r="AB26" s="250"/>
-      <c r="AC26" s="251"/>
-      <c r="AD26" s="168"/>
-      <c r="AF26" s="139" t="s">
+      <c r="Y26" s="150"/>
+      <c r="Z26" s="151"/>
+      <c r="AA26" s="151"/>
+      <c r="AB26" s="151"/>
+      <c r="AC26" s="152"/>
+      <c r="AD26" s="175"/>
+      <c r="AF26" s="133" t="s">
         <v>276</v>
       </c>
-      <c r="AG26" s="140" t="str">
+      <c r="AG26" s="134" t="str">
         <f t="shared" si="1"/>
         <v>705AW01000</v>
       </c>
-      <c r="AH26" s="140" t="s">
+      <c r="AH26" s="134" t="s">
         <v>280</v>
       </c>
-      <c r="AI26" s="140" t="s">
+      <c r="AI26" s="134" t="s">
         <v>277</v>
       </c>
-      <c r="AJ26" s="141">
+      <c r="AJ26" s="168">
         <f>$T$34</f>
         <v>9000000000</v>
       </c>
-      <c r="AK26" s="259" t="s">
-        <v>288</v>
+      <c r="AK26" s="184" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:37" x14ac:dyDescent="0.35">
@@ -4512,7 +4545,7 @@
       <c r="P27" t="s">
         <v>159</v>
       </c>
-      <c r="S27" s="172"/>
+      <c r="S27" s="179"/>
       <c r="T27" s="117" t="s">
         <v>259</v>
       </c>
@@ -4525,13 +4558,13 @@
       <c r="W27" s="113" t="s">
         <v>211</v>
       </c>
-      <c r="Y27" s="126"/>
-      <c r="Z27" s="252"/>
-      <c r="AA27" s="252"/>
-      <c r="AB27" s="252"/>
-      <c r="AC27" s="253"/>
-      <c r="AD27" s="168"/>
-      <c r="AF27" s="134" t="s">
+      <c r="Y27" s="123"/>
+      <c r="Z27" s="119"/>
+      <c r="AA27" s="119"/>
+      <c r="AB27" s="119"/>
+      <c r="AC27" s="153"/>
+      <c r="AD27" s="175"/>
+      <c r="AF27" s="130" t="s">
         <v>276</v>
       </c>
       <c r="AG27" s="107" t="str">
@@ -4544,11 +4577,11 @@
       <c r="AI27" s="107" t="s">
         <v>277</v>
       </c>
-      <c r="AJ27" s="135">
-        <f t="shared" ref="AJ27:AJ31" si="8">$T$34</f>
+      <c r="AJ27" s="165">
+        <f t="shared" ref="AJ27:AJ31" si="7">$T$34</f>
         <v>9000000000</v>
       </c>
-      <c r="AK27" s="168"/>
+      <c r="AK27" s="175"/>
     </row>
     <row r="28" spans="1:37" x14ac:dyDescent="0.35">
       <c r="H28" s="80" t="s">
@@ -4558,7 +4591,7 @@
         <v>150</v>
       </c>
       <c r="N28" s="90"/>
-      <c r="S28" s="172"/>
+      <c r="S28" s="179"/>
       <c r="T28" s="117" t="s">
         <v>251</v>
       </c>
@@ -4571,13 +4604,13 @@
       <c r="W28" s="113" t="s">
         <v>211</v>
       </c>
-      <c r="Y28" s="126"/>
-      <c r="Z28" s="252"/>
-      <c r="AA28" s="252"/>
-      <c r="AB28" s="252"/>
-      <c r="AC28" s="253"/>
-      <c r="AD28" s="168"/>
-      <c r="AF28" s="134" t="s">
+      <c r="Y28" s="123"/>
+      <c r="Z28" s="119"/>
+      <c r="AA28" s="119"/>
+      <c r="AB28" s="119"/>
+      <c r="AC28" s="153"/>
+      <c r="AD28" s="175"/>
+      <c r="AF28" s="130" t="s">
         <v>276</v>
       </c>
       <c r="AG28" s="107" t="str">
@@ -4590,11 +4623,11 @@
       <c r="AI28" s="107" t="s">
         <v>277</v>
       </c>
-      <c r="AJ28" s="135">
-        <f t="shared" si="8"/>
+      <c r="AJ28" s="165">
+        <f t="shared" si="7"/>
         <v>9000000000</v>
       </c>
-      <c r="AK28" s="168"/>
+      <c r="AK28" s="175"/>
     </row>
     <row r="29" spans="1:37" x14ac:dyDescent="0.35">
       <c r="H29" s="80" t="s">
@@ -4604,7 +4637,7 @@
         <v>152</v>
       </c>
       <c r="N29" s="90"/>
-      <c r="S29" s="172"/>
+      <c r="S29" s="179"/>
       <c r="T29" s="117" t="s">
         <v>253</v>
       </c>
@@ -4617,13 +4650,13 @@
       <c r="W29" s="113" t="s">
         <v>211</v>
       </c>
-      <c r="Y29" s="126"/>
-      <c r="Z29" s="252"/>
-      <c r="AA29" s="252"/>
-      <c r="AB29" s="252"/>
-      <c r="AC29" s="253"/>
-      <c r="AD29" s="168"/>
-      <c r="AF29" s="134" t="s">
+      <c r="Y29" s="123"/>
+      <c r="Z29" s="119"/>
+      <c r="AA29" s="119"/>
+      <c r="AB29" s="119"/>
+      <c r="AC29" s="153"/>
+      <c r="AD29" s="175"/>
+      <c r="AF29" s="130" t="s">
         <v>276</v>
       </c>
       <c r="AG29" s="107" t="str">
@@ -4636,11 +4669,11 @@
       <c r="AI29" s="107" t="s">
         <v>277</v>
       </c>
-      <c r="AJ29" s="135">
-        <f t="shared" si="8"/>
+      <c r="AJ29" s="165">
+        <f t="shared" si="7"/>
         <v>9000000000</v>
       </c>
-      <c r="AK29" s="168"/>
+      <c r="AK29" s="175"/>
     </row>
     <row r="30" spans="1:37" x14ac:dyDescent="0.35">
       <c r="H30" s="80" t="s">
@@ -4650,7 +4683,7 @@
         <v>153</v>
       </c>
       <c r="N30" s="90"/>
-      <c r="S30" s="172"/>
+      <c r="S30" s="179"/>
       <c r="T30" s="117" t="s">
         <v>257</v>
       </c>
@@ -4663,13 +4696,13 @@
       <c r="W30" s="113" t="s">
         <v>203</v>
       </c>
-      <c r="Y30" s="126"/>
-      <c r="Z30" s="252"/>
-      <c r="AA30" s="252"/>
-      <c r="AB30" s="252"/>
-      <c r="AC30" s="253"/>
-      <c r="AD30" s="168"/>
-      <c r="AF30" s="134" t="s">
+      <c r="Y30" s="123"/>
+      <c r="Z30" s="119"/>
+      <c r="AA30" s="119"/>
+      <c r="AB30" s="119"/>
+      <c r="AC30" s="153"/>
+      <c r="AD30" s="175"/>
+      <c r="AF30" s="130" t="s">
         <v>277</v>
       </c>
       <c r="AG30" s="107" t="str">
@@ -4682,11 +4715,11 @@
       <c r="AI30" s="107" t="s">
         <v>276</v>
       </c>
-      <c r="AJ30" s="135">
-        <f t="shared" si="8"/>
+      <c r="AJ30" s="165">
+        <f t="shared" si="7"/>
         <v>9000000000</v>
       </c>
-      <c r="AK30" s="168"/>
+      <c r="AK30" s="175"/>
     </row>
     <row r="31" spans="1:37" x14ac:dyDescent="0.35">
       <c r="H31" s="80" t="s">
@@ -4699,7 +4732,7 @@
         <v>150</v>
       </c>
       <c r="N31" s="90"/>
-      <c r="S31" s="171"/>
+      <c r="S31" s="178"/>
       <c r="T31" s="117" t="s">
         <v>255</v>
       </c>
@@ -4712,30 +4745,30 @@
       <c r="W31" s="113" t="s">
         <v>203</v>
       </c>
-      <c r="Y31" s="128"/>
-      <c r="Z31" s="129"/>
-      <c r="AA31" s="129"/>
-      <c r="AB31" s="129"/>
-      <c r="AC31" s="254"/>
-      <c r="AD31" s="169"/>
-      <c r="AF31" s="136" t="s">
+      <c r="Y31" s="125"/>
+      <c r="Z31" s="126"/>
+      <c r="AA31" s="126"/>
+      <c r="AB31" s="126"/>
+      <c r="AC31" s="154"/>
+      <c r="AD31" s="176"/>
+      <c r="AF31" s="131" t="s">
         <v>277</v>
       </c>
-      <c r="AG31" s="137" t="str">
+      <c r="AG31" s="132" t="str">
         <f t="shared" si="1"/>
         <v>810DQ00000</v>
       </c>
-      <c r="AH31" s="137" t="s">
+      <c r="AH31" s="132" t="s">
         <v>280</v>
       </c>
-      <c r="AI31" s="137" t="s">
+      <c r="AI31" s="132" t="s">
         <v>276</v>
       </c>
-      <c r="AJ31" s="138">
-        <f t="shared" si="8"/>
+      <c r="AJ31" s="166">
+        <f t="shared" si="7"/>
         <v>9000000000</v>
       </c>
-      <c r="AK31" s="169"/>
+      <c r="AK31" s="176"/>
     </row>
     <row r="32" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="H32" s="82" t="s">
@@ -4752,12 +4785,15 @@
       </c>
       <c r="N32" s="84"/>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="AF33" s="260" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="Y33" s="143" t="s">
+        <v>288</v>
+      </c>
+      <c r="AF33" s="143" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A34" s="92">
         <v>7</v>
       </c>
@@ -4770,10 +4806,10 @@
       </c>
       <c r="E34" s="93"/>
       <c r="F34" s="93"/>
-      <c r="S34" s="173" t="s">
+      <c r="S34" s="180" t="s">
         <v>217</v>
       </c>
-      <c r="T34" s="118">
+      <c r="T34" s="159">
         <v>9000000000</v>
       </c>
       <c r="U34" s="114" t="s">
@@ -4785,10 +4821,13 @@
       <c r="W34" s="114" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="S35" s="174"/>
-      <c r="T35" s="118">
+      <c r="AF34" s="143" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="35" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="S35" s="181"/>
+      <c r="T35" s="159">
         <v>9000000001</v>
       </c>
       <c r="U35" s="114" t="s">
@@ -4800,10 +4839,13 @@
       <c r="W35" s="114" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="S36" s="174"/>
-      <c r="T36" s="118">
+      <c r="AG35" s="143" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="S36" s="181"/>
+      <c r="T36" s="159">
         <v>9000000002</v>
       </c>
       <c r="U36" s="114" t="s">
@@ -4815,8 +4857,11 @@
       <c r="W36" s="114" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AG36" s="143" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="37" spans="1:33" x14ac:dyDescent="0.35">
       <c r="B37" s="95" t="s">
         <v>166</v>
       </c>
@@ -4832,8 +4877,8 @@
       <c r="K37" s="96"/>
       <c r="L37" s="96"/>
       <c r="M37" s="97"/>
-      <c r="S37" s="174"/>
-      <c r="T37" s="118">
+      <c r="S37" s="181"/>
+      <c r="T37" s="159">
         <v>9000000003</v>
       </c>
       <c r="U37" s="114" t="s">
@@ -4845,8 +4890,11 @@
       <c r="W37" s="114" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AG37" s="143" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="38" spans="1:33" x14ac:dyDescent="0.35">
       <c r="B38" s="98">
         <v>1</v>
       </c>
@@ -4861,8 +4909,8 @@
         <v>179</v>
       </c>
       <c r="M38" s="99"/>
-      <c r="S38" s="174"/>
-      <c r="T38" s="118">
+      <c r="S38" s="181"/>
+      <c r="T38" s="159">
         <v>9000000004</v>
       </c>
       <c r="U38" s="114" t="s">
@@ -4874,8 +4922,11 @@
       <c r="W38" s="114" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AG38" s="143" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="39" spans="1:33" x14ac:dyDescent="0.35">
       <c r="B39" s="98"/>
       <c r="D39" s="107" t="s">
         <v>195</v>
@@ -4893,8 +4944,8 @@
       <c r="M39" s="106" t="s">
         <v>170</v>
       </c>
-      <c r="S39" s="174"/>
-      <c r="T39" s="118">
+      <c r="S39" s="181"/>
+      <c r="T39" s="159">
         <v>9000000005</v>
       </c>
       <c r="U39" s="114" t="s">
@@ -4906,8 +4957,11 @@
       <c r="W39" s="114" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AG39" s="143" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="40" spans="1:33" x14ac:dyDescent="0.35">
       <c r="B40" s="98">
         <v>2</v>
       </c>
@@ -4922,8 +4976,8 @@
         <v>181</v>
       </c>
       <c r="M40" s="99"/>
-      <c r="S40" s="175"/>
-      <c r="T40" s="118">
+      <c r="S40" s="182"/>
+      <c r="T40" s="159">
         <v>9000000006</v>
       </c>
       <c r="U40" s="114" t="s">
@@ -4935,8 +4989,11 @@
       <c r="W40" s="114" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AG40" s="143" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="41" spans="1:33" x14ac:dyDescent="0.35">
       <c r="B41" s="98"/>
       <c r="D41" s="107" t="s">
         <v>171</v>
@@ -4955,7 +5012,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.35">
       <c r="B42" s="98">
         <v>3</v>
       </c>
@@ -4971,7 +5028,7 @@
       </c>
       <c r="M42" s="99"/>
     </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.35">
       <c r="B43" s="98"/>
       <c r="D43" s="107" t="s">
         <v>197</v>
@@ -4990,7 +5047,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="44" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.35">
       <c r="B44" s="98">
         <v>4</v>
       </c>
@@ -5006,7 +5063,7 @@
       </c>
       <c r="M44" s="99"/>
     </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.35">
       <c r="B45" s="98"/>
       <c r="D45" s="107" t="s">
         <v>174</v>
@@ -5021,7 +5078,7 @@
       </c>
       <c r="M45" s="99"/>
     </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.35">
       <c r="B46" s="98">
         <v>5</v>
       </c>
@@ -5037,7 +5094,7 @@
       </c>
       <c r="M46" s="99"/>
     </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.35">
       <c r="B47" s="98"/>
       <c r="D47" s="107" t="s">
         <v>198</v>
@@ -5056,7 +5113,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.35">
       <c r="B48" s="98">
         <v>6</v>
       </c>
@@ -5155,30 +5212,31 @@
       <c r="M53" s="102"/>
     </row>
     <row r="55" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B55" s="165" t="s">
+      <c r="B55" s="172" t="s">
         <v>186</v>
       </c>
-      <c r="C55" s="165"/>
-      <c r="D55" s="165"/>
-      <c r="E55" s="165"/>
-      <c r="F55" s="165"/>
-      <c r="G55" s="165"/>
-      <c r="H55" s="165"/>
-      <c r="I55" s="165"/>
-      <c r="J55" s="165"/>
-      <c r="K55" s="165"/>
-      <c r="L55" s="165"/>
-      <c r="M55" s="165"/>
+      <c r="C55" s="172"/>
+      <c r="D55" s="172"/>
+      <c r="E55" s="172"/>
+      <c r="F55" s="172"/>
+      <c r="G55" s="172"/>
+      <c r="H55" s="172"/>
+      <c r="I55" s="172"/>
+      <c r="J55" s="172"/>
+      <c r="K55" s="172"/>
+      <c r="L55" s="172"/>
+      <c r="M55" s="172"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="18">
     <mergeCell ref="AD4:AD31"/>
-    <mergeCell ref="AK4:AK9"/>
     <mergeCell ref="AK10:AK11"/>
     <mergeCell ref="AK12:AK13"/>
     <mergeCell ref="AK14:AK17"/>
     <mergeCell ref="AK18:AK25"/>
     <mergeCell ref="AK26:AK31"/>
+    <mergeCell ref="AK4:AK7"/>
+    <mergeCell ref="AK8:AK9"/>
     <mergeCell ref="S4:S7"/>
     <mergeCell ref="S8:S9"/>
     <mergeCell ref="S16:S25"/>
@@ -5203,10 +5261,10 @@
   <cols>
     <col min="1" max="1" width="9.26953125" style="1"/>
     <col min="2" max="2" width="10.81640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="84.08984375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20.6328125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="17.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.08984375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="84.1796875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.54296875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.1796875" style="2" customWidth="1"/>
     <col min="7" max="7" width="27.26953125" style="1" customWidth="1"/>
     <col min="8" max="12" width="9.26953125" style="1"/>
     <col min="13" max="13" width="48.26953125" style="1" bestFit="1" customWidth="1"/>
@@ -5215,14 +5273,14 @@
   <sheetData>
     <row r="1" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:20" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="203" t="s">
+      <c r="B2" s="215" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="204"/>
-      <c r="D2" s="197" t="s">
+      <c r="C2" s="216"/>
+      <c r="D2" s="209" t="s">
         <v>121</v>
       </c>
-      <c r="E2" s="199" t="s">
+      <c r="E2" s="211" t="s">
         <v>117</v>
       </c>
       <c r="F2" s="1"/>
@@ -5235,10 +5293,10 @@
       <c r="M2" s="8"/>
     </row>
     <row r="3" spans="2:20" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="205"/>
-      <c r="C3" s="206"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="200"/>
+      <c r="B3" s="217"/>
+      <c r="C3" s="218"/>
+      <c r="D3" s="210"/>
+      <c r="E3" s="212"/>
       <c r="F3" s="1"/>
       <c r="G3" s="10" t="s">
         <v>17</v>
@@ -5249,7 +5307,7 @@
       <c r="K3" s="2"/>
     </row>
     <row r="4" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B4" s="194" t="s">
+      <c r="B4" s="206" t="s">
         <v>86</v>
       </c>
       <c r="C4" s="54" t="s">
@@ -5258,7 +5316,7 @@
       <c r="D4" s="75" t="s">
         <v>122</v>
       </c>
-      <c r="E4" s="208" t="s">
+      <c r="E4" s="220" t="s">
         <v>81</v>
       </c>
       <c r="F4" s="1"/>
@@ -5282,12 +5340,12 @@
       <c r="T4" s="17"/>
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B5" s="201"/>
+      <c r="B5" s="213"/>
       <c r="C5" s="40" t="s">
         <v>90</v>
       </c>
       <c r="D5" s="9"/>
-      <c r="E5" s="209"/>
+      <c r="E5" s="221"/>
       <c r="F5"/>
       <c r="G5" s="48"/>
       <c r="H5" s="10" t="s">
@@ -5297,12 +5355,12 @@
       <c r="T5" s="19"/>
     </row>
     <row r="6" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="207"/>
+      <c r="B6" s="219"/>
       <c r="C6" s="55" t="s">
         <v>91</v>
       </c>
       <c r="D6" s="65"/>
-      <c r="E6" s="210"/>
+      <c r="E6" s="222"/>
       <c r="F6"/>
       <c r="G6" s="48"/>
       <c r="H6" s="10" t="s">
@@ -5312,16 +5370,16 @@
       <c r="T6" s="19"/>
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B7" s="194" t="s">
+      <c r="B7" s="206" t="s">
         <v>87</v>
       </c>
       <c r="C7" s="54" t="s">
         <v>92</v>
       </c>
-      <c r="D7" s="185" t="s">
+      <c r="D7" s="197" t="s">
         <v>127</v>
       </c>
-      <c r="E7" s="182" t="s">
+      <c r="E7" s="194" t="s">
         <v>81</v>
       </c>
       <c r="F7"/>
@@ -5343,12 +5401,12 @@
       <c r="T7" s="31"/>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B8" s="201"/>
+      <c r="B8" s="213"/>
       <c r="C8" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="D8" s="186"/>
-      <c r="E8" s="183"/>
+      <c r="D8" s="198"/>
+      <c r="E8" s="195"/>
       <c r="F8"/>
       <c r="G8" s="46" t="s">
         <v>18</v>
@@ -5360,12 +5418,12 @@
       <c r="T8" s="19"/>
     </row>
     <row r="9" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="202"/>
+      <c r="B9" s="214"/>
       <c r="C9" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="D9" s="187"/>
-      <c r="E9" s="184"/>
+      <c r="D9" s="199"/>
+      <c r="E9" s="196"/>
       <c r="F9"/>
       <c r="G9" s="46"/>
       <c r="H9" s="20" t="s">
@@ -5375,7 +5433,7 @@
       <c r="T9" s="19"/>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B10" s="194" t="s">
+      <c r="B10" s="206" t="s">
         <v>88</v>
       </c>
       <c r="C10" s="73" t="s">
@@ -5384,7 +5442,7 @@
       <c r="D10" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="E10" s="188" t="s">
+      <c r="E10" s="200" t="s">
         <v>81</v>
       </c>
       <c r="F10"/>
@@ -5396,12 +5454,12 @@
       <c r="T10" s="19"/>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B11" s="195"/>
+      <c r="B11" s="207"/>
       <c r="C11" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="D11" s="179"/>
-      <c r="E11" s="189"/>
+      <c r="D11" s="191"/>
+      <c r="E11" s="201"/>
       <c r="F11"/>
       <c r="G11" s="48"/>
       <c r="H11" s="24" t="s">
@@ -5421,12 +5479,12 @@
       <c r="T11" s="31"/>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B12" s="195"/>
+      <c r="B12" s="207"/>
       <c r="C12" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="180"/>
-      <c r="E12" s="189"/>
+      <c r="D12" s="192"/>
+      <c r="E12" s="201"/>
       <c r="F12"/>
       <c r="G12" s="46" t="s">
         <v>28</v>
@@ -5438,12 +5496,12 @@
       <c r="T12" s="19"/>
     </row>
     <row r="13" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="196"/>
+      <c r="B13" s="208"/>
       <c r="C13" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="181"/>
-      <c r="E13" s="190"/>
+      <c r="D13" s="193"/>
+      <c r="E13" s="202"/>
       <c r="F13" s="1"/>
       <c r="G13" s="21"/>
       <c r="H13" s="25" t="s">
@@ -5479,7 +5537,7 @@
       <c r="C16" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="D16" s="191">
+      <c r="D16" s="203">
         <v>2025</v>
       </c>
       <c r="E16" s="43" t="s">
@@ -5491,8 +5549,8 @@
       <c r="C17" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="D17" s="192"/>
-      <c r="E17" s="178" t="s">
+      <c r="D17" s="204"/>
+      <c r="E17" s="190" t="s">
         <v>118</v>
       </c>
       <c r="F17" s="1"/>
@@ -5501,8 +5559,8 @@
       <c r="C18" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="D18" s="193"/>
-      <c r="E18" s="178"/>
+      <c r="D18" s="205"/>
+      <c r="E18" s="190"/>
       <c r="F18" s="1"/>
     </row>
     <row r="19" spans="3:6" x14ac:dyDescent="0.35">
@@ -5512,7 +5570,7 @@
       <c r="C20" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="D20" s="176">
+      <c r="D20" s="188">
         <v>2026</v>
       </c>
       <c r="E20" s="43" t="s">
@@ -5524,7 +5582,7 @@
       <c r="C21" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="D21" s="177"/>
+      <c r="D21" s="189"/>
       <c r="E21" s="67" t="s">
         <v>119</v>
       </c>
@@ -5607,13 +5665,13 @@
   <cols>
     <col min="1" max="1" width="9.26953125" style="1"/>
     <col min="2" max="2" width="10.81640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="68.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.6328125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="22.90625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="19.6328125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="68.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.54296875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="22.81640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19.54296875" style="2" customWidth="1"/>
     <col min="7" max="7" width="26.54296875" style="2" customWidth="1"/>
     <col min="8" max="8" width="9.26953125" style="1"/>
-    <col min="9" max="9" width="9.08984375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="9.1796875" style="2" customWidth="1"/>
     <col min="10" max="10" width="27.26953125" style="1" customWidth="1"/>
     <col min="11" max="15" width="9.26953125" style="1"/>
     <col min="16" max="16" width="48.26953125" style="1" bestFit="1" customWidth="1"/>
@@ -5621,18 +5679,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:24" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="211" t="s">
+      <c r="B2" s="223" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="211"/>
-      <c r="D2" s="234" t="s">
+      <c r="C2" s="223"/>
+      <c r="D2" s="246" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="235"/>
-      <c r="F2" s="236" t="s">
+      <c r="E2" s="247"/>
+      <c r="F2" s="248" t="s">
         <v>80</v>
       </c>
-      <c r="G2" s="237"/>
+      <c r="G2" s="249"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
         <v>79</v>
@@ -5645,8 +5703,8 @@
       </c>
     </row>
     <row r="3" spans="2:24" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="212"/>
-      <c r="C3" s="212"/>
+      <c r="B3" s="224"/>
+      <c r="C3" s="224"/>
       <c r="D3" s="56" t="s">
         <v>22</v>
       </c>
@@ -5669,7 +5727,7 @@
       <c r="N3" s="2"/>
     </row>
     <row r="4" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="213" t="s">
+      <c r="B4" s="225" t="s">
         <v>86</v>
       </c>
       <c r="C4" s="70" t="s">
@@ -5692,14 +5750,14 @@
       <c r="M4" s="2"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="B5" s="214"/>
+      <c r="B5" s="226"/>
       <c r="C5" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="233" t="s">
+      <c r="D5" s="245" t="s">
         <v>108</v>
       </c>
-      <c r="E5" s="233"/>
+      <c r="E5" s="245"/>
       <c r="F5" s="43" t="s">
         <v>85</v>
       </c>
@@ -5730,14 +5788,14 @@
       <c r="X5" s="17"/>
     </row>
     <row r="6" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="215"/>
+      <c r="B6" s="227"/>
       <c r="C6" s="69" t="s">
         <v>91</v>
       </c>
-      <c r="D6" s="232" t="s">
+      <c r="D6" s="244" t="s">
         <v>108</v>
       </c>
-      <c r="E6" s="232"/>
+      <c r="E6" s="244"/>
       <c r="F6" s="60" t="s">
         <v>83</v>
       </c>
@@ -5753,18 +5811,18 @@
       <c r="X6" s="19"/>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="B7" s="216" t="s">
+      <c r="B7" s="228" t="s">
         <v>87</v>
       </c>
       <c r="C7" s="64" t="s">
         <v>92</v>
       </c>
-      <c r="D7" s="238" t="s">
+      <c r="D7" s="250" t="s">
         <v>81</v>
       </c>
-      <c r="E7" s="239"/>
-      <c r="F7" s="239"/>
-      <c r="G7" s="240"/>
+      <c r="E7" s="251"/>
+      <c r="F7" s="251"/>
+      <c r="G7" s="252"/>
       <c r="I7" s="1"/>
       <c r="J7" s="46"/>
       <c r="K7" s="24" t="s">
@@ -5785,16 +5843,16 @@
       <c r="X7" s="31"/>
     </row>
     <row r="8" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="B8" s="201"/>
+      <c r="B8" s="213"/>
       <c r="C8" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="D8" s="241" t="s">
+      <c r="D8" s="253" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="242"/>
-      <c r="F8" s="242"/>
-      <c r="G8" s="243"/>
+      <c r="E8" s="254"/>
+      <c r="F8" s="254"/>
+      <c r="G8" s="255"/>
       <c r="I8" s="1"/>
       <c r="J8" s="46" t="s">
         <v>18</v>
@@ -5806,16 +5864,16 @@
       <c r="X8" s="19"/>
     </row>
     <row r="9" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="207"/>
+      <c r="B9" s="219"/>
       <c r="C9" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="D9" s="244" t="s">
+      <c r="D9" s="256" t="s">
         <v>81</v>
       </c>
-      <c r="E9" s="245"/>
-      <c r="F9" s="245"/>
-      <c r="G9" s="246"/>
+      <c r="E9" s="257"/>
+      <c r="F9" s="257"/>
+      <c r="G9" s="258"/>
       <c r="I9" s="1"/>
       <c r="J9" s="46"/>
       <c r="K9" s="20" t="s">
@@ -5825,18 +5883,18 @@
       <c r="X9" s="19"/>
     </row>
     <row r="10" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="B10" s="194" t="s">
+      <c r="B10" s="206" t="s">
         <v>88</v>
       </c>
       <c r="C10" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="217" t="s">
+      <c r="D10" s="229" t="s">
         <v>81</v>
       </c>
-      <c r="E10" s="218"/>
-      <c r="F10" s="218"/>
-      <c r="G10" s="219"/>
+      <c r="E10" s="230"/>
+      <c r="F10" s="230"/>
+      <c r="G10" s="231"/>
       <c r="I10" s="1"/>
       <c r="J10" s="46"/>
       <c r="K10" s="35" t="s">
@@ -5857,14 +5915,14 @@
       <c r="X10" s="38"/>
     </row>
     <row r="11" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="B11" s="201"/>
+      <c r="B11" s="213"/>
       <c r="C11" s="49" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="220"/>
-      <c r="E11" s="221"/>
-      <c r="F11" s="221"/>
-      <c r="G11" s="222"/>
+      <c r="D11" s="232"/>
+      <c r="E11" s="233"/>
+      <c r="F11" s="233"/>
+      <c r="G11" s="234"/>
       <c r="I11" s="1"/>
       <c r="J11" s="46" t="s">
         <v>28</v>
@@ -5876,18 +5934,18 @@
       <c r="X11" s="19"/>
     </row>
     <row r="12" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="201"/>
+      <c r="B12" s="213"/>
       <c r="C12" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="D12" s="229" t="s">
+      <c r="D12" s="241" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="179"/>
-      <c r="F12" s="223" t="s">
+      <c r="E12" s="191"/>
+      <c r="F12" s="235" t="s">
         <v>81</v>
       </c>
-      <c r="G12" s="224"/>
+      <c r="G12" s="236"/>
       <c r="I12" s="1"/>
       <c r="J12" s="47"/>
       <c r="K12" s="25" t="s">
@@ -5908,14 +5966,14 @@
       <c r="X12" s="29"/>
     </row>
     <row r="13" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="B13" s="201"/>
+      <c r="B13" s="213"/>
       <c r="C13" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="D13" s="230"/>
-      <c r="E13" s="180"/>
-      <c r="F13" s="225"/>
-      <c r="G13" s="226"/>
+      <c r="D13" s="242"/>
+      <c r="E13" s="192"/>
+      <c r="F13" s="237"/>
+      <c r="G13" s="238"/>
       <c r="I13" s="1" t="s">
         <v>23</v>
       </c>
@@ -5940,14 +5998,14 @@
       <c r="X13" s="17"/>
     </row>
     <row r="14" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="B14" s="201"/>
+      <c r="B14" s="213"/>
       <c r="C14" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="230"/>
-      <c r="E14" s="180"/>
-      <c r="F14" s="225"/>
-      <c r="G14" s="226"/>
+      <c r="D14" s="242"/>
+      <c r="E14" s="192"/>
+      <c r="F14" s="237"/>
+      <c r="G14" s="238"/>
       <c r="I14" s="1"/>
       <c r="J14" s="48"/>
       <c r="K14" s="10" t="s">
@@ -5957,14 +6015,14 @@
       <c r="X14" s="19"/>
     </row>
     <row r="15" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="207"/>
+      <c r="B15" s="219"/>
       <c r="C15" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="D15" s="231"/>
-      <c r="E15" s="181"/>
-      <c r="F15" s="227"/>
-      <c r="G15" s="228"/>
+      <c r="D15" s="243"/>
+      <c r="E15" s="193"/>
+      <c r="F15" s="239"/>
+      <c r="G15" s="240"/>
       <c r="I15" s="1"/>
       <c r="J15" s="48"/>
       <c r="K15" s="10" t="s">
@@ -6310,21 +6368,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B2" s="211" t="s">
+      <c r="B2" s="223" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="248" t="s">
+      <c r="C2" s="260" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="236">
+      <c r="D2" s="248">
         <v>46203</v>
       </c>
-      <c r="E2" s="247"/>
-      <c r="F2" s="237"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="249"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B3" s="211"/>
-      <c r="C3" s="248"/>
+      <c r="B3" s="223"/>
+      <c r="C3" s="260"/>
       <c r="D3" s="7" t="s">
         <v>6</v>
       </c>
@@ -6770,7 +6828,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="2.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.81640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -6930,17 +6988,16 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="24.1796875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.54296875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.1796875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="30.9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="31" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>32</v>
       </c>

--- a/DCT - Guide/Migration Approach.xlsx
+++ b/DCT - Guide/Migration Approach.xlsx
@@ -5,20 +5,21 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\70023796\Desktop\Project\Main_Link\RepoGit\Additional\DCT - Guide\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\70023796\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D664F6B-F89F-4C5A-8A3D-5872CF68DE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA65659D-A77D-4E0E-97B2-971C319EC073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{7CAA1510-BEF0-44FB-B9DF-6BA498C876D6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{7CAA1510-BEF0-44FB-B9DF-6BA498C876D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Recap" sheetId="6" r:id="rId1"/>
-    <sheet name="Opt3 (Final)" sheetId="5" r:id="rId2"/>
-    <sheet name="Opt3" sheetId="4" r:id="rId3"/>
-    <sheet name="Strategy Options" sheetId="1" r:id="rId4"/>
-    <sheet name="LSMW Table" sheetId="2" r:id="rId5"/>
-    <sheet name="LSMW Temp" sheetId="3" r:id="rId6"/>
+    <sheet name="Reversal Scenarios" sheetId="7" r:id="rId2"/>
+    <sheet name="Opt3 (Final)" sheetId="5" r:id="rId3"/>
+    <sheet name="Opt3" sheetId="4" r:id="rId4"/>
+    <sheet name="Strategy Options" sheetId="1" r:id="rId5"/>
+    <sheet name="LSMW Table" sheetId="2" r:id="rId6"/>
+    <sheet name="LSMW Temp" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -82,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="350">
   <si>
     <t>Asset Cumulative values (Acquisition + Accum. Depreciation)</t>
   </si>
@@ -1130,28 +1131,12 @@
     <t>Material</t>
   </si>
   <si>
-    <t>Post on 31-Dec-2025 then reverse on 30-June-2026</t>
-  </si>
-  <si>
-    <t>Auto Post based on config for RED GLACs</t>
-  </si>
-  <si>
-    <t>GL Template</t>
-  </si>
-  <si>
     <t>WBS migration will use custom template specifically designed for Project migration</t>
   </si>
   <si>
     <t>Cross Workstream</t>
   </si>
   <si>
-    <t>Use F.80 or upload LTMC with opposite sign to reverse</t>
-  </si>
-  <si>
-    <t>GL Template
-(Enter Dummy WBS if project-related)</t>
-  </si>
-  <si>
     <t>Project migration program will transfer the WBS info between Dummy WBS -&gt; Real WBS</t>
   </si>
   <si>
@@ -1173,19 +1158,497 @@
     <t>Cr Input Cost (Dummy WBS)</t>
   </si>
   <si>
-    <t>Open AR Template
-(Enter Dummy WBS if project-related)</t>
-  </si>
-  <si>
-    <t>Open AP Template
-(Enter Dummy WBS if project-related)</t>
+    <t>Dr/Cr 9*1 -&gt; Cr/Dr 9*0</t>
+  </si>
+  <si>
+    <t>Cr 900000001 / Dr 90000000</t>
+  </si>
+  <si>
+    <t>Dr/Cr 9*2 -&gt; Cr/Dr 9*0</t>
+  </si>
+  <si>
+    <t>Dr 900000002 / Cr 90000000</t>
+  </si>
+  <si>
+    <t>Dr/Cr 9*3 -&gt; Cr/Dr 9*0</t>
+  </si>
+  <si>
+    <t>Dr 900000003 / Cr 90000000</t>
+  </si>
+  <si>
+    <t>Dr/Cr 9*4 -&gt; Cr/Dr 9*0</t>
+  </si>
+  <si>
+    <t>Dr 900000004 / Cr 90000000</t>
+  </si>
+  <si>
+    <t>FA</t>
+  </si>
+  <si>
+    <t>Dr/Cr 9*5 -&gt; Cr/Dr 9*0</t>
+  </si>
+  <si>
+    <t>Dr 900000005 / Cr 90000000</t>
+  </si>
+  <si>
+    <t>AP Downpayment</t>
+  </si>
+  <si>
+    <t>Dr/Cr 9*6 -&gt; Cr/Dr 9*0</t>
+  </si>
+  <si>
+    <t>Cr 900000006 / Dr 90000000</t>
+  </si>
+  <si>
+    <t>AR Downpayment</t>
+  </si>
+  <si>
+    <t>RED GLACs are Auto Posted based on config</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GL Template
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_Transactional details</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Asset Template
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_Ending Balances only</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Open AR Template
+_Enter Dummy WBS if project-related
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_Open items at 30-June-2026 only</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GL Template
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_Ending Balances only</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Open AP Template
+_Enter Dummy WBS if project-related
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_Open items at 30-June-2026 only</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GL Template
+_Enter Dummy WBS if project-related
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_Open items at 30-June-2026 only</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GL Template
+_Enter Dummy WBS if project-related
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_Transactional details</t>
+    </r>
+  </si>
+  <si>
+    <t>31.01.2026</t>
+  </si>
+  <si>
+    <t>2nd Cleared</t>
+  </si>
+  <si>
+    <t>Transaction</t>
+  </si>
+  <si>
+    <t>1st Cleared</t>
+  </si>
+  <si>
+    <t>31.12.2025</t>
+  </si>
+  <si>
+    <t>GL</t>
+  </si>
+  <si>
+    <t>2nd Trans</t>
+  </si>
+  <si>
+    <t>1st Trans</t>
+  </si>
+  <si>
+    <t>Open AR
+Open AP</t>
+  </si>
+  <si>
+    <t>Fiscal Year</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Posting Date</t>
+  </si>
+  <si>
+    <t>3rd Additional Open</t>
+  </si>
+  <si>
+    <t>3rd Trans</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Open AR per </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Migration GLACs 9*1/9*5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Open AP per </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Migration GLACs 9*2/9*6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Open AR per </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Customer No.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Open AP per </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Vendor No.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Inventory per</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Material No.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Asset per </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Asset No.</t>
+    </r>
+  </si>
+  <si>
+    <t>Post on 31-Dec-2025 then reverse on 30-June-2026 (Refer to Reversal Scenarios Sheet)</t>
+  </si>
+  <si>
+    <r>
+      <t>Use F.80/LTMC w. opposite sign to reverse</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Excl. Non-Open BS not related to Inventory)</t>
+    </r>
+  </si>
+  <si>
+    <t>P&amp;L GLAC 1</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3rd Trans </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P&amp;L GLAC 1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2nd Trans </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P&amp;L GLAC 1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1st Trans </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P&amp;L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GLAC 1</t>
+    </r>
+  </si>
+  <si>
+    <t>BS Open item GLAC 1</t>
+  </si>
+  <si>
+    <t>BS Non-Open item GLAC 1</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inventory per </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GLACs</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Asset per </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GLACs (Acquisition + Accum. Dep)</t>
+    </r>
+  </si>
+  <si>
+    <t>9*0</t>
+  </si>
+  <si>
+    <t>Offsetting</t>
+  </si>
+  <si>
+    <t>9*2 for AR
+9*1 for AP</t>
+  </si>
+  <si>
+    <t>9*3</t>
+  </si>
+  <si>
+    <t>9*4</t>
+  </si>
+  <si>
+    <t>REVERSAL
+on 31.01.2026</t>
+  </si>
+  <si>
+    <t>NO REVERSAL
+on 31.01.2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1309,8 +1772,126 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="7" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1371,8 +1952,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="57">
+  <borders count="60">
     <border>
       <left/>
       <right/>
@@ -2056,11 +2649,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="263">
+  <cellXfs count="307">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2283,127 +2913,378 @@
     <xf numFmtId="14" fontId="11" fillId="6" borderId="32" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="55" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="55" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="55" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="56" xfId="0" applyFill="1" applyBorder="1"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2414,7 +3295,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2444,75 +3325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="47" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="49" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="48" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="6" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="6" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="6" borderId="29" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2566,6 +3378,60 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="47" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="49" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="48" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="6" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="6" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="6" borderId="29" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2680,8 +3546,66 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3121,2132 +4045,2208 @@
   <dimension ref="A2:AK55"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.54296875" customWidth="1"/>
-    <col min="5" max="5" width="16.54296875" customWidth="1"/>
-    <col min="6" max="6" width="18.54296875" customWidth="1"/>
-    <col min="10" max="10" width="12.453125" customWidth="1"/>
-    <col min="11" max="11" width="18.7265625" customWidth="1"/>
-    <col min="12" max="12" width="17.453125" customWidth="1"/>
-    <col min="13" max="13" width="18.81640625" customWidth="1"/>
-    <col min="14" max="14" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.26953125" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" style="1"/>
+    <col min="2" max="2" width="14.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" style="1"/>
+    <col min="4" max="4" width="21.54296875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.54296875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.54296875" style="1" customWidth="1"/>
+    <col min="7" max="9" width="8.7265625" style="1"/>
+    <col min="10" max="10" width="12.453125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.7265625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.453125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="18.81640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="13.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="8.7265625" style="1"/>
+    <col min="17" max="17" width="13.26953125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="8.7265625" style="1"/>
     <col min="19" max="19" width="13.1796875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="12.1796875" style="109" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="47.453125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.7265625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.453125" customWidth="1"/>
-    <col min="25" max="25" width="5.7265625" customWidth="1"/>
-    <col min="26" max="26" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.81640625" style="109" customWidth="1"/>
-    <col min="32" max="32" width="6.1796875" customWidth="1"/>
-    <col min="33" max="33" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="35.81640625" style="109" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="47.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.453125" style="1" customWidth="1"/>
+    <col min="24" max="24" width="8.7265625" style="1"/>
+    <col min="25" max="25" width="5.7265625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="21.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="2.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="22.1796875" style="2" customWidth="1"/>
+    <col min="31" max="31" width="8.7265625" style="1"/>
+    <col min="32" max="32" width="6.1796875" style="1" customWidth="1"/>
+    <col min="33" max="33" width="18.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="9.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="2.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="35.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="Y2" s="156">
+    <row r="2" spans="19:37" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Y2" s="78">
         <v>2025</v>
       </c>
-      <c r="Z2" s="143" t="s">
-        <v>283</v>
-      </c>
-      <c r="AF2" s="156">
+      <c r="Z2" s="79" t="s">
+        <v>333</v>
+      </c>
+      <c r="AF2" s="78">
         <v>2026</v>
       </c>
-      <c r="AG2" s="143" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="3" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="S3" s="110" t="s">
+      <c r="AG2" s="79" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="3" spans="19:37" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="S3" s="77" t="s">
         <v>232</v>
       </c>
-      <c r="T3" s="115" t="s">
+      <c r="T3" s="77" t="s">
         <v>199</v>
       </c>
-      <c r="U3" s="111" t="s">
+      <c r="U3" s="80" t="s">
         <v>214</v>
       </c>
-      <c r="V3" s="111" t="s">
+      <c r="V3" s="80" t="s">
         <v>200</v>
       </c>
-      <c r="W3" s="111" t="s">
+      <c r="W3" s="80" t="s">
         <v>206</v>
       </c>
-      <c r="Z3" s="76" t="s">
+      <c r="Y3" s="112"/>
+      <c r="Z3" s="113" t="s">
         <v>279</v>
       </c>
-      <c r="AA3" s="76" t="s">
+      <c r="AA3" s="113" t="s">
         <v>206</v>
       </c>
-      <c r="AC3" s="76" t="s">
+      <c r="AB3" s="112"/>
+      <c r="AC3" s="113" t="s">
         <v>278</v>
       </c>
-      <c r="AD3" s="155" t="s">
+      <c r="AD3" s="114" t="s">
         <v>81</v>
       </c>
-      <c r="AG3" s="76" t="s">
+      <c r="AF3" s="112"/>
+      <c r="AG3" s="113" t="s">
         <v>281</v>
       </c>
-      <c r="AH3" s="76" t="s">
+      <c r="AH3" s="113" t="s">
         <v>206</v>
       </c>
-      <c r="AJ3" s="76" t="s">
+      <c r="AI3" s="112"/>
+      <c r="AJ3" s="113" t="s">
         <v>278</v>
       </c>
-      <c r="AK3" s="155" t="s">
+      <c r="AK3" s="114" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="S4" s="174" t="s">
+    <row r="4" spans="19:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S4" s="205" t="s">
         <v>243</v>
       </c>
-      <c r="T4" s="116" t="s">
+      <c r="T4" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="U4" s="112" t="s">
+      <c r="U4" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="W4" s="112" t="s">
+      <c r="W4" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="Y4" s="121" t="s">
+      <c r="Y4" s="116" t="s">
         <v>276</v>
       </c>
-      <c r="Z4" s="122" t="str">
+      <c r="Z4" s="117" t="str">
         <f>T4</f>
         <v>100CP02C00</v>
       </c>
-      <c r="AA4" s="122" t="s">
+      <c r="AA4" s="117" t="s">
         <v>280</v>
       </c>
-      <c r="AB4" s="122" t="s">
+      <c r="AB4" s="117" t="s">
         <v>277</v>
       </c>
-      <c r="AC4" s="160">
+      <c r="AC4" s="118">
         <f>$T$34</f>
         <v>9000000000</v>
       </c>
-      <c r="AD4" s="174" t="s">
-        <v>285</v>
-      </c>
-      <c r="AF4" s="121" t="s">
+      <c r="AD4" s="191" t="s">
+        <v>311</v>
+      </c>
+      <c r="AF4" s="116" t="s">
         <v>276</v>
       </c>
-      <c r="AG4" s="144" t="str">
+      <c r="AG4" s="150" t="str">
         <f>T4</f>
         <v>100CP02C00</v>
       </c>
-      <c r="AH4" s="122" t="s">
+      <c r="AH4" s="117" t="s">
         <v>86</v>
       </c>
-      <c r="AI4" s="122" t="s">
+      <c r="AI4" s="117" t="s">
         <v>277</v>
       </c>
-      <c r="AJ4" s="160">
+      <c r="AJ4" s="118">
         <f>$T$38</f>
         <v>9000000004</v>
       </c>
-      <c r="AK4" s="174" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="S5" s="175"/>
-      <c r="T5" s="116" t="s">
+      <c r="AK4" s="191" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="5" spans="19:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S5" s="206"/>
+      <c r="T5" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="U5" s="112" t="s">
+      <c r="U5" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="V5" s="112" t="s">
+      <c r="V5" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="W5" s="112" t="s">
+      <c r="W5" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="Y5" s="118" t="s">
+      <c r="Y5" s="119" t="s">
         <v>276</v>
       </c>
-      <c r="Z5" s="120" t="str">
+      <c r="Z5" s="115" t="str">
         <f t="shared" ref="Z5:Z7" si="0">T5</f>
         <v>100CP03C00</v>
       </c>
-      <c r="AA5" s="120" t="s">
+      <c r="AA5" s="115" t="s">
         <v>280</v>
       </c>
-      <c r="AB5" s="120" t="s">
+      <c r="AB5" s="115" t="s">
         <v>277</v>
       </c>
-      <c r="AC5" s="161">
+      <c r="AC5" s="120">
         <f>$T$34</f>
         <v>9000000000</v>
       </c>
-      <c r="AD5" s="175"/>
-      <c r="AF5" s="118" t="s">
+      <c r="AD5" s="197"/>
+      <c r="AF5" s="119" t="s">
         <v>276</v>
       </c>
-      <c r="AG5" s="145" t="str">
+      <c r="AG5" s="133" t="str">
         <f t="shared" ref="AG5:AG31" si="1">T5</f>
         <v>100CP03C00</v>
       </c>
-      <c r="AH5" s="120" t="s">
+      <c r="AH5" s="115" t="s">
         <v>86</v>
       </c>
-      <c r="AI5" s="120" t="s">
+      <c r="AI5" s="115" t="s">
         <v>277</v>
       </c>
-      <c r="AJ5" s="161">
-        <f t="shared" ref="AJ5:AJ9" si="2">$T$38</f>
+      <c r="AJ5" s="120">
+        <f t="shared" ref="AJ5:AJ7" si="2">$T$38</f>
         <v>9000000004</v>
       </c>
-      <c r="AK5" s="175"/>
-    </row>
-    <row r="6" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="S6" s="175"/>
-      <c r="T6" s="116" t="s">
+      <c r="AK5" s="197"/>
+    </row>
+    <row r="6" spans="19:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S6" s="206"/>
+      <c r="T6" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="U6" s="112" t="s">
+      <c r="U6" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="V6" s="112" t="s">
+      <c r="V6" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="W6" s="112" t="s">
+      <c r="W6" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="Y6" s="118" t="s">
+      <c r="Y6" s="119" t="s">
         <v>277</v>
       </c>
-      <c r="Z6" s="120" t="str">
+      <c r="Z6" s="115" t="str">
         <f t="shared" si="0"/>
         <v>100FL01A00</v>
       </c>
-      <c r="AA6" s="120" t="s">
+      <c r="AA6" s="115" t="s">
         <v>280</v>
       </c>
-      <c r="AB6" s="120" t="s">
+      <c r="AB6" s="115" t="s">
         <v>276</v>
       </c>
-      <c r="AC6" s="161">
+      <c r="AC6" s="120">
         <f>$T$34</f>
         <v>9000000000</v>
       </c>
-      <c r="AD6" s="175"/>
-      <c r="AF6" s="118" t="s">
+      <c r="AD6" s="197"/>
+      <c r="AF6" s="119" t="s">
         <v>277</v>
       </c>
-      <c r="AG6" s="145" t="str">
+      <c r="AG6" s="133" t="str">
         <f t="shared" si="1"/>
         <v>100FL01A00</v>
       </c>
-      <c r="AH6" s="120" t="s">
+      <c r="AH6" s="115" t="s">
         <v>86</v>
       </c>
-      <c r="AI6" s="120" t="s">
+      <c r="AI6" s="115" t="s">
         <v>276</v>
       </c>
-      <c r="AJ6" s="161">
+      <c r="AJ6" s="120">
         <f t="shared" si="2"/>
         <v>9000000004</v>
       </c>
-      <c r="AK6" s="175"/>
-    </row>
-    <row r="7" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="S7" s="176"/>
-      <c r="T7" s="116" t="s">
+      <c r="AK6" s="197"/>
+    </row>
+    <row r="7" spans="19:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S7" s="207"/>
+      <c r="T7" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="U7" s="112" t="s">
+      <c r="U7" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="V7" s="112" t="s">
+      <c r="V7" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="W7" s="112" t="s">
+      <c r="W7" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="Y7" s="118" t="s">
+      <c r="Y7" s="119" t="s">
         <v>277</v>
       </c>
-      <c r="Z7" s="120" t="str">
+      <c r="Z7" s="115" t="str">
         <f t="shared" si="0"/>
         <v>100PM01A00</v>
       </c>
-      <c r="AA7" s="120" t="s">
+      <c r="AA7" s="115" t="s">
         <v>280</v>
       </c>
-      <c r="AB7" s="120" t="s">
+      <c r="AB7" s="115" t="s">
         <v>276</v>
       </c>
-      <c r="AC7" s="161">
+      <c r="AC7" s="120">
         <f>$T$34</f>
         <v>9000000000</v>
       </c>
-      <c r="AD7" s="175"/>
-      <c r="AF7" s="118" t="s">
+      <c r="AD7" s="197"/>
+      <c r="AF7" s="119" t="s">
         <v>277</v>
       </c>
-      <c r="AG7" s="145" t="str">
+      <c r="AG7" s="133" t="str">
         <f t="shared" si="1"/>
         <v>100PM01A00</v>
       </c>
-      <c r="AH7" s="120" t="s">
+      <c r="AH7" s="115" t="s">
         <v>86</v>
       </c>
-      <c r="AI7" s="120" t="s">
+      <c r="AI7" s="115" t="s">
         <v>276</v>
       </c>
-      <c r="AJ7" s="161">
+      <c r="AJ7" s="120">
         <f t="shared" si="2"/>
         <v>9000000004</v>
       </c>
-      <c r="AK7" s="176"/>
-    </row>
-    <row r="8" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="S8" s="177" t="s">
+      <c r="AK7" s="192"/>
+    </row>
+    <row r="8" spans="19:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S8" s="208" t="s">
         <v>244</v>
       </c>
-      <c r="T8" s="117" t="s">
+      <c r="T8" s="81" t="s">
         <v>239</v>
       </c>
-      <c r="U8" s="113" t="s">
+      <c r="U8" s="82" t="s">
         <v>240</v>
       </c>
-      <c r="V8" s="113" t="s">
+      <c r="V8" s="82" t="s">
         <v>202</v>
       </c>
-      <c r="W8" s="113" t="s">
+      <c r="W8" s="82" t="s">
         <v>86</v>
       </c>
-      <c r="Y8" s="123"/>
-      <c r="Z8" s="119"/>
-      <c r="AA8" s="119"/>
-      <c r="AB8" s="119"/>
-      <c r="AC8" s="124"/>
-      <c r="AD8" s="175"/>
-      <c r="AF8" s="130" t="s">
+      <c r="Y8" s="121"/>
+      <c r="Z8" s="122"/>
+      <c r="AA8" s="122"/>
+      <c r="AB8" s="122"/>
+      <c r="AC8" s="123"/>
+      <c r="AD8" s="197"/>
+      <c r="AF8" s="151" t="s">
         <v>276</v>
       </c>
-      <c r="AG8" s="261" t="str">
+      <c r="AG8" s="134" t="str">
         <f t="shared" si="1"/>
         <v>711PP11000</v>
       </c>
-      <c r="AH8" s="107" t="s">
+      <c r="AH8" s="135" t="s">
         <v>280</v>
       </c>
-      <c r="AI8" s="107" t="s">
+      <c r="AI8" s="135" t="s">
+        <v>277</v>
+      </c>
+      <c r="AJ8" s="152">
+        <v>9000000000</v>
+      </c>
+      <c r="AK8" s="191" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="9" spans="19:37" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="S9" s="209"/>
+      <c r="T9" s="81" t="s">
+        <v>241</v>
+      </c>
+      <c r="U9" s="82" t="s">
+        <v>242</v>
+      </c>
+      <c r="V9" s="82" t="s">
+        <v>202</v>
+      </c>
+      <c r="W9" s="82" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y9" s="124"/>
+      <c r="Z9" s="125"/>
+      <c r="AA9" s="125"/>
+      <c r="AB9" s="125"/>
+      <c r="AC9" s="126"/>
+      <c r="AD9" s="197"/>
+      <c r="AF9" s="153" t="s">
         <v>276</v>
       </c>
-      <c r="AJ8" s="165">
-        <v>9000000000</v>
-      </c>
-      <c r="AK8" s="174" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="9" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="S9" s="178"/>
-      <c r="T9" s="117" t="s">
-        <v>241</v>
-      </c>
-      <c r="U9" s="113" t="s">
-        <v>242</v>
-      </c>
-      <c r="V9" s="113" t="s">
-        <v>202</v>
-      </c>
-      <c r="W9" s="113" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y9" s="125"/>
-      <c r="Z9" s="126"/>
-      <c r="AA9" s="126"/>
-      <c r="AB9" s="126"/>
-      <c r="AC9" s="127"/>
-      <c r="AD9" s="175"/>
-      <c r="AF9" s="131" t="s">
-        <v>276</v>
-      </c>
-      <c r="AG9" s="262" t="str">
+      <c r="AG9" s="154" t="str">
         <f t="shared" si="1"/>
         <v>711PP12000</v>
       </c>
-      <c r="AH9" s="132" t="s">
+      <c r="AH9" s="155" t="s">
         <v>280</v>
       </c>
-      <c r="AI9" s="132" t="s">
+      <c r="AI9" s="155" t="s">
+        <v>277</v>
+      </c>
+      <c r="AJ9" s="156">
+        <v>9000000000</v>
+      </c>
+      <c r="AK9" s="192"/>
+    </row>
+    <row r="10" spans="19:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S10" s="204" t="s">
+        <v>93</v>
+      </c>
+      <c r="T10" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y10" s="116" t="s">
         <v>276</v>
       </c>
-      <c r="AJ9" s="166">
-        <v>9000000000</v>
-      </c>
-      <c r="AK9" s="176"/>
-    </row>
-    <row r="10" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="S10" s="173" t="s">
-        <v>93</v>
-      </c>
-      <c r="T10" s="116" t="s">
-        <v>224</v>
-      </c>
-      <c r="U10" s="112" t="s">
-        <v>225</v>
-      </c>
-      <c r="V10" s="112" t="s">
-        <v>201</v>
-      </c>
-      <c r="W10" s="112" t="s">
-        <v>207</v>
-      </c>
-      <c r="Y10" s="121" t="s">
-        <v>276</v>
-      </c>
-      <c r="Z10" s="157">
+      <c r="Z10" s="127">
         <f>T36</f>
         <v>9000000002</v>
       </c>
-      <c r="AA10" s="122" t="s">
+      <c r="AA10" s="117" t="s">
         <v>280</v>
       </c>
-      <c r="AB10" s="122" t="s">
+      <c r="AB10" s="117" t="s">
         <v>277</v>
       </c>
-      <c r="AC10" s="160">
+      <c r="AC10" s="118">
         <f>$T$34</f>
         <v>9000000000</v>
       </c>
-      <c r="AD10" s="175"/>
-      <c r="AF10" s="121" t="s">
+      <c r="AD10" s="197"/>
+      <c r="AF10" s="116" t="s">
         <v>276</v>
       </c>
-      <c r="AG10" s="144" t="str">
+      <c r="AG10" s="150" t="str">
         <f t="shared" si="1"/>
         <v>156TD00000</v>
       </c>
-      <c r="AH10" s="122" t="s">
+      <c r="AH10" s="117" t="s">
         <v>207</v>
       </c>
-      <c r="AI10" s="122" t="s">
+      <c r="AI10" s="117" t="s">
         <v>277</v>
       </c>
-      <c r="AJ10" s="160">
+      <c r="AJ10" s="118">
         <f>T36</f>
         <v>9000000002</v>
       </c>
-      <c r="AK10" s="183" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="11" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="S11" s="173"/>
-      <c r="T11" s="116" t="s">
+      <c r="AK10" s="191" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="11" spans="19:37" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="S11" s="204"/>
+      <c r="T11" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="U11" s="112" t="s">
+      <c r="U11" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="V11" s="112" t="s">
+      <c r="V11" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="W11" s="112" t="s">
+      <c r="W11" s="3" t="s">
         <v>207</v>
       </c>
       <c r="Y11" s="128" t="s">
         <v>277</v>
       </c>
-      <c r="Z11" s="158">
+      <c r="Z11" s="129">
         <f>T40</f>
         <v>9000000006</v>
       </c>
-      <c r="AA11" s="129" t="s">
+      <c r="AA11" s="130" t="s">
         <v>280</v>
       </c>
-      <c r="AB11" s="129" t="s">
+      <c r="AB11" s="130" t="s">
         <v>276</v>
       </c>
-      <c r="AC11" s="162">
+      <c r="AC11" s="131">
         <f t="shared" ref="AC11:AC25" si="3">$T$34</f>
         <v>9000000000</v>
       </c>
-      <c r="AD11" s="175"/>
+      <c r="AD11" s="197"/>
       <c r="AF11" s="128" t="s">
         <v>277</v>
       </c>
-      <c r="AG11" s="146" t="str">
+      <c r="AG11" s="157" t="str">
         <f t="shared" si="1"/>
         <v>153AC01000</v>
       </c>
-      <c r="AH11" s="129" t="s">
+      <c r="AH11" s="130" t="s">
         <v>207</v>
       </c>
-      <c r="AI11" s="129" t="s">
+      <c r="AI11" s="130" t="s">
         <v>276</v>
       </c>
-      <c r="AJ11" s="162">
+      <c r="AJ11" s="131">
         <f>T40</f>
         <v>9000000006</v>
       </c>
-      <c r="AK11" s="176"/>
-    </row>
-    <row r="12" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="S12" s="173" t="s">
+      <c r="AK11" s="192"/>
+    </row>
+    <row r="12" spans="19:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S12" s="204" t="s">
         <v>94</v>
       </c>
-      <c r="T12" s="116" t="s">
+      <c r="T12" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="U12" s="112" t="s">
+      <c r="U12" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="V12" s="112" t="s">
+      <c r="V12" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="W12" s="112" t="s">
+      <c r="W12" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="Y12" s="121" t="s">
+      <c r="Y12" s="116" t="s">
         <v>277</v>
       </c>
-      <c r="Z12" s="157">
+      <c r="Z12" s="127">
         <f>T35</f>
         <v>9000000001</v>
       </c>
-      <c r="AA12" s="122" t="s">
+      <c r="AA12" s="117" t="s">
         <v>280</v>
       </c>
-      <c r="AB12" s="122" t="s">
+      <c r="AB12" s="117" t="s">
         <v>276</v>
       </c>
-      <c r="AC12" s="160">
+      <c r="AC12" s="118">
         <f t="shared" si="3"/>
         <v>9000000000</v>
       </c>
-      <c r="AD12" s="175"/>
-      <c r="AF12" s="121" t="s">
+      <c r="AD12" s="197"/>
+      <c r="AF12" s="116" t="s">
         <v>277</v>
       </c>
-      <c r="AG12" s="144" t="str">
+      <c r="AG12" s="150" t="str">
         <f t="shared" si="1"/>
         <v>206AP00000</v>
       </c>
-      <c r="AH12" s="122" t="s">
+      <c r="AH12" s="117" t="s">
         <v>208</v>
       </c>
-      <c r="AI12" s="122" t="s">
+      <c r="AI12" s="117" t="s">
         <v>276</v>
       </c>
-      <c r="AJ12" s="160">
+      <c r="AJ12" s="118">
         <f>T35</f>
         <v>9000000001</v>
       </c>
-      <c r="AK12" s="183" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="13" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="S13" s="173"/>
-      <c r="T13" s="116" t="s">
+      <c r="AK12" s="191" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="13" spans="19:37" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="S13" s="204"/>
+      <c r="T13" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="U13" s="112" t="s">
+      <c r="U13" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="V13" s="112" t="s">
+      <c r="V13" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="W13" s="112" t="s">
+      <c r="W13" s="3" t="s">
         <v>208</v>
       </c>
       <c r="Y13" s="128" t="s">
         <v>276</v>
       </c>
-      <c r="Z13" s="158">
+      <c r="Z13" s="129">
         <f>T39</f>
         <v>9000000005</v>
       </c>
-      <c r="AA13" s="129" t="s">
+      <c r="AA13" s="130" t="s">
         <v>280</v>
       </c>
-      <c r="AB13" s="129" t="s">
+      <c r="AB13" s="130" t="s">
         <v>277</v>
       </c>
-      <c r="AC13" s="162">
+      <c r="AC13" s="131">
         <f t="shared" si="3"/>
         <v>9000000000</v>
       </c>
-      <c r="AD13" s="175"/>
+      <c r="AD13" s="197"/>
       <c r="AF13" s="128" t="s">
         <v>276</v>
       </c>
-      <c r="AG13" s="146" t="str">
+      <c r="AG13" s="157" t="str">
         <f t="shared" si="1"/>
         <v>159AP00000</v>
       </c>
-      <c r="AH13" s="129" t="s">
+      <c r="AH13" s="130" t="s">
         <v>208</v>
       </c>
-      <c r="AI13" s="129" t="s">
+      <c r="AI13" s="130" t="s">
         <v>277</v>
       </c>
-      <c r="AJ13" s="162">
+      <c r="AJ13" s="131">
         <f>T39</f>
         <v>9000000005</v>
       </c>
-      <c r="AK13" s="176"/>
-    </row>
-    <row r="14" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="S14" s="173" t="s">
+      <c r="AK13" s="192"/>
+    </row>
+    <row r="14" spans="19:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S14" s="204" t="s">
         <v>234</v>
       </c>
-      <c r="T14" s="116" t="s">
+      <c r="T14" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="U14" s="112" t="s">
+      <c r="U14" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="V14" s="112" t="s">
+      <c r="V14" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="W14" s="112" t="s">
+      <c r="W14" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="Y14" s="121" t="s">
+      <c r="Y14" s="116" t="s">
         <v>276</v>
       </c>
-      <c r="Z14" s="122" t="str">
+      <c r="Z14" s="117" t="str">
         <f>T14</f>
         <v>158NT05000</v>
       </c>
-      <c r="AA14" s="122" t="s">
+      <c r="AA14" s="117" t="s">
         <v>280</v>
       </c>
-      <c r="AB14" s="122" t="s">
+      <c r="AB14" s="117" t="s">
         <v>277</v>
       </c>
-      <c r="AC14" s="160">
+      <c r="AC14" s="118">
         <f t="shared" si="3"/>
         <v>9000000000</v>
       </c>
-      <c r="AD14" s="175"/>
-      <c r="AF14" s="121" t="s">
+      <c r="AD14" s="197"/>
+      <c r="AF14" s="116" t="s">
         <v>276</v>
       </c>
-      <c r="AG14" s="122" t="str">
+      <c r="AG14" s="117" t="str">
         <f t="shared" si="1"/>
         <v>158NT05000</v>
       </c>
-      <c r="AH14" s="122" t="s">
+      <c r="AH14" s="117" t="s">
         <v>280</v>
       </c>
-      <c r="AI14" s="122" t="s">
+      <c r="AI14" s="117" t="s">
         <v>277</v>
       </c>
-      <c r="AJ14" s="160">
+      <c r="AJ14" s="118">
         <f t="shared" ref="AJ14:AJ17" si="4">$T$34</f>
         <v>9000000000</v>
       </c>
-      <c r="AK14" s="184" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="15" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="S15" s="173"/>
-      <c r="T15" s="116" t="s">
+      <c r="AK14" s="191" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="15" spans="19:37" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="S15" s="204"/>
+      <c r="T15" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="U15" s="112" t="s">
+      <c r="U15" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="V15" s="112" t="s">
+      <c r="V15" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="W15" s="112" t="s">
+      <c r="W15" s="3" t="s">
         <v>209</v>
       </c>
       <c r="Y15" s="128" t="s">
         <v>277</v>
       </c>
-      <c r="Z15" s="129" t="str">
+      <c r="Z15" s="130" t="str">
         <f t="shared" ref="Z15:Z25" si="5">T15</f>
         <v>206OT54000</v>
       </c>
-      <c r="AA15" s="129" t="s">
+      <c r="AA15" s="130" t="s">
         <v>280</v>
       </c>
-      <c r="AB15" s="129" t="s">
+      <c r="AB15" s="130" t="s">
         <v>276</v>
       </c>
-      <c r="AC15" s="162">
+      <c r="AC15" s="131">
         <f t="shared" si="3"/>
         <v>9000000000</v>
       </c>
-      <c r="AD15" s="175"/>
+      <c r="AD15" s="197"/>
       <c r="AF15" s="128" t="s">
         <v>277</v>
       </c>
-      <c r="AG15" s="129" t="str">
+      <c r="AG15" s="130" t="str">
         <f t="shared" si="1"/>
         <v>206OT54000</v>
       </c>
-      <c r="AH15" s="129" t="s">
+      <c r="AH15" s="130" t="s">
         <v>280</v>
       </c>
-      <c r="AI15" s="129" t="s">
+      <c r="AI15" s="130" t="s">
         <v>276</v>
       </c>
-      <c r="AJ15" s="162">
+      <c r="AJ15" s="131">
         <f t="shared" si="4"/>
         <v>9000000000</v>
       </c>
-      <c r="AK15" s="175"/>
-    </row>
-    <row r="16" spans="19:37" x14ac:dyDescent="0.35">
-      <c r="S16" s="173" t="s">
+      <c r="AK15" s="196"/>
+    </row>
+    <row r="16" spans="19:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S16" s="204" t="s">
         <v>233</v>
       </c>
-      <c r="T16" s="116" t="s">
+      <c r="T16" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="U16" s="112" t="s">
+      <c r="U16" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="V16" s="112" t="s">
+      <c r="V16" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="W16" s="112" t="s">
+      <c r="W16" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="Y16" s="121" t="s">
+      <c r="Y16" s="116" t="s">
         <v>276</v>
       </c>
-      <c r="Z16" s="122" t="str">
+      <c r="Z16" s="137" t="str">
         <f t="shared" si="5"/>
         <v>188CC01M00</v>
       </c>
-      <c r="AA16" s="122" t="s">
+      <c r="AA16" s="117" t="s">
         <v>280</v>
       </c>
-      <c r="AB16" s="122" t="s">
+      <c r="AB16" s="117" t="s">
         <v>277</v>
       </c>
-      <c r="AC16" s="160">
+      <c r="AC16" s="118">
         <f t="shared" si="3"/>
         <v>9000000000</v>
       </c>
-      <c r="AD16" s="175"/>
-      <c r="AF16" s="121" t="s">
+      <c r="AD16" s="197"/>
+      <c r="AF16" s="158" t="s">
         <v>276</v>
       </c>
-      <c r="AG16" s="122" t="str">
+      <c r="AG16" s="159" t="str">
         <f t="shared" si="1"/>
         <v>188CC01M00</v>
       </c>
-      <c r="AH16" s="122" t="s">
+      <c r="AH16" s="159" t="s">
         <v>280</v>
       </c>
-      <c r="AI16" s="122" t="s">
+      <c r="AI16" s="159" t="s">
         <v>277</v>
       </c>
       <c r="AJ16" s="160">
         <f t="shared" si="4"/>
         <v>9000000000</v>
       </c>
-      <c r="AK16" s="175"/>
-    </row>
-    <row r="17" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="76" t="s">
+      <c r="AK16" s="191" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="17" spans="1:37" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B17" s="62" t="s">
         <v>137</v>
       </c>
-      <c r="D17" s="76" t="s">
+      <c r="D17" s="62" t="s">
         <v>138</v>
       </c>
-      <c r="E17" s="76" t="s">
+      <c r="E17" s="62" t="s">
         <v>139</v>
       </c>
-      <c r="H17" s="76" t="s">
+      <c r="H17" s="62" t="s">
         <v>140</v>
       </c>
-      <c r="I17" s="76" t="s">
+      <c r="I17" s="62" t="s">
         <v>141</v>
       </c>
-      <c r="S17" s="173"/>
-      <c r="T17" s="116" t="s">
+      <c r="S17" s="204"/>
+      <c r="T17" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="U17" s="112" t="s">
+      <c r="U17" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="V17" s="112" t="s">
+      <c r="V17" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="W17" s="112" t="s">
+      <c r="W17" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="Y17" s="118" t="s">
+      <c r="Y17" s="138" t="s">
         <v>277</v>
       </c>
-      <c r="Z17" s="120" t="str">
+      <c r="Z17" s="84" t="str">
         <f t="shared" si="5"/>
         <v>300SC01000</v>
       </c>
-      <c r="AA17" s="120" t="s">
+      <c r="AA17" s="30" t="s">
         <v>280</v>
       </c>
-      <c r="AB17" s="120" t="s">
+      <c r="AB17" s="30" t="s">
         <v>276</v>
       </c>
-      <c r="AC17" s="161">
+      <c r="AC17" s="139">
         <f t="shared" si="3"/>
         <v>9000000000</v>
       </c>
-      <c r="AD17" s="175"/>
-      <c r="AF17" s="118" t="s">
+      <c r="AD17" s="197"/>
+      <c r="AF17" s="138" t="s">
         <v>277</v>
       </c>
-      <c r="AG17" s="120" t="str">
+      <c r="AG17" s="30" t="str">
         <f t="shared" si="1"/>
         <v>300SC01000</v>
       </c>
-      <c r="AH17" s="120" t="s">
+      <c r="AH17" s="30" t="s">
         <v>280</v>
       </c>
-      <c r="AI17" s="120" t="s">
+      <c r="AI17" s="30" t="s">
         <v>276</v>
       </c>
-      <c r="AJ17" s="161">
+      <c r="AJ17" s="139">
         <f t="shared" si="4"/>
         <v>9000000000</v>
       </c>
-      <c r="AK17" s="175"/>
-    </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="AK17" s="196"/>
+    </row>
+    <row r="18" spans="1:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>1</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D18" s="77" t="s">
+      <c r="D18" s="85" t="s">
         <v>142</v>
       </c>
-      <c r="E18" s="78"/>
-      <c r="F18" s="79" t="s">
+      <c r="E18" s="16"/>
+      <c r="F18" s="86" t="s">
         <v>143</v>
       </c>
-      <c r="H18" s="77" t="s">
+      <c r="H18" s="85" t="s">
         <v>144</v>
       </c>
-      <c r="I18" s="78"/>
-      <c r="J18" s="78"/>
-      <c r="K18" s="78"/>
-      <c r="L18" s="78"/>
-      <c r="M18" s="88" t="s">
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="87" t="s">
         <v>145</v>
       </c>
-      <c r="N18" s="79"/>
-      <c r="P18" t="s">
+      <c r="N18" s="86"/>
+      <c r="P18" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="Q18" s="169" t="s">
+      <c r="Q18" s="200" t="s">
         <v>147</v>
       </c>
-      <c r="S18" s="173"/>
-      <c r="T18" s="135" t="s">
+      <c r="S18" s="204"/>
+      <c r="T18" s="88" t="s">
         <v>261</v>
       </c>
-      <c r="U18" s="136" t="s">
+      <c r="U18" s="32" t="s">
         <v>262</v>
       </c>
-      <c r="V18" s="136" t="s">
+      <c r="V18" s="32" t="s">
         <v>201</v>
       </c>
-      <c r="W18" s="136" t="s">
+      <c r="W18" s="32" t="s">
         <v>275</v>
       </c>
-      <c r="Y18" s="137" t="s">
+      <c r="Y18" s="140" t="s">
         <v>276</v>
       </c>
-      <c r="Z18" s="138" t="str">
+      <c r="Z18" s="132" t="str">
         <f t="shared" si="5"/>
         <v>152RM00000</v>
       </c>
-      <c r="AA18" s="138" t="s">
+      <c r="AA18" s="132" t="s">
         <v>280</v>
       </c>
-      <c r="AB18" s="138" t="s">
+      <c r="AB18" s="132" t="s">
         <v>277</v>
       </c>
-      <c r="AC18" s="163">
+      <c r="AC18" s="141">
         <f t="shared" si="3"/>
         <v>9000000000</v>
       </c>
-      <c r="AD18" s="175"/>
-      <c r="AF18" s="141" t="s">
+      <c r="AD18" s="197"/>
+      <c r="AF18" s="140" t="s">
         <v>276</v>
       </c>
-      <c r="AG18" s="147" t="str">
+      <c r="AG18" s="136" t="str">
         <f t="shared" si="1"/>
         <v>152RM00000</v>
       </c>
-      <c r="AH18" s="142" t="s">
+      <c r="AH18" s="132" t="s">
         <v>282</v>
       </c>
-      <c r="AI18" s="142" t="s">
+      <c r="AI18" s="132" t="s">
         <v>277</v>
       </c>
-      <c r="AJ18" s="167">
+      <c r="AJ18" s="141">
         <f>$T$37</f>
         <v>9000000003</v>
       </c>
-      <c r="AK18" s="185" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="AK18" s="193" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>2</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D19" s="80" t="s">
+      <c r="D19" s="48" t="s">
         <v>149</v>
       </c>
-      <c r="F19" s="81" t="s">
+      <c r="F19" s="89" t="s">
         <v>150</v>
       </c>
-      <c r="H19" s="80" t="s">
+      <c r="H19" s="48" t="s">
         <v>151</v>
       </c>
-      <c r="M19" s="34" t="s">
+      <c r="M19" s="90" t="s">
         <v>145</v>
       </c>
-      <c r="N19" s="81"/>
-      <c r="Q19" s="170"/>
-      <c r="S19" s="173"/>
-      <c r="T19" s="135" t="s">
+      <c r="N19" s="89"/>
+      <c r="Q19" s="201"/>
+      <c r="S19" s="204"/>
+      <c r="T19" s="88" t="s">
         <v>263</v>
       </c>
-      <c r="U19" s="136" t="s">
+      <c r="U19" s="32" t="s">
         <v>264</v>
       </c>
-      <c r="V19" s="136" t="s">
+      <c r="V19" s="32" t="s">
         <v>201</v>
       </c>
-      <c r="W19" s="136" t="s">
+      <c r="W19" s="32" t="s">
         <v>275</v>
       </c>
-      <c r="Y19" s="137" t="s">
+      <c r="Y19" s="140" t="s">
         <v>276</v>
       </c>
-      <c r="Z19" s="138" t="str">
+      <c r="Z19" s="132" t="str">
         <f t="shared" si="5"/>
         <v>152TG00000</v>
       </c>
-      <c r="AA19" s="138" t="s">
+      <c r="AA19" s="132" t="s">
         <v>280</v>
       </c>
-      <c r="AB19" s="138" t="s">
+      <c r="AB19" s="132" t="s">
         <v>277</v>
       </c>
-      <c r="AC19" s="163">
+      <c r="AC19" s="141">
         <f t="shared" si="3"/>
         <v>9000000000</v>
       </c>
-      <c r="AD19" s="175"/>
-      <c r="AF19" s="137" t="s">
+      <c r="AD19" s="197"/>
+      <c r="AF19" s="140" t="s">
         <v>276</v>
       </c>
-      <c r="AG19" s="148" t="str">
+      <c r="AG19" s="136" t="str">
         <f t="shared" si="1"/>
         <v>152TG00000</v>
       </c>
-      <c r="AH19" s="138" t="s">
+      <c r="AH19" s="132" t="s">
         <v>282</v>
       </c>
-      <c r="AI19" s="138" t="s">
+      <c r="AI19" s="132" t="s">
         <v>277</v>
       </c>
-      <c r="AJ19" s="163">
+      <c r="AJ19" s="141">
         <f t="shared" ref="AJ19:AJ25" si="6">$T$37</f>
         <v>9000000003</v>
       </c>
-      <c r="AK19" s="186"/>
-    </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="AK19" s="194"/>
+    </row>
+    <row r="20" spans="1:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>3</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D20" s="80" t="s">
+      <c r="D20" s="48" t="s">
         <v>149</v>
       </c>
-      <c r="F20" s="81" t="s">
+      <c r="F20" s="89" t="s">
         <v>152</v>
       </c>
-      <c r="H20" s="80" t="s">
+      <c r="H20" s="48" t="s">
         <v>151</v>
       </c>
-      <c r="M20" s="34" t="s">
+      <c r="M20" s="90" t="s">
         <v>145</v>
       </c>
-      <c r="N20" s="81"/>
-      <c r="Q20" s="170"/>
-      <c r="S20" s="173"/>
-      <c r="T20" s="135" t="s">
+      <c r="N20" s="89"/>
+      <c r="Q20" s="201"/>
+      <c r="S20" s="204"/>
+      <c r="T20" s="88" t="s">
         <v>265</v>
       </c>
-      <c r="U20" s="136" t="s">
+      <c r="U20" s="32" t="s">
         <v>266</v>
       </c>
-      <c r="V20" s="136" t="s">
+      <c r="V20" s="32" t="s">
         <v>201</v>
       </c>
-      <c r="W20" s="136" t="s">
+      <c r="W20" s="32" t="s">
         <v>275</v>
       </c>
-      <c r="Y20" s="137" t="s">
+      <c r="Y20" s="140" t="s">
         <v>276</v>
       </c>
-      <c r="Z20" s="138" t="str">
+      <c r="Z20" s="132" t="str">
         <f t="shared" si="5"/>
         <v>152SP00000</v>
       </c>
-      <c r="AA20" s="138" t="s">
+      <c r="AA20" s="132" t="s">
         <v>280</v>
       </c>
-      <c r="AB20" s="138" t="s">
+      <c r="AB20" s="132" t="s">
         <v>277</v>
       </c>
-      <c r="AC20" s="163">
+      <c r="AC20" s="141">
         <f t="shared" si="3"/>
         <v>9000000000</v>
       </c>
-      <c r="AD20" s="175"/>
-      <c r="AF20" s="137" t="s">
+      <c r="AD20" s="197"/>
+      <c r="AF20" s="140" t="s">
         <v>276</v>
       </c>
-      <c r="AG20" s="148" t="str">
+      <c r="AG20" s="136" t="str">
         <f t="shared" si="1"/>
         <v>152SP00000</v>
       </c>
-      <c r="AH20" s="138" t="s">
+      <c r="AH20" s="132" t="s">
         <v>282</v>
       </c>
-      <c r="AI20" s="138" t="s">
+      <c r="AI20" s="132" t="s">
         <v>277</v>
       </c>
-      <c r="AJ20" s="163">
+      <c r="AJ20" s="141">
         <f t="shared" si="6"/>
         <v>9000000003</v>
       </c>
-      <c r="AK20" s="186"/>
-    </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="AK20" s="194"/>
+    </row>
+    <row r="21" spans="1:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>4</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="80" t="s">
+      <c r="D21" s="48" t="s">
         <v>149</v>
       </c>
-      <c r="F21" s="81" t="s">
+      <c r="F21" s="89" t="s">
         <v>153</v>
       </c>
-      <c r="H21" s="80" t="s">
+      <c r="H21" s="48" t="s">
         <v>151</v>
       </c>
-      <c r="M21" s="34" t="s">
+      <c r="M21" s="90" t="s">
         <v>145</v>
       </c>
-      <c r="N21" s="81"/>
-      <c r="Q21" s="170"/>
-      <c r="S21" s="173"/>
-      <c r="T21" s="135" t="s">
+      <c r="N21" s="89"/>
+      <c r="Q21" s="201"/>
+      <c r="S21" s="204"/>
+      <c r="T21" s="88" t="s">
         <v>267</v>
       </c>
-      <c r="U21" s="136" t="s">
+      <c r="U21" s="32" t="s">
         <v>268</v>
       </c>
-      <c r="V21" s="136" t="s">
+      <c r="V21" s="32" t="s">
         <v>201</v>
       </c>
-      <c r="W21" s="136" t="s">
+      <c r="W21" s="32" t="s">
         <v>275</v>
       </c>
-      <c r="Y21" s="137" t="s">
+      <c r="Y21" s="140" t="s">
         <v>276</v>
       </c>
-      <c r="Z21" s="138" t="str">
+      <c r="Z21" s="132" t="str">
         <f t="shared" si="5"/>
         <v>152PG00000</v>
       </c>
-      <c r="AA21" s="138" t="s">
+      <c r="AA21" s="132" t="s">
         <v>280</v>
       </c>
-      <c r="AB21" s="138" t="s">
+      <c r="AB21" s="132" t="s">
         <v>277</v>
       </c>
-      <c r="AC21" s="163">
+      <c r="AC21" s="141">
         <f t="shared" si="3"/>
         <v>9000000000</v>
       </c>
-      <c r="AD21" s="175"/>
-      <c r="AF21" s="137" t="s">
+      <c r="AD21" s="197"/>
+      <c r="AF21" s="140" t="s">
         <v>276</v>
       </c>
-      <c r="AG21" s="148" t="str">
+      <c r="AG21" s="136" t="str">
         <f t="shared" si="1"/>
         <v>152PG00000</v>
       </c>
-      <c r="AH21" s="138" t="s">
+      <c r="AH21" s="132" t="s">
         <v>282</v>
       </c>
-      <c r="AI21" s="138" t="s">
+      <c r="AI21" s="132" t="s">
         <v>277</v>
       </c>
-      <c r="AJ21" s="163">
+      <c r="AJ21" s="141">
         <f t="shared" si="6"/>
         <v>9000000003</v>
       </c>
-      <c r="AK21" s="186"/>
-    </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="AK21" s="194"/>
+    </row>
+    <row r="22" spans="1:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>5</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="D22" s="80" t="s">
+      <c r="D22" s="48" t="s">
         <v>151</v>
       </c>
-      <c r="F22" s="81" t="s">
+      <c r="F22" s="89" t="s">
         <v>150</v>
       </c>
-      <c r="H22" s="80" t="s">
+      <c r="H22" s="48" t="s">
         <v>151</v>
       </c>
-      <c r="M22" s="34" t="s">
+      <c r="M22" s="90" t="s">
         <v>150</v>
       </c>
-      <c r="N22" s="81"/>
-      <c r="Q22" s="170"/>
-      <c r="S22" s="173"/>
-      <c r="T22" s="135" t="s">
+      <c r="N22" s="89"/>
+      <c r="Q22" s="201"/>
+      <c r="S22" s="204"/>
+      <c r="T22" s="88" t="s">
         <v>265</v>
       </c>
-      <c r="U22" s="136" t="s">
+      <c r="U22" s="32" t="s">
         <v>266</v>
       </c>
-      <c r="V22" s="136" t="s">
+      <c r="V22" s="32" t="s">
         <v>201</v>
       </c>
-      <c r="W22" s="136" t="s">
+      <c r="W22" s="32" t="s">
         <v>275</v>
       </c>
-      <c r="Y22" s="137" t="s">
+      <c r="Y22" s="140" t="s">
         <v>276</v>
       </c>
-      <c r="Z22" s="138" t="str">
+      <c r="Z22" s="132" t="str">
         <f t="shared" si="5"/>
         <v>152SP00000</v>
       </c>
-      <c r="AA22" s="138" t="s">
+      <c r="AA22" s="132" t="s">
         <v>280</v>
       </c>
-      <c r="AB22" s="138" t="s">
+      <c r="AB22" s="132" t="s">
         <v>277</v>
       </c>
-      <c r="AC22" s="163">
+      <c r="AC22" s="141">
         <f t="shared" si="3"/>
         <v>9000000000</v>
       </c>
-      <c r="AD22" s="175"/>
-      <c r="AF22" s="137" t="s">
+      <c r="AD22" s="197"/>
+      <c r="AF22" s="140" t="s">
         <v>276</v>
       </c>
-      <c r="AG22" s="148" t="str">
+      <c r="AG22" s="136" t="str">
         <f t="shared" si="1"/>
         <v>152SP00000</v>
       </c>
-      <c r="AH22" s="138" t="s">
+      <c r="AH22" s="132" t="s">
         <v>282</v>
       </c>
-      <c r="AI22" s="138" t="s">
+      <c r="AI22" s="132" t="s">
         <v>277</v>
       </c>
-      <c r="AJ22" s="163">
+      <c r="AJ22" s="141">
         <f t="shared" si="6"/>
         <v>9000000003</v>
       </c>
-      <c r="AK22" s="186"/>
-    </row>
-    <row r="23" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AK22" s="194"/>
+    </row>
+    <row r="23" spans="1:37" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>6</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D23" s="82" t="s">
+      <c r="D23" s="91" t="s">
         <v>108</v>
       </c>
-      <c r="E23" s="83"/>
-      <c r="F23" s="84"/>
-      <c r="H23" s="82" t="s">
+      <c r="E23" s="92"/>
+      <c r="F23" s="93"/>
+      <c r="H23" s="91" t="s">
         <v>108</v>
       </c>
-      <c r="I23" s="83"/>
-      <c r="J23" s="83"/>
-      <c r="K23" s="83"/>
-      <c r="L23" s="83"/>
-      <c r="M23" s="83"/>
-      <c r="N23" s="84"/>
-      <c r="Q23" s="170"/>
-      <c r="S23" s="173"/>
-      <c r="T23" s="135" t="s">
+      <c r="I23" s="92"/>
+      <c r="J23" s="92"/>
+      <c r="K23" s="92"/>
+      <c r="L23" s="92"/>
+      <c r="M23" s="92"/>
+      <c r="N23" s="93"/>
+      <c r="Q23" s="201"/>
+      <c r="S23" s="204"/>
+      <c r="T23" s="88" t="s">
         <v>269</v>
       </c>
-      <c r="U23" s="136" t="s">
+      <c r="U23" s="32" t="s">
         <v>270</v>
       </c>
-      <c r="V23" s="136" t="s">
+      <c r="V23" s="32" t="s">
         <v>201</v>
       </c>
-      <c r="W23" s="136" t="s">
+      <c r="W23" s="32" t="s">
         <v>275</v>
       </c>
-      <c r="Y23" s="137" t="s">
+      <c r="Y23" s="140" t="s">
         <v>276</v>
       </c>
-      <c r="Z23" s="138" t="str">
+      <c r="Z23" s="132" t="str">
         <f t="shared" si="5"/>
         <v>152OS00000</v>
       </c>
-      <c r="AA23" s="138" t="s">
+      <c r="AA23" s="132" t="s">
         <v>280</v>
       </c>
-      <c r="AB23" s="138" t="s">
+      <c r="AB23" s="132" t="s">
         <v>277</v>
       </c>
-      <c r="AC23" s="163">
+      <c r="AC23" s="141">
         <f t="shared" si="3"/>
         <v>9000000000</v>
       </c>
-      <c r="AD23" s="175"/>
-      <c r="AF23" s="137" t="s">
+      <c r="AD23" s="197"/>
+      <c r="AF23" s="140" t="s">
         <v>276</v>
       </c>
-      <c r="AG23" s="148" t="str">
+      <c r="AG23" s="136" t="str">
         <f t="shared" si="1"/>
         <v>152OS00000</v>
       </c>
-      <c r="AH23" s="138" t="s">
+      <c r="AH23" s="132" t="s">
         <v>282</v>
       </c>
-      <c r="AI23" s="138" t="s">
+      <c r="AI23" s="132" t="s">
         <v>277</v>
       </c>
-      <c r="AJ23" s="163">
+      <c r="AJ23" s="141">
         <f t="shared" si="6"/>
         <v>9000000003</v>
       </c>
-      <c r="AK23" s="186"/>
-    </row>
-    <row r="24" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="Q24" s="170"/>
-      <c r="S24" s="173"/>
-      <c r="T24" s="135" t="s">
+      <c r="AK23" s="194"/>
+    </row>
+    <row r="24" spans="1:37" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="Q24" s="201"/>
+      <c r="S24" s="204"/>
+      <c r="T24" s="88" t="s">
         <v>271</v>
       </c>
-      <c r="U24" s="136" t="s">
+      <c r="U24" s="32" t="s">
         <v>272</v>
       </c>
-      <c r="V24" s="136" t="s">
+      <c r="V24" s="32" t="s">
         <v>201</v>
       </c>
-      <c r="W24" s="136" t="s">
+      <c r="W24" s="32" t="s">
         <v>275</v>
       </c>
-      <c r="Y24" s="137" t="s">
+      <c r="Y24" s="140" t="s">
         <v>276</v>
       </c>
-      <c r="Z24" s="138" t="str">
+      <c r="Z24" s="132" t="str">
         <f t="shared" si="5"/>
         <v>152SF00000</v>
       </c>
-      <c r="AA24" s="138" t="s">
+      <c r="AA24" s="132" t="s">
         <v>280</v>
       </c>
-      <c r="AB24" s="138" t="s">
+      <c r="AB24" s="132" t="s">
         <v>277</v>
       </c>
-      <c r="AC24" s="163">
+      <c r="AC24" s="141">
         <f t="shared" si="3"/>
         <v>9000000000</v>
       </c>
-      <c r="AD24" s="175"/>
-      <c r="AF24" s="137" t="s">
+      <c r="AD24" s="197"/>
+      <c r="AF24" s="140" t="s">
         <v>276</v>
       </c>
-      <c r="AG24" s="148" t="str">
+      <c r="AG24" s="136" t="str">
         <f t="shared" si="1"/>
         <v>152SF00000</v>
       </c>
-      <c r="AH24" s="138" t="s">
+      <c r="AH24" s="132" t="s">
         <v>282</v>
       </c>
-      <c r="AI24" s="138" t="s">
+      <c r="AI24" s="132" t="s">
         <v>277</v>
       </c>
-      <c r="AJ24" s="163">
+      <c r="AJ24" s="141">
         <f t="shared" si="6"/>
         <v>9000000003</v>
       </c>
-      <c r="AK24" s="186"/>
-    </row>
-    <row r="25" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="H25" s="85" t="s">
+      <c r="AK24" s="194"/>
+    </row>
+    <row r="25" spans="1:37" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H25" s="94" t="s">
         <v>156</v>
       </c>
-      <c r="I25" s="86"/>
-      <c r="J25" s="86"/>
-      <c r="K25" s="86"/>
-      <c r="L25" s="86"/>
-      <c r="M25" s="86"/>
-      <c r="N25" s="87"/>
-      <c r="P25" t="s">
+      <c r="I25" s="95"/>
+      <c r="J25" s="95"/>
+      <c r="K25" s="95"/>
+      <c r="L25" s="95"/>
+      <c r="M25" s="95"/>
+      <c r="N25" s="96"/>
+      <c r="P25" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="Q25" s="171"/>
-      <c r="S25" s="173"/>
-      <c r="T25" s="135" t="s">
+      <c r="Q25" s="202"/>
+      <c r="S25" s="204"/>
+      <c r="T25" s="88" t="s">
         <v>273</v>
       </c>
-      <c r="U25" s="136" t="s">
+      <c r="U25" s="32" t="s">
         <v>274</v>
       </c>
-      <c r="V25" s="136" t="s">
+      <c r="V25" s="32" t="s">
         <v>201</v>
       </c>
-      <c r="W25" s="136" t="s">
+      <c r="W25" s="32" t="s">
         <v>275</v>
       </c>
-      <c r="Y25" s="139" t="s">
+      <c r="Y25" s="142" t="s">
         <v>276</v>
       </c>
-      <c r="Z25" s="140" t="str">
+      <c r="Z25" s="143" t="str">
         <f t="shared" si="5"/>
         <v>152FG00000</v>
       </c>
-      <c r="AA25" s="140" t="s">
+      <c r="AA25" s="143" t="s">
         <v>280</v>
       </c>
-      <c r="AB25" s="140" t="s">
+      <c r="AB25" s="143" t="s">
         <v>277</v>
       </c>
-      <c r="AC25" s="164">
+      <c r="AC25" s="144">
         <f t="shared" si="3"/>
         <v>9000000000</v>
       </c>
-      <c r="AD25" s="175"/>
-      <c r="AF25" s="139" t="s">
+      <c r="AD25" s="197"/>
+      <c r="AF25" s="142" t="s">
         <v>276</v>
       </c>
-      <c r="AG25" s="149" t="str">
+      <c r="AG25" s="161" t="str">
         <f t="shared" si="1"/>
         <v>152FG00000</v>
       </c>
-      <c r="AH25" s="140" t="s">
+      <c r="AH25" s="143" t="s">
         <v>282</v>
       </c>
-      <c r="AI25" s="140" t="s">
+      <c r="AI25" s="143" t="s">
         <v>277</v>
       </c>
-      <c r="AJ25" s="164">
+      <c r="AJ25" s="144">
         <f t="shared" si="6"/>
         <v>9000000003</v>
       </c>
-      <c r="AK25" s="187"/>
-    </row>
-    <row r="26" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="S26" s="177" t="s">
+      <c r="AK25" s="195"/>
+    </row>
+    <row r="26" spans="1:37" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="S26" s="208" t="s">
         <v>155</v>
       </c>
-      <c r="T26" s="117" t="s">
+      <c r="T26" s="81" t="s">
         <v>249</v>
       </c>
-      <c r="U26" s="113" t="s">
+      <c r="U26" s="82" t="s">
         <v>250</v>
       </c>
-      <c r="V26" s="113" t="s">
+      <c r="V26" s="82" t="s">
         <v>202</v>
       </c>
-      <c r="W26" s="113" t="s">
+      <c r="W26" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="Y26" s="150"/>
-      <c r="Z26" s="151"/>
-      <c r="AA26" s="151"/>
-      <c r="AB26" s="151"/>
-      <c r="AC26" s="152"/>
-      <c r="AD26" s="175"/>
-      <c r="AF26" s="133" t="s">
+      <c r="Y26" s="145"/>
+      <c r="Z26" s="146"/>
+      <c r="AA26" s="146"/>
+      <c r="AB26" s="146"/>
+      <c r="AC26" s="147"/>
+      <c r="AD26" s="197"/>
+      <c r="AF26" s="162" t="s">
         <v>276</v>
       </c>
-      <c r="AG26" s="134" t="str">
+      <c r="AG26" s="163" t="str">
         <f t="shared" si="1"/>
         <v>705AW01000</v>
       </c>
-      <c r="AH26" s="134" t="s">
+      <c r="AH26" s="163" t="s">
         <v>280</v>
       </c>
-      <c r="AI26" s="134" t="s">
+      <c r="AI26" s="163" t="s">
         <v>277</v>
       </c>
-      <c r="AJ26" s="168">
+      <c r="AJ26" s="164">
         <f>$T$34</f>
         <v>9000000000</v>
       </c>
-      <c r="AK26" s="184" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="H27" s="77" t="s">
+      <c r="AK26" s="196" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="27" spans="1:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H27" s="85" t="s">
         <v>158</v>
       </c>
-      <c r="I27" s="78"/>
-      <c r="J27" s="78"/>
-      <c r="K27" s="78"/>
-      <c r="L27" s="78"/>
-      <c r="M27" s="88" t="s">
+      <c r="I27" s="16"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="87" t="s">
         <v>143</v>
       </c>
-      <c r="N27" s="89"/>
-      <c r="P27" t="s">
+      <c r="N27" s="17"/>
+      <c r="P27" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="S27" s="179"/>
-      <c r="T27" s="117" t="s">
+      <c r="S27" s="210"/>
+      <c r="T27" s="81" t="s">
         <v>259</v>
       </c>
-      <c r="U27" s="113" t="s">
+      <c r="U27" s="82" t="s">
         <v>260</v>
       </c>
-      <c r="V27" s="113" t="s">
+      <c r="V27" s="82" t="s">
         <v>202</v>
       </c>
-      <c r="W27" s="113" t="s">
+      <c r="W27" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="Y27" s="123"/>
-      <c r="Z27" s="119"/>
-      <c r="AA27" s="119"/>
-      <c r="AB27" s="119"/>
-      <c r="AC27" s="153"/>
-      <c r="AD27" s="175"/>
-      <c r="AF27" s="130" t="s">
+      <c r="Y27" s="121"/>
+      <c r="Z27" s="122"/>
+      <c r="AA27" s="122"/>
+      <c r="AB27" s="122"/>
+      <c r="AC27" s="148"/>
+      <c r="AD27" s="197"/>
+      <c r="AF27" s="151" t="s">
         <v>276</v>
       </c>
-      <c r="AG27" s="107" t="str">
+      <c r="AG27" s="135" t="str">
         <f t="shared" si="1"/>
         <v>735EX06000</v>
       </c>
-      <c r="AH27" s="107" t="s">
+      <c r="AH27" s="135" t="s">
         <v>280</v>
       </c>
-      <c r="AI27" s="107" t="s">
+      <c r="AI27" s="135" t="s">
         <v>277</v>
       </c>
-      <c r="AJ27" s="165">
+      <c r="AJ27" s="152">
         <f t="shared" ref="AJ27:AJ31" si="7">$T$34</f>
         <v>9000000000</v>
       </c>
-      <c r="AK27" s="175"/>
-    </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="H28" s="80" t="s">
+      <c r="AK27" s="197"/>
+    </row>
+    <row r="28" spans="1:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H28" s="48" t="s">
         <v>160</v>
       </c>
-      <c r="M28" s="34" t="s">
+      <c r="M28" s="90" t="s">
         <v>150</v>
       </c>
-      <c r="N28" s="90"/>
-      <c r="S28" s="179"/>
-      <c r="T28" s="117" t="s">
+      <c r="N28" s="19"/>
+      <c r="S28" s="210"/>
+      <c r="T28" s="81" t="s">
         <v>251</v>
       </c>
-      <c r="U28" s="113" t="s">
+      <c r="U28" s="82" t="s">
         <v>252</v>
       </c>
-      <c r="V28" s="113" t="s">
+      <c r="V28" s="82" t="s">
         <v>202</v>
       </c>
-      <c r="W28" s="113" t="s">
+      <c r="W28" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="Y28" s="123"/>
-      <c r="Z28" s="119"/>
-      <c r="AA28" s="119"/>
-      <c r="AB28" s="119"/>
-      <c r="AC28" s="153"/>
-      <c r="AD28" s="175"/>
-      <c r="AF28" s="130" t="s">
+      <c r="Y28" s="121"/>
+      <c r="Z28" s="122"/>
+      <c r="AA28" s="122"/>
+      <c r="AB28" s="122"/>
+      <c r="AC28" s="148"/>
+      <c r="AD28" s="197"/>
+      <c r="AF28" s="151" t="s">
         <v>276</v>
       </c>
-      <c r="AG28" s="107" t="str">
+      <c r="AG28" s="135" t="str">
         <f t="shared" si="1"/>
         <v>610SC02000</v>
       </c>
-      <c r="AH28" s="107" t="s">
+      <c r="AH28" s="135" t="s">
         <v>280</v>
       </c>
-      <c r="AI28" s="107" t="s">
+      <c r="AI28" s="135" t="s">
         <v>277</v>
       </c>
-      <c r="AJ28" s="165">
+      <c r="AJ28" s="152">
         <f t="shared" si="7"/>
         <v>9000000000</v>
       </c>
-      <c r="AK28" s="175"/>
-    </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="H29" s="80" t="s">
+      <c r="AK28" s="197"/>
+    </row>
+    <row r="29" spans="1:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H29" s="48" t="s">
         <v>160</v>
       </c>
-      <c r="M29" s="34" t="s">
+      <c r="M29" s="90" t="s">
         <v>152</v>
       </c>
-      <c r="N29" s="90"/>
-      <c r="S29" s="179"/>
-      <c r="T29" s="117" t="s">
+      <c r="N29" s="19"/>
+      <c r="S29" s="210"/>
+      <c r="T29" s="81" t="s">
         <v>253</v>
       </c>
-      <c r="U29" s="113" t="s">
+      <c r="U29" s="82" t="s">
         <v>254</v>
       </c>
-      <c r="V29" s="113" t="s">
+      <c r="V29" s="82" t="s">
         <v>202</v>
       </c>
-      <c r="W29" s="113" t="s">
+      <c r="W29" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="Y29" s="123"/>
-      <c r="Z29" s="119"/>
-      <c r="AA29" s="119"/>
-      <c r="AB29" s="119"/>
-      <c r="AC29" s="153"/>
-      <c r="AD29" s="175"/>
-      <c r="AF29" s="130" t="s">
+      <c r="Y29" s="121"/>
+      <c r="Z29" s="122"/>
+      <c r="AA29" s="122"/>
+      <c r="AB29" s="122"/>
+      <c r="AC29" s="148"/>
+      <c r="AD29" s="197"/>
+      <c r="AF29" s="151" t="s">
         <v>276</v>
       </c>
-      <c r="AG29" s="107" t="str">
+      <c r="AG29" s="135" t="str">
         <f t="shared" si="1"/>
         <v>610OH01000</v>
       </c>
-      <c r="AH29" s="107" t="s">
+      <c r="AH29" s="135" t="s">
         <v>280</v>
       </c>
-      <c r="AI29" s="107" t="s">
+      <c r="AI29" s="135" t="s">
         <v>277</v>
       </c>
-      <c r="AJ29" s="165">
+      <c r="AJ29" s="152">
         <f t="shared" si="7"/>
         <v>9000000000</v>
       </c>
-      <c r="AK29" s="175"/>
-    </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="H30" s="80" t="s">
+      <c r="AK29" s="197"/>
+    </row>
+    <row r="30" spans="1:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H30" s="48" t="s">
         <v>160</v>
       </c>
-      <c r="M30" s="34" t="s">
+      <c r="M30" s="90" t="s">
         <v>153</v>
       </c>
-      <c r="N30" s="90"/>
-      <c r="S30" s="179"/>
-      <c r="T30" s="117" t="s">
+      <c r="N30" s="19"/>
+      <c r="S30" s="210"/>
+      <c r="T30" s="81" t="s">
         <v>257</v>
       </c>
-      <c r="U30" s="113" t="s">
+      <c r="U30" s="82" t="s">
         <v>258</v>
       </c>
-      <c r="V30" s="113" t="s">
+      <c r="V30" s="82" t="s">
         <v>202</v>
       </c>
-      <c r="W30" s="113" t="s">
+      <c r="W30" s="82" t="s">
         <v>203</v>
       </c>
-      <c r="Y30" s="123"/>
-      <c r="Z30" s="119"/>
-      <c r="AA30" s="119"/>
-      <c r="AB30" s="119"/>
-      <c r="AC30" s="153"/>
-      <c r="AD30" s="175"/>
-      <c r="AF30" s="130" t="s">
+      <c r="Y30" s="121"/>
+      <c r="Z30" s="122"/>
+      <c r="AA30" s="122"/>
+      <c r="AB30" s="122"/>
+      <c r="AC30" s="148"/>
+      <c r="AD30" s="197"/>
+      <c r="AF30" s="151" t="s">
         <v>277</v>
       </c>
-      <c r="AG30" s="107" t="str">
+      <c r="AG30" s="135" t="str">
         <f t="shared" si="1"/>
         <v>500SD01000</v>
       </c>
-      <c r="AH30" s="107" t="s">
+      <c r="AH30" s="135" t="s">
         <v>280</v>
       </c>
-      <c r="AI30" s="107" t="s">
+      <c r="AI30" s="135" t="s">
         <v>276</v>
       </c>
-      <c r="AJ30" s="165">
+      <c r="AJ30" s="152">
         <f t="shared" si="7"/>
         <v>9000000000</v>
       </c>
-      <c r="AK30" s="175"/>
-    </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="H31" s="80" t="s">
+      <c r="AK30" s="197"/>
+    </row>
+    <row r="31" spans="1:37" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H31" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="L31" t="s">
+      <c r="L31" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="M31" s="34" t="s">
+      <c r="M31" s="90" t="s">
         <v>150</v>
       </c>
-      <c r="N31" s="90"/>
-      <c r="S31" s="178"/>
-      <c r="T31" s="117" t="s">
+      <c r="N31" s="19"/>
+      <c r="S31" s="209"/>
+      <c r="T31" s="81" t="s">
         <v>255</v>
       </c>
-      <c r="U31" s="113" t="s">
+      <c r="U31" s="82" t="s">
         <v>256</v>
       </c>
-      <c r="V31" s="113" t="s">
+      <c r="V31" s="82" t="s">
         <v>202</v>
       </c>
-      <c r="W31" s="113" t="s">
+      <c r="W31" s="82" t="s">
         <v>203</v>
       </c>
-      <c r="Y31" s="125"/>
-      <c r="Z31" s="126"/>
-      <c r="AA31" s="126"/>
-      <c r="AB31" s="126"/>
-      <c r="AC31" s="154"/>
-      <c r="AD31" s="176"/>
-      <c r="AF31" s="131" t="s">
+      <c r="Y31" s="124"/>
+      <c r="Z31" s="125"/>
+      <c r="AA31" s="125"/>
+      <c r="AB31" s="125"/>
+      <c r="AC31" s="149"/>
+      <c r="AD31" s="192"/>
+      <c r="AF31" s="153" t="s">
         <v>277</v>
       </c>
-      <c r="AG31" s="132" t="str">
+      <c r="AG31" s="155" t="str">
         <f t="shared" si="1"/>
         <v>810DQ00000</v>
       </c>
-      <c r="AH31" s="132" t="s">
+      <c r="AH31" s="155" t="s">
         <v>280</v>
       </c>
-      <c r="AI31" s="132" t="s">
+      <c r="AI31" s="155" t="s">
         <v>276</v>
       </c>
-      <c r="AJ31" s="166">
+      <c r="AJ31" s="156">
         <f t="shared" si="7"/>
         <v>9000000000</v>
       </c>
-      <c r="AK31" s="176"/>
-    </row>
-    <row r="32" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="H32" s="82" t="s">
+      <c r="AK31" s="192"/>
+    </row>
+    <row r="32" spans="1:37" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H32" s="91" t="s">
         <v>161</v>
       </c>
-      <c r="I32" s="83"/>
-      <c r="J32" s="83"/>
-      <c r="K32" s="83"/>
-      <c r="L32" s="83" t="s">
+      <c r="I32" s="92"/>
+      <c r="J32" s="92"/>
+      <c r="K32" s="92"/>
+      <c r="L32" s="92" t="s">
         <v>163</v>
       </c>
-      <c r="M32" s="91" t="s">
+      <c r="M32" s="97" t="s">
         <v>150</v>
       </c>
-      <c r="N32" s="84"/>
-    </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="Y33" s="143" t="s">
+      <c r="N32" s="93"/>
+    </row>
+    <row r="33" spans="1:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Y33" s="198" t="s">
+        <v>334</v>
+      </c>
+      <c r="Z33" s="199"/>
+      <c r="AA33" s="199"/>
+      <c r="AB33" s="199"/>
+      <c r="AC33" s="199"/>
+      <c r="AD33" s="199"/>
+      <c r="AF33" s="79" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="34" spans="1:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="36">
+        <v>7</v>
+      </c>
+      <c r="B34" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37" t="s">
+        <v>165</v>
+      </c>
+      <c r="E34" s="37"/>
+      <c r="F34" s="37"/>
+      <c r="S34" s="211" t="s">
+        <v>217</v>
+      </c>
+      <c r="T34" s="98">
+        <v>9000000000</v>
+      </c>
+      <c r="U34" s="99" t="s">
+        <v>170</v>
+      </c>
+      <c r="V34" s="99" t="s">
+        <v>201</v>
+      </c>
+      <c r="W34" s="99" t="s">
+        <v>217</v>
+      </c>
+      <c r="Y34" s="165"/>
+      <c r="AF34" s="79" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="35" spans="1:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S35" s="212"/>
+      <c r="T35" s="98">
+        <v>9000000001</v>
+      </c>
+      <c r="U35" s="99" t="s">
+        <v>171</v>
+      </c>
+      <c r="V35" s="99" t="s">
+        <v>201</v>
+      </c>
+      <c r="W35" s="99" t="s">
+        <v>217</v>
+      </c>
+      <c r="AG35" s="79" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="36" spans="1:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S36" s="212"/>
+      <c r="T36" s="98">
+        <v>9000000002</v>
+      </c>
+      <c r="U36" s="99" t="s">
+        <v>174</v>
+      </c>
+      <c r="V36" s="99" t="s">
+        <v>201</v>
+      </c>
+      <c r="W36" s="99" t="s">
+        <v>217</v>
+      </c>
+      <c r="AG36" s="79" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="37" spans="1:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="100" t="s">
+        <v>166</v>
+      </c>
+      <c r="C37" s="101"/>
+      <c r="D37" s="101"/>
+      <c r="E37" s="101"/>
+      <c r="F37" s="102"/>
+      <c r="H37" s="100" t="s">
+        <v>167</v>
+      </c>
+      <c r="I37" s="101"/>
+      <c r="J37" s="101"/>
+      <c r="K37" s="101"/>
+      <c r="L37" s="101"/>
+      <c r="M37" s="102"/>
+      <c r="S37" s="212"/>
+      <c r="T37" s="98">
+        <v>9000000003</v>
+      </c>
+      <c r="U37" s="99" t="s">
+        <v>215</v>
+      </c>
+      <c r="V37" s="99" t="s">
+        <v>201</v>
+      </c>
+      <c r="W37" s="99" t="s">
+        <v>217</v>
+      </c>
+      <c r="AG37" s="79" t="s">
         <v>288</v>
       </c>
-      <c r="AF33" s="143" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A34" s="92">
+    </row>
+    <row r="38" spans="1:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="76">
+        <v>1</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="F38" s="103"/>
+      <c r="H38" s="76">
+        <v>1</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="M38" s="103"/>
+      <c r="S38" s="212"/>
+      <c r="T38" s="98">
+        <v>9000000004</v>
+      </c>
+      <c r="U38" s="99" t="s">
+        <v>216</v>
+      </c>
+      <c r="V38" s="99" t="s">
+        <v>201</v>
+      </c>
+      <c r="W38" s="99" t="s">
+        <v>217</v>
+      </c>
+      <c r="AG38" s="79" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="39" spans="1:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="76"/>
+      <c r="D39" s="83" t="s">
+        <v>195</v>
+      </c>
+      <c r="E39" s="83"/>
+      <c r="F39" s="104" t="s">
+        <v>170</v>
+      </c>
+      <c r="H39" s="76"/>
+      <c r="J39" s="84" t="s">
+        <v>148</v>
+      </c>
+      <c r="K39" s="84"/>
+      <c r="L39" s="84"/>
+      <c r="M39" s="105" t="s">
+        <v>170</v>
+      </c>
+      <c r="S39" s="212"/>
+      <c r="T39" s="98">
+        <v>9000000005</v>
+      </c>
+      <c r="U39" s="99" t="s">
+        <v>218</v>
+      </c>
+      <c r="V39" s="99" t="s">
+        <v>201</v>
+      </c>
+      <c r="W39" s="99" t="s">
+        <v>217</v>
+      </c>
+      <c r="AG39" s="79" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="40" spans="1:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="76">
+        <v>2</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F40" s="103"/>
+      <c r="H40" s="76">
+        <v>2</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="M40" s="103"/>
+      <c r="S40" s="213"/>
+      <c r="T40" s="98">
+        <v>9000000006</v>
+      </c>
+      <c r="U40" s="99" t="s">
+        <v>219</v>
+      </c>
+      <c r="V40" s="99" t="s">
+        <v>201</v>
+      </c>
+      <c r="W40" s="99" t="s">
+        <v>217</v>
+      </c>
+      <c r="AG40" s="79" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="41" spans="1:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="76"/>
+      <c r="D41" s="83" t="s">
+        <v>171</v>
+      </c>
+      <c r="E41" s="83"/>
+      <c r="F41" s="104" t="s">
+        <v>170</v>
+      </c>
+      <c r="H41" s="76"/>
+      <c r="J41" s="84" t="s">
+        <v>187</v>
+      </c>
+      <c r="K41" s="84"/>
+      <c r="L41" s="84"/>
+      <c r="M41" s="105" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="42" spans="1:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="76">
+        <v>3</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F42" s="103"/>
+      <c r="H42" s="76">
+        <v>3</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="M42" s="103"/>
+      <c r="AF42" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="AH42" s="79" t="s">
+        <v>293</v>
+      </c>
+      <c r="AK42" s="106" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="43" spans="1:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B43" s="76"/>
+      <c r="D43" s="83" t="s">
+        <v>197</v>
+      </c>
+      <c r="E43" s="83"/>
+      <c r="F43" s="104" t="s">
+        <v>170</v>
+      </c>
+      <c r="H43" s="76"/>
+      <c r="J43" s="84" t="s">
+        <v>188</v>
+      </c>
+      <c r="K43" s="84"/>
+      <c r="L43" s="84"/>
+      <c r="M43" s="105" t="s">
+        <v>174</v>
+      </c>
+      <c r="AF43" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="AH43" s="79" t="s">
+        <v>295</v>
+      </c>
+      <c r="AK43" s="106" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="44" spans="1:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="76">
+        <v>4</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F44" s="103"/>
+      <c r="H44" s="76">
+        <v>4</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="M44" s="103"/>
+      <c r="AF44" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="AH44" s="79" t="s">
+        <v>297</v>
+      </c>
+      <c r="AK44" s="106" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="45" spans="1:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="76"/>
+      <c r="D45" s="83" t="s">
+        <v>174</v>
+      </c>
+      <c r="E45" s="83"/>
+      <c r="F45" s="104" t="s">
+        <v>170</v>
+      </c>
+      <c r="H45" s="76"/>
+      <c r="J45" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="M45" s="103"/>
+      <c r="AF45" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="AH45" s="79" t="s">
+        <v>299</v>
+      </c>
+      <c r="AK45" s="106" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="46" spans="1:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B46" s="76">
+        <v>5</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F46" s="103"/>
+      <c r="H46" s="76">
+        <v>5</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="M46" s="103"/>
+      <c r="AF46" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="AH46" s="79" t="s">
+        <v>302</v>
+      </c>
+      <c r="AK46" s="106" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="47" spans="1:37" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="76"/>
+      <c r="D47" s="83" t="s">
+        <v>198</v>
+      </c>
+      <c r="E47" s="83"/>
+      <c r="F47" s="104" t="s">
+        <v>170</v>
+      </c>
+      <c r="H47" s="76"/>
+      <c r="J47" s="84" t="s">
+        <v>189</v>
+      </c>
+      <c r="K47" s="84"/>
+      <c r="L47" s="84"/>
+      <c r="M47" s="105" t="s">
+        <v>190</v>
+      </c>
+      <c r="AF47" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="AH47" s="79" t="s">
+        <v>305</v>
+      </c>
+      <c r="AK47" s="106" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="48" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="B48" s="76">
+        <v>6</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="F48" s="103"/>
+      <c r="H48" s="76">
+        <v>6</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="M48" s="103"/>
+    </row>
+    <row r="49" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B49" s="76"/>
+      <c r="D49" s="83" t="s">
+        <v>169</v>
+      </c>
+      <c r="E49" s="83"/>
+      <c r="F49" s="104" t="s">
+        <v>170</v>
+      </c>
+      <c r="H49" s="76"/>
+      <c r="J49" s="84" t="s">
+        <v>154</v>
+      </c>
+      <c r="K49" s="84"/>
+      <c r="L49" s="84"/>
+      <c r="M49" s="105" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B50" s="76">
         <v>7</v>
       </c>
-      <c r="B34" s="93" t="s">
-        <v>164</v>
-      </c>
-      <c r="C34" s="93"/>
-      <c r="D34" s="93" t="s">
-        <v>165</v>
-      </c>
-      <c r="E34" s="93"/>
-      <c r="F34" s="93"/>
-      <c r="S34" s="180" t="s">
-        <v>217</v>
-      </c>
-      <c r="T34" s="159">
-        <v>9000000000</v>
-      </c>
-      <c r="U34" s="114" t="s">
+      <c r="C50" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F50" s="103"/>
+      <c r="H50" s="76">
+        <v>7</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="M50" s="103"/>
+    </row>
+    <row r="51" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B51" s="76"/>
+      <c r="D51" s="84" t="s">
+        <v>196</v>
+      </c>
+      <c r="E51" s="84"/>
+      <c r="F51" s="105" t="s">
         <v>170</v>
       </c>
-      <c r="V34" s="114" t="s">
-        <v>201</v>
-      </c>
-      <c r="W34" s="114" t="s">
-        <v>217</v>
-      </c>
-      <c r="AF34" s="143" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="S35" s="181"/>
-      <c r="T35" s="159">
-        <v>9000000001</v>
-      </c>
-      <c r="U35" s="114" t="s">
-        <v>171</v>
-      </c>
-      <c r="V35" s="114" t="s">
-        <v>201</v>
-      </c>
-      <c r="W35" s="114" t="s">
-        <v>217</v>
-      </c>
-      <c r="AG35" s="143" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="S36" s="181"/>
-      <c r="T36" s="159">
-        <v>9000000002</v>
-      </c>
-      <c r="U36" s="114" t="s">
-        <v>174</v>
-      </c>
-      <c r="V36" s="114" t="s">
-        <v>201</v>
-      </c>
-      <c r="W36" s="114" t="s">
-        <v>217</v>
-      </c>
-      <c r="AG36" s="143" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="B37" s="95" t="s">
-        <v>166</v>
-      </c>
-      <c r="C37" s="96"/>
-      <c r="D37" s="96"/>
-      <c r="E37" s="96"/>
-      <c r="F37" s="97"/>
-      <c r="H37" s="95" t="s">
-        <v>167</v>
-      </c>
-      <c r="I37" s="96"/>
-      <c r="J37" s="96"/>
-      <c r="K37" s="96"/>
-      <c r="L37" s="96"/>
-      <c r="M37" s="97"/>
-      <c r="S37" s="181"/>
-      <c r="T37" s="159">
-        <v>9000000003</v>
-      </c>
-      <c r="U37" s="114" t="s">
-        <v>215</v>
-      </c>
-      <c r="V37" s="114" t="s">
-        <v>201</v>
-      </c>
-      <c r="W37" s="114" t="s">
-        <v>217</v>
-      </c>
-      <c r="AG37" s="143" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="B38" s="98">
-        <v>1</v>
-      </c>
-      <c r="C38" t="s">
-        <v>193</v>
-      </c>
-      <c r="F38" s="99"/>
-      <c r="H38" s="94">
-        <v>1</v>
-      </c>
-      <c r="I38" t="s">
-        <v>179</v>
-      </c>
-      <c r="M38" s="99"/>
-      <c r="S38" s="181"/>
-      <c r="T38" s="159">
-        <v>9000000004</v>
-      </c>
-      <c r="U38" s="114" t="s">
-        <v>216</v>
-      </c>
-      <c r="V38" s="114" t="s">
-        <v>201</v>
-      </c>
-      <c r="W38" s="114" t="s">
-        <v>217</v>
-      </c>
-      <c r="AG38" s="143" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="B39" s="98"/>
-      <c r="D39" s="107" t="s">
-        <v>195</v>
-      </c>
-      <c r="E39" s="107"/>
-      <c r="F39" s="108" t="s">
+      <c r="H51" s="107"/>
+      <c r="J51" s="84" t="s">
+        <v>191</v>
+      </c>
+      <c r="K51" s="84"/>
+      <c r="L51" s="84"/>
+      <c r="M51" s="105" t="s">
         <v>170</v>
       </c>
-      <c r="H39" s="94"/>
-      <c r="J39" s="105" t="s">
-        <v>148</v>
-      </c>
-      <c r="K39" s="105"/>
-      <c r="L39" s="105"/>
-      <c r="M39" s="106" t="s">
-        <v>170</v>
-      </c>
-      <c r="S39" s="181"/>
-      <c r="T39" s="159">
-        <v>9000000005</v>
-      </c>
-      <c r="U39" s="114" t="s">
-        <v>218</v>
-      </c>
-      <c r="V39" s="114" t="s">
-        <v>201</v>
-      </c>
-      <c r="W39" s="114" t="s">
-        <v>217</v>
-      </c>
-      <c r="AG39" s="143" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="B40" s="98">
-        <v>2</v>
-      </c>
-      <c r="C40" t="s">
-        <v>172</v>
-      </c>
-      <c r="F40" s="99"/>
-      <c r="H40" s="94">
-        <v>2</v>
-      </c>
-      <c r="I40" t="s">
-        <v>181</v>
-      </c>
-      <c r="M40" s="99"/>
-      <c r="S40" s="182"/>
-      <c r="T40" s="159">
-        <v>9000000006</v>
-      </c>
-      <c r="U40" s="114" t="s">
-        <v>219</v>
-      </c>
-      <c r="V40" s="114" t="s">
-        <v>201</v>
-      </c>
-      <c r="W40" s="114" t="s">
-        <v>217</v>
-      </c>
-      <c r="AG40" s="143" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="B41" s="98"/>
-      <c r="D41" s="107" t="s">
-        <v>171</v>
-      </c>
-      <c r="E41" s="107"/>
-      <c r="F41" s="108" t="s">
-        <v>170</v>
-      </c>
-      <c r="H41" s="94"/>
-      <c r="J41" s="105" t="s">
-        <v>187</v>
-      </c>
-      <c r="K41" s="105"/>
-      <c r="L41" s="105"/>
-      <c r="M41" s="106" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="B42" s="98">
-        <v>3</v>
-      </c>
-      <c r="C42" t="s">
-        <v>173</v>
-      </c>
-      <c r="F42" s="99"/>
-      <c r="H42" s="94">
-        <v>3</v>
-      </c>
-      <c r="I42" t="s">
-        <v>180</v>
-      </c>
-      <c r="M42" s="99"/>
-    </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="B43" s="98"/>
-      <c r="D43" s="107" t="s">
-        <v>197</v>
-      </c>
-      <c r="E43" s="107"/>
-      <c r="F43" s="108" t="s">
-        <v>170</v>
-      </c>
-      <c r="H43" s="94"/>
-      <c r="J43" s="105" t="s">
-        <v>188</v>
-      </c>
-      <c r="K43" s="105"/>
-      <c r="L43" s="105"/>
-      <c r="M43" s="106" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="B44" s="98">
-        <v>4</v>
-      </c>
-      <c r="C44" t="s">
-        <v>175</v>
-      </c>
-      <c r="F44" s="99"/>
-      <c r="H44" s="94">
-        <v>4</v>
-      </c>
-      <c r="I44" t="s">
-        <v>182</v>
-      </c>
-      <c r="M44" s="99"/>
-    </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="B45" s="98"/>
-      <c r="D45" s="107" t="s">
-        <v>174</v>
-      </c>
-      <c r="E45" s="107"/>
-      <c r="F45" s="108" t="s">
-        <v>170</v>
-      </c>
-      <c r="H45" s="94"/>
-      <c r="J45" t="s">
-        <v>178</v>
-      </c>
-      <c r="M45" s="99"/>
-    </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="B46" s="98">
-        <v>5</v>
-      </c>
-      <c r="C46" t="s">
-        <v>176</v>
-      </c>
-      <c r="F46" s="99"/>
-      <c r="H46" s="94">
-        <v>5</v>
-      </c>
-      <c r="I46" t="s">
-        <v>183</v>
-      </c>
-      <c r="M46" s="99"/>
-    </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="B47" s="98"/>
-      <c r="D47" s="107" t="s">
-        <v>198</v>
-      </c>
-      <c r="E47" s="107"/>
-      <c r="F47" s="108" t="s">
-        <v>170</v>
-      </c>
-      <c r="H47" s="94"/>
-      <c r="J47" s="105" t="s">
-        <v>189</v>
-      </c>
-      <c r="K47" s="105"/>
-      <c r="L47" s="105"/>
-      <c r="M47" s="106" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="B48" s="98">
-        <v>6</v>
-      </c>
-      <c r="C48" t="s">
-        <v>194</v>
-      </c>
-      <c r="F48" s="99"/>
-      <c r="H48" s="94">
-        <v>6</v>
-      </c>
-      <c r="I48" t="s">
-        <v>185</v>
-      </c>
-      <c r="M48" s="99"/>
-    </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B49" s="98"/>
-      <c r="D49" s="107" t="s">
-        <v>169</v>
-      </c>
-      <c r="E49" s="107"/>
-      <c r="F49" s="108" t="s">
-        <v>170</v>
-      </c>
-      <c r="H49" s="94"/>
-      <c r="J49" s="105" t="s">
-        <v>154</v>
-      </c>
-      <c r="K49" s="105"/>
-      <c r="L49" s="105"/>
-      <c r="M49" s="106" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B50" s="98">
-        <v>7</v>
-      </c>
-      <c r="C50" t="s">
-        <v>184</v>
-      </c>
-      <c r="F50" s="99"/>
-      <c r="H50" s="94">
-        <v>7</v>
-      </c>
-      <c r="I50" t="s">
+    </row>
+    <row r="52" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B52" s="76">
+        <v>8</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="M50" s="99"/>
-    </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B51" s="98"/>
-      <c r="D51" s="105" t="s">
-        <v>196</v>
-      </c>
-      <c r="E51" s="105"/>
-      <c r="F51" s="106" t="s">
-        <v>170</v>
-      </c>
-      <c r="H51" s="103"/>
-      <c r="J51" s="105" t="s">
-        <v>191</v>
-      </c>
-      <c r="K51" s="105"/>
-      <c r="L51" s="105"/>
-      <c r="M51" s="106" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B52" s="98">
-        <v>8</v>
-      </c>
-      <c r="C52" t="s">
-        <v>177</v>
-      </c>
-      <c r="F52" s="99"/>
-      <c r="H52" s="103"/>
-      <c r="M52" s="99"/>
+      <c r="F52" s="103"/>
+      <c r="H52" s="107"/>
+      <c r="M52" s="103"/>
     </row>
     <row r="53" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B53" s="100"/>
-      <c r="C53" s="101"/>
-      <c r="D53" s="101" t="s">
+      <c r="B53" s="108"/>
+      <c r="C53" s="109"/>
+      <c r="D53" s="109" t="s">
         <v>168</v>
       </c>
-      <c r="E53" s="101"/>
-      <c r="F53" s="102"/>
-      <c r="H53" s="104" t="s">
+      <c r="E53" s="109"/>
+      <c r="F53" s="110"/>
+      <c r="H53" s="111" t="s">
         <v>192</v>
       </c>
-      <c r="I53" s="101"/>
-      <c r="J53" s="101"/>
-      <c r="K53" s="101"/>
-      <c r="L53" s="101"/>
-      <c r="M53" s="102"/>
+      <c r="I53" s="109"/>
+      <c r="J53" s="109"/>
+      <c r="K53" s="109"/>
+      <c r="L53" s="109"/>
+      <c r="M53" s="110"/>
     </row>
     <row r="55" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B55" s="172" t="s">
+      <c r="B55" s="203" t="s">
         <v>186</v>
       </c>
-      <c r="C55" s="172"/>
-      <c r="D55" s="172"/>
-      <c r="E55" s="172"/>
-      <c r="F55" s="172"/>
-      <c r="G55" s="172"/>
-      <c r="H55" s="172"/>
-      <c r="I55" s="172"/>
-      <c r="J55" s="172"/>
-      <c r="K55" s="172"/>
-      <c r="L55" s="172"/>
-      <c r="M55" s="172"/>
+      <c r="C55" s="203"/>
+      <c r="D55" s="203"/>
+      <c r="E55" s="203"/>
+      <c r="F55" s="203"/>
+      <c r="G55" s="203"/>
+      <c r="H55" s="203"/>
+      <c r="I55" s="203"/>
+      <c r="J55" s="203"/>
+      <c r="K55" s="203"/>
+      <c r="L55" s="203"/>
+      <c r="M55" s="203"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="20">
+    <mergeCell ref="Y33:AD33"/>
+    <mergeCell ref="Q18:Q25"/>
+    <mergeCell ref="B55:M55"/>
+    <mergeCell ref="S10:S11"/>
+    <mergeCell ref="S12:S13"/>
+    <mergeCell ref="S14:S15"/>
     <mergeCell ref="AD4:AD31"/>
-    <mergeCell ref="AK10:AK11"/>
-    <mergeCell ref="AK12:AK13"/>
-    <mergeCell ref="AK14:AK17"/>
-    <mergeCell ref="AK18:AK25"/>
-    <mergeCell ref="AK26:AK31"/>
-    <mergeCell ref="AK4:AK7"/>
-    <mergeCell ref="AK8:AK9"/>
     <mergeCell ref="S4:S7"/>
     <mergeCell ref="S8:S9"/>
     <mergeCell ref="S16:S25"/>
     <mergeCell ref="S26:S31"/>
     <mergeCell ref="S34:S40"/>
-    <mergeCell ref="Q18:Q25"/>
-    <mergeCell ref="B55:M55"/>
-    <mergeCell ref="S10:S11"/>
-    <mergeCell ref="S12:S13"/>
-    <mergeCell ref="S14:S15"/>
+    <mergeCell ref="AK10:AK11"/>
+    <mergeCell ref="AK12:AK13"/>
+    <mergeCell ref="AK18:AK25"/>
+    <mergeCell ref="AK26:AK31"/>
+    <mergeCell ref="AK4:AK7"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AK14:AK15"/>
+    <mergeCell ref="AK16:AK17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -5254,6 +6254,626 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8271045-A738-4572-89B8-9B0088A7251A}">
+  <dimension ref="A2:W31"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.7265625" style="166"/>
+    <col min="2" max="2" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.54296875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7265625" style="62" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.7265625" style="1"/>
+    <col min="9" max="9" width="8.7265625" style="166"/>
+    <col min="10" max="10" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7265625" style="1"/>
+    <col min="13" max="13" width="9" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="12.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="8.7265625" style="1"/>
+    <col min="18" max="18" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7265625" style="1"/>
+    <col min="21" max="21" width="9" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.7265625" style="2"/>
+    <col min="23" max="16384" width="8.7265625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="179" t="s">
+        <v>320</v>
+      </c>
+      <c r="B3" s="173" t="s">
+        <v>319</v>
+      </c>
+      <c r="C3" s="172" t="s">
+        <v>339</v>
+      </c>
+      <c r="D3" s="172">
+        <v>2000</v>
+      </c>
+      <c r="E3" s="287" t="s">
+        <v>343</v>
+      </c>
+      <c r="F3" s="298">
+        <v>2025</v>
+      </c>
+      <c r="G3" s="296" t="s">
+        <v>348</v>
+      </c>
+      <c r="I3" s="179" t="s">
+        <v>320</v>
+      </c>
+      <c r="J3" s="173" t="s">
+        <v>319</v>
+      </c>
+      <c r="K3" s="172" t="s">
+        <v>340</v>
+      </c>
+      <c r="L3" s="172">
+        <v>2000</v>
+      </c>
+      <c r="M3" s="287" t="s">
+        <v>343</v>
+      </c>
+      <c r="N3" s="298">
+        <v>2025</v>
+      </c>
+      <c r="O3" s="297" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q3" s="166"/>
+      <c r="R3" s="85"/>
+      <c r="S3" s="189" t="s">
+        <v>335</v>
+      </c>
+      <c r="T3" s="189">
+        <v>0</v>
+      </c>
+      <c r="U3" s="295"/>
+      <c r="V3" s="306">
+        <v>2025</v>
+      </c>
+      <c r="W3" s="190" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B4" s="48"/>
+      <c r="C4" s="188" t="s">
+        <v>317</v>
+      </c>
+      <c r="F4" s="187"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="188" t="s">
+        <v>317</v>
+      </c>
+      <c r="N4" s="187"/>
+      <c r="Q4" s="166"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="188" t="s">
+        <v>317</v>
+      </c>
+      <c r="V4" s="187"/>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B5" s="48"/>
+      <c r="C5" s="174" t="s">
+        <v>318</v>
+      </c>
+      <c r="D5" s="168">
+        <v>-200</v>
+      </c>
+      <c r="E5" s="288"/>
+      <c r="F5" s="299">
+        <v>2026</v>
+      </c>
+      <c r="I5" s="179" t="s">
+        <v>320</v>
+      </c>
+      <c r="J5" s="171" t="s">
+        <v>315</v>
+      </c>
+      <c r="K5" s="175" t="s">
+        <v>322</v>
+      </c>
+      <c r="L5" s="84">
+        <v>-200</v>
+      </c>
+      <c r="M5" s="293" t="s">
+        <v>343</v>
+      </c>
+      <c r="N5" s="304">
+        <v>2026</v>
+      </c>
+      <c r="Q5" s="179" t="s">
+        <v>320</v>
+      </c>
+      <c r="R5" s="171" t="s">
+        <v>315</v>
+      </c>
+      <c r="S5" s="175" t="s">
+        <v>338</v>
+      </c>
+      <c r="T5" s="84">
+        <v>-200</v>
+      </c>
+      <c r="U5" s="293" t="s">
+        <v>343</v>
+      </c>
+      <c r="V5" s="304">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B6" s="48"/>
+      <c r="C6" s="174" t="s">
+        <v>316</v>
+      </c>
+      <c r="D6" s="168">
+        <v>-300</v>
+      </c>
+      <c r="E6" s="288"/>
+      <c r="F6" s="299">
+        <v>2026</v>
+      </c>
+      <c r="I6" s="179" t="s">
+        <v>320</v>
+      </c>
+      <c r="J6" s="171" t="s">
+        <v>315</v>
+      </c>
+      <c r="K6" s="175" t="s">
+        <v>321</v>
+      </c>
+      <c r="L6" s="84">
+        <v>-300</v>
+      </c>
+      <c r="M6" s="293" t="s">
+        <v>343</v>
+      </c>
+      <c r="N6" s="304">
+        <v>2026</v>
+      </c>
+      <c r="Q6" s="179" t="s">
+        <v>320</v>
+      </c>
+      <c r="R6" s="171" t="s">
+        <v>315</v>
+      </c>
+      <c r="S6" s="175" t="s">
+        <v>337</v>
+      </c>
+      <c r="T6" s="84">
+        <v>-300</v>
+      </c>
+      <c r="U6" s="293" t="s">
+        <v>343</v>
+      </c>
+      <c r="V6" s="304">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B7" s="48"/>
+      <c r="C7" s="174" t="s">
+        <v>327</v>
+      </c>
+      <c r="D7" s="168">
+        <v>400</v>
+      </c>
+      <c r="E7" s="288"/>
+      <c r="F7" s="299">
+        <v>2026</v>
+      </c>
+      <c r="I7" s="179" t="s">
+        <v>320</v>
+      </c>
+      <c r="J7" s="171" t="s">
+        <v>315</v>
+      </c>
+      <c r="K7" s="175" t="s">
+        <v>328</v>
+      </c>
+      <c r="L7" s="84">
+        <v>400</v>
+      </c>
+      <c r="M7" s="293" t="s">
+        <v>343</v>
+      </c>
+      <c r="N7" s="304">
+        <v>2026</v>
+      </c>
+      <c r="Q7" s="179" t="s">
+        <v>320</v>
+      </c>
+      <c r="R7" s="171" t="s">
+        <v>315</v>
+      </c>
+      <c r="S7" s="175" t="s">
+        <v>336</v>
+      </c>
+      <c r="T7" s="84">
+        <v>400</v>
+      </c>
+      <c r="U7" s="293" t="s">
+        <v>343</v>
+      </c>
+      <c r="V7" s="304">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B8" s="48"/>
+      <c r="F8" s="187"/>
+      <c r="J8" s="48"/>
+      <c r="N8" s="187"/>
+      <c r="Q8" s="166"/>
+      <c r="R8" s="48"/>
+      <c r="V8" s="187"/>
+    </row>
+    <row r="9" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="179" t="s">
+        <v>320</v>
+      </c>
+      <c r="B9" s="176" t="s">
+        <v>315</v>
+      </c>
+      <c r="C9" s="177" t="s">
+        <v>339</v>
+      </c>
+      <c r="D9" s="177">
+        <f>D3+D5+D6+D7</f>
+        <v>1900</v>
+      </c>
+      <c r="E9" s="289" t="s">
+        <v>343</v>
+      </c>
+      <c r="F9" s="300">
+        <v>2026</v>
+      </c>
+      <c r="J9" s="91"/>
+      <c r="K9" s="170" t="s">
+        <v>340</v>
+      </c>
+      <c r="L9" s="170">
+        <f>L3+L5+L6+L7</f>
+        <v>1900</v>
+      </c>
+      <c r="M9" s="294"/>
+      <c r="N9" s="305">
+        <v>2026</v>
+      </c>
+      <c r="Q9" s="166"/>
+      <c r="R9" s="91"/>
+      <c r="S9" s="170" t="s">
+        <v>335</v>
+      </c>
+      <c r="T9" s="170">
+        <f>T3+T5+T6+T7</f>
+        <v>-100</v>
+      </c>
+      <c r="U9" s="294"/>
+      <c r="V9" s="305">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="11" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+      <c r="A11" s="179" t="s">
+        <v>320</v>
+      </c>
+      <c r="B11" s="173" t="s">
+        <v>319</v>
+      </c>
+      <c r="C11" s="178" t="s">
+        <v>329</v>
+      </c>
+      <c r="D11" s="172">
+        <v>2000</v>
+      </c>
+      <c r="E11" s="287" t="s">
+        <v>343</v>
+      </c>
+      <c r="F11" s="298">
+        <v>2025</v>
+      </c>
+      <c r="G11" s="296" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B12" s="48"/>
+      <c r="C12" s="188" t="s">
+        <v>317</v>
+      </c>
+      <c r="F12" s="187"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B13" s="48"/>
+      <c r="C13" s="174" t="s">
+        <v>318</v>
+      </c>
+      <c r="D13" s="168">
+        <v>-200</v>
+      </c>
+      <c r="E13" s="288"/>
+      <c r="F13" s="299">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B14" s="48"/>
+      <c r="C14" s="174" t="s">
+        <v>316</v>
+      </c>
+      <c r="D14" s="168">
+        <v>-300</v>
+      </c>
+      <c r="E14" s="288"/>
+      <c r="F14" s="299">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B15" s="48"/>
+      <c r="C15" s="174" t="s">
+        <v>327</v>
+      </c>
+      <c r="D15" s="168">
+        <v>400</v>
+      </c>
+      <c r="E15" s="288"/>
+      <c r="F15" s="299">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B16" s="48"/>
+      <c r="F16" s="187"/>
+    </row>
+    <row r="17" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="180" t="s">
+        <v>323</v>
+      </c>
+      <c r="B17" s="167" t="s">
+        <v>315</v>
+      </c>
+      <c r="C17" s="169" t="s">
+        <v>330</v>
+      </c>
+      <c r="D17" s="28">
+        <f>D11+D13+D14+D15</f>
+        <v>1900</v>
+      </c>
+      <c r="E17" s="292" t="s">
+        <v>345</v>
+      </c>
+      <c r="F17" s="301">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="19" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A19" s="179" t="s">
+        <v>320</v>
+      </c>
+      <c r="B19" s="173" t="s">
+        <v>319</v>
+      </c>
+      <c r="C19" s="178" t="s">
+        <v>341</v>
+      </c>
+      <c r="D19" s="172">
+        <v>2000</v>
+      </c>
+      <c r="E19" s="287" t="s">
+        <v>343</v>
+      </c>
+      <c r="F19" s="298">
+        <v>2025</v>
+      </c>
+      <c r="G19" s="296" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B20" s="48"/>
+      <c r="C20" s="188" t="s">
+        <v>317</v>
+      </c>
+      <c r="F20" s="187"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B21" s="48"/>
+      <c r="C21" s="168" t="s">
+        <v>322</v>
+      </c>
+      <c r="D21" s="168">
+        <v>-200</v>
+      </c>
+      <c r="E21" s="288"/>
+      <c r="F21" s="299">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B22" s="48"/>
+      <c r="C22" s="168" t="s">
+        <v>321</v>
+      </c>
+      <c r="D22" s="168">
+        <v>-300</v>
+      </c>
+      <c r="E22" s="288"/>
+      <c r="F22" s="299">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B23" s="48"/>
+      <c r="F23" s="187"/>
+    </row>
+    <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="183" t="s">
+        <v>282</v>
+      </c>
+      <c r="B24" s="181" t="s">
+        <v>315</v>
+      </c>
+      <c r="C24" s="182" t="s">
+        <v>331</v>
+      </c>
+      <c r="D24" s="182">
+        <f>D19+D21+D22</f>
+        <v>1500</v>
+      </c>
+      <c r="E24" s="290" t="s">
+        <v>346</v>
+      </c>
+      <c r="F24" s="302">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="26" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A26" s="179" t="s">
+        <v>320</v>
+      </c>
+      <c r="B26" s="173" t="s">
+        <v>319</v>
+      </c>
+      <c r="C26" s="178" t="s">
+        <v>342</v>
+      </c>
+      <c r="D26" s="172">
+        <v>2000</v>
+      </c>
+      <c r="E26" s="287" t="s">
+        <v>343</v>
+      </c>
+      <c r="F26" s="298">
+        <v>2025</v>
+      </c>
+      <c r="G26" s="296" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B27" s="48"/>
+      <c r="C27" s="188" t="s">
+        <v>317</v>
+      </c>
+      <c r="F27" s="187"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B28" s="48"/>
+      <c r="C28" s="174" t="s">
+        <v>322</v>
+      </c>
+      <c r="D28" s="168">
+        <v>-200</v>
+      </c>
+      <c r="E28" s="288"/>
+      <c r="F28" s="299">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B29" s="48"/>
+      <c r="C29" s="174" t="s">
+        <v>321</v>
+      </c>
+      <c r="D29" s="168">
+        <v>-300</v>
+      </c>
+      <c r="E29" s="288"/>
+      <c r="F29" s="299">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B30" s="48"/>
+      <c r="F30" s="187"/>
+    </row>
+    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="184" t="s">
+        <v>86</v>
+      </c>
+      <c r="B31" s="185" t="s">
+        <v>315</v>
+      </c>
+      <c r="C31" s="186" t="s">
+        <v>332</v>
+      </c>
+      <c r="D31" s="186">
+        <f>D26+D28+D29</f>
+        <v>1500</v>
+      </c>
+      <c r="E31" s="291" t="s">
+        <v>347</v>
+      </c>
+      <c r="F31" s="303">
+        <v>2026</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3357B9CC-5A3A-40CC-AF80-897C28F6CB19}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B1:T35"/>
@@ -5273,14 +6893,14 @@
   <sheetData>
     <row r="1" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:20" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="215" t="s">
+      <c r="B2" s="223" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="216"/>
-      <c r="D2" s="209" t="s">
+      <c r="C2" s="224"/>
+      <c r="D2" s="217" t="s">
         <v>121</v>
       </c>
-      <c r="E2" s="211" t="s">
+      <c r="E2" s="219" t="s">
         <v>117</v>
       </c>
       <c r="F2" s="1"/>
@@ -5293,10 +6913,10 @@
       <c r="M2" s="8"/>
     </row>
     <row r="3" spans="2:20" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="217"/>
-      <c r="C3" s="218"/>
-      <c r="D3" s="210"/>
-      <c r="E3" s="212"/>
+      <c r="B3" s="225"/>
+      <c r="C3" s="226"/>
+      <c r="D3" s="218"/>
+      <c r="E3" s="220"/>
       <c r="F3" s="1"/>
       <c r="G3" s="10" t="s">
         <v>17</v>
@@ -5307,7 +6927,7 @@
       <c r="K3" s="2"/>
     </row>
     <row r="4" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B4" s="206" t="s">
+      <c r="B4" s="214" t="s">
         <v>86</v>
       </c>
       <c r="C4" s="54" t="s">
@@ -5316,7 +6936,7 @@
       <c r="D4" s="75" t="s">
         <v>122</v>
       </c>
-      <c r="E4" s="220" t="s">
+      <c r="E4" s="228" t="s">
         <v>81</v>
       </c>
       <c r="F4" s="1"/>
@@ -5340,12 +6960,12 @@
       <c r="T4" s="17"/>
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B5" s="213"/>
+      <c r="B5" s="221"/>
       <c r="C5" s="40" t="s">
         <v>90</v>
       </c>
       <c r="D5" s="9"/>
-      <c r="E5" s="221"/>
+      <c r="E5" s="229"/>
       <c r="F5"/>
       <c r="G5" s="48"/>
       <c r="H5" s="10" t="s">
@@ -5355,12 +6975,12 @@
       <c r="T5" s="19"/>
     </row>
     <row r="6" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="219"/>
+      <c r="B6" s="227"/>
       <c r="C6" s="55" t="s">
         <v>91</v>
       </c>
       <c r="D6" s="65"/>
-      <c r="E6" s="222"/>
+      <c r="E6" s="230"/>
       <c r="F6"/>
       <c r="G6" s="48"/>
       <c r="H6" s="10" t="s">
@@ -5370,16 +6990,16 @@
       <c r="T6" s="19"/>
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B7" s="206" t="s">
+      <c r="B7" s="214" t="s">
         <v>87</v>
       </c>
       <c r="C7" s="54" t="s">
         <v>92</v>
       </c>
-      <c r="D7" s="197" t="s">
+      <c r="D7" s="240" t="s">
         <v>127</v>
       </c>
-      <c r="E7" s="194" t="s">
+      <c r="E7" s="237" t="s">
         <v>81</v>
       </c>
       <c r="F7"/>
@@ -5401,12 +7021,12 @@
       <c r="T7" s="31"/>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B8" s="213"/>
+      <c r="B8" s="221"/>
       <c r="C8" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="D8" s="198"/>
-      <c r="E8" s="195"/>
+      <c r="D8" s="241"/>
+      <c r="E8" s="238"/>
       <c r="F8"/>
       <c r="G8" s="46" t="s">
         <v>18</v>
@@ -5418,12 +7038,12 @@
       <c r="T8" s="19"/>
     </row>
     <row r="9" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="214"/>
+      <c r="B9" s="222"/>
       <c r="C9" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="D9" s="199"/>
-      <c r="E9" s="196"/>
+      <c r="D9" s="242"/>
+      <c r="E9" s="239"/>
       <c r="F9"/>
       <c r="G9" s="46"/>
       <c r="H9" s="20" t="s">
@@ -5433,7 +7053,7 @@
       <c r="T9" s="19"/>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B10" s="206" t="s">
+      <c r="B10" s="214" t="s">
         <v>88</v>
       </c>
       <c r="C10" s="73" t="s">
@@ -5442,7 +7062,7 @@
       <c r="D10" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="E10" s="200" t="s">
+      <c r="E10" s="243" t="s">
         <v>81</v>
       </c>
       <c r="F10"/>
@@ -5454,12 +7074,12 @@
       <c r="T10" s="19"/>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B11" s="207"/>
+      <c r="B11" s="215"/>
       <c r="C11" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="D11" s="191"/>
-      <c r="E11" s="201"/>
+      <c r="D11" s="234"/>
+      <c r="E11" s="244"/>
       <c r="F11"/>
       <c r="G11" s="48"/>
       <c r="H11" s="24" t="s">
@@ -5479,12 +7099,12 @@
       <c r="T11" s="31"/>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B12" s="207"/>
+      <c r="B12" s="215"/>
       <c r="C12" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="192"/>
-      <c r="E12" s="201"/>
+      <c r="D12" s="235"/>
+      <c r="E12" s="244"/>
       <c r="F12"/>
       <c r="G12" s="46" t="s">
         <v>28</v>
@@ -5496,12 +7116,12 @@
       <c r="T12" s="19"/>
     </row>
     <row r="13" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="208"/>
+      <c r="B13" s="216"/>
       <c r="C13" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="193"/>
-      <c r="E13" s="202"/>
+      <c r="D13" s="236"/>
+      <c r="E13" s="245"/>
       <c r="F13" s="1"/>
       <c r="G13" s="21"/>
       <c r="H13" s="25" t="s">
@@ -5537,7 +7157,7 @@
       <c r="C16" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="D16" s="203">
+      <c r="D16" s="246">
         <v>2025</v>
       </c>
       <c r="E16" s="43" t="s">
@@ -5549,8 +7169,8 @@
       <c r="C17" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="D17" s="204"/>
-      <c r="E17" s="190" t="s">
+      <c r="D17" s="247"/>
+      <c r="E17" s="233" t="s">
         <v>118</v>
       </c>
       <c r="F17" s="1"/>
@@ -5559,8 +7179,8 @@
       <c r="C18" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="D18" s="205"/>
-      <c r="E18" s="190"/>
+      <c r="D18" s="248"/>
+      <c r="E18" s="233"/>
       <c r="F18" s="1"/>
     </row>
     <row r="19" spans="3:6" x14ac:dyDescent="0.35">
@@ -5570,7 +7190,7 @@
       <c r="C20" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="D20" s="188">
+      <c r="D20" s="231">
         <v>2026</v>
       </c>
       <c r="E20" s="43" t="s">
@@ -5582,7 +7202,7 @@
       <c r="C21" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="D21" s="189"/>
+      <c r="D21" s="232"/>
       <c r="E21" s="67" t="s">
         <v>119</v>
       </c>
@@ -5637,6 +7257,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E10:E13"/>
+    <mergeCell ref="D16:D18"/>
     <mergeCell ref="B10:B13"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
@@ -5644,20 +7271,13 @@
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="E4:E6"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="E10:E13"/>
-    <mergeCell ref="D16:D18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB4B1054-9445-434F-B8C4-4275AFE8E718}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="B2:X37"/>
@@ -5679,18 +7299,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:24" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="223" t="s">
+      <c r="B2" s="249" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="223"/>
-      <c r="D2" s="246" t="s">
+      <c r="C2" s="249"/>
+      <c r="D2" s="272" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="247"/>
-      <c r="F2" s="248" t="s">
+      <c r="E2" s="273"/>
+      <c r="F2" s="274" t="s">
         <v>80</v>
       </c>
-      <c r="G2" s="249"/>
+      <c r="G2" s="275"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
         <v>79</v>
@@ -5703,8 +7323,8 @@
       </c>
     </row>
     <row r="3" spans="2:24" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="224"/>
-      <c r="C3" s="224"/>
+      <c r="B3" s="250"/>
+      <c r="C3" s="250"/>
       <c r="D3" s="56" t="s">
         <v>22</v>
       </c>
@@ -5727,7 +7347,7 @@
       <c r="N3" s="2"/>
     </row>
     <row r="4" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="225" t="s">
+      <c r="B4" s="251" t="s">
         <v>86</v>
       </c>
       <c r="C4" s="70" t="s">
@@ -5750,14 +7370,14 @@
       <c r="M4" s="2"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="B5" s="226"/>
+      <c r="B5" s="252"/>
       <c r="C5" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="245" t="s">
+      <c r="D5" s="271" t="s">
         <v>108</v>
       </c>
-      <c r="E5" s="245"/>
+      <c r="E5" s="271"/>
       <c r="F5" s="43" t="s">
         <v>85</v>
       </c>
@@ -5788,14 +7408,14 @@
       <c r="X5" s="17"/>
     </row>
     <row r="6" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="227"/>
+      <c r="B6" s="253"/>
       <c r="C6" s="69" t="s">
         <v>91</v>
       </c>
-      <c r="D6" s="244" t="s">
+      <c r="D6" s="270" t="s">
         <v>108</v>
       </c>
-      <c r="E6" s="244"/>
+      <c r="E6" s="270"/>
       <c r="F6" s="60" t="s">
         <v>83</v>
       </c>
@@ -5811,18 +7431,18 @@
       <c r="X6" s="19"/>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="B7" s="228" t="s">
+      <c r="B7" s="254" t="s">
         <v>87</v>
       </c>
       <c r="C7" s="64" t="s">
         <v>92</v>
       </c>
-      <c r="D7" s="250" t="s">
+      <c r="D7" s="276" t="s">
         <v>81</v>
       </c>
-      <c r="E7" s="251"/>
-      <c r="F7" s="251"/>
-      <c r="G7" s="252"/>
+      <c r="E7" s="277"/>
+      <c r="F7" s="277"/>
+      <c r="G7" s="278"/>
       <c r="I7" s="1"/>
       <c r="J7" s="46"/>
       <c r="K7" s="24" t="s">
@@ -5843,16 +7463,16 @@
       <c r="X7" s="31"/>
     </row>
     <row r="8" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="B8" s="213"/>
+      <c r="B8" s="221"/>
       <c r="C8" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="D8" s="253" t="s">
+      <c r="D8" s="279" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="254"/>
-      <c r="F8" s="254"/>
-      <c r="G8" s="255"/>
+      <c r="E8" s="280"/>
+      <c r="F8" s="280"/>
+      <c r="G8" s="281"/>
       <c r="I8" s="1"/>
       <c r="J8" s="46" t="s">
         <v>18</v>
@@ -5864,16 +7484,16 @@
       <c r="X8" s="19"/>
     </row>
     <row r="9" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="219"/>
+      <c r="B9" s="227"/>
       <c r="C9" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="D9" s="256" t="s">
+      <c r="D9" s="282" t="s">
         <v>81</v>
       </c>
-      <c r="E9" s="257"/>
-      <c r="F9" s="257"/>
-      <c r="G9" s="258"/>
+      <c r="E9" s="283"/>
+      <c r="F9" s="283"/>
+      <c r="G9" s="284"/>
       <c r="I9" s="1"/>
       <c r="J9" s="46"/>
       <c r="K9" s="20" t="s">
@@ -5883,18 +7503,18 @@
       <c r="X9" s="19"/>
     </row>
     <row r="10" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="B10" s="206" t="s">
+      <c r="B10" s="214" t="s">
         <v>88</v>
       </c>
       <c r="C10" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="229" t="s">
+      <c r="D10" s="255" t="s">
         <v>81</v>
       </c>
-      <c r="E10" s="230"/>
-      <c r="F10" s="230"/>
-      <c r="G10" s="231"/>
+      <c r="E10" s="256"/>
+      <c r="F10" s="256"/>
+      <c r="G10" s="257"/>
       <c r="I10" s="1"/>
       <c r="J10" s="46"/>
       <c r="K10" s="35" t="s">
@@ -5915,14 +7535,14 @@
       <c r="X10" s="38"/>
     </row>
     <row r="11" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="B11" s="213"/>
+      <c r="B11" s="221"/>
       <c r="C11" s="49" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="232"/>
-      <c r="E11" s="233"/>
-      <c r="F11" s="233"/>
-      <c r="G11" s="234"/>
+      <c r="D11" s="258"/>
+      <c r="E11" s="259"/>
+      <c r="F11" s="259"/>
+      <c r="G11" s="260"/>
       <c r="I11" s="1"/>
       <c r="J11" s="46" t="s">
         <v>28</v>
@@ -5934,18 +7554,18 @@
       <c r="X11" s="19"/>
     </row>
     <row r="12" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="213"/>
+      <c r="B12" s="221"/>
       <c r="C12" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="D12" s="241" t="s">
+      <c r="D12" s="267" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="191"/>
-      <c r="F12" s="235" t="s">
+      <c r="E12" s="234"/>
+      <c r="F12" s="261" t="s">
         <v>81</v>
       </c>
-      <c r="G12" s="236"/>
+      <c r="G12" s="262"/>
       <c r="I12" s="1"/>
       <c r="J12" s="47"/>
       <c r="K12" s="25" t="s">
@@ -5966,14 +7586,14 @@
       <c r="X12" s="29"/>
     </row>
     <row r="13" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="B13" s="213"/>
+      <c r="B13" s="221"/>
       <c r="C13" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="D13" s="242"/>
-      <c r="E13" s="192"/>
-      <c r="F13" s="237"/>
-      <c r="G13" s="238"/>
+      <c r="D13" s="268"/>
+      <c r="E13" s="235"/>
+      <c r="F13" s="263"/>
+      <c r="G13" s="264"/>
       <c r="I13" s="1" t="s">
         <v>23</v>
       </c>
@@ -5998,14 +7618,14 @@
       <c r="X13" s="17"/>
     </row>
     <row r="14" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="B14" s="213"/>
+      <c r="B14" s="221"/>
       <c r="C14" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="242"/>
-      <c r="E14" s="192"/>
-      <c r="F14" s="237"/>
-      <c r="G14" s="238"/>
+      <c r="D14" s="268"/>
+      <c r="E14" s="235"/>
+      <c r="F14" s="263"/>
+      <c r="G14" s="264"/>
       <c r="I14" s="1"/>
       <c r="J14" s="48"/>
       <c r="K14" s="10" t="s">
@@ -6015,14 +7635,14 @@
       <c r="X14" s="19"/>
     </row>
     <row r="15" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="219"/>
+      <c r="B15" s="227"/>
       <c r="C15" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="D15" s="243"/>
-      <c r="E15" s="193"/>
-      <c r="F15" s="239"/>
-      <c r="G15" s="240"/>
+      <c r="D15" s="269"/>
+      <c r="E15" s="236"/>
+      <c r="F15" s="265"/>
+      <c r="G15" s="266"/>
       <c r="I15" s="1"/>
       <c r="J15" s="48"/>
       <c r="K15" s="10" t="s">
@@ -6353,7 +7973,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A16251E-9A23-4E00-B427-42544FA8AA6F}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="B2:R36"/>
@@ -6368,21 +7988,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B2" s="223" t="s">
+      <c r="B2" s="249" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="260" t="s">
+      <c r="C2" s="286" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="248">
+      <c r="D2" s="274">
         <v>46203</v>
       </c>
-      <c r="E2" s="259"/>
-      <c r="F2" s="249"/>
+      <c r="E2" s="285"/>
+      <c r="F2" s="275"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B3" s="223"/>
-      <c r="C3" s="260"/>
+      <c r="B3" s="249"/>
+      <c r="C3" s="286"/>
       <c r="D3" s="7" t="s">
         <v>6</v>
       </c>
@@ -6821,7 +8441,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0970813E-53AE-4159-B6D6-1146B744B584}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:E10"/>
@@ -6981,7 +8601,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43016F89-DC87-4D67-AF59-135AD0C8A97B}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:I5"/>
